--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio\uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABC488D-C5F6-49D7-890F-734781C7D8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3CE43F-14DE-454F-A431-1933281EBCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="11170" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="119">
   <si>
     <t>NomCarte</t>
   </si>
@@ -372,6 +372,27 @@
   </si>
   <si>
     <t>Mono Rouge</t>
+  </si>
+  <si>
+    <t>Force of Will</t>
+  </si>
+  <si>
+    <t>Alliances</t>
+  </si>
+  <si>
+    <t>Elvish Spirit Guide</t>
+  </si>
+  <si>
+    <t>Kaysa</t>
+  </si>
+  <si>
+    <t>Lim-Dûl's Vault</t>
+  </si>
+  <si>
+    <t>Heart of Yavimaya</t>
+  </si>
+  <si>
+    <t>Lake of the Dead</t>
   </si>
 </sst>
 </file>
@@ -781,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -3442,6 +3463,108 @@
         <v>111</v>
       </c>
     </row>
+    <row r="157" spans="1:5" ht="15">
+      <c r="A157" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C157" t="s">
+        <v>36</v>
+      </c>
+      <c r="D157" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="15">
+      <c r="A158" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C158" t="s">
+        <v>36</v>
+      </c>
+      <c r="D158" t="s">
+        <v>7</v>
+      </c>
+      <c r="E158" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="15">
+      <c r="A159" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C159" t="s">
+        <v>36</v>
+      </c>
+      <c r="D159" t="s">
+        <v>7</v>
+      </c>
+      <c r="E159" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="15">
+      <c r="A160" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C160" t="s">
+        <v>36</v>
+      </c>
+      <c r="D160" t="s">
+        <v>10</v>
+      </c>
+      <c r="E160" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="15">
+      <c r="A161" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C161" t="s">
+        <v>36</v>
+      </c>
+      <c r="D161" t="s">
+        <v>10</v>
+      </c>
+      <c r="E161" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="15">
+      <c r="A162" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C162" t="s">
+        <v>36</v>
+      </c>
+      <c r="D162" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3CE43F-14DE-454F-A431-1933281EBCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C2C625-4289-473B-91F9-3767E8F51350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="11170" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="121">
   <si>
     <t>NomCarte</t>
   </si>
@@ -393,6 +393,12 @@
   </si>
   <si>
     <t>Lake of the Dead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Army of Allah (V.1) </t>
+  </si>
+  <si>
+    <t>Mono Blanc</t>
   </si>
 </sst>
 </file>
@@ -434,7 +440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -442,17 +448,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -3565,6 +3585,23 @@
         <v>22</v>
       </c>
     </row>
+    <row r="163" spans="1:5" ht="15">
+      <c r="A163" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" t="s">
+        <v>6</v>
+      </c>
+      <c r="D163" t="s">
+        <v>7</v>
+      </c>
+      <c r="E163" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C2C625-4289-473B-91F9-3767E8F51350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085F2552-D196-4C4D-A65C-C77C473AD40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="11170" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="124">
   <si>
     <t>NomCarte</t>
   </si>
@@ -399,6 +399,15 @@
   </si>
   <si>
     <t>Mono Blanc</t>
+  </si>
+  <si>
+    <t>Jihad</t>
+  </si>
+  <si>
+    <t>Karakas</t>
+  </si>
+  <si>
+    <t>Dust to Dust</t>
   </si>
 </sst>
 </file>
@@ -463,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -472,7 +481,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -822,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E163"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -3602,6 +3614,108 @@
         <v>120</v>
       </c>
     </row>
+    <row r="164" spans="1:5" ht="15">
+      <c r="A164" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C164" t="s">
+        <v>36</v>
+      </c>
+      <c r="D164" t="s">
+        <v>10</v>
+      </c>
+      <c r="E164" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="15">
+      <c r="A165" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C165" t="s">
+        <v>6</v>
+      </c>
+      <c r="D165" t="s">
+        <v>10</v>
+      </c>
+      <c r="E165" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="15">
+      <c r="A166" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C166" t="s">
+        <v>6</v>
+      </c>
+      <c r="D166" t="s">
+        <v>10</v>
+      </c>
+      <c r="E166" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="15">
+      <c r="A167" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C167" t="s">
+        <v>6</v>
+      </c>
+      <c r="D167" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="15">
+      <c r="A168" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C168" t="s">
+        <v>6</v>
+      </c>
+      <c r="D168" t="s">
+        <v>49</v>
+      </c>
+      <c r="E168" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="15">
+      <c r="A169" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C169" t="s">
+        <v>6</v>
+      </c>
+      <c r="D169" t="s">
+        <v>49</v>
+      </c>
+      <c r="E169" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085F2552-D196-4C4D-A65C-C77C473AD40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D5DFFC-B963-4514-B3AC-AA06BD16F28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="11170" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="128">
   <si>
     <t>NomCarte</t>
   </si>
@@ -408,6 +408,18 @@
   </si>
   <si>
     <t>Dust to Dust</t>
+  </si>
+  <si>
+    <t>Aeolipile</t>
+  </si>
+  <si>
+    <t>Crusade</t>
+  </si>
+  <si>
+    <t>Swords to Plowshares</t>
+  </si>
+  <si>
+    <t>Preacher</t>
   </si>
 </sst>
 </file>
@@ -472,7 +484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -482,9 +494,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -834,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -3669,7 +3678,7 @@
       <c r="A167" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B167" s="5" t="s">
+      <c r="B167" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C167" t="s">
@@ -3713,6 +3722,125 @@
         <v>49</v>
       </c>
       <c r="E169" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="15">
+      <c r="A170" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" t="s">
+        <v>6</v>
+      </c>
+      <c r="D170" t="s">
+        <v>10</v>
+      </c>
+      <c r="E170" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="15">
+      <c r="A171" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C171" t="s">
+        <v>36</v>
+      </c>
+      <c r="D171" t="s">
+        <v>49</v>
+      </c>
+      <c r="E171" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="15">
+      <c r="A172" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C172" t="s">
+        <v>6</v>
+      </c>
+      <c r="D172" t="s">
+        <v>7</v>
+      </c>
+      <c r="E172" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="15">
+      <c r="A173" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C173" t="s">
+        <v>36</v>
+      </c>
+      <c r="D173" t="s">
+        <v>49</v>
+      </c>
+      <c r="E173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="15">
+      <c r="A174" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C174" t="s">
+        <v>6</v>
+      </c>
+      <c r="D174" t="s">
+        <v>10</v>
+      </c>
+      <c r="E174" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="15">
+      <c r="A175" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C175" t="s">
+        <v>36</v>
+      </c>
+      <c r="D175" t="s">
+        <v>49</v>
+      </c>
+      <c r="E175" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="15">
+      <c r="A176" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C176" t="s">
+        <v>6</v>
+      </c>
+      <c r="D176" t="s">
+        <v>10</v>
+      </c>
+      <c r="E176" t="s">
         <v>120</v>
       </c>
     </row>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D5DFFC-B963-4514-B3AC-AA06BD16F28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB721E3F-ED01-421D-9C58-87C921EBA182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="11170" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="133">
   <si>
     <t>NomCarte</t>
   </si>
@@ -420,6 +420,21 @@
   </si>
   <si>
     <t>Preacher</t>
+  </si>
+  <si>
+    <t>Holy Light</t>
+  </si>
+  <si>
+    <t>Witch Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaissance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armageddon </t>
+  </si>
+  <si>
+    <t>Land Tax</t>
   </si>
 </sst>
 </file>
@@ -843,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -3844,6 +3859,176 @@
         <v>120</v>
       </c>
     </row>
+    <row r="177" spans="1:5" ht="15">
+      <c r="A177" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C177" t="s">
+        <v>6</v>
+      </c>
+      <c r="D177" t="s">
+        <v>10</v>
+      </c>
+      <c r="E177" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="15">
+      <c r="A178" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C178" t="s">
+        <v>6</v>
+      </c>
+      <c r="D178" t="s">
+        <v>49</v>
+      </c>
+      <c r="E178" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="15">
+      <c r="A179" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C179" t="s">
+        <v>36</v>
+      </c>
+      <c r="D179" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="15">
+      <c r="A180" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C180" t="s">
+        <v>6</v>
+      </c>
+      <c r="D180" t="s">
+        <v>10</v>
+      </c>
+      <c r="E180" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="15">
+      <c r="A181" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C181" t="s">
+        <v>6</v>
+      </c>
+      <c r="D181" t="s">
+        <v>10</v>
+      </c>
+      <c r="E181" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="15">
+      <c r="A182" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C182" t="s">
+        <v>6</v>
+      </c>
+      <c r="D182" t="s">
+        <v>10</v>
+      </c>
+      <c r="E182" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="15">
+      <c r="A183" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C183" t="s">
+        <v>36</v>
+      </c>
+      <c r="D183" t="s">
+        <v>10</v>
+      </c>
+      <c r="E183" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="15">
+      <c r="A184" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C184" t="s">
+        <v>36</v>
+      </c>
+      <c r="D184" t="s">
+        <v>10</v>
+      </c>
+      <c r="E184" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E185" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="15">
+      <c r="A186" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E186" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB721E3F-ED01-421D-9C58-87C921EBA182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7904D906-867E-4AB0-8F89-83BF5B303466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="11170" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="720" yWindow="720" windowWidth="19200" windowHeight="11170" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="139">
   <si>
     <t>NomCarte</t>
   </si>
@@ -435,6 +435,24 @@
   </si>
   <si>
     <t>Land Tax</t>
+  </si>
+  <si>
+    <t>Greater Realm of Preservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legends </t>
+  </si>
+  <si>
+    <t>Thunder Spirit</t>
+  </si>
+  <si>
+    <t>Divine Offering</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Jayemdae Tome</t>
   </si>
 </sst>
 </file>
@@ -529,13 +547,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F6F83A0D-001C-4980-961A-2565EB2F789B}" name="CollectionTable" displayName="CollectionTable" ref="A1:E125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B3B21DC4-923F-4727-9F0C-EF5FEDA85AED}" name="CollectionTable3" displayName="CollectionTable3" ref="A1:E125">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8E3C60EC-3A28-4C48-B9B1-1B2624CF1251}" name="NomCarte"/>
-    <tableColumn id="2" xr3:uid="{3F5E76D1-5A9D-4E9D-A780-399DCD653477}" name="Edition"/>
-    <tableColumn id="3" xr3:uid="{7274A1E9-98AA-4B2E-B956-E13C236D62E4}" name="Langue"/>
-    <tableColumn id="4" xr3:uid="{0AA597DB-18C6-4D8D-AB48-132AC534DFCB}" name="Etat"/>
-    <tableColumn id="5" xr3:uid="{9BCF75EC-B68C-49F5-BB87-21E603B55C4A}" name="Categorie"/>
+    <tableColumn id="1" xr3:uid="{1656BE50-9DE8-4279-B5FD-BB04A1DF8A62}" name="NomCarte"/>
+    <tableColumn id="2" xr3:uid="{F6028D99-F237-4CBA-A099-59A39EA0DF37}" name="Edition"/>
+    <tableColumn id="3" xr3:uid="{F65E3881-5011-4470-AF8B-04D2A7B6BD78}" name="Langue"/>
+    <tableColumn id="4" xr3:uid="{F6BC52B8-227E-45CF-AF7B-CAC3E9308A35}" name="Etat"/>
+    <tableColumn id="5" xr3:uid="{94123DB3-543C-4E9B-BF77-563B493BED4E}" name="Categorie"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -858,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -4029,6 +4047,312 @@
         <v>120</v>
       </c>
     </row>
+    <row r="187" spans="1:5" ht="15">
+      <c r="A187" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C187" t="s">
+        <v>6</v>
+      </c>
+      <c r="D187" t="s">
+        <v>10</v>
+      </c>
+      <c r="E187" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="15">
+      <c r="A188" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C188" t="s">
+        <v>6</v>
+      </c>
+      <c r="D188" t="s">
+        <v>10</v>
+      </c>
+      <c r="E188" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="15">
+      <c r="A189" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C189" t="s">
+        <v>36</v>
+      </c>
+      <c r="D189" t="s">
+        <v>7</v>
+      </c>
+      <c r="E189" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="15">
+      <c r="A190" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C190" t="s">
+        <v>36</v>
+      </c>
+      <c r="D190" t="s">
+        <v>10</v>
+      </c>
+      <c r="E190" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="15">
+      <c r="A191" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C191" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" t="s">
+        <v>7</v>
+      </c>
+      <c r="E191" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="15">
+      <c r="A192" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C192" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
+        <v>10</v>
+      </c>
+      <c r="E192" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="15">
+      <c r="A193" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C193" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
+        <v>10</v>
+      </c>
+      <c r="E193" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="15">
+      <c r="A194" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C194" t="s">
+        <v>36</v>
+      </c>
+      <c r="D194" t="s">
+        <v>10</v>
+      </c>
+      <c r="E194" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="15">
+      <c r="A195" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C195" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" t="s">
+        <v>10</v>
+      </c>
+      <c r="E195" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="15">
+      <c r="A196" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C196" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" t="s">
+        <v>10</v>
+      </c>
+      <c r="E196" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="15">
+      <c r="A197" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C197" t="s">
+        <v>6</v>
+      </c>
+      <c r="D197" t="s">
+        <v>10</v>
+      </c>
+      <c r="E197" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="15">
+      <c r="A198" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C198" t="s">
+        <v>36</v>
+      </c>
+      <c r="D198" t="s">
+        <v>10</v>
+      </c>
+      <c r="E198" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="15">
+      <c r="A199" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C199" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>10</v>
+      </c>
+      <c r="E199" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="15">
+      <c r="A200" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C200" t="s">
+        <v>36</v>
+      </c>
+      <c r="D200" t="s">
+        <v>10</v>
+      </c>
+      <c r="E200" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="15">
+      <c r="A201" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C201" t="s">
+        <v>6</v>
+      </c>
+      <c r="D201" t="s">
+        <v>10</v>
+      </c>
+      <c r="E201" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="15">
+      <c r="A202" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C202" t="s">
+        <v>36</v>
+      </c>
+      <c r="D202" t="s">
+        <v>10</v>
+      </c>
+      <c r="E202" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="15">
+      <c r="A203" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C203" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" t="s">
+        <v>49</v>
+      </c>
+      <c r="E203" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="15">
+      <c r="A204" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C204" t="s">
+        <v>6</v>
+      </c>
+      <c r="D204" t="s">
+        <v>49</v>
+      </c>
+      <c r="E204" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D22BF8-4827-4C90-A5DF-EEB378E7E34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E173E164-6767-4CC3-85CA-ABD02C9A13E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="1400" windowWidth="19200" windowHeight="11170" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$E$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -5589,7 +5592,7 @@
         <v>92</v>
       </c>
       <c r="C273" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>3</v>
@@ -5606,7 +5609,7 @@
         <v>92</v>
       </c>
       <c r="C274" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>3</v>
@@ -5623,7 +5626,7 @@
         <v>92</v>
       </c>
       <c r="C275" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>6</v>
@@ -5701,6 +5704,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E173E164-6767-4CC3-85CA-ABD02C9A13E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6334F87-B25B-46F9-BBEF-91D332C9F297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="163">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -951,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E279"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -5703,6 +5703,40 @@
         <v>145</v>
       </c>
     </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6334F87-B25B-46F9-BBEF-91D332C9F297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6377F2E-44DC-43D9-9D24-D8ABA38D3963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="164">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -528,6 +528,9 @@
   </si>
   <si>
     <t>Categorie</t>
+  </si>
+  <si>
+    <t>Rukh Egg (V.1)</t>
   </si>
 </sst>
 </file>
@@ -951,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:E282"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -5737,6 +5740,23 @@
         <v>17</v>
       </c>
     </row>
+    <row r="282" spans="1:5" ht="15">
+      <c r="A282" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C282" t="s">
+        <v>2</v>
+      </c>
+      <c r="D282" t="s">
+        <v>6</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6377F2E-44DC-43D9-9D24-D8ABA38D3963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88960A05-8B0C-45CC-A6FE-F3C05534F554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="182">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -531,6 +531,60 @@
   </si>
   <si>
     <t>Rukh Egg (V.1)</t>
+  </si>
+  <si>
+    <t>Benalish Hero</t>
+  </si>
+  <si>
+    <t>Holy Strength</t>
+  </si>
+  <si>
+    <t>Creature Bond</t>
+  </si>
+  <si>
+    <t>Jump</t>
+  </si>
+  <si>
+    <t>Merfolk of the Pearl Trident</t>
+  </si>
+  <si>
+    <t>Terror</t>
+  </si>
+  <si>
+    <t>Weakness</t>
+  </si>
+  <si>
+    <t>Hurloon Minotaur</t>
+  </si>
+  <si>
+    <t>Giant Growth</t>
+  </si>
+  <si>
+    <t>Giant Spider</t>
+  </si>
+  <si>
+    <t>Regeneration</t>
+  </si>
+  <si>
+    <t>Scryb Sprites</t>
+  </si>
+  <si>
+    <t>Thicket Basilisk</t>
+  </si>
+  <si>
+    <t>War Mammoth</t>
+  </si>
+  <si>
+    <t>Demonic Torment</t>
+  </si>
+  <si>
+    <t>Ifh-Bíff Efreet</t>
+  </si>
+  <si>
+    <t>Wyluli Wolf (V.1)</t>
+  </si>
+  <si>
+    <t>Ivory Tower</t>
   </si>
 </sst>
 </file>
@@ -954,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E282"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -5757,6 +5811,618 @@
         <v>17</v>
       </c>
     </row>
+    <row r="283" spans="1:5" ht="15">
+      <c r="A283" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="15">
+      <c r="A284" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" ht="15">
+      <c r="A285" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" ht="15">
+      <c r="A286" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" ht="15">
+      <c r="A287" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" ht="15">
+      <c r="A288" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" ht="15">
+      <c r="A289" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" ht="15">
+      <c r="A290" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" ht="15">
+      <c r="A291" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" ht="15">
+      <c r="A292" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" ht="15">
+      <c r="A293" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" ht="15">
+      <c r="A294" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" ht="15">
+      <c r="A295" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" ht="15">
+      <c r="A296" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" ht="15">
+      <c r="A297" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" ht="15">
+      <c r="A298" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C298" t="s">
+        <v>2</v>
+      </c>
+      <c r="D298" t="s">
+        <v>6</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" ht="15">
+      <c r="A299" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C299" t="s">
+        <v>2</v>
+      </c>
+      <c r="D299" t="s">
+        <v>6</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" ht="15">
+      <c r="A300" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C300" t="s">
+        <v>2</v>
+      </c>
+      <c r="D300" t="s">
+        <v>6</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" ht="15">
+      <c r="A301" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C301" t="s">
+        <v>2</v>
+      </c>
+      <c r="D301" t="s">
+        <v>6</v>
+      </c>
+      <c r="E301" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" ht="15">
+      <c r="A302" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C302" t="s">
+        <v>2</v>
+      </c>
+      <c r="D302" t="s">
+        <v>6</v>
+      </c>
+      <c r="E302" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" ht="15">
+      <c r="A303" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C303" t="s">
+        <v>2</v>
+      </c>
+      <c r="D303" t="s">
+        <v>3</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" ht="15">
+      <c r="A304" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C304" t="s">
+        <v>2</v>
+      </c>
+      <c r="D304" t="s">
+        <v>6</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" ht="15">
+      <c r="A305" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C305" t="s">
+        <v>2</v>
+      </c>
+      <c r="D305" t="s">
+        <v>6</v>
+      </c>
+      <c r="E305" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" ht="15">
+      <c r="A306" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C306" t="s">
+        <v>2</v>
+      </c>
+      <c r="D306" t="s">
+        <v>3</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" ht="15">
+      <c r="A307" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C307" t="s">
+        <v>2</v>
+      </c>
+      <c r="D307" t="s">
+        <v>6</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" ht="15">
+      <c r="A308" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C308" t="s">
+        <v>2</v>
+      </c>
+      <c r="D308" t="s">
+        <v>6</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" ht="15">
+      <c r="A309" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C309" t="s">
+        <v>2</v>
+      </c>
+      <c r="D309" t="s">
+        <v>6</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" ht="15">
+      <c r="A310" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C310" t="s">
+        <v>2</v>
+      </c>
+      <c r="D310" t="s">
+        <v>6</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" ht="15">
+      <c r="A311" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C311" t="s">
+        <v>2</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" ht="15">
+      <c r="A312" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C312" t="s">
+        <v>2</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" ht="15">
+      <c r="A313" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C313" t="s">
+        <v>2</v>
+      </c>
+      <c r="D313" t="s">
+        <v>6</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" ht="15">
+      <c r="A314" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C314" t="s">
+        <v>2</v>
+      </c>
+      <c r="D314" t="s">
+        <v>6</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" ht="15">
+      <c r="A315" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C315" t="s">
+        <v>2</v>
+      </c>
+      <c r="D315" t="s">
+        <v>6</v>
+      </c>
+      <c r="E315" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" ht="15">
+      <c r="A316" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C316" t="s">
+        <v>2</v>
+      </c>
+      <c r="D316" t="s">
+        <v>6</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" ht="15">
+      <c r="A317" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" ht="15">
+      <c r="A318" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88960A05-8B0C-45CC-A6FE-F3C05534F554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943EA8EA-A2A2-4DD3-83E1-01993914D73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="191">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -585,6 +585,33 @@
   </si>
   <si>
     <t>Ivory Tower</t>
+  </si>
+  <si>
+    <t>Mountain (V.1)</t>
+  </si>
+  <si>
+    <t>Forest (V.2)</t>
+  </si>
+  <si>
+    <t>Forest (V.1)</t>
+  </si>
+  <si>
+    <t>Forest (V.3)</t>
+  </si>
+  <si>
+    <t>Island (V.2)</t>
+  </si>
+  <si>
+    <t>Plains (V.1)</t>
+  </si>
+  <si>
+    <t>Plains (V.2)</t>
+  </si>
+  <si>
+    <t>Swamp (V.1)</t>
+  </si>
+  <si>
+    <t>Swamp (V.3)</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E318"/>
+  <dimension ref="A1:E328"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -6423,6 +6450,176 @@
         <v>17</v>
       </c>
     </row>
+    <row r="319" spans="1:5" ht="15">
+      <c r="A319" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" ht="15">
+      <c r="A320" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="15">
+      <c r="A321" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="15">
+      <c r="A322" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" ht="15">
+      <c r="A323" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" ht="15">
+      <c r="A324" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" ht="15">
+      <c r="A325" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" ht="15">
+      <c r="A326" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" ht="15">
+      <c r="A327" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" ht="15">
+      <c r="A328" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943EA8EA-A2A2-4DD3-83E1-01993914D73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D83E23-A932-462E-BB9A-0437DBF69FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-19125" yWindow="3075" windowWidth="19200" windowHeight="17805" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="210">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -612,13 +612,70 @@
   </si>
   <si>
     <t>Swamp (V.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swords to Plowshares </t>
+  </si>
+  <si>
+    <t>Island Sanctuary</t>
+  </si>
+  <si>
+    <t>Wrath of God</t>
+  </si>
+  <si>
+    <t>Animate Dead</t>
+  </si>
+  <si>
+    <t>Bad Moon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning Bolt </t>
+  </si>
+  <si>
+    <t>Shivan Dragon</t>
+  </si>
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Force of Nature </t>
+  </si>
+  <si>
+    <t>Howling Mine</t>
+  </si>
+  <si>
+    <t>Hell's Caretaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concordant Crossroads </t>
+  </si>
+  <si>
+    <t>Nicol Bolas</t>
+  </si>
+  <si>
+    <t>Arena of the Ancients</t>
+  </si>
+  <si>
+    <t>Ashnod's Altar</t>
+  </si>
+  <si>
+    <t>City of Brass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sylvan Library </t>
+  </si>
+  <si>
+    <t>Fellwar Stone</t>
+  </si>
+  <si>
+    <t>Classeur2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -639,6 +696,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -653,7 +716,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -672,11 +735,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -687,6 +763,16 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1035,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E328"/>
+  <dimension ref="A1:E371"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -6620,8 +6706,740 @@
         <v>17</v>
       </c>
     </row>
+    <row r="329" spans="1:5" ht="15">
+      <c r="A329" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" ht="15">
+      <c r="A330" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" ht="15">
+      <c r="A331" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E331" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" ht="15">
+      <c r="A332" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" ht="15">
+      <c r="A333" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" ht="15">
+      <c r="A334" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" ht="15">
+      <c r="A335" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D335" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" ht="15">
+      <c r="A336" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D336" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" ht="15">
+      <c r="A337" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" ht="15">
+      <c r="A338" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C338" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D338" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" ht="15">
+      <c r="A339" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D339" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" ht="15">
+      <c r="A340" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D340" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" ht="15">
+      <c r="A341" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E341" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" ht="15">
+      <c r="A342" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D342" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" ht="15">
+      <c r="A343" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" ht="15">
+      <c r="A344" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C344" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D344" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E344" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" ht="15">
+      <c r="A345" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D345" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" ht="15">
+      <c r="A346" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D346" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" ht="15">
+      <c r="A347" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D347" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" ht="15">
+      <c r="A348" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D348" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" ht="15">
+      <c r="A349" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D349" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E349" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" ht="15">
+      <c r="A350" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D350" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E350" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" ht="15">
+      <c r="A351" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D351" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E351" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" ht="15">
+      <c r="A352" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D352" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E352" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" ht="15">
+      <c r="A353" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D353" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E353" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" ht="15">
+      <c r="A354" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D354" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" ht="15">
+      <c r="A355" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D355" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" ht="15">
+      <c r="A356" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D356" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" ht="15">
+      <c r="A357" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D357" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" ht="15">
+      <c r="A358" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D358" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E358" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" ht="15">
+      <c r="A359" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D359" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E359" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" ht="15">
+      <c r="A360" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D360" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E360" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" ht="15">
+      <c r="A361" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D361" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E361" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" ht="15">
+      <c r="A362" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E362" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" ht="15">
+      <c r="A363" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D363" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" ht="15">
+      <c r="A364" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D364" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" ht="15">
+      <c r="A365" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D365" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E365" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" ht="15">
+      <c r="A366" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E366" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" ht="15">
+      <c r="A367" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" ht="15">
+      <c r="A368" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" ht="15">
+      <c r="A369" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E369" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" ht="15">
+      <c r="A370" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D370" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" ht="15">
+      <c r="A371" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C371" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D371" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E371" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D83E23-A932-462E-BB9A-0437DBF69FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377338D8-B7E5-4B64-9171-483B7571DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19125" yWindow="3075" windowWidth="19200" windowHeight="17805" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-38520" yWindow="2340" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="211">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -669,6 +669,9 @@
   </si>
   <si>
     <t>Classeur2</t>
+  </si>
+  <si>
+    <t>Classeur3</t>
   </si>
 </sst>
 </file>
@@ -752,7 +755,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -764,14 +767,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3813,7 +3809,7 @@
         <v>6</v>
       </c>
       <c r="E158" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="15">
@@ -3830,7 +3826,7 @@
         <v>3</v>
       </c>
       <c r="E159" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="15">
@@ -3847,7 +3843,7 @@
         <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="15">
@@ -3864,7 +3860,7 @@
         <v>6</v>
       </c>
       <c r="E161" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="15">
@@ -3881,7 +3877,7 @@
         <v>6</v>
       </c>
       <c r="E162" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="15">
@@ -3898,7 +3894,7 @@
         <v>6</v>
       </c>
       <c r="E163" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="15">
@@ -6815,10 +6811,10 @@
       <c r="B335" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C335" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D335" s="6" t="s">
+      <c r="C335" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D335" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E335" s="2" t="s">
@@ -6832,10 +6828,10 @@
       <c r="B336" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C336" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D336" s="6" t="s">
+      <c r="C336" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D336" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E336" s="2" t="s">
@@ -6843,7 +6839,7 @@
       </c>
     </row>
     <row r="337" spans="1:5" ht="15">
-      <c r="A337" s="7" t="s">
+      <c r="A337" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B337" s="1" t="s">
@@ -6860,16 +6856,16 @@
       </c>
     </row>
     <row r="338" spans="1:5" ht="15">
-      <c r="A338" s="7" t="s">
+      <c r="A338" s="1" t="s">
         <v>196</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C338" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D338" s="6" t="s">
+      <c r="C338" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D338" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E338" s="2" t="s">
@@ -6883,10 +6879,10 @@
       <c r="B339" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C339" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D339" s="6" t="s">
+      <c r="C339" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D339" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E339" s="2" t="s">
@@ -6894,16 +6890,16 @@
       </c>
     </row>
     <row r="340" spans="1:5" ht="15">
-      <c r="A340" s="7" t="s">
+      <c r="A340" s="1" t="s">
         <v>197</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C340" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D340" s="6" t="s">
+      <c r="C340" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D340" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E340" s="2" t="s">
@@ -6917,10 +6913,10 @@
       <c r="B341" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C341" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D341" s="6" t="s">
+      <c r="C341" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D341" s="3" t="s">
         <v>198</v>
       </c>
       <c r="E341" s="2" t="s">
@@ -6928,16 +6924,16 @@
       </c>
     </row>
     <row r="342" spans="1:5" ht="15">
-      <c r="A342" s="7" t="s">
+      <c r="A342" s="1" t="s">
         <v>199</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C342" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D342" s="6" t="s">
+      <c r="C342" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D342" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E342" s="2" t="s">
@@ -6945,7 +6941,7 @@
       </c>
     </row>
     <row r="343" spans="1:5" ht="15">
-      <c r="A343" s="8" t="s">
+      <c r="A343" s="2" t="s">
         <v>200</v>
       </c>
       <c r="B343" s="1" t="s">
@@ -6954,7 +6950,7 @@
       <c r="C343" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D343" s="6" t="s">
+      <c r="D343" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E343" s="2" t="s">
@@ -6962,16 +6958,16 @@
       </c>
     </row>
     <row r="344" spans="1:5" ht="15">
-      <c r="A344" s="7" t="s">
+      <c r="A344" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C344" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D344" s="6" t="s">
+      <c r="C344" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D344" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E344" s="2" t="s">
@@ -6979,16 +6975,16 @@
       </c>
     </row>
     <row r="345" spans="1:5" ht="15">
-      <c r="A345" s="8" t="s">
+      <c r="A345" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C345" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D345" s="6" t="s">
+      <c r="C345" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D345" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E345" s="2" t="s">
@@ -6996,7 +6992,7 @@
       </c>
     </row>
     <row r="346" spans="1:5" ht="15">
-      <c r="A346" s="7" t="s">
+      <c r="A346" s="1" t="s">
         <v>201</v>
       </c>
       <c r="B346" s="1" t="s">
@@ -7005,7 +7001,7 @@
       <c r="C346" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D346" s="6" t="s">
+      <c r="D346" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E346" s="2" t="s">
@@ -7013,7 +7009,7 @@
       </c>
     </row>
     <row r="347" spans="1:5" ht="15">
-      <c r="A347" s="8" t="s">
+      <c r="A347" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B347" s="1" t="s">
@@ -7022,7 +7018,7 @@
       <c r="C347" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D347" s="8" t="s">
+      <c r="D347" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E347" s="2" t="s">
@@ -7030,7 +7026,7 @@
       </c>
     </row>
     <row r="348" spans="1:5" ht="15">
-      <c r="A348" s="7" t="s">
+      <c r="A348" s="1" t="s">
         <v>202</v>
       </c>
       <c r="B348" s="1" t="s">
@@ -7039,7 +7035,7 @@
       <c r="C348" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D348" s="6" t="s">
+      <c r="D348" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E348" s="2" t="s">
@@ -7047,7 +7043,7 @@
       </c>
     </row>
     <row r="349" spans="1:5" ht="15">
-      <c r="A349" s="8" t="s">
+      <c r="A349" s="2" t="s">
         <v>203</v>
       </c>
       <c r="B349" s="1" t="s">
@@ -7056,7 +7052,7 @@
       <c r="C349" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D349" s="6" t="s">
+      <c r="D349" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E349" s="2" t="s">
@@ -7064,7 +7060,7 @@
       </c>
     </row>
     <row r="350" spans="1:5" ht="15">
-      <c r="A350" s="7" t="s">
+      <c r="A350" s="1" t="s">
         <v>204</v>
       </c>
       <c r="B350" s="1" t="s">
@@ -7073,7 +7069,7 @@
       <c r="C350" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D350" s="8" t="s">
+      <c r="D350" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E350" s="2" t="s">
@@ -7081,7 +7077,7 @@
       </c>
     </row>
     <row r="351" spans="1:5" ht="15">
-      <c r="A351" s="8" t="s">
+      <c r="A351" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B351" s="1" t="s">
@@ -7090,7 +7086,7 @@
       <c r="C351" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D351" s="8" t="s">
+      <c r="D351" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E351" s="2" t="s">
@@ -7098,7 +7094,7 @@
       </c>
     </row>
     <row r="352" spans="1:5" ht="15">
-      <c r="A352" s="7" t="s">
+      <c r="A352" s="1" t="s">
         <v>206</v>
       </c>
       <c r="B352" s="1" t="s">
@@ -7107,7 +7103,7 @@
       <c r="C352" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D352" s="6" t="s">
+      <c r="D352" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E352" s="2" t="s">
@@ -7115,16 +7111,16 @@
       </c>
     </row>
     <row r="353" spans="1:5" ht="15">
-      <c r="A353" s="8" t="s">
+      <c r="A353" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C353" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D353" s="6" t="s">
+      <c r="C353" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D353" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E353" s="2" t="s">
@@ -7132,16 +7128,16 @@
       </c>
     </row>
     <row r="354" spans="1:5" ht="15">
-      <c r="A354" s="7" t="s">
+      <c r="A354" s="1" t="s">
         <v>207</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C354" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D354" s="6" t="s">
+      <c r="C354" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D354" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E354" s="2" t="s">
@@ -7149,16 +7145,16 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="15">
-      <c r="A355" s="8" t="s">
+      <c r="A355" s="2" t="s">
         <v>208</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C355" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D355" s="6" t="s">
+      <c r="C355" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D355" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E355" s="2" t="s">
@@ -7166,16 +7162,16 @@
       </c>
     </row>
     <row r="356" spans="1:5" ht="15">
-      <c r="A356" s="7" t="s">
+      <c r="A356" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C356" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D356" s="6" t="s">
+      <c r="C356" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D356" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E356" s="2" t="s">
@@ -7183,7 +7179,7 @@
       </c>
     </row>
     <row r="357" spans="1:5" ht="15">
-      <c r="A357" s="8" t="s">
+      <c r="A357" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B357" s="1" t="s">
@@ -7192,7 +7188,7 @@
       <c r="C357" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D357" s="8" t="s">
+      <c r="D357" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E357" s="2" t="s">
@@ -7200,7 +7196,7 @@
       </c>
     </row>
     <row r="358" spans="1:5" ht="15">
-      <c r="A358" s="8" t="s">
+      <c r="A358" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B358" s="1" t="s">
@@ -7209,7 +7205,7 @@
       <c r="C358" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D358" s="8" t="s">
+      <c r="D358" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E358" s="2" t="s">
@@ -7217,7 +7213,7 @@
       </c>
     </row>
     <row r="359" spans="1:5" ht="15">
-      <c r="A359" s="8" t="s">
+      <c r="A359" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B359" s="1" t="s">
@@ -7226,7 +7222,7 @@
       <c r="C359" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D359" s="8" t="s">
+      <c r="D359" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E359" s="2" t="s">
@@ -7234,7 +7230,7 @@
       </c>
     </row>
     <row r="360" spans="1:5" ht="15">
-      <c r="A360" s="7" t="s">
+      <c r="A360" s="1" t="s">
         <v>204</v>
       </c>
       <c r="B360" s="1" t="s">
@@ -7243,7 +7239,7 @@
       <c r="C360" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D360" s="8" t="s">
+      <c r="D360" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E360" s="2" t="s">
@@ -7251,16 +7247,16 @@
       </c>
     </row>
     <row r="361" spans="1:5" ht="15">
-      <c r="A361" s="7" t="s">
+      <c r="A361" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C361" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D361" s="6" t="s">
+      <c r="C361" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D361" s="3" t="s">
         <v>198</v>
       </c>
       <c r="E361" s="2" t="s">
@@ -7285,7 +7281,7 @@
       </c>
     </row>
     <row r="363" spans="1:5" ht="15">
-      <c r="A363" s="8" t="s">
+      <c r="A363" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B363" s="1" t="s">
@@ -7294,7 +7290,7 @@
       <c r="C363" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D363" s="8" t="s">
+      <c r="D363" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E363" s="2" t="s">
@@ -7302,7 +7298,7 @@
       </c>
     </row>
     <row r="364" spans="1:5" ht="15">
-      <c r="A364" s="8" t="s">
+      <c r="A364" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B364" s="1" t="s">
@@ -7311,7 +7307,7 @@
       <c r="C364" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D364" s="8" t="s">
+      <c r="D364" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E364" s="2" t="s">
@@ -7319,7 +7315,7 @@
       </c>
     </row>
     <row r="365" spans="1:5" ht="15">
-      <c r="A365" s="8" t="s">
+      <c r="A365" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B365" s="1" t="s">
@@ -7328,7 +7324,7 @@
       <c r="C365" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D365" s="8" t="s">
+      <c r="D365" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E365" s="2" t="s">
@@ -7404,16 +7400,16 @@
       </c>
     </row>
     <row r="370" spans="1:5" ht="15">
-      <c r="A370" s="7" t="s">
+      <c r="A370" s="1" t="s">
         <v>199</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C370" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D370" s="6" t="s">
+      <c r="C370" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D370" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E370" s="2" t="s">
@@ -7421,16 +7417,16 @@
       </c>
     </row>
     <row r="371" spans="1:5" ht="15">
-      <c r="A371" s="8" t="s">
+      <c r="A371" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C371" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D371" s="6" t="s">
+      <c r="C371" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D371" s="3" t="s">
         <v>198</v>
       </c>
       <c r="E371" s="2" t="s">

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377338D8-B7E5-4B64-9171-483B7571DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE7F562B-BD0E-4DA0-933F-8C917AD559F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="2340" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="278">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -672,6 +672,207 @@
   </si>
   <si>
     <t>Classeur3</t>
+  </si>
+  <si>
+    <t>Enlightened Tutor</t>
+  </si>
+  <si>
+    <t>Classeur4</t>
+  </si>
+  <si>
+    <t>Mirage</t>
+  </si>
+  <si>
+    <t>Mystical Tutor</t>
+  </si>
+  <si>
+    <t>Infernal Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaosphere </t>
+  </si>
+  <si>
+    <t>Hivis of the Scale</t>
+  </si>
+  <si>
+    <t>Zirilan of the Claw</t>
+  </si>
+  <si>
+    <t>Early Harvest</t>
+  </si>
+  <si>
+    <t>Hall of Gemstone</t>
+  </si>
+  <si>
+    <t>Natural Balance</t>
+  </si>
+  <si>
+    <t>Worldly Tutor</t>
+  </si>
+  <si>
+    <t>Grim Feast</t>
+  </si>
+  <si>
+    <t>Teeka's Dragon</t>
+  </si>
+  <si>
+    <t>Crystal Vein</t>
+  </si>
+  <si>
+    <t>Bad River</t>
+  </si>
+  <si>
+    <t>Chronatog</t>
+  </si>
+  <si>
+    <t>Visions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancy </t>
+  </si>
+  <si>
+    <t>Vampiric Tutor</t>
+  </si>
+  <si>
+    <t>City of Solitude</t>
+  </si>
+  <si>
+    <t>Quirion Ranger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Righteous War </t>
+  </si>
+  <si>
+    <t>Squandered Resources</t>
+  </si>
+  <si>
+    <t>Anvil of Bogardan</t>
+  </si>
+  <si>
+    <t>Undiscovered Paradise</t>
+  </si>
+  <si>
+    <t>Griffin Canyon</t>
+  </si>
+  <si>
+    <t>Fifth Edition</t>
+  </si>
+  <si>
+    <t>Dance of Many</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>Dandân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leviathan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pox </t>
+  </si>
+  <si>
+    <t>Primal Order</t>
+  </si>
+  <si>
+    <t>Underground River</t>
+  </si>
+  <si>
+    <t>Weatherlight</t>
+  </si>
+  <si>
+    <t>Aura of Silence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abjure </t>
+  </si>
+  <si>
+    <t>Spinning Darkness</t>
+  </si>
+  <si>
+    <t>Urborg Justice</t>
+  </si>
+  <si>
+    <t>Urborg Stalker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goblin Bomb </t>
+  </si>
+  <si>
+    <t>Null Rod</t>
+  </si>
+  <si>
+    <t>Bubble Matrix</t>
+  </si>
+  <si>
+    <t>Lotus Vale</t>
+  </si>
+  <si>
+    <t>Hanna's Custody</t>
+  </si>
+  <si>
+    <t>Tempest</t>
+  </si>
+  <si>
+    <t>Orim, Samite Healer</t>
+  </si>
+  <si>
+    <t>Shadow Rift</t>
+  </si>
+  <si>
+    <t>Whim of Volrath</t>
+  </si>
+  <si>
+    <t>Maddening Imp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reanimate </t>
+  </si>
+  <si>
+    <t>Sadistic Glee</t>
+  </si>
+  <si>
+    <t>Goblin Bombardment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aluren </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choke </t>
+  </si>
+  <si>
+    <t>Horned Sliver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recycle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotus Petal </t>
+  </si>
+  <si>
+    <t>Emerald Medallion</t>
+  </si>
+  <si>
+    <t>Helm of Possession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jinxed Idol </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sapphire Medallion </t>
+  </si>
+  <si>
+    <t>Caldera Lake</t>
+  </si>
+  <si>
+    <t>Ghost Town</t>
+  </si>
+  <si>
+    <t>Pine Barrens</t>
+  </si>
+  <si>
+    <t>Ancient Tomb</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E371"/>
+  <dimension ref="A1:E451"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -7433,6 +7634,1366 @@
         <v>209</v>
       </c>
     </row>
+    <row r="372" spans="1:5" ht="15">
+      <c r="A372" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C372" t="s">
+        <v>2</v>
+      </c>
+      <c r="D372" t="s">
+        <v>41</v>
+      </c>
+      <c r="E372" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" ht="15">
+      <c r="A373" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D373" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E373" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" ht="15">
+      <c r="A374" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D374" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E374" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" ht="15">
+      <c r="A375" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D375" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E375" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" ht="15">
+      <c r="A376" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D376" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E376" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" ht="15">
+      <c r="A377" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D377" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E377" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" ht="15">
+      <c r="A378" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D378" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E378" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" ht="15">
+      <c r="A379" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C379" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D379" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E379" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" ht="15">
+      <c r="A380" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D380" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E380" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" ht="15">
+      <c r="A381" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D381" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E381" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" ht="15">
+      <c r="A382" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D382" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E382" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" ht="15">
+      <c r="A383" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D383" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E383" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" ht="15">
+      <c r="A384" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C384" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D384" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E384" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" ht="15">
+      <c r="A385" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D385" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E385" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" ht="15">
+      <c r="A386" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D386" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E386" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" ht="15">
+      <c r="A387" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D387" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E387" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" ht="15">
+      <c r="A388" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D388" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E388" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" ht="15">
+      <c r="A389" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D389" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E389" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" ht="15">
+      <c r="A390" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D390" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E390" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" ht="15">
+      <c r="A391" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D391" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E391" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" ht="15">
+      <c r="A392" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D392" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E392" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" ht="15">
+      <c r="A393" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D393" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E393" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" ht="15">
+      <c r="A394" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C394" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D394" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E394" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" ht="15">
+      <c r="A395" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C395" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D395" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E395" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" ht="15">
+      <c r="A396" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C396" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D396" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E396" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" ht="15">
+      <c r="A397" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E397" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" ht="15">
+      <c r="A398" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E398" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" ht="15">
+      <c r="A399" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E399" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" ht="15">
+      <c r="A400" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D400" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E400" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" ht="15">
+      <c r="A401" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C401" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E401" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" ht="15">
+      <c r="A402" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C402" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D402" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E402" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" ht="15">
+      <c r="A403" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C403" t="s">
+        <v>31</v>
+      </c>
+      <c r="D403" t="s">
+        <v>3</v>
+      </c>
+      <c r="E403" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" ht="15">
+      <c r="A404" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C404" t="s">
+        <v>31</v>
+      </c>
+      <c r="D404" t="s">
+        <v>44</v>
+      </c>
+      <c r="E404" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" ht="15">
+      <c r="A405" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C405" t="s">
+        <v>31</v>
+      </c>
+      <c r="D405" t="s">
+        <v>3</v>
+      </c>
+      <c r="E405" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" ht="15">
+      <c r="A406" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C406" t="s">
+        <v>31</v>
+      </c>
+      <c r="D406" t="s">
+        <v>3</v>
+      </c>
+      <c r="E406" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" ht="15">
+      <c r="A407" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C407" t="s">
+        <v>31</v>
+      </c>
+      <c r="D407" t="s">
+        <v>6</v>
+      </c>
+      <c r="E407" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" ht="15">
+      <c r="A408" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C408" t="s">
+        <v>31</v>
+      </c>
+      <c r="D408" t="s">
+        <v>3</v>
+      </c>
+      <c r="E408" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" ht="15">
+      <c r="A409" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C409" t="s">
+        <v>31</v>
+      </c>
+      <c r="D409" t="s">
+        <v>3</v>
+      </c>
+      <c r="E409" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" ht="15">
+      <c r="A410" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C410" t="s">
+        <v>31</v>
+      </c>
+      <c r="D410" t="s">
+        <v>3</v>
+      </c>
+      <c r="E410" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" ht="15">
+      <c r="A411" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C411" t="s">
+        <v>31</v>
+      </c>
+      <c r="D411" t="s">
+        <v>3</v>
+      </c>
+      <c r="E411" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" ht="15">
+      <c r="A412" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C412" t="s">
+        <v>31</v>
+      </c>
+      <c r="D412" t="s">
+        <v>3</v>
+      </c>
+      <c r="E412" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" ht="15">
+      <c r="A413" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C413" t="s">
+        <v>31</v>
+      </c>
+      <c r="D413" t="s">
+        <v>3</v>
+      </c>
+      <c r="E413" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" ht="15">
+      <c r="A414" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C414" t="s">
+        <v>31</v>
+      </c>
+      <c r="D414" t="s">
+        <v>3</v>
+      </c>
+      <c r="E414" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" ht="15">
+      <c r="A415" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C415" t="s">
+        <v>31</v>
+      </c>
+      <c r="D415" t="s">
+        <v>3</v>
+      </c>
+      <c r="E415" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" ht="15">
+      <c r="A416" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C416" t="s">
+        <v>31</v>
+      </c>
+      <c r="D416" t="s">
+        <v>3</v>
+      </c>
+      <c r="E416" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" ht="15">
+      <c r="A417" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C417" t="s">
+        <v>31</v>
+      </c>
+      <c r="D417" t="s">
+        <v>6</v>
+      </c>
+      <c r="E417" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" ht="15">
+      <c r="A418" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C418" t="s">
+        <v>31</v>
+      </c>
+      <c r="D418" t="s">
+        <v>6</v>
+      </c>
+      <c r="E418" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" ht="15">
+      <c r="A419" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C419" t="s">
+        <v>31</v>
+      </c>
+      <c r="D419" t="s">
+        <v>3</v>
+      </c>
+      <c r="E419" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" ht="15">
+      <c r="A420" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C420" t="s">
+        <v>31</v>
+      </c>
+      <c r="D420" t="s">
+        <v>3</v>
+      </c>
+      <c r="E420" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" ht="15">
+      <c r="A421" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C421" t="s">
+        <v>31</v>
+      </c>
+      <c r="D421" t="s">
+        <v>3</v>
+      </c>
+      <c r="E421" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" ht="15">
+      <c r="A422" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C422" t="s">
+        <v>31</v>
+      </c>
+      <c r="D422" t="s">
+        <v>3</v>
+      </c>
+      <c r="E422" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" ht="15">
+      <c r="A423" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C423" t="s">
+        <v>31</v>
+      </c>
+      <c r="D423" t="s">
+        <v>3</v>
+      </c>
+      <c r="E423" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" ht="15">
+      <c r="A424" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C424" t="s">
+        <v>31</v>
+      </c>
+      <c r="D424" t="s">
+        <v>3</v>
+      </c>
+      <c r="E424" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" ht="15">
+      <c r="A425" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C425" t="s">
+        <v>31</v>
+      </c>
+      <c r="D425" t="s">
+        <v>6</v>
+      </c>
+      <c r="E425" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" ht="15">
+      <c r="A426" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C426" t="s">
+        <v>31</v>
+      </c>
+      <c r="D426" t="s">
+        <v>3</v>
+      </c>
+      <c r="E426" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" ht="15">
+      <c r="A427" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C427" t="s">
+        <v>31</v>
+      </c>
+      <c r="D427" t="s">
+        <v>3</v>
+      </c>
+      <c r="E427" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" ht="15">
+      <c r="A428" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C428" t="s">
+        <v>31</v>
+      </c>
+      <c r="D428" t="s">
+        <v>3</v>
+      </c>
+      <c r="E428" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" ht="15">
+      <c r="A429" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C429" t="s">
+        <v>31</v>
+      </c>
+      <c r="D429" t="s">
+        <v>6</v>
+      </c>
+      <c r="E429" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" ht="15">
+      <c r="A430" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C430" t="s">
+        <v>31</v>
+      </c>
+      <c r="D430" t="s">
+        <v>3</v>
+      </c>
+      <c r="E430" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" ht="15">
+      <c r="A431" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C431" t="s">
+        <v>31</v>
+      </c>
+      <c r="D431" t="s">
+        <v>3</v>
+      </c>
+      <c r="E431" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" ht="15">
+      <c r="A432" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C432" t="s">
+        <v>31</v>
+      </c>
+      <c r="D432" t="s">
+        <v>6</v>
+      </c>
+      <c r="E432" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" ht="15">
+      <c r="A433" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C433" t="s">
+        <v>31</v>
+      </c>
+      <c r="D433" t="s">
+        <v>6</v>
+      </c>
+      <c r="E433" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" ht="15">
+      <c r="A434" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C434" t="s">
+        <v>31</v>
+      </c>
+      <c r="D434" t="s">
+        <v>3</v>
+      </c>
+      <c r="E434" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" ht="15">
+      <c r="A435" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C435" t="s">
+        <v>31</v>
+      </c>
+      <c r="D435" t="s">
+        <v>3</v>
+      </c>
+      <c r="E435" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" ht="15">
+      <c r="A436" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C436" t="s">
+        <v>31</v>
+      </c>
+      <c r="D436" t="s">
+        <v>6</v>
+      </c>
+      <c r="E436" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" ht="15">
+      <c r="A437" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C437" t="s">
+        <v>31</v>
+      </c>
+      <c r="D437" t="s">
+        <v>3</v>
+      </c>
+      <c r="E437" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" ht="15">
+      <c r="A438" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C438" t="s">
+        <v>31</v>
+      </c>
+      <c r="D438" t="s">
+        <v>6</v>
+      </c>
+      <c r="E438" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" ht="15">
+      <c r="A439" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C439" t="s">
+        <v>31</v>
+      </c>
+      <c r="D439" t="s">
+        <v>3</v>
+      </c>
+      <c r="E439" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" ht="15">
+      <c r="A440" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C440" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D440" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E440" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" ht="15">
+      <c r="A441" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D441" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E441" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" ht="15">
+      <c r="A442" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C442" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D442" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E442" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" ht="15">
+      <c r="A443" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C443" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D443" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E443" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" ht="15">
+      <c r="A444" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C444" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D444" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E444" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" ht="15">
+      <c r="A445" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C445" t="s">
+        <v>31</v>
+      </c>
+      <c r="D445" t="s">
+        <v>6</v>
+      </c>
+      <c r="E445" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" ht="15">
+      <c r="A446" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B446" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C446" t="s">
+        <v>31</v>
+      </c>
+      <c r="D446" t="s">
+        <v>3</v>
+      </c>
+      <c r="E446" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" ht="15">
+      <c r="A447" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B447" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C447" t="s">
+        <v>31</v>
+      </c>
+      <c r="D447" t="s">
+        <v>3</v>
+      </c>
+      <c r="E447" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" ht="15">
+      <c r="A448" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B448" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C448" t="s">
+        <v>31</v>
+      </c>
+      <c r="D448" t="s">
+        <v>3</v>
+      </c>
+      <c r="E448" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" ht="15">
+      <c r="A449" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C449" t="s">
+        <v>31</v>
+      </c>
+      <c r="D449" t="s">
+        <v>3</v>
+      </c>
+      <c r="E449" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" ht="15">
+      <c r="A450" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B450" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C450" t="s">
+        <v>31</v>
+      </c>
+      <c r="D450" t="s">
+        <v>3</v>
+      </c>
+      <c r="E450" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" ht="15">
+      <c r="A451" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B451" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C451" t="s">
+        <v>31</v>
+      </c>
+      <c r="D451" t="s">
+        <v>3</v>
+      </c>
+      <c r="E451" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE7F562B-BD0E-4DA0-933F-8C917AD559F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A05C080-D57B-4C6F-97AD-B9FFC7066D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="336">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -873,6 +873,180 @@
   </si>
   <si>
     <t>Ancient Tomb</t>
+  </si>
+  <si>
+    <t>Rolling Stones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stronghold </t>
+  </si>
+  <si>
+    <t>Classeur5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream Halls </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evacuation </t>
+  </si>
+  <si>
+    <t>Reins of Power</t>
+  </si>
+  <si>
+    <t>Thalakos Deceiver</t>
+  </si>
+  <si>
+    <t>Volrath's Shapeshifter</t>
+  </si>
+  <si>
+    <t>Bottomless Pit </t>
+  </si>
+  <si>
+    <t>Mogg Infestation</t>
+  </si>
+  <si>
+    <t>Burgeoning </t>
+  </si>
+  <si>
+    <t>Constant Mists </t>
+  </si>
+  <si>
+    <t>Hermit Druid</t>
+  </si>
+  <si>
+    <t>Primal Rage</t>
+  </si>
+  <si>
+    <t>Horn of Greed</t>
+  </si>
+  <si>
+    <t>Heartstone </t>
+  </si>
+  <si>
+    <t>Mox Diamond</t>
+  </si>
+  <si>
+    <t>Limited Resources</t>
+  </si>
+  <si>
+    <t>Exodus</t>
+  </si>
+  <si>
+    <t>Penance </t>
+  </si>
+  <si>
+    <t>Wall of Nets</t>
+  </si>
+  <si>
+    <t>Curiosity </t>
+  </si>
+  <si>
+    <t>Culling the Weak</t>
+  </si>
+  <si>
+    <t>Hatred </t>
+  </si>
+  <si>
+    <t>Ravenous Baboons</t>
+  </si>
+  <si>
+    <t>Spellshock </t>
+  </si>
+  <si>
+    <t>Oath of Druids</t>
+  </si>
+  <si>
+    <t>Mirri, Cat Warrior </t>
+  </si>
+  <si>
+    <t>Incoming!</t>
+  </si>
+  <si>
+    <t>Unglued</t>
+  </si>
+  <si>
+    <t>Ashnod's Coupon</t>
+  </si>
+  <si>
+    <t>Island </t>
+  </si>
+  <si>
+    <t>Goblin Token (Red 1/1)</t>
+  </si>
+  <si>
+    <t>Plains</t>
+  </si>
+  <si>
+    <t>Herald of Serra</t>
+  </si>
+  <si>
+    <t>Urza's Saga</t>
+  </si>
+  <si>
+    <t>Hibernation</t>
+  </si>
+  <si>
+    <t>Annul </t>
+  </si>
+  <si>
+    <t>Morphling</t>
+  </si>
+  <si>
+    <t>Sunder </t>
+  </si>
+  <si>
+    <t>Darkest Hour </t>
+  </si>
+  <si>
+    <t>Duress</t>
+  </si>
+  <si>
+    <t>Exhume </t>
+  </si>
+  <si>
+    <t>Rain of Filth</t>
+  </si>
+  <si>
+    <t>Raze</t>
+  </si>
+  <si>
+    <t>Sneak Attack</t>
+  </si>
+  <si>
+    <t>Meltdown </t>
+  </si>
+  <si>
+    <t>Wildfire </t>
+  </si>
+  <si>
+    <t>Argothian Enchantress</t>
+  </si>
+  <si>
+    <t>Priest of Titania</t>
+  </si>
+  <si>
+    <t>Vernal Bloom</t>
+  </si>
+  <si>
+    <t>Carpet of Flowers</t>
+  </si>
+  <si>
+    <t>Gaea's Cradle</t>
+  </si>
+  <si>
+    <t>Shivan Gorge</t>
+  </si>
+  <si>
+    <t>Tolarian Academy</t>
+  </si>
+  <si>
+    <t>Illicit Auction</t>
+  </si>
+  <si>
+    <t>Sixth Edition</t>
+  </si>
+  <si>
+    <t>Jokulhaups</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E451"/>
+  <dimension ref="A1:E511"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -8979,7 +9153,7 @@
     </row>
     <row r="451" spans="1:5" ht="15">
       <c r="A451" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>257</v>
@@ -8992,6 +9166,1026 @@
       </c>
       <c r="E451" s="2" t="s">
         <v>212</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" ht="15">
+      <c r="A452" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B452" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C452" t="s">
+        <v>31</v>
+      </c>
+      <c r="D452" t="s">
+        <v>3</v>
+      </c>
+      <c r="E452" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" ht="15">
+      <c r="A453" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B453" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C453" t="s">
+        <v>31</v>
+      </c>
+      <c r="D453" t="s">
+        <v>3</v>
+      </c>
+      <c r="E453" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" ht="15">
+      <c r="A454" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B454" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C454" t="s">
+        <v>31</v>
+      </c>
+      <c r="D454" t="s">
+        <v>3</v>
+      </c>
+      <c r="E454" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" ht="15">
+      <c r="A455" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C455" t="s">
+        <v>31</v>
+      </c>
+      <c r="D455" t="s">
+        <v>6</v>
+      </c>
+      <c r="E455" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" ht="15">
+      <c r="A456" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B456" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C456" t="s">
+        <v>31</v>
+      </c>
+      <c r="D456" t="s">
+        <v>3</v>
+      </c>
+      <c r="E456" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" ht="15">
+      <c r="A457" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C457" t="s">
+        <v>31</v>
+      </c>
+      <c r="D457" t="s">
+        <v>3</v>
+      </c>
+      <c r="E457" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" ht="15">
+      <c r="A458" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C458" t="s">
+        <v>31</v>
+      </c>
+      <c r="D458" t="s">
+        <v>3</v>
+      </c>
+      <c r="E458" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" ht="15">
+      <c r="A459" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C459" t="s">
+        <v>31</v>
+      </c>
+      <c r="D459" t="s">
+        <v>6</v>
+      </c>
+      <c r="E459" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" ht="15">
+      <c r="A460" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C460" t="s">
+        <v>31</v>
+      </c>
+      <c r="D460" t="s">
+        <v>3</v>
+      </c>
+      <c r="E460" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" ht="15">
+      <c r="A461" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C461" t="s">
+        <v>31</v>
+      </c>
+      <c r="D461" t="s">
+        <v>3</v>
+      </c>
+      <c r="E461" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" ht="15">
+      <c r="A462" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C462" t="s">
+        <v>31</v>
+      </c>
+      <c r="D462" t="s">
+        <v>6</v>
+      </c>
+      <c r="E462" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" ht="15">
+      <c r="A463" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C463" t="s">
+        <v>31</v>
+      </c>
+      <c r="D463" t="s">
+        <v>3</v>
+      </c>
+      <c r="E463" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" ht="15">
+      <c r="A464" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C464" t="s">
+        <v>31</v>
+      </c>
+      <c r="D464" t="s">
+        <v>3</v>
+      </c>
+      <c r="E464" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" ht="15">
+      <c r="A465" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C465" t="s">
+        <v>31</v>
+      </c>
+      <c r="D465" t="s">
+        <v>6</v>
+      </c>
+      <c r="E465" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" ht="15">
+      <c r="A466" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C466" t="s">
+        <v>31</v>
+      </c>
+      <c r="D466" t="s">
+        <v>6</v>
+      </c>
+      <c r="E466" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" ht="15">
+      <c r="A467" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C467" t="s">
+        <v>31</v>
+      </c>
+      <c r="D467" t="s">
+        <v>3</v>
+      </c>
+      <c r="E467" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" ht="15">
+      <c r="A468" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C468" t="s">
+        <v>31</v>
+      </c>
+      <c r="D468" t="s">
+        <v>3</v>
+      </c>
+      <c r="E468" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" ht="15">
+      <c r="A469" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C469" t="s">
+        <v>31</v>
+      </c>
+      <c r="D469" t="s">
+        <v>3</v>
+      </c>
+      <c r="E469" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" ht="15">
+      <c r="A470" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C470" t="s">
+        <v>31</v>
+      </c>
+      <c r="D470" t="s">
+        <v>3</v>
+      </c>
+      <c r="E470" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" ht="15">
+      <c r="A471" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C471" t="s">
+        <v>31</v>
+      </c>
+      <c r="D471" t="s">
+        <v>3</v>
+      </c>
+      <c r="E471" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" ht="15">
+      <c r="A472" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C472" t="s">
+        <v>31</v>
+      </c>
+      <c r="D472" t="s">
+        <v>3</v>
+      </c>
+      <c r="E472" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" ht="15">
+      <c r="A473" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C473" t="s">
+        <v>31</v>
+      </c>
+      <c r="D473" t="s">
+        <v>3</v>
+      </c>
+      <c r="E473" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" ht="15">
+      <c r="A474" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C474" t="s">
+        <v>31</v>
+      </c>
+      <c r="D474" t="s">
+        <v>3</v>
+      </c>
+      <c r="E474" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" ht="15">
+      <c r="A475" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C475" t="s">
+        <v>31</v>
+      </c>
+      <c r="D475" t="s">
+        <v>6</v>
+      </c>
+      <c r="E475" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" ht="15">
+      <c r="A476" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C476" t="s">
+        <v>31</v>
+      </c>
+      <c r="D476" t="s">
+        <v>6</v>
+      </c>
+      <c r="E476" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" ht="15">
+      <c r="A477" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C477" t="s">
+        <v>2</v>
+      </c>
+      <c r="D477" t="s">
+        <v>3</v>
+      </c>
+      <c r="E477" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" ht="15">
+      <c r="A478" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C478" t="s">
+        <v>2</v>
+      </c>
+      <c r="D478" t="s">
+        <v>3</v>
+      </c>
+      <c r="E478" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" ht="15">
+      <c r="A479" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C479" t="s">
+        <v>2</v>
+      </c>
+      <c r="D479" t="s">
+        <v>3</v>
+      </c>
+      <c r="E479" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" ht="15">
+      <c r="A480" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C480" t="s">
+        <v>2</v>
+      </c>
+      <c r="D480" t="s">
+        <v>3</v>
+      </c>
+      <c r="E480" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" ht="15">
+      <c r="A481" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C481" t="s">
+        <v>2</v>
+      </c>
+      <c r="D481" t="s">
+        <v>3</v>
+      </c>
+      <c r="E481" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" ht="15">
+      <c r="A482" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C482" t="s">
+        <v>31</v>
+      </c>
+      <c r="D482" t="s">
+        <v>3</v>
+      </c>
+      <c r="E482" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" ht="15">
+      <c r="A483" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C483" t="s">
+        <v>31</v>
+      </c>
+      <c r="D483" t="s">
+        <v>3</v>
+      </c>
+      <c r="E483" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" ht="15">
+      <c r="A484" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C484" t="s">
+        <v>31</v>
+      </c>
+      <c r="D484" t="s">
+        <v>3</v>
+      </c>
+      <c r="E484" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" ht="15">
+      <c r="A485" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C485" t="s">
+        <v>31</v>
+      </c>
+      <c r="D485" t="s">
+        <v>3</v>
+      </c>
+      <c r="E485" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" ht="15">
+      <c r="A486" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C486" t="s">
+        <v>31</v>
+      </c>
+      <c r="D486" t="s">
+        <v>3</v>
+      </c>
+      <c r="E486" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" ht="15">
+      <c r="A487" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C487" t="s">
+        <v>31</v>
+      </c>
+      <c r="D487" t="s">
+        <v>3</v>
+      </c>
+      <c r="E487" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" ht="15">
+      <c r="A488" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C488" t="s">
+        <v>31</v>
+      </c>
+      <c r="D488" t="s">
+        <v>3</v>
+      </c>
+      <c r="E488" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" ht="15">
+      <c r="A489" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C489" t="s">
+        <v>31</v>
+      </c>
+      <c r="D489" t="s">
+        <v>3</v>
+      </c>
+      <c r="E489" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" ht="15">
+      <c r="A490" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C490" t="s">
+        <v>31</v>
+      </c>
+      <c r="D490" t="s">
+        <v>3</v>
+      </c>
+      <c r="E490" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" ht="15">
+      <c r="A491" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C491" t="s">
+        <v>31</v>
+      </c>
+      <c r="D491" t="s">
+        <v>3</v>
+      </c>
+      <c r="E491" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" ht="15">
+      <c r="A492" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C492" t="s">
+        <v>31</v>
+      </c>
+      <c r="D492" t="s">
+        <v>3</v>
+      </c>
+      <c r="E492" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" ht="15">
+      <c r="A493" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C493" t="s">
+        <v>31</v>
+      </c>
+      <c r="D493" t="s">
+        <v>3</v>
+      </c>
+      <c r="E493" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" ht="15">
+      <c r="A494" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C494" t="s">
+        <v>31</v>
+      </c>
+      <c r="D494" t="s">
+        <v>3</v>
+      </c>
+      <c r="E494" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" ht="15">
+      <c r="A495" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C495" t="s">
+        <v>31</v>
+      </c>
+      <c r="D495" t="s">
+        <v>3</v>
+      </c>
+      <c r="E495" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" ht="15">
+      <c r="A496" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C496" t="s">
+        <v>31</v>
+      </c>
+      <c r="D496" t="s">
+        <v>6</v>
+      </c>
+      <c r="E496" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" ht="15">
+      <c r="A497" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C497" t="s">
+        <v>31</v>
+      </c>
+      <c r="D497" t="s">
+        <v>6</v>
+      </c>
+      <c r="E497" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" ht="15">
+      <c r="A498" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C498" t="s">
+        <v>31</v>
+      </c>
+      <c r="D498" t="s">
+        <v>3</v>
+      </c>
+      <c r="E498" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" ht="15">
+      <c r="A499" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C499" t="s">
+        <v>31</v>
+      </c>
+      <c r="D499" t="s">
+        <v>6</v>
+      </c>
+      <c r="E499" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" ht="15">
+      <c r="A500" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C500" t="s">
+        <v>31</v>
+      </c>
+      <c r="D500" t="s">
+        <v>3</v>
+      </c>
+      <c r="E500" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" ht="15">
+      <c r="A501" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C501" t="s">
+        <v>31</v>
+      </c>
+      <c r="D501" t="s">
+        <v>3</v>
+      </c>
+      <c r="E501" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" ht="15">
+      <c r="A502" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C502" t="s">
+        <v>31</v>
+      </c>
+      <c r="D502" t="s">
+        <v>3</v>
+      </c>
+      <c r="E502" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" ht="15">
+      <c r="A503" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C503" t="s">
+        <v>31</v>
+      </c>
+      <c r="D503" t="s">
+        <v>3</v>
+      </c>
+      <c r="E503" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" ht="15">
+      <c r="A504" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C504" t="s">
+        <v>31</v>
+      </c>
+      <c r="D504" t="s">
+        <v>3</v>
+      </c>
+      <c r="E504" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" ht="15">
+      <c r="A505" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C505" t="s">
+        <v>31</v>
+      </c>
+      <c r="D505" t="s">
+        <v>3</v>
+      </c>
+      <c r="E505" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" ht="15">
+      <c r="A506" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C506" t="s">
+        <v>31</v>
+      </c>
+      <c r="D506" t="s">
+        <v>6</v>
+      </c>
+      <c r="E506" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" ht="15">
+      <c r="A507" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C507" t="s">
+        <v>31</v>
+      </c>
+      <c r="D507" t="s">
+        <v>3</v>
+      </c>
+      <c r="E507" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" ht="15">
+      <c r="A508" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C508" t="s">
+        <v>31</v>
+      </c>
+      <c r="D508" t="s">
+        <v>6</v>
+      </c>
+      <c r="E508" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" ht="15">
+      <c r="A509" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C509" t="s">
+        <v>31</v>
+      </c>
+      <c r="D509" t="s">
+        <v>6</v>
+      </c>
+      <c r="E509" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" ht="15">
+      <c r="A510" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C510" t="s">
+        <v>31</v>
+      </c>
+      <c r="D510" t="s">
+        <v>3</v>
+      </c>
+      <c r="E510" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" ht="15">
+      <c r="A511" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C511" t="s">
+        <v>31</v>
+      </c>
+      <c r="D511" t="s">
+        <v>6</v>
+      </c>
+      <c r="E511" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A05C080-D57B-4C6F-97AD-B9FFC7066D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447F040D-155A-438A-A8D1-EB96F873574D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="337">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1047,6 +1047,9 @@
   </si>
   <si>
     <t>Jokulhaups</t>
+  </si>
+  <si>
+    <t>Portal Second Age</t>
   </si>
 </sst>
 </file>
@@ -1492,7 +1495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E511"/>
+  <dimension ref="A1:E512"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -10188,6 +10191,23 @@
         <v>280</v>
       </c>
     </row>
+    <row r="512" spans="1:5" ht="15">
+      <c r="A512" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C512" t="s">
+        <v>31</v>
+      </c>
+      <c r="D512" t="s">
+        <v>6</v>
+      </c>
+      <c r="E512" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447F040D-155A-438A-A8D1-EB96F873574D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3355A800-5091-44AC-A0A0-BEF829C8A946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="371">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1050,6 +1050,108 @@
   </si>
   <si>
     <t>Portal Second Age</t>
+  </si>
+  <si>
+    <t>Energy Storm</t>
+  </si>
+  <si>
+    <t>Ice Age</t>
+  </si>
+  <si>
+    <t>Enduring Renewal</t>
+  </si>
+  <si>
+    <t>Polar Kraken</t>
+  </si>
+  <si>
+    <t>Dance of the Dead</t>
+  </si>
+  <si>
+    <t>Burnt Offering</t>
+  </si>
+  <si>
+    <t>Songs of the Damned</t>
+  </si>
+  <si>
+    <t>Pyroblast </t>
+  </si>
+  <si>
+    <t>Anarchy </t>
+  </si>
+  <si>
+    <t>Jokulhaups </t>
+  </si>
+  <si>
+    <t>Pyroclasm </t>
+  </si>
+  <si>
+    <t>Balduvian Hydra</t>
+  </si>
+  <si>
+    <t>Thermokarst</t>
+  </si>
+  <si>
+    <t>Nature's Lore</t>
+  </si>
+  <si>
+    <t>Fyndhorn Elves</t>
+  </si>
+  <si>
+    <t>Lhurgoyf</t>
+  </si>
+  <si>
+    <t>Jeweled Amulet</t>
+  </si>
+  <si>
+    <t>Fire Covenant</t>
+  </si>
+  <si>
+    <t>Snow-Covered Plains</t>
+  </si>
+  <si>
+    <t>Snow-Covered Island</t>
+  </si>
+  <si>
+    <t>Snow-Covered Swamp</t>
+  </si>
+  <si>
+    <t>Snow-Covered Forest</t>
+  </si>
+  <si>
+    <t>Adarkar Wastes</t>
+  </si>
+  <si>
+    <t>Glacial Chasm</t>
+  </si>
+  <si>
+    <t>Karplusan Forest</t>
+  </si>
+  <si>
+    <t>Brushland </t>
+  </si>
+  <si>
+    <t>Soraya the Falconer</t>
+  </si>
+  <si>
+    <t>Homelands </t>
+  </si>
+  <si>
+    <t>Serra Aviary</t>
+  </si>
+  <si>
+    <t>Baron Sengir</t>
+  </si>
+  <si>
+    <t>Koskun Falls</t>
+  </si>
+  <si>
+    <t>Veldrane of Sengir </t>
+  </si>
+  <si>
+    <t>An-Zerrin Ruins</t>
+  </si>
+  <si>
+    <t>Didgeridoo </t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E512"/>
+  <dimension ref="A1:E546"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -10208,6 +10310,584 @@
         <v>280</v>
       </c>
     </row>
+    <row r="513" spans="1:5" ht="15">
+      <c r="A513" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C513" t="s">
+        <v>31</v>
+      </c>
+      <c r="D513" t="s">
+        <v>6</v>
+      </c>
+      <c r="E513" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" ht="15">
+      <c r="A514" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C514" t="s">
+        <v>31</v>
+      </c>
+      <c r="D514" t="s">
+        <v>6</v>
+      </c>
+      <c r="E514" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" ht="15">
+      <c r="A515" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C515" t="s">
+        <v>31</v>
+      </c>
+      <c r="D515" t="s">
+        <v>6</v>
+      </c>
+      <c r="E515" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" ht="15">
+      <c r="A516" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C516" t="s">
+        <v>2</v>
+      </c>
+      <c r="D516" t="s">
+        <v>33</v>
+      </c>
+      <c r="E516" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" ht="15">
+      <c r="A517" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C517" t="s">
+        <v>31</v>
+      </c>
+      <c r="D517" t="s">
+        <v>3</v>
+      </c>
+      <c r="E517" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" ht="15">
+      <c r="A518" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C518" t="s">
+        <v>2</v>
+      </c>
+      <c r="D518" t="s">
+        <v>44</v>
+      </c>
+      <c r="E518" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" ht="15">
+      <c r="A519" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C519" t="s">
+        <v>2</v>
+      </c>
+      <c r="D519" t="s">
+        <v>44</v>
+      </c>
+      <c r="E519" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" ht="15">
+      <c r="A520" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C520" t="s">
+        <v>2</v>
+      </c>
+      <c r="D520" t="s">
+        <v>6</v>
+      </c>
+      <c r="E520" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" ht="15">
+      <c r="A521" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C521" t="s">
+        <v>31</v>
+      </c>
+      <c r="D521" t="s">
+        <v>198</v>
+      </c>
+      <c r="E521" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" ht="15">
+      <c r="A522" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C522" t="s">
+        <v>2</v>
+      </c>
+      <c r="D522" t="s">
+        <v>44</v>
+      </c>
+      <c r="E522" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" ht="15">
+      <c r="A523" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C523" t="s">
+        <v>31</v>
+      </c>
+      <c r="D523" t="s">
+        <v>6</v>
+      </c>
+      <c r="E523" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" ht="15">
+      <c r="A524" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C524" t="s">
+        <v>31</v>
+      </c>
+      <c r="D524" t="s">
+        <v>3</v>
+      </c>
+      <c r="E524" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" ht="15">
+      <c r="A525" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C525" t="s">
+        <v>31</v>
+      </c>
+      <c r="D525" t="s">
+        <v>44</v>
+      </c>
+      <c r="E525" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" ht="15">
+      <c r="A526" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C526" t="s">
+        <v>31</v>
+      </c>
+      <c r="D526" t="s">
+        <v>44</v>
+      </c>
+      <c r="E526" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" ht="15">
+      <c r="A527" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C527" t="s">
+        <v>2</v>
+      </c>
+      <c r="D527" t="s">
+        <v>6</v>
+      </c>
+      <c r="E527" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" ht="15">
+      <c r="A528" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C528" t="s">
+        <v>2</v>
+      </c>
+      <c r="D528" t="s">
+        <v>198</v>
+      </c>
+      <c r="E528" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" ht="15">
+      <c r="A529" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C529" t="s">
+        <v>2</v>
+      </c>
+      <c r="D529" t="s">
+        <v>33</v>
+      </c>
+      <c r="E529" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" ht="15">
+      <c r="A530" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C530" t="s">
+        <v>2</v>
+      </c>
+      <c r="D530" t="s">
+        <v>44</v>
+      </c>
+      <c r="E530" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" ht="15">
+      <c r="A531" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C531" t="s">
+        <v>31</v>
+      </c>
+      <c r="D531" t="s">
+        <v>44</v>
+      </c>
+      <c r="E531" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" ht="15">
+      <c r="A532" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C532" t="s">
+        <v>31</v>
+      </c>
+      <c r="D532" t="s">
+        <v>44</v>
+      </c>
+      <c r="E532" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" ht="15">
+      <c r="A533" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C533" t="s">
+        <v>2</v>
+      </c>
+      <c r="D533" t="s">
+        <v>6</v>
+      </c>
+      <c r="E533" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" ht="15">
+      <c r="A534" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C534" t="s">
+        <v>2</v>
+      </c>
+      <c r="D534" t="s">
+        <v>6</v>
+      </c>
+      <c r="E534" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" ht="15">
+      <c r="A535" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C535" t="s">
+        <v>2</v>
+      </c>
+      <c r="D535" t="s">
+        <v>6</v>
+      </c>
+      <c r="E535" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" ht="15">
+      <c r="A536" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C536" t="s">
+        <v>2</v>
+      </c>
+      <c r="D536" t="s">
+        <v>6</v>
+      </c>
+      <c r="E536" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" ht="15">
+      <c r="A537" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C537" t="s">
+        <v>2</v>
+      </c>
+      <c r="D537" t="s">
+        <v>6</v>
+      </c>
+      <c r="E537" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" ht="15">
+      <c r="A538" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C538" t="s">
+        <v>31</v>
+      </c>
+      <c r="D538" t="s">
+        <v>6</v>
+      </c>
+      <c r="E538" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" ht="15">
+      <c r="A539" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C539" t="s">
+        <v>31</v>
+      </c>
+      <c r="D539" t="s">
+        <v>6</v>
+      </c>
+      <c r="E539" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" ht="15">
+      <c r="A540" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C540" t="s">
+        <v>31</v>
+      </c>
+      <c r="D540" t="s">
+        <v>3</v>
+      </c>
+      <c r="E540" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" ht="15">
+      <c r="A541" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C541" t="s">
+        <v>31</v>
+      </c>
+      <c r="D541" t="s">
+        <v>44</v>
+      </c>
+      <c r="E541" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" ht="15">
+      <c r="A542" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C542" t="s">
+        <v>31</v>
+      </c>
+      <c r="D542" t="s">
+        <v>3</v>
+      </c>
+      <c r="E542" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" ht="15">
+      <c r="A543" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C543" t="s">
+        <v>31</v>
+      </c>
+      <c r="D543" t="s">
+        <v>6</v>
+      </c>
+      <c r="E543" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" ht="15">
+      <c r="A544" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C544" t="s">
+        <v>31</v>
+      </c>
+      <c r="D544" t="s">
+        <v>44</v>
+      </c>
+      <c r="E544" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" ht="15">
+      <c r="A545" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C545" t="s">
+        <v>2</v>
+      </c>
+      <c r="D545" t="s">
+        <v>41</v>
+      </c>
+      <c r="E545" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" ht="15">
+      <c r="A546" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C546" t="s">
+        <v>2</v>
+      </c>
+      <c r="D546" t="s">
+        <v>33</v>
+      </c>
+      <c r="E546" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3355A800-5091-44AC-A0A0-BEF829C8A946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670CF89D-1473-4010-AF91-9DEA7D390E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2935" uniqueCount="377">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1152,6 +1152,24 @@
   </si>
   <si>
     <t>Didgeridoo </t>
+  </si>
+  <si>
+    <t>Blanc Vert</t>
+  </si>
+  <si>
+    <t>Savannah</t>
+  </si>
+  <si>
+    <t>Foreign White Border</t>
+  </si>
+  <si>
+    <t>Spirit Link</t>
+  </si>
+  <si>
+    <t>Regrowth</t>
+  </si>
+  <si>
+    <t>Tsunami</t>
   </si>
 </sst>
 </file>
@@ -1186,7 +1204,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1198,8 +1216,14 @@
         <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1231,11 +1255,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1248,6 +1285,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1597,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E546"/>
+  <dimension ref="A1:E587"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -10888,6 +10937,703 @@
         <v>210</v>
       </c>
     </row>
+    <row r="547" spans="1:5">
+      <c r="A547" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B547" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D547" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E547" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" ht="15">
+      <c r="A548" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B548" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C548" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D548" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E548" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" ht="15">
+      <c r="A549" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C549" t="s">
+        <v>2</v>
+      </c>
+      <c r="D549" t="s">
+        <v>6</v>
+      </c>
+      <c r="E549" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" ht="15">
+      <c r="A550" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C550" t="s">
+        <v>2</v>
+      </c>
+      <c r="D550" t="s">
+        <v>44</v>
+      </c>
+      <c r="E550" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5">
+      <c r="A551" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B551" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C551" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D551" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E551" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" ht="15">
+      <c r="A552" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B552" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C552" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D552" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E552" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" ht="15">
+      <c r="A553" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B553" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C553" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D553" t="s">
+        <v>6</v>
+      </c>
+      <c r="E553" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" ht="15">
+      <c r="A554" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B554" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C554" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D554" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E554" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5">
+      <c r="A555" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B555" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D555" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E555" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5">
+      <c r="A556" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B556" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C556" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D556" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E556" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" ht="15">
+      <c r="A557" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B557" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D557" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E557" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" ht="15">
+      <c r="A558" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C558" t="s">
+        <v>2</v>
+      </c>
+      <c r="D558" t="s">
+        <v>6</v>
+      </c>
+      <c r="E558" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" ht="15">
+      <c r="A559" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B559" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D559" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E559" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" ht="15">
+      <c r="A560" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B560" t="s">
+        <v>129</v>
+      </c>
+      <c r="C560" t="s">
+        <v>2</v>
+      </c>
+      <c r="D560" t="s">
+        <v>6</v>
+      </c>
+      <c r="E560" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5">
+      <c r="A561" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B561" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C561" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D561" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E561" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" ht="15">
+      <c r="A562" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C562" t="s">
+        <v>2</v>
+      </c>
+      <c r="D562" t="s">
+        <v>3</v>
+      </c>
+      <c r="E562" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" ht="15">
+      <c r="A563" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B563" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D563" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E563" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" ht="15">
+      <c r="A564" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D564" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E564" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" ht="15">
+      <c r="A565" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B565" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D565" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E565" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" ht="15">
+      <c r="A566" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B566" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C566" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D566" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E566" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5" ht="15">
+      <c r="A567" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D567" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E567" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5">
+      <c r="A568" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B568" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C568" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D568" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E568" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5" ht="15">
+      <c r="A569" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B569" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D569" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E569" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5">
+      <c r="A570" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B570" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D570" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E570" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5" ht="15">
+      <c r="A571" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B571" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D571" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E571" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5">
+      <c r="A572" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B572" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C572" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D572" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E572" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5">
+      <c r="A573" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B573" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D573" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E573" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="574" spans="1:5" ht="15">
+      <c r="A574" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C574" t="s">
+        <v>2</v>
+      </c>
+      <c r="D574" t="s">
+        <v>6</v>
+      </c>
+      <c r="E574" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="575" spans="1:5" ht="15">
+      <c r="A575" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B575" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D575" t="s">
+        <v>6</v>
+      </c>
+      <c r="E575" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="576" spans="1:5">
+      <c r="A576" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B576" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D576" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E576" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5">
+      <c r="A577" t="s">
+        <v>76</v>
+      </c>
+      <c r="B577" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D577" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E577" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5">
+      <c r="A578" t="s">
+        <v>132</v>
+      </c>
+      <c r="B578" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C578" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D578" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E578" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5" ht="15">
+      <c r="A579" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B579" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C579" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D579" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E579" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5" ht="15">
+      <c r="A580" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B580" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C580" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D580" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E580" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="581" spans="1:5">
+      <c r="A581" t="s">
+        <v>375</v>
+      </c>
+      <c r="B581" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D581" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E581" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5">
+      <c r="A582" t="s">
+        <v>376</v>
+      </c>
+      <c r="B582" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C582" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D582" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E582" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5">
+      <c r="A583" t="s">
+        <v>127</v>
+      </c>
+      <c r="B583" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C583" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D583" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E583" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="584" spans="1:5">
+      <c r="A584" t="s">
+        <v>127</v>
+      </c>
+      <c r="B584" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C584" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D584" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E584" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="585" spans="1:5" ht="15">
+      <c r="A585" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B585" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D585" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E585" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5" ht="15">
+      <c r="A586" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C586" t="s">
+        <v>2</v>
+      </c>
+      <c r="D586" t="s">
+        <v>198</v>
+      </c>
+      <c r="E586" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="587" spans="1:5">
+      <c r="A587" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B587" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D587" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E587" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DEDDB6-281F-498B-8F9B-0D26A67DA9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A412428-F3A7-4178-85BF-D91210035383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3075" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="400">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1236,6 +1236,9 @@
   </si>
   <si>
     <t>Mystic Remora</t>
+  </si>
+  <si>
+    <t>Ice Cauldron</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1389,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E3A1B72-86A8-4DFD-8879-567FFC9FD99E}" name="CollectionTable" displayName="CollectionTable" ref="A2:E126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E3A1B72-86A8-4DFD-8879-567FFC9FD99E}" name="CollectionTable" displayName="CollectionTable" ref="A2:E125">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{EE1C50BD-064E-4522-9D0B-4633B36785C8}" name="Artifact Blast"/>
     <tableColumn id="2" xr3:uid="{8CA90749-E92E-4160-B2D6-403EE9CBCFC2}" name="Antiquities"/>
@@ -1715,7 +1718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E615"/>
+  <dimension ref="A1:E616"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -3849,29 +3852,29 @@
         <v>374</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>374</v>
+    <row r="126" spans="1:5" ht="15">
+      <c r="A126" t="s">
+        <v>89</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C126" t="s">
+        <v>29</v>
+      </c>
+      <c r="D126" t="s">
+        <v>6</v>
+      </c>
+      <c r="E126" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15">
       <c r="A127" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="C127" t="s">
         <v>29</v>
@@ -3884,11 +3887,11 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15">
-      <c r="A128" t="s">
-        <v>91</v>
+      <c r="A128" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="C128" t="s">
         <v>29</v>
@@ -3902,33 +3905,33 @@
     </row>
     <row r="129" spans="1:5" ht="15">
       <c r="A129" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C129" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E129" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15">
-      <c r="A130" s="1" t="s">
-        <v>93</v>
+      <c r="A130" t="s">
+        <v>94</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C130" t="s">
         <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E130" t="s">
         <v>371</v>
@@ -3936,16 +3939,16 @@
     </row>
     <row r="131" spans="1:5" ht="15">
       <c r="A131" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C131" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D131" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E131" t="s">
         <v>371</v>
@@ -3953,16 +3956,16 @@
     </row>
     <row r="132" spans="1:5" ht="15">
       <c r="A132" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="C132" t="s">
         <v>29</v>
       </c>
       <c r="D132" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E132" t="s">
         <v>371</v>
@@ -3970,16 +3973,16 @@
     </row>
     <row r="133" spans="1:5" ht="15">
       <c r="A133" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C133" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E133" t="s">
         <v>371</v>
@@ -3987,16 +3990,16 @@
     </row>
     <row r="134" spans="1:5" ht="15">
       <c r="A134" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C134" t="s">
         <v>2</v>
       </c>
       <c r="D134" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E134" t="s">
         <v>371</v>
@@ -4004,33 +4007,33 @@
     </row>
     <row r="135" spans="1:5" ht="15">
       <c r="A135" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C135" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D135" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E135" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15">
-      <c r="A136" t="s">
-        <v>89</v>
+      <c r="A136" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C136" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D136" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E136" t="s">
         <v>371</v>
@@ -4038,13 +4041,13 @@
     </row>
     <row r="137" spans="1:5" ht="15">
       <c r="A137" s="1" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C137" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D137" t="s">
         <v>6</v>
@@ -4054,8 +4057,8 @@
       </c>
     </row>
     <row r="138" spans="1:5" ht="15">
-      <c r="A138" s="1" t="s">
-        <v>50</v>
+      <c r="A138" t="s">
+        <v>49</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>90</v>
@@ -4072,13 +4075,13 @@
     </row>
     <row r="139" spans="1:5" ht="15">
       <c r="A139" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C139" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D139" t="s">
         <v>6</v>
@@ -4105,17 +4108,17 @@
       </c>
     </row>
     <row r="141" spans="1:5" ht="15">
-      <c r="A141" t="s">
-        <v>100</v>
+      <c r="A141" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="C141" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D141" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E141" t="s">
         <v>371</v>
@@ -4132,7 +4135,7 @@
         <v>29</v>
       </c>
       <c r="D142" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E142" t="s">
         <v>371</v>
@@ -4140,16 +4143,16 @@
     </row>
     <row r="143" spans="1:5" ht="15">
       <c r="A143" s="1" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C143" t="s">
         <v>29</v>
       </c>
       <c r="D143" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E143" t="s">
         <v>371</v>
@@ -4157,16 +4160,16 @@
     </row>
     <row r="144" spans="1:5" ht="15">
       <c r="A144" s="1" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C144" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D144" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E144" t="s">
         <v>371</v>
@@ -4174,13 +4177,13 @@
     </row>
     <row r="145" spans="1:5" ht="15">
       <c r="A145" s="1" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C145" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D145" t="s">
         <v>6</v>
@@ -4191,10 +4194,10 @@
     </row>
     <row r="146" spans="1:5" ht="15">
       <c r="A146" s="1" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="C146" t="s">
         <v>29</v>
@@ -4259,13 +4262,13 @@
     </row>
     <row r="150" spans="1:5" ht="15">
       <c r="A150" s="1" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C150" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D150" t="s">
         <v>6</v>
@@ -4276,13 +4279,13 @@
     </row>
     <row r="151" spans="1:5" ht="15">
       <c r="A151" s="1" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C151" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D151" t="s">
         <v>6</v>
@@ -4293,7 +4296,7 @@
     </row>
     <row r="152" spans="1:5" ht="15">
       <c r="A152" s="1" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>92</v>
@@ -4310,16 +4313,16 @@
     </row>
     <row r="153" spans="1:5" ht="15">
       <c r="A153" s="1" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C153" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D153" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E153" t="s">
         <v>371</v>
@@ -4327,16 +4330,16 @@
     </row>
     <row r="154" spans="1:5" ht="15">
       <c r="A154" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C154" t="s">
         <v>2</v>
       </c>
       <c r="D154" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E154" t="s">
         <v>371</v>
@@ -4353,7 +4356,7 @@
         <v>2</v>
       </c>
       <c r="D155" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E155" t="s">
         <v>371</v>
@@ -4378,24 +4381,24 @@
     </row>
     <row r="157" spans="1:5" ht="15">
       <c r="A157" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C157" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D157" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E157" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="15">
       <c r="A158" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>105</v>
@@ -4404,7 +4407,7 @@
         <v>29</v>
       </c>
       <c r="D158" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E158" t="s">
         <v>368</v>
@@ -4412,7 +4415,7 @@
     </row>
     <row r="159" spans="1:5" ht="15">
       <c r="A159" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>105</v>
@@ -4429,7 +4432,7 @@
     </row>
     <row r="160" spans="1:5" ht="15">
       <c r="A160" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>105</v>
@@ -4438,7 +4441,7 @@
         <v>29</v>
       </c>
       <c r="D160" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E160" t="s">
         <v>368</v>
@@ -4446,7 +4449,7 @@
     </row>
     <row r="161" spans="1:5" ht="15">
       <c r="A161" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>105</v>
@@ -4463,7 +4466,7 @@
     </row>
     <row r="162" spans="1:5" ht="15">
       <c r="A162" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>105</v>
@@ -4480,33 +4483,33 @@
     </row>
     <row r="163" spans="1:5" ht="15">
       <c r="A163" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C163" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D163" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E163" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="15">
       <c r="A164" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>5</v>
+        <v>34</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C164" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D164" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E164" t="s">
         <v>375</v>
@@ -4514,13 +4517,13 @@
     </row>
     <row r="165" spans="1:5" ht="15">
       <c r="A165" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>28</v>
+        <v>112</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C165" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D165" t="s">
         <v>6</v>
@@ -4531,10 +4534,10 @@
     </row>
     <row r="166" spans="1:5" ht="15">
       <c r="A166" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>5</v>
+        <v>113</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C166" t="s">
         <v>2</v>
@@ -4548,10 +4551,10 @@
     </row>
     <row r="167" spans="1:5" ht="15">
       <c r="A167" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C167" t="s">
         <v>2</v>
@@ -4565,16 +4568,16 @@
     </row>
     <row r="168" spans="1:5" ht="15">
       <c r="A168" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>76</v>
+        <v>114</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C168" t="s">
         <v>2</v>
       </c>
       <c r="D168" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E168" t="s">
         <v>375</v>
@@ -4599,16 +4602,16 @@
     </row>
     <row r="170" spans="1:5" ht="15">
       <c r="A170" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="C170" t="s">
         <v>2</v>
       </c>
       <c r="D170" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E170" t="s">
         <v>375</v>
@@ -4616,16 +4619,16 @@
     </row>
     <row r="171" spans="1:5" ht="15">
       <c r="A171" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="C171" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D171" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E171" t="s">
         <v>375</v>
@@ -4633,16 +4636,16 @@
     </row>
     <row r="172" spans="1:5" ht="15">
       <c r="A172" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="C172" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D172" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="E172" t="s">
         <v>375</v>
@@ -4650,16 +4653,16 @@
     </row>
     <row r="173" spans="1:5" ht="15">
       <c r="A173" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="C173" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D173" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E173" t="s">
         <v>375</v>
@@ -4667,16 +4670,16 @@
     </row>
     <row r="174" spans="1:5" ht="15">
       <c r="A174" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C174" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D174" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E174" t="s">
         <v>375</v>
@@ -4684,16 +4687,16 @@
     </row>
     <row r="175" spans="1:5" ht="15">
       <c r="A175" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C175" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D175" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E175" t="s">
         <v>375</v>
@@ -4704,13 +4707,13 @@
         <v>117</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C176" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D176" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E176" t="s">
         <v>375</v>
@@ -4718,10 +4721,10 @@
     </row>
     <row r="177" spans="1:5" ht="15">
       <c r="A177" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C177" t="s">
         <v>2</v>
@@ -4735,7 +4738,7 @@
     </row>
     <row r="178" spans="1:5" ht="15">
       <c r="A178" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>84</v>
@@ -4744,7 +4747,7 @@
         <v>2</v>
       </c>
       <c r="D178" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E178" t="s">
         <v>375</v>
@@ -4752,16 +4755,16 @@
     </row>
     <row r="179" spans="1:5" ht="15">
       <c r="A179" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C179" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D179" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E179" t="s">
         <v>375</v>
@@ -4769,13 +4772,13 @@
     </row>
     <row r="180" spans="1:5" ht="15">
       <c r="A180" s="1" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C180" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D180" t="s">
         <v>6</v>
@@ -4786,7 +4789,7 @@
     </row>
     <row r="181" spans="1:5" ht="15">
       <c r="A181" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>76</v>
@@ -4820,13 +4823,13 @@
     </row>
     <row r="183" spans="1:5" ht="15">
       <c r="A183" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C183" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D183" t="s">
         <v>6</v>
@@ -4837,10 +4840,10 @@
     </row>
     <row r="184" spans="1:5" ht="15">
       <c r="A184" s="1" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="C184" t="s">
         <v>29</v>
@@ -4852,26 +4855,26 @@
         <v>375</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15">
-      <c r="A185" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C185" t="s">
-        <v>29</v>
-      </c>
-      <c r="D185" t="s">
+    <row r="185" spans="1:5">
+      <c r="A185" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D185" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E185" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
-      <c r="A186" s="2" t="s">
-        <v>74</v>
+    <row r="186" spans="1:5" ht="15">
+      <c r="A186" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>73</v>
@@ -4880,7 +4883,7 @@
         <v>29</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E186" t="s">
         <v>375</v>
@@ -4888,16 +4891,16 @@
     </row>
     <row r="187" spans="1:5" ht="15">
       <c r="A187" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>3</v>
+        <v>122</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C187" t="s">
+        <v>2</v>
+      </c>
+      <c r="D187" t="s">
+        <v>6</v>
       </c>
       <c r="E187" t="s">
         <v>375</v>
@@ -4905,10 +4908,10 @@
     </row>
     <row r="188" spans="1:5" ht="15">
       <c r="A188" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="C188" t="s">
         <v>2</v>
@@ -4922,16 +4925,16 @@
     </row>
     <row r="189" spans="1:5" ht="15">
       <c r="A189" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C189" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D189" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E189" t="s">
         <v>375</v>
@@ -4939,16 +4942,16 @@
     </row>
     <row r="190" spans="1:5" ht="15">
       <c r="A190" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C190" t="s">
         <v>29</v>
       </c>
       <c r="D190" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E190" t="s">
         <v>375</v>
@@ -4956,16 +4959,16 @@
     </row>
     <row r="191" spans="1:5" ht="15">
       <c r="A191" s="1" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C191" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D191" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E191" t="s">
         <v>375</v>
@@ -4973,16 +4976,16 @@
     </row>
     <row r="192" spans="1:5" ht="15">
       <c r="A192" s="1" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C192" t="s">
         <v>2</v>
       </c>
       <c r="D192" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E192" t="s">
         <v>375</v>
@@ -4990,7 +4993,7 @@
     </row>
     <row r="193" spans="1:5" ht="15">
       <c r="A193" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>76</v>
@@ -5007,13 +5010,13 @@
     </row>
     <row r="194" spans="1:5" ht="15">
       <c r="A194" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C194" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D194" t="s">
         <v>6</v>
@@ -5024,13 +5027,13 @@
     </row>
     <row r="195" spans="1:5" ht="15">
       <c r="A195" s="1" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="C195" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D195" t="s">
         <v>6</v>
@@ -5058,7 +5061,7 @@
     </row>
     <row r="197" spans="1:5" ht="15">
       <c r="A197" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>125</v>
@@ -5075,13 +5078,13 @@
     </row>
     <row r="198" spans="1:5" ht="15">
       <c r="A198" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C198" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D198" t="s">
         <v>6</v>
@@ -5092,13 +5095,13 @@
     </row>
     <row r="199" spans="1:5" ht="15">
       <c r="A199" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>58</v>
+        <v>117</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C199" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D199" t="s">
         <v>6</v>
@@ -5109,13 +5112,13 @@
     </row>
     <row r="200" spans="1:5" ht="15">
       <c r="A200" s="1" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C200" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D200" t="s">
         <v>6</v>
@@ -5126,13 +5129,13 @@
     </row>
     <row r="201" spans="1:5" ht="15">
       <c r="A201" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C201" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D201" t="s">
         <v>6</v>
@@ -5143,13 +5146,13 @@
     </row>
     <row r="202" spans="1:5" ht="15">
       <c r="A202" s="1" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C202" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D202" t="s">
         <v>6</v>
@@ -5160,24 +5163,24 @@
     </row>
     <row r="203" spans="1:5" ht="15">
       <c r="A203" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C203" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D203" t="s">
-        <v>6</v>
-      </c>
-      <c r="E203" t="s">
-        <v>375</v>
+        <v>42</v>
+      </c>
+      <c r="E203" s="10" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="15">
       <c r="A204" s="1" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>76</v>
@@ -5192,35 +5195,35 @@
         <v>366</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="15">
-      <c r="A205" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C205" t="s">
-        <v>2</v>
-      </c>
-      <c r="D205" t="s">
+    <row r="205" spans="1:5">
+      <c r="A205" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="15">
+      <c r="A206" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C206" t="s">
+        <v>2</v>
+      </c>
+      <c r="D206" t="s">
         <v>42</v>
-      </c>
-      <c r="E205" s="10" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
-      <c r="A206" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>373</v>
@@ -5228,16 +5231,16 @@
     </row>
     <row r="207" spans="1:5" ht="15">
       <c r="A207" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C207" t="s">
-        <v>2</v>
-      </c>
-      <c r="D207" t="s">
-        <v>42</v>
+        <v>131</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>373</v>
@@ -5245,16 +5248,16 @@
     </row>
     <row r="208" spans="1:5" ht="15">
       <c r="A208" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>73</v>
+        <v>132</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>373</v>
@@ -5262,16 +5265,16 @@
     </row>
     <row r="209" spans="1:5" ht="15">
       <c r="A209" s="1" t="s">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="C209" t="s">
+        <v>29</v>
+      </c>
+      <c r="D209" t="s">
+        <v>6</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>373</v>
@@ -5279,16 +5282,16 @@
     </row>
     <row r="210" spans="1:5" ht="15">
       <c r="A210" s="1" t="s">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C210" t="s">
-        <v>29</v>
-      </c>
-      <c r="D210" t="s">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>373</v>
@@ -5296,7 +5299,7 @@
     </row>
     <row r="211" spans="1:5" ht="15">
       <c r="A211" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>1</v>
@@ -5305,7 +5308,7 @@
         <v>2</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>373</v>
@@ -5313,50 +5316,50 @@
     </row>
     <row r="212" spans="1:5" ht="15">
       <c r="A212" s="1" t="s">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D212" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C212" t="s">
+        <v>29</v>
+      </c>
+      <c r="D212" t="s">
         <v>6</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="15">
-      <c r="A213" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C213" t="s">
-        <v>29</v>
-      </c>
-      <c r="D213" t="s">
+    <row r="213" spans="1:5">
+      <c r="A213" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D213" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
-      <c r="A214" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>16</v>
+    <row r="214" spans="1:5" ht="15">
+      <c r="A214" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>373</v>
@@ -5364,16 +5367,16 @@
     </row>
     <row r="215" spans="1:5" ht="15">
       <c r="A215" s="1" t="s">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="C215" t="s">
+        <v>29</v>
+      </c>
+      <c r="D215" t="s">
+        <v>6</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>373</v>
@@ -5381,16 +5384,16 @@
     </row>
     <row r="216" spans="1:5" ht="15">
       <c r="A216" s="1" t="s">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="C216" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D216" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>373</v>
@@ -5398,16 +5401,16 @@
     </row>
     <row r="217" spans="1:5" ht="15">
       <c r="A217" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C217" t="s">
-        <v>2</v>
-      </c>
-      <c r="D217" t="s">
-        <v>42</v>
+        <v>131</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>373</v>
@@ -5415,15 +5418,15 @@
     </row>
     <row r="218" spans="1:5" ht="15">
       <c r="A218" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D218" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C218" t="s">
+        <v>29</v>
+      </c>
+      <c r="D218" t="s">
         <v>6</v>
       </c>
       <c r="E218" s="2" t="s">
@@ -5432,10 +5435,10 @@
     </row>
     <row r="219" spans="1:5" ht="15">
       <c r="A219" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="C219" t="s">
         <v>29</v>
@@ -5449,16 +5452,16 @@
     </row>
     <row r="220" spans="1:5" ht="15">
       <c r="A220" s="1" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C220" t="s">
-        <v>29</v>
-      </c>
-      <c r="D220" t="s">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>373</v>
@@ -5466,16 +5469,16 @@
     </row>
     <row r="221" spans="1:5" ht="15">
       <c r="A221" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="C221" t="s">
+        <v>29</v>
+      </c>
+      <c r="D221" t="s">
+        <v>6</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>373</v>
@@ -5483,16 +5486,16 @@
     </row>
     <row r="222" spans="1:5" ht="15">
       <c r="A222" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C222" t="s">
-        <v>29</v>
-      </c>
-      <c r="D222" t="s">
-        <v>6</v>
+        <v>16</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>373</v>
@@ -5500,16 +5503,16 @@
     </row>
     <row r="223" spans="1:5" ht="15">
       <c r="A223" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>373</v>
@@ -5517,15 +5520,15 @@
     </row>
     <row r="224" spans="1:5" ht="15">
       <c r="A224" s="1" t="s">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D224" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D224" t="s">
         <v>6</v>
       </c>
       <c r="E224" s="2" t="s">
@@ -5534,15 +5537,15 @@
     </row>
     <row r="225" spans="1:5" ht="15">
       <c r="A225" s="1" t="s">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C225" t="s">
-        <v>29</v>
-      </c>
-      <c r="D225" t="s">
+        <v>1</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D225" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E225" s="2" t="s">
@@ -5551,15 +5554,15 @@
     </row>
     <row r="226" spans="1:5" ht="15">
       <c r="A226" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D226" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C226" t="s">
+        <v>29</v>
+      </c>
+      <c r="D226" t="s">
         <v>6</v>
       </c>
       <c r="E226" s="2" t="s">
@@ -5568,13 +5571,13 @@
     </row>
     <row r="227" spans="1:5" ht="15">
       <c r="A227" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="C227" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D227" t="s">
         <v>6</v>
@@ -5585,15 +5588,15 @@
     </row>
     <row r="228" spans="1:5" ht="15">
       <c r="A228" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C228" t="s">
-        <v>2</v>
-      </c>
-      <c r="D228" t="s">
+        <v>1</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D228" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E228" s="2" t="s">
@@ -5602,15 +5605,15 @@
     </row>
     <row r="229" spans="1:5" ht="15">
       <c r="A229" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D229" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C229" t="s">
+        <v>29</v>
+      </c>
+      <c r="D229" t="s">
         <v>6</v>
       </c>
       <c r="E229" s="2" t="s">
@@ -5619,15 +5622,15 @@
     </row>
     <row r="230" spans="1:5" ht="15">
       <c r="A230" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C230" t="s">
-        <v>29</v>
-      </c>
-      <c r="D230" t="s">
+        <v>16</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D230" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E230" s="2" t="s">
@@ -5662,7 +5665,7 @@
         <v>2</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>373</v>
@@ -5687,7 +5690,7 @@
     </row>
     <row r="234" spans="1:5" ht="15">
       <c r="A234" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>16</v>
@@ -5713,7 +5716,7 @@
         <v>2</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>373</v>
@@ -5730,7 +5733,7 @@
         <v>2</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>373</v>
@@ -5747,7 +5750,7 @@
         <v>2</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>373</v>
@@ -5755,10 +5758,10 @@
     </row>
     <row r="238" spans="1:5" ht="15">
       <c r="A238" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>2</v>
@@ -5767,7 +5770,7 @@
         <v>6</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="15">
@@ -5789,16 +5792,16 @@
     </row>
     <row r="240" spans="1:5" ht="15">
       <c r="A240" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>6</v>
+        <v>90</v>
+      </c>
+      <c r="C240" t="s">
+        <v>29</v>
+      </c>
+      <c r="D240" t="s">
+        <v>42</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>372</v>
@@ -5806,16 +5809,16 @@
     </row>
     <row r="241" spans="1:5" ht="15">
       <c r="A241" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>90</v>
+        <v>141</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C241" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D241" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>372</v>
@@ -5840,16 +5843,16 @@
     </row>
     <row r="243" spans="1:5" ht="15">
       <c r="A243" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>5</v>
+        <v>43</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C243" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D243" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>372</v>
@@ -5889,31 +5892,31 @@
         <v>372</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="15">
-      <c r="A246" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C246" t="s">
-        <v>29</v>
-      </c>
-      <c r="D246" t="s">
-        <v>3</v>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
-      <c r="A247" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C247" s="2" t="s">
+    <row r="247" spans="1:5" ht="15">
+      <c r="A247" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C247" t="s">
         <v>29</v>
       </c>
       <c r="D247" s="2" t="s">
@@ -5925,7 +5928,7 @@
     </row>
     <row r="248" spans="1:5" ht="15">
       <c r="A248" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>90</v>
@@ -5959,15 +5962,15 @@
     </row>
     <row r="250" spans="1:5" ht="15">
       <c r="A250" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="C250" t="s">
-        <v>29</v>
-      </c>
-      <c r="D250" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D250" t="s">
         <v>6</v>
       </c>
       <c r="E250" s="2" t="s">
@@ -5976,7 +5979,7 @@
     </row>
     <row r="251" spans="1:5" ht="15">
       <c r="A251" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>125</v>
@@ -6010,16 +6013,16 @@
     </row>
     <row r="253" spans="1:5" ht="15">
       <c r="A253" s="1" t="s">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C253" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D253" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>372</v>
@@ -6027,16 +6030,16 @@
     </row>
     <row r="254" spans="1:5" ht="15">
       <c r="A254" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>90</v>
+        <v>141</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C254" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D254" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>372</v>
@@ -6044,13 +6047,13 @@
     </row>
     <row r="255" spans="1:5" ht="15">
       <c r="A255" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>5</v>
+        <v>140</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C255" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D255" t="s">
         <v>6</v>
@@ -6061,10 +6064,10 @@
     </row>
     <row r="256" spans="1:5" ht="15">
       <c r="A256" s="1" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="C256" t="s">
         <v>29</v>
@@ -6078,10 +6081,10 @@
     </row>
     <row r="257" spans="1:5" ht="15">
       <c r="A257" s="1" t="s">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="C257" t="s">
         <v>29</v>
@@ -6095,15 +6098,15 @@
     </row>
     <row r="258" spans="1:5" ht="15">
       <c r="A258" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C258" t="s">
-        <v>29</v>
-      </c>
-      <c r="D258" t="s">
+        <v>1</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D258" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E258" s="2" t="s">
@@ -6112,10 +6115,10 @@
     </row>
     <row r="259" spans="1:5" ht="15">
       <c r="A259" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>2</v>
@@ -6129,16 +6132,16 @@
     </row>
     <row r="260" spans="1:5" ht="15">
       <c r="A260" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>372</v>
@@ -6146,16 +6149,16 @@
     </row>
     <row r="261" spans="1:5" ht="15">
       <c r="A261" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D261" s="2" t="s">
-        <v>3</v>
+        <v>141</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C261" t="s">
+        <v>2</v>
+      </c>
+      <c r="D261" t="s">
+        <v>6</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>372</v>
@@ -6163,10 +6166,10 @@
     </row>
     <row r="262" spans="1:5" ht="15">
       <c r="A262" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>5</v>
+        <v>144</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C262" t="s">
         <v>2</v>
@@ -6180,10 +6183,10 @@
     </row>
     <row r="263" spans="1:5" ht="15">
       <c r="A263" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>125</v>
+        <v>148</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C263" t="s">
         <v>2</v>
@@ -6214,16 +6217,16 @@
     </row>
     <row r="265" spans="1:5" ht="15">
       <c r="A265" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B265" s="3" t="s">
-        <v>5</v>
+        <v>149</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C265" t="s">
         <v>2</v>
       </c>
-      <c r="D265" t="s">
-        <v>6</v>
+      <c r="D265" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>372</v>
@@ -6231,7 +6234,7 @@
     </row>
     <row r="266" spans="1:5" ht="15">
       <c r="A266" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>76</v>
@@ -6248,16 +6251,16 @@
     </row>
     <row r="267" spans="1:5" ht="15">
       <c r="A267" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>76</v>
+        <v>148</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C267" t="s">
         <v>2</v>
       </c>
-      <c r="D267" s="2" t="s">
-        <v>3</v>
+      <c r="D267" t="s">
+        <v>6</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>372</v>
@@ -6265,13 +6268,13 @@
     </row>
     <row r="268" spans="1:5" ht="15">
       <c r="A268" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>5</v>
+        <v>140</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C268" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D268" t="s">
         <v>6</v>
@@ -6282,10 +6285,10 @@
     </row>
     <row r="269" spans="1:5" ht="15">
       <c r="A269" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>90</v>
+        <v>151</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C269" t="s">
         <v>29</v>
@@ -6299,15 +6302,15 @@
     </row>
     <row r="270" spans="1:5" ht="15">
       <c r="A270" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C270" t="s">
-        <v>29</v>
-      </c>
-      <c r="D270" t="s">
+        <v>147</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D270" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E270" s="2" t="s">
@@ -6316,16 +6319,16 @@
     </row>
     <row r="271" spans="1:5" ht="15">
       <c r="A271" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>2</v>
+        <v>90</v>
+      </c>
+      <c r="C271" t="s">
+        <v>29</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>372</v>
@@ -6333,7 +6336,7 @@
     </row>
     <row r="272" spans="1:5" ht="15">
       <c r="A272" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>90</v>
@@ -6342,7 +6345,7 @@
         <v>29</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>372</v>
@@ -6376,7 +6379,7 @@
         <v>29</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>372</v>
@@ -6384,15 +6387,15 @@
     </row>
     <row r="275" spans="1:5" ht="15">
       <c r="A275" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>90</v>
+        <v>148</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C275" t="s">
-        <v>29</v>
-      </c>
-      <c r="D275" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D275" t="s">
         <v>6</v>
       </c>
       <c r="E275" s="2" t="s">
@@ -6401,13 +6404,13 @@
     </row>
     <row r="276" spans="1:5" ht="15">
       <c r="A276" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B276" s="3" t="s">
-        <v>5</v>
+        <v>140</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C276" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D276" t="s">
         <v>6</v>
@@ -6418,7 +6421,7 @@
     </row>
     <row r="277" spans="1:5" ht="15">
       <c r="A277" s="1" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>90</v>
@@ -6435,7 +6438,7 @@
     </row>
     <row r="278" spans="1:5" ht="15">
       <c r="A278" s="1" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>90</v>
@@ -6443,33 +6446,33 @@
       <c r="C278" t="s">
         <v>29</v>
       </c>
-      <c r="D278" t="s">
+      <c r="D278" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="15">
-      <c r="A279" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C279" t="s">
+    <row r="279" spans="1:5">
+      <c r="A279" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C279" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E279" s="2" t="s">
-        <v>372</v>
+      <c r="E279" s="10" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>41</v>
@@ -6484,17 +6487,17 @@
         <v>366</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
-      <c r="A281" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D281" s="2" t="s">
+    <row r="281" spans="1:5" ht="15">
+      <c r="A281" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C281" t="s">
+        <v>2</v>
+      </c>
+      <c r="D281" t="s">
         <v>6</v>
       </c>
       <c r="E281" s="10" t="s">
@@ -6503,16 +6506,16 @@
     </row>
     <row r="282" spans="1:5" ht="15">
       <c r="A282" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C282" t="s">
-        <v>2</v>
-      </c>
-      <c r="D282" t="s">
-        <v>6</v>
+        <v>158</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E282" s="10" t="s">
         <v>366</v>
@@ -6520,7 +6523,7 @@
     </row>
     <row r="283" spans="1:5" ht="15">
       <c r="A283" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>1</v>
@@ -6529,7 +6532,7 @@
         <v>2</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E283" s="10" t="s">
         <v>366</v>
@@ -6537,7 +6540,7 @@
     </row>
     <row r="284" spans="1:5" ht="15">
       <c r="A284" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>1</v>
@@ -6546,7 +6549,7 @@
         <v>2</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E284" s="10" t="s">
         <v>366</v>
@@ -6554,7 +6557,7 @@
     </row>
     <row r="285" spans="1:5" ht="15">
       <c r="A285" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>1</v>
@@ -6563,7 +6566,7 @@
         <v>2</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E285" s="10" t="s">
         <v>366</v>
@@ -6571,7 +6574,7 @@
     </row>
     <row r="286" spans="1:5" ht="15">
       <c r="A286" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>1</v>
@@ -6580,7 +6583,7 @@
         <v>2</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E286" s="10" t="s">
         <v>366</v>
@@ -6588,7 +6591,7 @@
     </row>
     <row r="287" spans="1:5" ht="15">
       <c r="A287" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>1</v>
@@ -6622,7 +6625,7 @@
     </row>
     <row r="289" spans="1:5" ht="15">
       <c r="A289" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>1</v>
@@ -6639,7 +6642,7 @@
     </row>
     <row r="290" spans="1:5" ht="15">
       <c r="A290" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>1</v>
@@ -6648,7 +6651,7 @@
         <v>2</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E290" s="10" t="s">
         <v>366</v>
@@ -6656,7 +6659,7 @@
     </row>
     <row r="291" spans="1:5" ht="15">
       <c r="A291" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>1</v>
@@ -6673,7 +6676,7 @@
     </row>
     <row r="292" spans="1:5" ht="15">
       <c r="A292" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>1</v>
@@ -6682,7 +6685,7 @@
         <v>2</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E292" s="10" t="s">
         <v>366</v>
@@ -6690,7 +6693,7 @@
     </row>
     <row r="293" spans="1:5" ht="15">
       <c r="A293" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>1</v>
@@ -6707,7 +6710,7 @@
     </row>
     <row r="294" spans="1:5" ht="15">
       <c r="A294" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>1</v>
@@ -6724,7 +6727,7 @@
     </row>
     <row r="295" spans="1:5" ht="15">
       <c r="A295" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>1</v>
@@ -6733,7 +6736,7 @@
         <v>2</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E295" s="10" t="s">
         <v>366</v>
@@ -6741,7 +6744,7 @@
     </row>
     <row r="296" spans="1:5" ht="15">
       <c r="A296" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>1</v>
@@ -6750,7 +6753,7 @@
         <v>2</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E296" s="10" t="s">
         <v>366</v>
@@ -6758,16 +6761,16 @@
     </row>
     <row r="297" spans="1:5" ht="15">
       <c r="A297" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D297" s="2" t="s">
-        <v>3</v>
+        <v>141</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C297" t="s">
+        <v>2</v>
+      </c>
+      <c r="D297" t="s">
+        <v>6</v>
       </c>
       <c r="E297" s="10" t="s">
         <v>366</v>
@@ -6843,7 +6846,7 @@
     </row>
     <row r="302" spans="1:5" ht="15">
       <c r="A302" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>5</v>
@@ -6852,7 +6855,7 @@
         <v>2</v>
       </c>
       <c r="D302" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E302" s="10" t="s">
         <v>366</v>
@@ -6869,7 +6872,7 @@
         <v>2</v>
       </c>
       <c r="D303" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E303" s="10" t="s">
         <v>366</v>
@@ -6903,7 +6906,7 @@
         <v>2</v>
       </c>
       <c r="D305" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E305" s="10" t="s">
         <v>366</v>
@@ -6920,7 +6923,7 @@
         <v>2</v>
       </c>
       <c r="D306" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E306" s="10" t="s">
         <v>366</v>
@@ -6945,10 +6948,10 @@
     </row>
     <row r="308" spans="1:5" ht="15">
       <c r="A308" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B308" s="3" t="s">
-        <v>5</v>
+        <v>172</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C308" t="s">
         <v>2</v>
@@ -6987,8 +6990,8 @@
       <c r="C310" t="s">
         <v>2</v>
       </c>
-      <c r="D310" t="s">
-        <v>6</v>
+      <c r="D310" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E310" s="10" t="s">
         <v>366</v>
@@ -7013,16 +7016,16 @@
     </row>
     <row r="312" spans="1:5" ht="15">
       <c r="A312" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="C312" t="s">
         <v>2</v>
       </c>
-      <c r="D312" s="2" t="s">
-        <v>3</v>
+      <c r="D312" t="s">
+        <v>6</v>
       </c>
       <c r="E312" s="10" t="s">
         <v>366</v>
@@ -7047,7 +7050,7 @@
     </row>
     <row r="314" spans="1:5" ht="15">
       <c r="A314" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>5</v>
@@ -7081,15 +7084,15 @@
     </row>
     <row r="316" spans="1:5" ht="15">
       <c r="A316" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C316" t="s">
-        <v>2</v>
-      </c>
-      <c r="D316" t="s">
+        <v>175</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D316" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E316" s="10" t="s">
@@ -7098,7 +7101,7 @@
     </row>
     <row r="317" spans="1:5" ht="15">
       <c r="A317" s="1" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>41</v>
@@ -7115,13 +7118,13 @@
     </row>
     <row r="318" spans="1:5" ht="15">
       <c r="A318" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>41</v>
+        <v>176</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>6</v>
@@ -7132,7 +7135,7 @@
     </row>
     <row r="319" spans="1:5" ht="15">
       <c r="A319" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>1</v>
@@ -7141,7 +7144,7 @@
         <v>2</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E319" s="10" t="s">
         <v>366</v>
@@ -7149,7 +7152,7 @@
     </row>
     <row r="320" spans="1:5" ht="15">
       <c r="A320" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>1</v>
@@ -7158,7 +7161,7 @@
         <v>2</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E320" s="10" t="s">
         <v>366</v>
@@ -7166,7 +7169,7 @@
     </row>
     <row r="321" spans="1:5" ht="15">
       <c r="A321" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>1</v>
@@ -7183,7 +7186,7 @@
     </row>
     <row r="322" spans="1:5" ht="15">
       <c r="A322" s="1" t="s">
-        <v>179</v>
+        <v>36</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>1</v>
@@ -7200,7 +7203,7 @@
     </row>
     <row r="323" spans="1:5" ht="15">
       <c r="A323" s="1" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>1</v>
@@ -7217,7 +7220,7 @@
     </row>
     <row r="324" spans="1:5" ht="15">
       <c r="A324" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>1</v>
@@ -7226,7 +7229,7 @@
         <v>2</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E324" s="10" t="s">
         <v>366</v>
@@ -7234,7 +7237,7 @@
     </row>
     <row r="325" spans="1:5" ht="15">
       <c r="A325" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>1</v>
@@ -7251,7 +7254,7 @@
     </row>
     <row r="326" spans="1:5" ht="15">
       <c r="A326" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>1</v>
@@ -7260,7 +7263,7 @@
         <v>2</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E326" s="10" t="s">
         <v>366</v>
@@ -7268,7 +7271,7 @@
     </row>
     <row r="327" spans="1:5" ht="15">
       <c r="A327" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>1</v>
@@ -7285,24 +7288,24 @@
     </row>
     <row r="328" spans="1:5" ht="15">
       <c r="A328" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E328" s="10" t="s">
-        <v>366</v>
+      <c r="E328" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="329" spans="1:5" ht="15">
       <c r="A329" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>58</v>
@@ -7319,7 +7322,7 @@
     </row>
     <row r="330" spans="1:5" ht="15">
       <c r="A330" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>58</v>
@@ -7328,7 +7331,7 @@
         <v>29</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>367</v>
@@ -7336,7 +7339,7 @@
     </row>
     <row r="331" spans="1:5" ht="15">
       <c r="A331" s="1" t="s">
-        <v>187</v>
+        <v>51</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>58</v>
@@ -7345,7 +7348,7 @@
         <v>29</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>367</v>
@@ -7353,16 +7356,16 @@
     </row>
     <row r="332" spans="1:5" ht="15">
       <c r="A332" s="1" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>367</v>
@@ -7370,7 +7373,7 @@
     </row>
     <row r="333" spans="1:5" ht="15">
       <c r="A333" s="1" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>58</v>
@@ -7386,25 +7389,25 @@
       </c>
     </row>
     <row r="334" spans="1:5" ht="15">
-      <c r="A334" s="1" t="s">
-        <v>188</v>
+      <c r="A334" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C334" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D334" s="2" t="s">
-        <v>42</v>
+      <c r="C334" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="335" spans="1:5" ht="15">
-      <c r="A335" s="5" t="s">
-        <v>45</v>
+      <c r="A335" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>58</v>
@@ -7421,16 +7424,16 @@
     </row>
     <row r="336" spans="1:5" ht="15">
       <c r="A336" s="1" t="s">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C336" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D336" s="3" t="s">
-        <v>6</v>
+      <c r="C336" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>367</v>
@@ -7438,24 +7441,24 @@
     </row>
     <row r="337" spans="1:5" ht="15">
       <c r="A337" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C337" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D337" s="2" t="s">
-        <v>3</v>
+      <c r="C337" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D337" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="338" spans="1:5" ht="15">
-      <c r="A338" s="1" t="s">
-        <v>190</v>
+      <c r="A338" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>58</v>
@@ -7471,8 +7474,8 @@
       </c>
     </row>
     <row r="339" spans="1:5" ht="15">
-      <c r="A339" s="5" t="s">
-        <v>50</v>
+      <c r="A339" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>58</v>
@@ -7481,15 +7484,15 @@
         <v>29</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="340" spans="1:5" ht="15">
-      <c r="A340" s="1" t="s">
-        <v>191</v>
+      <c r="A340" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>58</v>
@@ -7498,15 +7501,15 @@
         <v>29</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="341" spans="1:5" ht="15">
-      <c r="A341" s="5" t="s">
-        <v>40</v>
+      <c r="A341" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>58</v>
@@ -7515,49 +7518,49 @@
         <v>29</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="342" spans="1:5" ht="15">
-      <c r="A342" s="1" t="s">
-        <v>193</v>
+      <c r="A342" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C342" s="3" t="s">
-        <v>29</v>
+      <c r="C342" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="343" spans="1:5" ht="15">
-      <c r="A343" s="2" t="s">
-        <v>194</v>
+      <c r="A343" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C343" s="2" t="s">
-        <v>2</v>
+      <c r="C343" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="344" spans="1:5" ht="15">
-      <c r="A344" s="1" t="s">
-        <v>72</v>
+      <c r="A344" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>58</v>
@@ -7573,14 +7576,14 @@
       </c>
     </row>
     <row r="345" spans="1:5" ht="15">
-      <c r="A345" s="2" t="s">
-        <v>74</v>
+      <c r="A345" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C345" s="3" t="s">
-        <v>29</v>
+        <v>101</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="D345" s="3" t="s">
         <v>6</v>
@@ -7590,8 +7593,8 @@
       </c>
     </row>
     <row r="346" spans="1:5" ht="15">
-      <c r="A346" s="1" t="s">
-        <v>195</v>
+      <c r="A346" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>101</v>
@@ -7599,16 +7602,16 @@
       <c r="C346" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D346" s="3" t="s">
-        <v>6</v>
+      <c r="D346" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="347" spans="1:5" ht="15">
-      <c r="A347" s="2" t="s">
-        <v>100</v>
+      <c r="A347" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>101</v>
@@ -7616,16 +7619,16 @@
       <c r="C347" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D347" s="2" t="s">
-        <v>3</v>
+      <c r="D347" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="348" spans="1:5" ht="15">
-      <c r="A348" s="1" t="s">
-        <v>196</v>
+      <c r="A348" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>101</v>
@@ -7641,8 +7644,8 @@
       </c>
     </row>
     <row r="349" spans="1:5" ht="15">
-      <c r="A349" s="2" t="s">
-        <v>197</v>
+      <c r="A349" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="B349" s="1" t="s">
         <v>101</v>
@@ -7650,16 +7653,16 @@
       <c r="C349" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D349" s="3" t="s">
-        <v>6</v>
+      <c r="D349" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="350" spans="1:5" ht="15">
-      <c r="A350" s="1" t="s">
-        <v>198</v>
+      <c r="A350" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>101</v>
@@ -7675,8 +7678,8 @@
       </c>
     </row>
     <row r="351" spans="1:5" ht="15">
-      <c r="A351" s="2" t="s">
-        <v>199</v>
+      <c r="A351" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>101</v>
@@ -7684,33 +7687,33 @@
       <c r="C351" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D351" s="2" t="s">
-        <v>3</v>
+      <c r="D351" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="352" spans="1:5" ht="15">
-      <c r="A352" s="1" t="s">
-        <v>200</v>
+      <c r="A352" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C352" s="2" t="s">
-        <v>2</v>
+        <v>121</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="353" spans="1:5" ht="15">
-      <c r="A353" s="2" t="s">
-        <v>102</v>
+      <c r="A353" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>121</v>
@@ -7719,15 +7722,15 @@
         <v>29</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="354" spans="1:5" ht="15">
-      <c r="A354" s="1" t="s">
-        <v>201</v>
+      <c r="A354" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>121</v>
@@ -7736,15 +7739,15 @@
         <v>29</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="355" spans="1:5" ht="15">
-      <c r="A355" s="2" t="s">
-        <v>202</v>
+      <c r="A355" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>121</v>
@@ -7760,16 +7763,16 @@
       </c>
     </row>
     <row r="356" spans="1:5" ht="15">
-      <c r="A356" s="1" t="s">
-        <v>72</v>
+      <c r="A356" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C356" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D356" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D356" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E356" s="2" t="s">
@@ -7787,7 +7790,7 @@
         <v>2</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>367</v>
@@ -7811,8 +7814,8 @@
       </c>
     </row>
     <row r="359" spans="1:5" ht="15">
-      <c r="A359" s="2" t="s">
-        <v>199</v>
+      <c r="A359" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>101</v>
@@ -7829,16 +7832,16 @@
     </row>
     <row r="360" spans="1:5" ht="15">
       <c r="A360" s="1" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C360" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D360" s="2" t="s">
-        <v>6</v>
+        <v>121</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>367</v>
@@ -7846,30 +7849,30 @@
     </row>
     <row r="361" spans="1:5" ht="15">
       <c r="A361" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C361" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D361" s="3" t="s">
-        <v>192</v>
+        <v>58</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="362" spans="1:5" ht="15">
-      <c r="A362" s="1" t="s">
-        <v>186</v>
+      <c r="A362" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>3</v>
@@ -7879,17 +7882,17 @@
       </c>
     </row>
     <row r="363" spans="1:5" ht="15">
-      <c r="A363" s="2" t="s">
-        <v>100</v>
+      <c r="A363" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>367</v>
@@ -7897,16 +7900,16 @@
     </row>
     <row r="364" spans="1:5" ht="15">
       <c r="A364" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>367</v>
@@ -7920,10 +7923,10 @@
         <v>58</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>367</v>
@@ -7937,10 +7940,10 @@
         <v>58</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>367</v>
@@ -7948,24 +7951,24 @@
     </row>
     <row r="367" spans="1:5" ht="15">
       <c r="A367" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C367" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D367" s="2" t="s">
-        <v>6</v>
+      <c r="C367" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D367" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="368" spans="1:5" ht="15">
-      <c r="A368" s="1" t="s">
-        <v>193</v>
+      <c r="A368" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>58</v>
@@ -7974,49 +7977,49 @@
         <v>29</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="369" spans="1:5" ht="15">
-      <c r="A369" s="2" t="s">
-        <v>74</v>
+      <c r="A369" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C369" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D369" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E369" s="2" t="s">
-        <v>367</v>
+        <v>105</v>
+      </c>
+      <c r="C369" t="s">
+        <v>2</v>
+      </c>
+      <c r="D369" t="s">
+        <v>39</v>
+      </c>
+      <c r="E369" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="370" spans="1:5" ht="15">
       <c r="A370" s="1" t="s">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C370" t="s">
-        <v>2</v>
-      </c>
-      <c r="D370" t="s">
-        <v>39</v>
-      </c>
-      <c r="E370" t="s">
-        <v>368</v>
+        <v>204</v>
+      </c>
+      <c r="C370" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D370" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="371" spans="1:5" ht="15">
       <c r="A371" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>204</v>
@@ -8033,7 +8036,7 @@
     </row>
     <row r="372" spans="1:5" ht="15">
       <c r="A372" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>204</v>
@@ -8050,7 +8053,7 @@
     </row>
     <row r="373" spans="1:5" ht="15">
       <c r="A373" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>204</v>
@@ -8059,7 +8062,7 @@
         <v>29</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>369</v>
@@ -8067,7 +8070,7 @@
     </row>
     <row r="374" spans="1:5" ht="15">
       <c r="A374" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>204</v>
@@ -8076,7 +8079,7 @@
         <v>29</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>369</v>
@@ -8084,7 +8087,7 @@
     </row>
     <row r="375" spans="1:5" ht="15">
       <c r="A375" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>204</v>
@@ -8101,7 +8104,7 @@
     </row>
     <row r="376" spans="1:5" ht="15">
       <c r="A376" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>204</v>
@@ -8118,7 +8121,7 @@
     </row>
     <row r="377" spans="1:5" ht="15">
       <c r="A377" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>204</v>
@@ -8135,7 +8138,7 @@
     </row>
     <row r="378" spans="1:5" ht="15">
       <c r="A378" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B378" s="1" t="s">
         <v>204</v>
@@ -8152,7 +8155,7 @@
     </row>
     <row r="379" spans="1:5" ht="15">
       <c r="A379" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>204</v>
@@ -8169,7 +8172,7 @@
     </row>
     <row r="380" spans="1:5" ht="15">
       <c r="A380" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>204</v>
@@ -8178,7 +8181,7 @@
         <v>29</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>369</v>
@@ -8186,7 +8189,7 @@
     </row>
     <row r="381" spans="1:5" ht="15">
       <c r="A381" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>204</v>
@@ -8195,7 +8198,7 @@
         <v>29</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>369</v>
@@ -8203,7 +8206,7 @@
     </row>
     <row r="382" spans="1:5" ht="15">
       <c r="A382" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>204</v>
@@ -8212,7 +8215,7 @@
         <v>29</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>369</v>
@@ -8220,7 +8223,7 @@
     </row>
     <row r="383" spans="1:5" ht="15">
       <c r="A383" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>204</v>
@@ -8229,7 +8232,7 @@
         <v>29</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>369</v>
@@ -8237,10 +8240,10 @@
     </row>
     <row r="384" spans="1:5" ht="15">
       <c r="A384" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="C384" s="3" t="s">
         <v>29</v>
@@ -8254,7 +8257,7 @@
     </row>
     <row r="385" spans="1:5" ht="15">
       <c r="A385" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>219</v>
@@ -8271,7 +8274,7 @@
     </row>
     <row r="386" spans="1:5" ht="15">
       <c r="A386" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>219</v>
@@ -8288,7 +8291,7 @@
     </row>
     <row r="387" spans="1:5" ht="15">
       <c r="A387" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>219</v>
@@ -8305,7 +8308,7 @@
     </row>
     <row r="388" spans="1:5" ht="15">
       <c r="A388" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>219</v>
@@ -8314,7 +8317,7 @@
         <v>29</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E388" s="2" t="s">
         <v>369</v>
@@ -8322,7 +8325,7 @@
     </row>
     <row r="389" spans="1:5" ht="15">
       <c r="A389" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>219</v>
@@ -8331,7 +8334,7 @@
         <v>29</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>369</v>
@@ -8339,7 +8342,7 @@
     </row>
     <row r="390" spans="1:5" ht="15">
       <c r="A390" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>219</v>
@@ -8348,7 +8351,7 @@
         <v>29</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>369</v>
@@ -8356,7 +8359,7 @@
     </row>
     <row r="391" spans="1:5" ht="15">
       <c r="A391" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>219</v>
@@ -8365,7 +8368,7 @@
         <v>29</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>369</v>
@@ -8373,7 +8376,7 @@
     </row>
     <row r="392" spans="1:5" ht="15">
       <c r="A392" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>219</v>
@@ -8390,7 +8393,7 @@
     </row>
     <row r="393" spans="1:5" ht="15">
       <c r="A393" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>219</v>
@@ -8407,16 +8410,16 @@
     </row>
     <row r="394" spans="1:5" ht="15">
       <c r="A394" s="1" t="s">
-        <v>228</v>
+        <v>186</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C394" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D394" s="3" t="s">
-        <v>3</v>
+        <v>229</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>369</v>
@@ -8424,16 +8427,16 @@
     </row>
     <row r="395" spans="1:5" ht="15">
       <c r="A395" s="1" t="s">
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>229</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>2</v>
+        <v>231</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>369</v>
@@ -8441,7 +8444,7 @@
     </row>
     <row r="396" spans="1:5" ht="15">
       <c r="A396" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>229</v>
@@ -8458,7 +8461,7 @@
     </row>
     <row r="397" spans="1:5" ht="15">
       <c r="A397" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>229</v>
@@ -8475,13 +8478,13 @@
     </row>
     <row r="398" spans="1:5" ht="15">
       <c r="A398" s="1" t="s">
-        <v>233</v>
+        <v>33</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C398" s="2" t="s">
-        <v>231</v>
+      <c r="C398" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>3</v>
@@ -8492,7 +8495,7 @@
     </row>
     <row r="399" spans="1:5" ht="15">
       <c r="A399" s="1" t="s">
-        <v>33</v>
+        <v>234</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>229</v>
@@ -8501,7 +8504,7 @@
         <v>29</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E399" s="2" t="s">
         <v>369</v>
@@ -8509,16 +8512,16 @@
     </row>
     <row r="400" spans="1:5" ht="15">
       <c r="A400" s="1" t="s">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C400" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D400" s="2" t="s">
-        <v>6</v>
+      <c r="C400" t="s">
+        <v>29</v>
+      </c>
+      <c r="D400" t="s">
+        <v>3</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>369</v>
@@ -8526,7 +8529,7 @@
     </row>
     <row r="401" spans="1:5" ht="15">
       <c r="A401" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>229</v>
@@ -8535,7 +8538,7 @@
         <v>29</v>
       </c>
       <c r="D401" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>369</v>
@@ -8543,7 +8546,7 @@
     </row>
     <row r="402" spans="1:5" ht="15">
       <c r="A402" s="1" t="s">
-        <v>89</v>
+        <v>235</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>229</v>
@@ -8552,7 +8555,7 @@
         <v>29</v>
       </c>
       <c r="D402" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>369</v>
@@ -8560,7 +8563,7 @@
     </row>
     <row r="403" spans="1:5" ht="15">
       <c r="A403" s="1" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>229</v>
@@ -8577,7 +8580,7 @@
     </row>
     <row r="404" spans="1:5" ht="15">
       <c r="A404" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>229</v>
@@ -8586,7 +8589,7 @@
         <v>29</v>
       </c>
       <c r="D404" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>369</v>
@@ -8594,16 +8597,16 @@
     </row>
     <row r="405" spans="1:5" ht="15">
       <c r="A405" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C405" t="s">
         <v>29</v>
       </c>
       <c r="D405" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>369</v>
@@ -8611,7 +8614,7 @@
     </row>
     <row r="406" spans="1:5" ht="15">
       <c r="A406" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>237</v>
@@ -8628,7 +8631,7 @@
     </row>
     <row r="407" spans="1:5" ht="15">
       <c r="A407" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>237</v>
@@ -8645,7 +8648,7 @@
     </row>
     <row r="408" spans="1:5" ht="15">
       <c r="A408" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>237</v>
@@ -8662,7 +8665,7 @@
     </row>
     <row r="409" spans="1:5" ht="15">
       <c r="A409" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>237</v>
@@ -8679,7 +8682,7 @@
     </row>
     <row r="410" spans="1:5" ht="15">
       <c r="A410" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>237</v>
@@ -8696,7 +8699,7 @@
     </row>
     <row r="411" spans="1:5" ht="15">
       <c r="A411" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>237</v>
@@ -8713,7 +8716,7 @@
     </row>
     <row r="412" spans="1:5" ht="15">
       <c r="A412" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>237</v>
@@ -8730,7 +8733,7 @@
     </row>
     <row r="413" spans="1:5" ht="15">
       <c r="A413" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>237</v>
@@ -8747,16 +8750,16 @@
     </row>
     <row r="414" spans="1:5" ht="15">
       <c r="A414" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C414" t="s">
         <v>29</v>
       </c>
       <c r="D414" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>369</v>
@@ -8764,7 +8767,7 @@
     </row>
     <row r="415" spans="1:5" ht="15">
       <c r="A415" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>248</v>
@@ -8781,7 +8784,7 @@
     </row>
     <row r="416" spans="1:5" ht="15">
       <c r="A416" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>248</v>
@@ -8790,7 +8793,7 @@
         <v>29</v>
       </c>
       <c r="D416" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>369</v>
@@ -8798,7 +8801,7 @@
     </row>
     <row r="417" spans="1:5" ht="15">
       <c r="A417" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>248</v>
@@ -8815,7 +8818,7 @@
     </row>
     <row r="418" spans="1:5" ht="15">
       <c r="A418" s="1" t="s">
-        <v>251</v>
+        <v>150</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>248</v>
@@ -8832,7 +8835,7 @@
     </row>
     <row r="419" spans="1:5" ht="15">
       <c r="A419" s="1" t="s">
-        <v>150</v>
+        <v>33</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>248</v>
@@ -8849,7 +8852,7 @@
     </row>
     <row r="420" spans="1:5" ht="15">
       <c r="A420" s="1" t="s">
-        <v>33</v>
+        <v>252</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>248</v>
@@ -8866,7 +8869,7 @@
     </row>
     <row r="421" spans="1:5" ht="15">
       <c r="A421" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>248</v>
@@ -8883,7 +8886,7 @@
     </row>
     <row r="422" spans="1:5" ht="15">
       <c r="A422" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>248</v>
@@ -8892,7 +8895,7 @@
         <v>29</v>
       </c>
       <c r="D422" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E422" s="2" t="s">
         <v>369</v>
@@ -8900,7 +8903,7 @@
     </row>
     <row r="423" spans="1:5" ht="15">
       <c r="A423" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>248</v>
@@ -8909,7 +8912,7 @@
         <v>29</v>
       </c>
       <c r="D423" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>369</v>
@@ -8917,7 +8920,7 @@
     </row>
     <row r="424" spans="1:5" ht="15">
       <c r="A424" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>248</v>
@@ -8934,7 +8937,7 @@
     </row>
     <row r="425" spans="1:5" ht="15">
       <c r="A425" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>248</v>
@@ -8951,7 +8954,7 @@
     </row>
     <row r="426" spans="1:5" ht="15">
       <c r="A426" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>248</v>
@@ -8960,7 +8963,7 @@
         <v>29</v>
       </c>
       <c r="D426" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>369</v>
@@ -8968,7 +8971,7 @@
     </row>
     <row r="427" spans="1:5" ht="15">
       <c r="A427" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>248</v>
@@ -8977,7 +8980,7 @@
         <v>29</v>
       </c>
       <c r="D427" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E427" s="2" t="s">
         <v>369</v>
@@ -8985,7 +8988,7 @@
     </row>
     <row r="428" spans="1:5" ht="15">
       <c r="A428" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>248</v>
@@ -9002,7 +9005,7 @@
     </row>
     <row r="429" spans="1:5" ht="15">
       <c r="A429" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>248</v>
@@ -9011,7 +9014,7 @@
         <v>29</v>
       </c>
       <c r="D429" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>369</v>
@@ -9019,7 +9022,7 @@
     </row>
     <row r="430" spans="1:5" ht="15">
       <c r="A430" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>248</v>
@@ -9036,7 +9039,7 @@
     </row>
     <row r="431" spans="1:5" ht="15">
       <c r="A431" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>248</v>
@@ -9045,7 +9048,7 @@
         <v>29</v>
       </c>
       <c r="D431" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>369</v>
@@ -9053,7 +9056,7 @@
     </row>
     <row r="432" spans="1:5" ht="15">
       <c r="A432" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>248</v>
@@ -9070,7 +9073,7 @@
     </row>
     <row r="433" spans="1:5" ht="15">
       <c r="A433" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>248</v>
@@ -9079,7 +9082,7 @@
         <v>29</v>
       </c>
       <c r="D433" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>369</v>
@@ -9087,7 +9090,7 @@
     </row>
     <row r="434" spans="1:5" ht="15">
       <c r="A434" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>248</v>
@@ -9096,7 +9099,7 @@
         <v>29</v>
       </c>
       <c r="D434" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>369</v>
@@ -9104,7 +9107,7 @@
     </row>
     <row r="435" spans="1:5" ht="15">
       <c r="A435" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>248</v>
@@ -9113,7 +9116,7 @@
         <v>29</v>
       </c>
       <c r="D435" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>369</v>
@@ -9121,7 +9124,7 @@
     </row>
     <row r="436" spans="1:5" ht="15">
       <c r="A436" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>248</v>
@@ -9130,7 +9133,7 @@
         <v>29</v>
       </c>
       <c r="D436" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>369</v>
@@ -9138,16 +9141,16 @@
     </row>
     <row r="437" spans="1:5" ht="15">
       <c r="A437" s="1" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C437" t="s">
-        <v>29</v>
-      </c>
-      <c r="D437" t="s">
-        <v>3</v>
+        <v>204</v>
+      </c>
+      <c r="C437" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D437" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>369</v>
@@ -9155,7 +9158,7 @@
     </row>
     <row r="438" spans="1:5" ht="15">
       <c r="A438" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>204</v>
@@ -9172,7 +9175,7 @@
     </row>
     <row r="439" spans="1:5" ht="15">
       <c r="A439" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>204</v>
@@ -9189,7 +9192,7 @@
     </row>
     <row r="440" spans="1:5" ht="15">
       <c r="A440" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>204</v>
@@ -9198,7 +9201,7 @@
         <v>29</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>369</v>
@@ -9206,16 +9209,16 @@
     </row>
     <row r="441" spans="1:5" ht="15">
       <c r="A441" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="C441" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>369</v>
@@ -9223,15 +9226,15 @@
     </row>
     <row r="442" spans="1:5" ht="15">
       <c r="A442" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C442" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D442" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C442" t="s">
+        <v>29</v>
+      </c>
+      <c r="D442" t="s">
         <v>6</v>
       </c>
       <c r="E442" s="2" t="s">
@@ -9240,7 +9243,7 @@
     </row>
     <row r="443" spans="1:5" ht="15">
       <c r="A443" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>237</v>
@@ -9249,7 +9252,7 @@
         <v>29</v>
       </c>
       <c r="D443" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>369</v>
@@ -9274,10 +9277,10 @@
     </row>
     <row r="445" spans="1:5" ht="15">
       <c r="A445" s="1" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C445" t="s">
         <v>29</v>
@@ -9308,7 +9311,7 @@
     </row>
     <row r="447" spans="1:5" ht="15">
       <c r="A447" s="1" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>248</v>
@@ -9325,7 +9328,7 @@
     </row>
     <row r="448" spans="1:5" ht="15">
       <c r="A448" s="1" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>248</v>
@@ -9342,10 +9345,10 @@
     </row>
     <row r="449" spans="1:5" ht="15">
       <c r="A449" s="1" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C449" t="s">
         <v>29</v>
@@ -9354,12 +9357,12 @@
         <v>3</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="450" spans="1:5" ht="15">
       <c r="A450" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>270</v>
@@ -9376,7 +9379,7 @@
     </row>
     <row r="451" spans="1:5" ht="15">
       <c r="A451" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>270</v>
@@ -9393,7 +9396,7 @@
     </row>
     <row r="452" spans="1:5" ht="15">
       <c r="A452" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>270</v>
@@ -9402,7 +9405,7 @@
         <v>29</v>
       </c>
       <c r="D452" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>370</v>
@@ -9410,7 +9413,7 @@
     </row>
     <row r="453" spans="1:5" ht="15">
       <c r="A453" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>270</v>
@@ -9419,7 +9422,7 @@
         <v>29</v>
       </c>
       <c r="D453" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>370</v>
@@ -9427,7 +9430,7 @@
     </row>
     <row r="454" spans="1:5" ht="15">
       <c r="A454" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>270</v>
@@ -9444,7 +9447,7 @@
     </row>
     <row r="455" spans="1:5" ht="15">
       <c r="A455" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>270</v>
@@ -9461,7 +9464,7 @@
     </row>
     <row r="456" spans="1:5" ht="15">
       <c r="A456" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>270</v>
@@ -9470,7 +9473,7 @@
         <v>29</v>
       </c>
       <c r="D456" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E456" s="2" t="s">
         <v>370</v>
@@ -9478,7 +9481,7 @@
     </row>
     <row r="457" spans="1:5" ht="15">
       <c r="A457" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>270</v>
@@ -9487,7 +9490,7 @@
         <v>29</v>
       </c>
       <c r="D457" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E457" s="2" t="s">
         <v>370</v>
@@ -9495,7 +9498,7 @@
     </row>
     <row r="458" spans="1:5" ht="15">
       <c r="A458" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>270</v>
@@ -9512,7 +9515,7 @@
     </row>
     <row r="459" spans="1:5" ht="15">
       <c r="A459" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>270</v>
@@ -9521,7 +9524,7 @@
         <v>29</v>
       </c>
       <c r="D459" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>370</v>
@@ -9529,7 +9532,7 @@
     </row>
     <row r="460" spans="1:5" ht="15">
       <c r="A460" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>270</v>
@@ -9538,7 +9541,7 @@
         <v>29</v>
       </c>
       <c r="D460" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>370</v>
@@ -9546,7 +9549,7 @@
     </row>
     <row r="461" spans="1:5" ht="15">
       <c r="A461" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>270</v>
@@ -9563,7 +9566,7 @@
     </row>
     <row r="462" spans="1:5" ht="15">
       <c r="A462" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>270</v>
@@ -9572,7 +9575,7 @@
         <v>29</v>
       </c>
       <c r="D462" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>370</v>
@@ -9580,7 +9583,7 @@
     </row>
     <row r="463" spans="1:5" ht="15">
       <c r="A463" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>270</v>
@@ -9597,16 +9600,16 @@
     </row>
     <row r="464" spans="1:5" ht="15">
       <c r="A464" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="C464" t="s">
         <v>29</v>
       </c>
       <c r="D464" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>370</v>
@@ -9614,7 +9617,7 @@
     </row>
     <row r="465" spans="1:5" ht="15">
       <c r="A465" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>286</v>
@@ -9631,7 +9634,7 @@
     </row>
     <row r="466" spans="1:5" ht="15">
       <c r="A466" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>286</v>
@@ -9648,7 +9651,7 @@
     </row>
     <row r="467" spans="1:5" ht="15">
       <c r="A467" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>286</v>
@@ -9665,7 +9668,7 @@
     </row>
     <row r="468" spans="1:5" ht="15">
       <c r="A468" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>286</v>
@@ -9682,7 +9685,7 @@
     </row>
     <row r="469" spans="1:5" ht="15">
       <c r="A469" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>286</v>
@@ -9699,7 +9702,7 @@
     </row>
     <row r="470" spans="1:5" ht="15">
       <c r="A470" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>286</v>
@@ -9716,7 +9719,7 @@
     </row>
     <row r="471" spans="1:5" ht="15">
       <c r="A471" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>286</v>
@@ -9733,7 +9736,7 @@
     </row>
     <row r="472" spans="1:5" ht="15">
       <c r="A472" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>286</v>
@@ -9742,7 +9745,7 @@
         <v>29</v>
       </c>
       <c r="D472" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>370</v>
@@ -9750,7 +9753,7 @@
     </row>
     <row r="473" spans="1:5" ht="15">
       <c r="A473" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>286</v>
@@ -9767,16 +9770,16 @@
     </row>
     <row r="474" spans="1:5" ht="15">
       <c r="A474" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C474" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D474" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>370</v>
@@ -9784,7 +9787,7 @@
     </row>
     <row r="475" spans="1:5" ht="15">
       <c r="A475" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>297</v>
@@ -9801,7 +9804,7 @@
     </row>
     <row r="476" spans="1:5" ht="15">
       <c r="A476" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>297</v>
@@ -9818,7 +9821,7 @@
     </row>
     <row r="477" spans="1:5" ht="15">
       <c r="A477" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>297</v>
@@ -9835,7 +9838,7 @@
     </row>
     <row r="478" spans="1:5" ht="15">
       <c r="A478" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>297</v>
@@ -9852,13 +9855,13 @@
     </row>
     <row r="479" spans="1:5" ht="15">
       <c r="A479" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C479" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D479" t="s">
         <v>3</v>
@@ -9869,7 +9872,7 @@
     </row>
     <row r="480" spans="1:5" ht="15">
       <c r="A480" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>303</v>
@@ -9886,7 +9889,7 @@
     </row>
     <row r="481" spans="1:5" ht="15">
       <c r="A481" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>303</v>
@@ -9903,7 +9906,7 @@
     </row>
     <row r="482" spans="1:5" ht="15">
       <c r="A482" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>303</v>
@@ -9920,7 +9923,7 @@
     </row>
     <row r="483" spans="1:5" ht="15">
       <c r="A483" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>303</v>
@@ -9937,7 +9940,7 @@
     </row>
     <row r="484" spans="1:5" ht="15">
       <c r="A484" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>303</v>
@@ -9954,7 +9957,7 @@
     </row>
     <row r="485" spans="1:5" ht="15">
       <c r="A485" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>303</v>
@@ -9971,7 +9974,7 @@
     </row>
     <row r="486" spans="1:5" ht="15">
       <c r="A486" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>303</v>
@@ -9988,7 +9991,7 @@
     </row>
     <row r="487" spans="1:5" ht="15">
       <c r="A487" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>303</v>
@@ -10005,7 +10008,7 @@
     </row>
     <row r="488" spans="1:5" ht="15">
       <c r="A488" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>303</v>
@@ -10022,7 +10025,7 @@
     </row>
     <row r="489" spans="1:5" ht="15">
       <c r="A489" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>303</v>
@@ -10039,7 +10042,7 @@
     </row>
     <row r="490" spans="1:5" ht="15">
       <c r="A490" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>303</v>
@@ -10056,7 +10059,7 @@
     </row>
     <row r="491" spans="1:5" ht="15">
       <c r="A491" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>303</v>
@@ -10073,7 +10076,7 @@
     </row>
     <row r="492" spans="1:5" ht="15">
       <c r="A492" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>303</v>
@@ -10090,7 +10093,7 @@
     </row>
     <row r="493" spans="1:5" ht="15">
       <c r="A493" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>303</v>
@@ -10099,7 +10102,7 @@
         <v>29</v>
       </c>
       <c r="D493" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>370</v>
@@ -10107,7 +10110,7 @@
     </row>
     <row r="494" spans="1:5" ht="15">
       <c r="A494" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>303</v>
@@ -10124,7 +10127,7 @@
     </row>
     <row r="495" spans="1:5" ht="15">
       <c r="A495" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>303</v>
@@ -10133,7 +10136,7 @@
         <v>29</v>
       </c>
       <c r="D495" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>370</v>
@@ -10141,7 +10144,7 @@
     </row>
     <row r="496" spans="1:5" ht="15">
       <c r="A496" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>303</v>
@@ -10150,7 +10153,7 @@
         <v>29</v>
       </c>
       <c r="D496" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>370</v>
@@ -10158,7 +10161,7 @@
     </row>
     <row r="497" spans="1:5" ht="15">
       <c r="A497" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>303</v>
@@ -10167,7 +10170,7 @@
         <v>29</v>
       </c>
       <c r="D497" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>370</v>
@@ -10175,7 +10178,7 @@
     </row>
     <row r="498" spans="1:5" ht="15">
       <c r="A498" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>303</v>
@@ -10192,10 +10195,10 @@
     </row>
     <row r="499" spans="1:5" ht="15">
       <c r="A499" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C499" t="s">
         <v>29</v>
@@ -10209,7 +10212,7 @@
     </row>
     <row r="500" spans="1:5" ht="15">
       <c r="A500" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>324</v>
@@ -10226,10 +10229,10 @@
     </row>
     <row r="501" spans="1:5" ht="15">
       <c r="A501" s="1" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="C501" t="s">
         <v>29</v>
@@ -10260,7 +10263,7 @@
     </row>
     <row r="503" spans="1:5" ht="15">
       <c r="A503" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>270</v>
@@ -10269,7 +10272,7 @@
         <v>29</v>
       </c>
       <c r="D503" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>370</v>
@@ -10277,7 +10280,7 @@
     </row>
     <row r="504" spans="1:5" ht="15">
       <c r="A504" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>270</v>
@@ -10286,7 +10289,7 @@
         <v>29</v>
       </c>
       <c r="D504" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E504" s="2" t="s">
         <v>370</v>
@@ -10303,7 +10306,7 @@
         <v>29</v>
       </c>
       <c r="D505" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E505" s="2" t="s">
         <v>370</v>
@@ -10311,10 +10314,10 @@
     </row>
     <row r="506" spans="1:5" ht="15">
       <c r="A506" s="1" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="C506" t="s">
         <v>29</v>
@@ -10328,16 +10331,16 @@
     </row>
     <row r="507" spans="1:5" ht="15">
       <c r="A507" s="1" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="C507" t="s">
         <v>29</v>
       </c>
       <c r="D507" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E507" s="2" t="s">
         <v>370</v>
@@ -10345,7 +10348,7 @@
     </row>
     <row r="508" spans="1:5" ht="15">
       <c r="A508" s="1" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B508" s="1" t="s">
         <v>303</v>
@@ -10354,7 +10357,7 @@
         <v>29</v>
       </c>
       <c r="D508" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>370</v>
@@ -10362,10 +10365,10 @@
     </row>
     <row r="509" spans="1:5" ht="15">
       <c r="A509" s="1" t="s">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C509" t="s">
         <v>29</v>
@@ -10379,10 +10382,10 @@
     </row>
     <row r="510" spans="1:5" ht="15">
       <c r="A510" s="1" t="s">
-        <v>75</v>
+        <v>327</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C510" t="s">
         <v>29</v>
@@ -10391,12 +10394,12 @@
         <v>6</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="511" spans="1:5" ht="15">
       <c r="A511" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B511" s="1" t="s">
         <v>328</v>
@@ -10413,7 +10416,7 @@
     </row>
     <row r="512" spans="1:5" ht="15">
       <c r="A512" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B512" s="1" t="s">
         <v>328</v>
@@ -10430,16 +10433,16 @@
     </row>
     <row r="513" spans="1:5" ht="15">
       <c r="A513" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B513" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C513" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D513" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E513" s="2" t="s">
         <v>368</v>
@@ -10447,16 +10450,16 @@
     </row>
     <row r="514" spans="1:5" ht="15">
       <c r="A514" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B514" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C514" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D514" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E514" s="2" t="s">
         <v>368</v>
@@ -10464,16 +10467,16 @@
     </row>
     <row r="515" spans="1:5" ht="15">
       <c r="A515" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B515" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C515" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D515" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E515" s="2" t="s">
         <v>368</v>
@@ -10481,7 +10484,7 @@
     </row>
     <row r="516" spans="1:5" ht="15">
       <c r="A516" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>328</v>
@@ -10498,7 +10501,7 @@
     </row>
     <row r="517" spans="1:5" ht="15">
       <c r="A517" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B517" s="1" t="s">
         <v>328</v>
@@ -10507,7 +10510,7 @@
         <v>2</v>
       </c>
       <c r="D517" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E517" s="2" t="s">
         <v>368</v>
@@ -10515,16 +10518,16 @@
     </row>
     <row r="518" spans="1:5" ht="15">
       <c r="A518" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C518" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D518" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="E518" s="2" t="s">
         <v>368</v>
@@ -10532,16 +10535,16 @@
     </row>
     <row r="519" spans="1:5" ht="15">
       <c r="A519" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B519" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C519" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D519" t="s">
-        <v>192</v>
+        <v>42</v>
       </c>
       <c r="E519" s="2" t="s">
         <v>368</v>
@@ -10549,16 +10552,16 @@
     </row>
     <row r="520" spans="1:5" ht="15">
       <c r="A520" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B520" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C520" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D520" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E520" s="2" t="s">
         <v>368</v>
@@ -10566,7 +10569,7 @@
     </row>
     <row r="521" spans="1:5" ht="15">
       <c r="A521" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B521" s="1" t="s">
         <v>328</v>
@@ -10575,7 +10578,7 @@
         <v>29</v>
       </c>
       <c r="D521" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E521" s="2" t="s">
         <v>368</v>
@@ -10583,7 +10586,7 @@
     </row>
     <row r="522" spans="1:5" ht="15">
       <c r="A522" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>328</v>
@@ -10592,7 +10595,7 @@
         <v>29</v>
       </c>
       <c r="D522" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E522" s="2" t="s">
         <v>368</v>
@@ -10600,7 +10603,7 @@
     </row>
     <row r="523" spans="1:5" ht="15">
       <c r="A523" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>328</v>
@@ -10617,16 +10620,16 @@
     </row>
     <row r="524" spans="1:5" ht="15">
       <c r="A524" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C524" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D524" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>368</v>
@@ -10634,7 +10637,7 @@
     </row>
     <row r="525" spans="1:5" ht="15">
       <c r="A525" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B525" s="1" t="s">
         <v>328</v>
@@ -10643,7 +10646,7 @@
         <v>2</v>
       </c>
       <c r="D525" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="E525" s="2" t="s">
         <v>368</v>
@@ -10651,7 +10654,7 @@
     </row>
     <row r="526" spans="1:5" ht="15">
       <c r="A526" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>328</v>
@@ -10660,7 +10663,7 @@
         <v>2</v>
       </c>
       <c r="D526" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>368</v>
@@ -10668,7 +10671,7 @@
     </row>
     <row r="527" spans="1:5" ht="15">
       <c r="A527" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>328</v>
@@ -10677,7 +10680,7 @@
         <v>2</v>
       </c>
       <c r="D527" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>368</v>
@@ -10685,13 +10688,13 @@
     </row>
     <row r="528" spans="1:5" ht="15">
       <c r="A528" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C528" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D528" t="s">
         <v>42</v>
@@ -10702,7 +10705,7 @@
     </row>
     <row r="529" spans="1:5" ht="15">
       <c r="A529" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>328</v>
@@ -10719,16 +10722,16 @@
     </row>
     <row r="530" spans="1:5" ht="15">
       <c r="A530" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C530" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D530" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E530" s="2" t="s">
         <v>368</v>
@@ -10736,7 +10739,7 @@
     </row>
     <row r="531" spans="1:5" ht="15">
       <c r="A531" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>328</v>
@@ -10753,7 +10756,7 @@
     </row>
     <row r="532" spans="1:5" ht="15">
       <c r="A532" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>328</v>
@@ -10770,7 +10773,7 @@
     </row>
     <row r="533" spans="1:5" ht="15">
       <c r="A533" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>328</v>
@@ -10787,7 +10790,7 @@
     </row>
     <row r="534" spans="1:5" ht="15">
       <c r="A534" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>328</v>
@@ -10804,13 +10807,13 @@
     </row>
     <row r="535" spans="1:5" ht="15">
       <c r="A535" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="C535" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D535" t="s">
         <v>6</v>
@@ -10821,7 +10824,7 @@
     </row>
     <row r="536" spans="1:5" ht="15">
       <c r="A536" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>354</v>
@@ -10838,7 +10841,7 @@
     </row>
     <row r="537" spans="1:5" ht="15">
       <c r="A537" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>354</v>
@@ -10847,7 +10850,7 @@
         <v>29</v>
       </c>
       <c r="D537" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E537" s="2" t="s">
         <v>368</v>
@@ -10855,7 +10858,7 @@
     </row>
     <row r="538" spans="1:5" ht="15">
       <c r="A538" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>354</v>
@@ -10864,7 +10867,7 @@
         <v>29</v>
       </c>
       <c r="D538" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E538" s="2" t="s">
         <v>368</v>
@@ -10872,7 +10875,7 @@
     </row>
     <row r="539" spans="1:5" ht="15">
       <c r="A539" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>354</v>
@@ -10881,7 +10884,7 @@
         <v>29</v>
       </c>
       <c r="D539" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="E539" s="2" t="s">
         <v>368</v>
@@ -10889,7 +10892,7 @@
     </row>
     <row r="540" spans="1:5" ht="15">
       <c r="A540" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>354</v>
@@ -10898,7 +10901,7 @@
         <v>29</v>
       </c>
       <c r="D540" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E540" s="2" t="s">
         <v>368</v>
@@ -10906,7 +10909,7 @@
     </row>
     <row r="541" spans="1:5" ht="15">
       <c r="A541" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>354</v>
@@ -10915,7 +10918,7 @@
         <v>29</v>
       </c>
       <c r="D541" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>368</v>
@@ -10923,41 +10926,41 @@
     </row>
     <row r="542" spans="1:5" ht="15">
       <c r="A542" s="1" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="C542" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D542" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E542" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="15">
-      <c r="A543" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B543" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C543" t="s">
-        <v>2</v>
-      </c>
-      <c r="D543" t="s">
-        <v>31</v>
-      </c>
-      <c r="E543" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="544" spans="1:5">
-      <c r="A544" s="5" t="s">
+    <row r="543" spans="1:5">
+      <c r="A543" s="5" t="s">
         <v>52</v>
+      </c>
+      <c r="B543" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D543" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E543" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" ht="15">
+      <c r="A544" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="B544" s="6" t="s">
         <v>58</v>
@@ -10966,7 +10969,7 @@
         <v>29</v>
       </c>
       <c r="D544" s="3" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="E544" s="7" t="s">
         <v>376</v>
@@ -10974,16 +10977,16 @@
     </row>
     <row r="545" spans="1:5" ht="15">
       <c r="A545" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B545" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C545" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D545" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C545" t="s">
+        <v>2</v>
+      </c>
+      <c r="D545" t="s">
+        <v>6</v>
       </c>
       <c r="E545" s="7" t="s">
         <v>376</v>
@@ -10991,50 +10994,50 @@
     </row>
     <row r="546" spans="1:5" ht="15">
       <c r="A546" s="1" t="s">
-        <v>200</v>
+        <v>361</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="C546" t="s">
         <v>2</v>
       </c>
       <c r="D546" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E546" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="15">
-      <c r="A547" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B547" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C547" t="s">
-        <v>2</v>
-      </c>
-      <c r="D547" t="s">
-        <v>42</v>
+    <row r="547" spans="1:5">
+      <c r="A547" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B547" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D547" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E547" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
-      <c r="A548" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B548" s="6" t="s">
-        <v>362</v>
+    <row r="548" spans="1:5" ht="15">
+      <c r="A548" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B548" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="C548" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E548" s="7" t="s">
         <v>376</v>
@@ -11042,15 +11045,15 @@
     </row>
     <row r="549" spans="1:5" ht="15">
       <c r="A549" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B549" s="8" t="s">
-        <v>121</v>
+        <v>361</v>
+      </c>
+      <c r="B549" s="6" t="s">
+        <v>362</v>
       </c>
       <c r="C549" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D549" s="3" t="s">
+      <c r="D549" t="s">
         <v>6</v>
       </c>
       <c r="E549" s="7" t="s">
@@ -11059,33 +11062,33 @@
     </row>
     <row r="550" spans="1:5" ht="15">
       <c r="A550" s="1" t="s">
-        <v>361</v>
+        <v>117</v>
       </c>
       <c r="B550" s="6" t="s">
-        <v>362</v>
+        <v>58</v>
       </c>
       <c r="C550" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D550" t="s">
+      <c r="D550" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E550" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="15">
-      <c r="A551" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B551" s="6" t="s">
-        <v>58</v>
+    <row r="551" spans="1:5">
+      <c r="A551" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B551" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="C551" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E551" s="7" t="s">
         <v>376</v>
@@ -11093,33 +11096,33 @@
     </row>
     <row r="552" spans="1:5">
       <c r="A552" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B552" s="3" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="C552" s="3" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D552" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E552" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
-      <c r="A553" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B553" s="3" t="s">
-        <v>76</v>
+    <row r="553" spans="1:5" ht="15">
+      <c r="A553" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B553" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="C553" s="3" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D553" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E553" s="7" t="s">
         <v>376</v>
@@ -11127,16 +11130,16 @@
     </row>
     <row r="554" spans="1:5" ht="15">
       <c r="A554" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B554" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C554" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D554" s="3" t="s">
-        <v>3</v>
+        <v>361</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C554" t="s">
+        <v>2</v>
+      </c>
+      <c r="D554" t="s">
+        <v>6</v>
       </c>
       <c r="E554" s="7" t="s">
         <v>376</v>
@@ -11144,15 +11147,15 @@
     </row>
     <row r="555" spans="1:5" ht="15">
       <c r="A555" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B555" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C555" t="s">
-        <v>2</v>
-      </c>
-      <c r="D555" t="s">
+        <v>201</v>
+      </c>
+      <c r="B555" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D555" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E555" s="7" t="s">
@@ -11161,50 +11164,50 @@
     </row>
     <row r="556" spans="1:5" ht="15">
       <c r="A556" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B556" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C556" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D556" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B556" t="s">
+        <v>125</v>
+      </c>
+      <c r="C556" t="s">
+        <v>2</v>
+      </c>
+      <c r="D556" t="s">
         <v>6</v>
       </c>
       <c r="E556" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="15">
-      <c r="A557" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B557" t="s">
-        <v>125</v>
-      </c>
-      <c r="C557" t="s">
-        <v>2</v>
-      </c>
-      <c r="D557" t="s">
-        <v>6</v>
+    <row r="557" spans="1:5">
+      <c r="A557" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B557" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D557" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E557" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="558" spans="1:5">
-      <c r="A558" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B558" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C558" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D558" s="3" t="s">
-        <v>42</v>
+    <row r="558" spans="1:5" ht="15">
+      <c r="A558" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C558" t="s">
+        <v>2</v>
+      </c>
+      <c r="D558" t="s">
+        <v>3</v>
       </c>
       <c r="E558" s="7" t="s">
         <v>376</v>
@@ -11212,15 +11215,15 @@
     </row>
     <row r="559" spans="1:5" ht="15">
       <c r="A559" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B559" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C559" t="s">
-        <v>2</v>
-      </c>
-      <c r="D559" t="s">
+        <v>117</v>
+      </c>
+      <c r="B559" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D559" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E559" s="7" t="s">
@@ -11229,16 +11232,16 @@
     </row>
     <row r="560" spans="1:5" ht="15">
       <c r="A560" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B560" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
+      </c>
+      <c r="B560" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="C560" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E560" s="7" t="s">
         <v>376</v>
@@ -11246,16 +11249,16 @@
     </row>
     <row r="561" spans="1:5" ht="15">
       <c r="A561" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B561" s="3" t="s">
-        <v>41</v>
+        <v>117</v>
+      </c>
+      <c r="B561" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C561" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D561" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E561" s="7" t="s">
         <v>376</v>
@@ -11263,16 +11266,16 @@
     </row>
     <row r="562" spans="1:5" ht="15">
       <c r="A562" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B562" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C562" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D562" s="3" t="s">
-        <v>3</v>
+        <v>129</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C562" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D562" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E562" s="7" t="s">
         <v>376</v>
@@ -11280,58 +11283,58 @@
     </row>
     <row r="563" spans="1:5" ht="15">
       <c r="A563" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B563" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B563" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C563" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D563" s="2" t="s">
-        <v>6</v>
+      <c r="C563" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D563" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E563" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="15">
-      <c r="A564" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B564" s="3" t="s">
+    <row r="564" spans="1:5">
+      <c r="A564" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B564" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C564" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D564" s="3" t="s">
-        <v>3</v>
+      <c r="C564" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D564" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E564" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="565" spans="1:5">
-      <c r="A565" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B565" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C565" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D565" s="6" t="s">
-        <v>31</v>
+    <row r="565" spans="1:5" ht="15">
+      <c r="A565" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B565" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D565" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E565" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="15">
-      <c r="A566" s="1" t="s">
-        <v>363</v>
+    <row r="566" spans="1:5">
+      <c r="A566" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="B566" s="8" t="s">
         <v>121</v>
@@ -11340,40 +11343,40 @@
         <v>29</v>
       </c>
       <c r="D566" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E566" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="567" spans="1:5">
-      <c r="A567" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B567" s="8" t="s">
-        <v>121</v>
+    <row r="567" spans="1:5" ht="15">
+      <c r="A567" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C567" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D567" s="3" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E567" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="15">
-      <c r="A568" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B568" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C568" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D568" s="3" t="s">
+    <row r="568" spans="1:5">
+      <c r="A568" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B568" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C568" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D568" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E568" s="7" t="s">
@@ -11381,33 +11384,33 @@
       </c>
     </row>
     <row r="569" spans="1:5">
-      <c r="A569" s="9" t="s">
-        <v>40</v>
+      <c r="A569" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="B569" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C569" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D569" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D569" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E569" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="570" spans="1:5">
-      <c r="A570" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B570" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C570" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D570" s="3" t="s">
+    <row r="570" spans="1:5" ht="15">
+      <c r="A570" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C570" t="s">
+        <v>2</v>
+      </c>
+      <c r="D570" t="s">
         <v>6</v>
       </c>
       <c r="E570" s="7" t="s">
@@ -11415,14 +11418,14 @@
       </c>
     </row>
     <row r="571" spans="1:5" ht="15">
-      <c r="A571" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B571" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C571" t="s">
-        <v>2</v>
+      <c r="A571" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B571" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D571" t="s">
         <v>6</v>
@@ -11431,17 +11434,17 @@
         <v>376</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="15">
-      <c r="A572" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B572" s="6" t="s">
-        <v>362</v>
+    <row r="572" spans="1:5">
+      <c r="A572" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B572" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="C572" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D572" t="s">
+        <v>2</v>
+      </c>
+      <c r="D572" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E572" s="7" t="s">
@@ -11449,14 +11452,14 @@
       </c>
     </row>
     <row r="573" spans="1:5">
-      <c r="A573" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B573" s="3" t="s">
-        <v>76</v>
+      <c r="A573" t="s">
+        <v>74</v>
+      </c>
+      <c r="B573" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="C573" s="3" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D573" s="3" t="s">
         <v>6</v>
@@ -11467,27 +11470,27 @@
     </row>
     <row r="574" spans="1:5">
       <c r="A574" t="s">
-        <v>74</v>
-      </c>
-      <c r="B574" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C574" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D574" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B574" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C574" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D574" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E574" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="575" spans="1:5">
-      <c r="A575" t="s">
-        <v>128</v>
-      </c>
-      <c r="B575" s="6" t="s">
-        <v>41</v>
+    <row r="575" spans="1:5" ht="15">
+      <c r="A575" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B575" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="C575" s="6" t="s">
         <v>29</v>
@@ -11516,18 +11519,18 @@
         <v>376</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="15">
-      <c r="A577" s="1" t="s">
-        <v>202</v>
+    <row r="577" spans="1:5">
+      <c r="A577" t="s">
+        <v>364</v>
       </c>
       <c r="B577" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C577" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D577" s="6" t="s">
-        <v>6</v>
+        <v>76</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D577" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E577" s="7" t="s">
         <v>376</v>
@@ -11535,16 +11538,16 @@
     </row>
     <row r="578" spans="1:5">
       <c r="A578" t="s">
-        <v>364</v>
-      </c>
-      <c r="B578" s="8" t="s">
-        <v>76</v>
+        <v>365</v>
+      </c>
+      <c r="B578" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D578" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E578" s="7" t="s">
         <v>376</v>
@@ -11552,16 +11555,16 @@
     </row>
     <row r="579" spans="1:5">
       <c r="A579" t="s">
-        <v>365</v>
-      </c>
-      <c r="B579" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C579" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D579" s="3" t="s">
-        <v>6</v>
+        <v>123</v>
+      </c>
+      <c r="B579" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C579" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D579" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="E579" s="7" t="s">
         <v>376</v>
@@ -11578,23 +11581,23 @@
         <v>29</v>
       </c>
       <c r="D580" s="6" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E580" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="581" spans="1:5">
-      <c r="A581" t="s">
-        <v>123</v>
-      </c>
-      <c r="B581" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C581" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D581" s="6" t="s">
+    <row r="581" spans="1:5" ht="15">
+      <c r="A581" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D581" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E581" s="7" t="s">
@@ -11602,54 +11605,54 @@
       </c>
     </row>
     <row r="582" spans="1:5" ht="15">
-      <c r="A582" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B582" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C582" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D582" s="3" t="s">
-        <v>6</v>
+      <c r="A582" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C582" t="s">
+        <v>2</v>
+      </c>
+      <c r="D582" t="s">
+        <v>192</v>
       </c>
       <c r="E582" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="15">
-      <c r="A583" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B583" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C583" t="s">
-        <v>2</v>
-      </c>
-      <c r="D583" t="s">
-        <v>192</v>
+    <row r="583" spans="1:5">
+      <c r="A583" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B583" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C583" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D583" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E583" s="7" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="584" spans="1:5">
-      <c r="A584" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B584" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="C584" s="3" t="s">
+      <c r="A584" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C584" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D584" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E584" s="7" t="s">
-        <v>376</v>
+      <c r="E584" s="2" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -11671,7 +11674,7 @@
     </row>
     <row r="586" spans="1:5">
       <c r="A586" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>28</v>
@@ -11679,7 +11682,7 @@
       <c r="C586" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D586" s="3" t="s">
+      <c r="D586" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E586" s="2" t="s">
@@ -11688,10 +11691,10 @@
     </row>
     <row r="587" spans="1:5">
       <c r="A587" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>29</v>
@@ -11720,86 +11723,86 @@
         <v>366</v>
       </c>
     </row>
-    <row r="589" spans="1:5">
-      <c r="A589" s="2" t="s">
-        <v>38</v>
+    <row r="589" spans="1:5" ht="15">
+      <c r="A589" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D589" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="590" spans="1:5" ht="15">
       <c r="A590" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="B590" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C590" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D590" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C590" t="s">
+        <v>29</v>
+      </c>
+      <c r="D590" t="s">
         <v>3</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="591" spans="1:5" ht="15">
-      <c r="A591" s="1" t="s">
-        <v>378</v>
+      <c r="A591" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>248</v>
+        <v>380</v>
       </c>
       <c r="C591" t="s">
         <v>29</v>
       </c>
       <c r="D591" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="592" spans="1:5" ht="15">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="592" spans="1:5">
       <c r="A592" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B592" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="C592" t="s">
         <v>29</v>
       </c>
       <c r="D592" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E592" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="593" spans="1:5">
-      <c r="A593" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B593" s="2" t="s">
-        <v>382</v>
+    <row r="593" spans="1:5" ht="15">
+      <c r="A593" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="C593" t="s">
         <v>29</v>
       </c>
       <c r="D593" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E593" s="2" t="s">
         <v>370</v>
@@ -11807,27 +11810,27 @@
     </row>
     <row r="594" spans="1:5" ht="15">
       <c r="A594" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B594" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C594" t="s">
-        <v>29</v>
-      </c>
-      <c r="D594" t="s">
+        <v>383</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C594" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D594" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="595" spans="1:5" ht="15">
       <c r="A595" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B595" s="2" t="s">
-        <v>105</v>
+        <v>384</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C595" s="2" t="s">
         <v>29</v>
@@ -11836,29 +11839,29 @@
         <v>6</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="596" spans="1:5" ht="15">
       <c r="A596" s="1" t="s">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C596" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D596" s="2" t="s">
-        <v>6</v>
+        <v>303</v>
+      </c>
+      <c r="C596" t="s">
+        <v>29</v>
+      </c>
+      <c r="D596" t="s">
+        <v>3</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="597" spans="1:5" ht="15">
       <c r="A597" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B597" s="1" t="s">
         <v>303</v>
@@ -11875,44 +11878,44 @@
     </row>
     <row r="598" spans="1:5" ht="15">
       <c r="A598" s="1" t="s">
-        <v>310</v>
+        <v>385</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C598" t="s">
-        <v>29</v>
-      </c>
-      <c r="D598" t="s">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="C598" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D598" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="599" spans="1:5" ht="15">
       <c r="A599" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C599" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D599" s="2" t="s">
-        <v>6</v>
+        <v>229</v>
+      </c>
+      <c r="C599" t="s">
+        <v>29</v>
+      </c>
+      <c r="D599" t="s">
+        <v>3</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="600" spans="1:5" ht="15">
       <c r="A600" s="1" t="s">
-        <v>386</v>
+        <v>317</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>229</v>
+        <v>303</v>
       </c>
       <c r="C600" t="s">
         <v>29</v>
@@ -11921,15 +11924,15 @@
         <v>3</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="601" spans="1:5" ht="15">
       <c r="A601" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B601" s="1" t="s">
-        <v>303</v>
+        <v>387</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="C601" t="s">
         <v>29</v>
@@ -11943,7 +11946,7 @@
     </row>
     <row r="602" spans="1:5" ht="15">
       <c r="A602" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>382</v>
@@ -11960,7 +11963,7 @@
     </row>
     <row r="603" spans="1:5" ht="15">
       <c r="A603" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>382</v>
@@ -11977,7 +11980,7 @@
     </row>
     <row r="604" spans="1:5" ht="15">
       <c r="A604" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>382</v>
@@ -11994,7 +11997,7 @@
     </row>
     <row r="605" spans="1:5" ht="15">
       <c r="A605" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>382</v>
@@ -12003,7 +12006,7 @@
         <v>29</v>
       </c>
       <c r="D605" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E605" s="2" t="s">
         <v>370</v>
@@ -12011,7 +12014,7 @@
     </row>
     <row r="606" spans="1:5" ht="15">
       <c r="A606" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>382</v>
@@ -12020,7 +12023,7 @@
         <v>29</v>
       </c>
       <c r="D606" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E606" s="2" t="s">
         <v>370</v>
@@ -12028,10 +12031,10 @@
     </row>
     <row r="607" spans="1:5" ht="15">
       <c r="A607" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B607" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="C607" t="s">
         <v>29</v>
@@ -12045,7 +12048,7 @@
     </row>
     <row r="608" spans="1:5" ht="15">
       <c r="A608" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B608" s="1" t="s">
         <v>380</v>
@@ -12062,7 +12065,7 @@
     </row>
     <row r="609" spans="1:5" ht="15">
       <c r="A609" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B609" s="1" t="s">
         <v>380</v>
@@ -12077,63 +12080,63 @@
         <v>370</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="15">
-      <c r="A610" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B610" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="C610" t="s">
-        <v>29</v>
-      </c>
-      <c r="D610" t="s">
+    <row r="610" spans="1:5">
+      <c r="A610" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D610" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E610" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" ht="15">
+      <c r="A611" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C611" t="s">
+        <v>29</v>
+      </c>
+      <c r="D611" t="s">
+        <v>3</v>
+      </c>
+      <c r="E611" s="2" t="s">
         <v>370</v>
-      </c>
-    </row>
-    <row r="611" spans="1:5">
-      <c r="A611" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B611" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C611" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D611" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E611" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="612" spans="1:5" ht="15">
       <c r="A612" s="1" t="s">
-        <v>290</v>
+        <v>396</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>286</v>
+        <v>354</v>
       </c>
       <c r="C612" t="s">
         <v>29</v>
       </c>
       <c r="D612" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="613" spans="1:5" ht="15">
       <c r="A613" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B613" s="1" t="s">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="C613" t="s">
         <v>29</v>
@@ -12147,10 +12150,10 @@
     </row>
     <row r="614" spans="1:5" ht="15">
       <c r="A614" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B614" s="1" t="s">
-        <v>105</v>
+        <v>328</v>
       </c>
       <c r="C614" t="s">
         <v>29</v>
@@ -12164,7 +12167,7 @@
     </row>
     <row r="615" spans="1:5" ht="15">
       <c r="A615" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B615" s="1" t="s">
         <v>328</v>
@@ -12176,6 +12179,23 @@
         <v>6</v>
       </c>
       <c r="E615" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" ht="15">
+      <c r="A616" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C616" t="s">
+        <v>29</v>
+      </c>
+      <c r="D616" t="s">
+        <v>42</v>
+      </c>
+      <c r="E616" s="2" t="s">
         <v>368</v>
       </c>
     </row>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A412428-F3A7-4178-85BF-D91210035383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5488BB17-25B3-4E62-9DB8-FDFA76785C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="399">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1125,9 +1125,6 @@
   </si>
   <si>
     <t>Savannah</t>
-  </si>
-  <si>
-    <t>Foreign White Border</t>
   </si>
   <si>
     <t>Spirit Link</t>
@@ -1758,7 +1755,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1775,7 +1772,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1792,7 +1789,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1809,7 +1806,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1826,7 +1823,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1843,7 +1840,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1860,7 +1857,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1877,7 +1874,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1894,7 +1891,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1911,7 +1908,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1928,7 +1925,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1945,7 +1942,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1962,7 +1959,7 @@
         <v>6</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1979,7 +1976,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1996,7 +1993,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2013,7 +2010,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2030,7 +2027,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2047,7 +2044,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2064,7 +2061,7 @@
         <v>6</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2081,7 +2078,7 @@
         <v>3</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2098,7 +2095,7 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2115,7 +2112,7 @@
         <v>3</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2132,7 +2129,7 @@
         <v>6</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2149,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2166,7 +2163,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2183,7 +2180,7 @@
         <v>6</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2200,7 +2197,7 @@
         <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2217,7 +2214,7 @@
         <v>6</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2234,7 +2231,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2251,7 +2248,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2268,7 +2265,7 @@
         <v>6</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2285,7 +2282,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2302,7 +2299,7 @@
         <v>6</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2319,7 +2316,7 @@
         <v>6</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2336,7 +2333,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2353,7 +2350,7 @@
         <v>6</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2370,7 +2367,7 @@
         <v>6</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2387,7 +2384,7 @@
         <v>6</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2404,7 +2401,7 @@
         <v>6</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2421,7 +2418,7 @@
         <v>6</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2438,7 +2435,7 @@
         <v>39</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2455,7 +2452,7 @@
         <v>6</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2472,7 +2469,7 @@
         <v>42</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2489,7 +2486,7 @@
         <v>42</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2506,7 +2503,7 @@
         <v>42</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2523,7 +2520,7 @@
         <v>6</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2540,7 +2537,7 @@
         <v>6</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2557,7 +2554,7 @@
         <v>6</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2574,7 +2571,7 @@
         <v>6</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2591,7 +2588,7 @@
         <v>6</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2608,7 +2605,7 @@
         <v>6</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2625,7 +2622,7 @@
         <v>42</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2642,7 +2639,7 @@
         <v>42</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2659,7 +2656,7 @@
         <v>6</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2676,7 +2673,7 @@
         <v>6</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2693,7 +2690,7 @@
         <v>6</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2710,7 +2707,7 @@
         <v>6</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2727,7 +2724,7 @@
         <v>6</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2744,7 +2741,7 @@
         <v>6</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2761,7 +2758,7 @@
         <v>3</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2778,7 +2775,7 @@
         <v>6</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2795,7 +2792,7 @@
         <v>6</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2812,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2829,7 +2826,7 @@
         <v>6</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2846,7 +2843,7 @@
         <v>6</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2863,7 +2860,7 @@
         <v>6</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2880,7 +2877,7 @@
         <v>6</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2897,7 +2894,7 @@
         <v>6</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2914,7 +2911,7 @@
         <v>3</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2931,7 +2928,7 @@
         <v>42</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2948,7 +2945,7 @@
         <v>6</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2965,7 +2962,7 @@
         <v>6</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2982,7 +2979,7 @@
         <v>6</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2999,7 +2996,7 @@
         <v>42</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3016,7 +3013,7 @@
         <v>6</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3033,7 +3030,7 @@
         <v>6</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3050,7 +3047,7 @@
         <v>3</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3067,7 +3064,7 @@
         <v>42</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3084,7 +3081,7 @@
         <v>3</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3101,7 +3098,7 @@
         <v>6</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3118,7 +3115,7 @@
         <v>6</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3135,7 +3132,7 @@
         <v>6</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3152,7 +3149,7 @@
         <v>6</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3169,7 +3166,7 @@
         <v>6</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3186,7 +3183,7 @@
         <v>6</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3203,7 +3200,7 @@
         <v>6</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3220,7 +3217,7 @@
         <v>6</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3237,7 +3234,7 @@
         <v>6</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3254,7 +3251,7 @@
         <v>6</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3271,7 +3268,7 @@
         <v>42</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3288,7 +3285,7 @@
         <v>6</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3305,7 +3302,7 @@
         <v>6</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3322,7 +3319,7 @@
         <v>6</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3339,7 +3336,7 @@
         <v>6</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3356,7 +3353,7 @@
         <v>6</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3373,7 +3370,7 @@
         <v>6</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3390,7 +3387,7 @@
         <v>6</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3407,7 +3404,7 @@
         <v>42</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3424,7 +3421,7 @@
         <v>42</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3441,7 +3438,7 @@
         <v>6</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3458,7 +3455,7 @@
         <v>6</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3475,7 +3472,7 @@
         <v>6</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3492,7 +3489,7 @@
         <v>6</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3509,7 +3506,7 @@
         <v>6</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3526,7 +3523,7 @@
         <v>3</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3543,7 +3540,7 @@
         <v>3</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3560,7 +3557,7 @@
         <v>39</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3577,7 +3574,7 @@
         <v>6</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3594,7 +3591,7 @@
         <v>6</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3611,7 +3608,7 @@
         <v>31</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3628,7 +3625,7 @@
         <v>6</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3645,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3662,7 +3659,7 @@
         <v>6</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3679,7 +3676,7 @@
         <v>6</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3696,7 +3693,7 @@
         <v>6</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3713,7 +3710,7 @@
         <v>42</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3730,7 +3727,7 @@
         <v>6</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3747,7 +3744,7 @@
         <v>6</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3764,7 +3761,7 @@
         <v>6</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3781,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3798,7 +3795,7 @@
         <v>6</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3815,7 +3812,7 @@
         <v>42</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3832,7 +3829,7 @@
         <v>42</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3849,7 +3846,7 @@
         <v>6</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15">
@@ -3866,7 +3863,7 @@
         <v>6</v>
       </c>
       <c r="E126" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15">
@@ -3883,7 +3880,7 @@
         <v>6</v>
       </c>
       <c r="E127" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15">
@@ -3900,7 +3897,7 @@
         <v>6</v>
       </c>
       <c r="E128" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15">
@@ -3917,7 +3914,7 @@
         <v>3</v>
       </c>
       <c r="E129" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15">
@@ -3934,7 +3931,7 @@
         <v>6</v>
       </c>
       <c r="E130" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15">
@@ -3951,7 +3948,7 @@
         <v>3</v>
       </c>
       <c r="E131" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15">
@@ -3968,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="E132" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15">
@@ -3985,7 +3982,7 @@
         <v>42</v>
       </c>
       <c r="E133" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15">
@@ -4002,7 +3999,7 @@
         <v>6</v>
       </c>
       <c r="E134" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15">
@@ -4019,7 +4016,7 @@
         <v>42</v>
       </c>
       <c r="E135" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15">
@@ -4036,7 +4033,7 @@
         <v>6</v>
       </c>
       <c r="E136" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15">
@@ -4053,7 +4050,7 @@
         <v>6</v>
       </c>
       <c r="E137" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15">
@@ -4070,7 +4067,7 @@
         <v>6</v>
       </c>
       <c r="E138" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15">
@@ -4087,7 +4084,7 @@
         <v>6</v>
       </c>
       <c r="E139" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15">
@@ -4104,7 +4101,7 @@
         <v>6</v>
       </c>
       <c r="E140" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15">
@@ -4121,7 +4118,7 @@
         <v>3</v>
       </c>
       <c r="E141" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15">
@@ -4138,7 +4135,7 @@
         <v>6</v>
       </c>
       <c r="E142" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15">
@@ -4155,7 +4152,7 @@
         <v>42</v>
       </c>
       <c r="E143" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15">
@@ -4172,7 +4169,7 @@
         <v>6</v>
       </c>
       <c r="E144" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="15">
@@ -4189,7 +4186,7 @@
         <v>6</v>
       </c>
       <c r="E145" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="15">
@@ -4206,7 +4203,7 @@
         <v>6</v>
       </c>
       <c r="E146" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="15">
@@ -4223,7 +4220,7 @@
         <v>6</v>
       </c>
       <c r="E147" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="15">
@@ -4240,7 +4237,7 @@
         <v>6</v>
       </c>
       <c r="E148" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="15">
@@ -4257,7 +4254,7 @@
         <v>6</v>
       </c>
       <c r="E149" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="15">
@@ -4274,7 +4271,7 @@
         <v>6</v>
       </c>
       <c r="E150" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="15">
@@ -4291,7 +4288,7 @@
         <v>6</v>
       </c>
       <c r="E151" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="15">
@@ -4308,7 +4305,7 @@
         <v>6</v>
       </c>
       <c r="E152" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="15">
@@ -4325,7 +4322,7 @@
         <v>3</v>
       </c>
       <c r="E153" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="15">
@@ -4342,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="E154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="15">
@@ -4359,7 +4356,7 @@
         <v>42</v>
       </c>
       <c r="E155" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="15">
@@ -4376,7 +4373,7 @@
         <v>42</v>
       </c>
       <c r="E156" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="15">
@@ -4393,7 +4390,7 @@
         <v>6</v>
       </c>
       <c r="E157" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="15">
@@ -4410,7 +4407,7 @@
         <v>3</v>
       </c>
       <c r="E158" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="15">
@@ -4427,7 +4424,7 @@
         <v>3</v>
       </c>
       <c r="E159" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="15">
@@ -4444,7 +4441,7 @@
         <v>6</v>
       </c>
       <c r="E160" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="15">
@@ -4461,7 +4458,7 @@
         <v>6</v>
       </c>
       <c r="E161" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="15">
@@ -4478,7 +4475,7 @@
         <v>6</v>
       </c>
       <c r="E162" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="15">
@@ -4495,7 +4492,7 @@
         <v>3</v>
       </c>
       <c r="E163" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="15">
@@ -4512,7 +4509,7 @@
         <v>6</v>
       </c>
       <c r="E164" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="15">
@@ -4529,7 +4526,7 @@
         <v>6</v>
       </c>
       <c r="E165" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="15">
@@ -4546,7 +4543,7 @@
         <v>6</v>
       </c>
       <c r="E166" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="15">
@@ -4563,7 +4560,7 @@
         <v>6</v>
       </c>
       <c r="E167" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="15">
@@ -4580,7 +4577,7 @@
         <v>42</v>
       </c>
       <c r="E168" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="15">
@@ -4597,7 +4594,7 @@
         <v>42</v>
       </c>
       <c r="E169" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="15">
@@ -4614,7 +4611,7 @@
         <v>6</v>
       </c>
       <c r="E170" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="15">
@@ -4631,7 +4628,7 @@
         <v>42</v>
       </c>
       <c r="E171" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="15">
@@ -4648,7 +4645,7 @@
         <v>3</v>
       </c>
       <c r="E172" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="15">
@@ -4665,7 +4662,7 @@
         <v>42</v>
       </c>
       <c r="E173" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="15">
@@ -4682,7 +4679,7 @@
         <v>6</v>
       </c>
       <c r="E174" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="15">
@@ -4699,7 +4696,7 @@
         <v>42</v>
       </c>
       <c r="E175" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="15">
@@ -4716,7 +4713,7 @@
         <v>6</v>
       </c>
       <c r="E176" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="15">
@@ -4733,7 +4730,7 @@
         <v>6</v>
       </c>
       <c r="E177" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="15">
@@ -4750,7 +4747,7 @@
         <v>42</v>
       </c>
       <c r="E178" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="15">
@@ -4767,7 +4764,7 @@
         <v>6</v>
       </c>
       <c r="E179" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="15">
@@ -4784,7 +4781,7 @@
         <v>6</v>
       </c>
       <c r="E180" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="15">
@@ -4801,7 +4798,7 @@
         <v>6</v>
       </c>
       <c r="E181" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="15">
@@ -4818,7 +4815,7 @@
         <v>6</v>
       </c>
       <c r="E182" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="15">
@@ -4835,7 +4832,7 @@
         <v>6</v>
       </c>
       <c r="E183" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="15">
@@ -4852,7 +4849,7 @@
         <v>6</v>
       </c>
       <c r="E184" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4869,7 +4866,7 @@
         <v>6</v>
       </c>
       <c r="E185" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="15">
@@ -4886,7 +4883,7 @@
         <v>3</v>
       </c>
       <c r="E186" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="15">
@@ -4903,7 +4900,7 @@
         <v>6</v>
       </c>
       <c r="E187" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="15">
@@ -4920,7 +4917,7 @@
         <v>6</v>
       </c>
       <c r="E188" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="15">
@@ -4937,7 +4934,7 @@
         <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="15">
@@ -4954,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="E190" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="15">
@@ -4971,7 +4968,7 @@
         <v>3</v>
       </c>
       <c r="E191" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="15">
@@ -4988,7 +4985,7 @@
         <v>6</v>
       </c>
       <c r="E192" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="15">
@@ -5005,7 +5002,7 @@
         <v>6</v>
       </c>
       <c r="E193" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="15">
@@ -5022,7 +5019,7 @@
         <v>6</v>
       </c>
       <c r="E194" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="15">
@@ -5039,7 +5036,7 @@
         <v>6</v>
       </c>
       <c r="E195" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="15">
@@ -5056,7 +5053,7 @@
         <v>6</v>
       </c>
       <c r="E196" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="15">
@@ -5073,7 +5070,7 @@
         <v>6</v>
       </c>
       <c r="E197" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="15">
@@ -5090,7 +5087,7 @@
         <v>6</v>
       </c>
       <c r="E198" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="15">
@@ -5107,7 +5104,7 @@
         <v>6</v>
       </c>
       <c r="E199" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="15">
@@ -5124,7 +5121,7 @@
         <v>6</v>
       </c>
       <c r="E200" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="15">
@@ -5141,7 +5138,7 @@
         <v>6</v>
       </c>
       <c r="E201" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="15">
@@ -5158,7 +5155,7 @@
         <v>6</v>
       </c>
       <c r="E202" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="15">
@@ -5175,7 +5172,7 @@
         <v>42</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="15">
@@ -5192,7 +5189,7 @@
         <v>42</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -5209,7 +5206,7 @@
         <v>3</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="15">
@@ -5226,7 +5223,7 @@
         <v>42</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="15">
@@ -5243,7 +5240,7 @@
         <v>6</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="208" spans="1:5" ht="15">
@@ -5260,7 +5257,7 @@
         <v>3</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="15">
@@ -5277,7 +5274,7 @@
         <v>6</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="210" spans="1:5" ht="15">
@@ -5294,7 +5291,7 @@
         <v>42</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="15">
@@ -5311,7 +5308,7 @@
         <v>6</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="212" spans="1:5" ht="15">
@@ -5328,7 +5325,7 @@
         <v>6</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -5345,7 +5342,7 @@
         <v>6</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="214" spans="1:5" ht="15">
@@ -5362,7 +5359,7 @@
         <v>42</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="15">
@@ -5379,7 +5376,7 @@
         <v>6</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="216" spans="1:5" ht="15">
@@ -5396,7 +5393,7 @@
         <v>42</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="15">
@@ -5413,7 +5410,7 @@
         <v>6</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="15">
@@ -5430,7 +5427,7 @@
         <v>6</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="15">
@@ -5447,7 +5444,7 @@
         <v>6</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="220" spans="1:5" ht="15">
@@ -5464,7 +5461,7 @@
         <v>42</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="221" spans="1:5" ht="15">
@@ -5481,7 +5478,7 @@
         <v>6</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="222" spans="1:5" ht="15">
@@ -5498,7 +5495,7 @@
         <v>3</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="223" spans="1:5" ht="15">
@@ -5515,7 +5512,7 @@
         <v>6</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="224" spans="1:5" ht="15">
@@ -5532,7 +5529,7 @@
         <v>6</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="225" spans="1:5" ht="15">
@@ -5549,7 +5546,7 @@
         <v>6</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="15">
@@ -5566,7 +5563,7 @@
         <v>6</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="227" spans="1:5" ht="15">
@@ -5583,7 +5580,7 @@
         <v>6</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="228" spans="1:5" ht="15">
@@ -5600,7 +5597,7 @@
         <v>6</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="229" spans="1:5" ht="15">
@@ -5617,7 +5614,7 @@
         <v>6</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="230" spans="1:5" ht="15">
@@ -5634,7 +5631,7 @@
         <v>6</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="15">
@@ -5651,7 +5648,7 @@
         <v>6</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="15">
@@ -5668,7 +5665,7 @@
         <v>3</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="233" spans="1:5" ht="15">
@@ -5685,7 +5682,7 @@
         <v>3</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="234" spans="1:5" ht="15">
@@ -5702,7 +5699,7 @@
         <v>3</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="235" spans="1:5" ht="15">
@@ -5719,7 +5716,7 @@
         <v>6</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="236" spans="1:5" ht="15">
@@ -5736,7 +5733,7 @@
         <v>3</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="237" spans="1:5" ht="15">
@@ -5753,7 +5750,7 @@
         <v>6</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="238" spans="1:5" ht="15">
@@ -5770,7 +5767,7 @@
         <v>6</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="15">
@@ -5787,7 +5784,7 @@
         <v>6</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="240" spans="1:5" ht="15">
@@ -5804,7 +5801,7 @@
         <v>42</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="241" spans="1:5" ht="15">
@@ -5821,7 +5818,7 @@
         <v>6</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="242" spans="1:5" ht="15">
@@ -5838,7 +5835,7 @@
         <v>6</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="15">
@@ -5855,7 +5852,7 @@
         <v>3</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="244" spans="1:5" ht="15">
@@ -5872,7 +5869,7 @@
         <v>3</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="245" spans="1:5" ht="15">
@@ -5889,7 +5886,7 @@
         <v>3</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -5906,7 +5903,7 @@
         <v>6</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="247" spans="1:5" ht="15">
@@ -5923,7 +5920,7 @@
         <v>6</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="248" spans="1:5" ht="15">
@@ -5940,7 +5937,7 @@
         <v>6</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="249" spans="1:5" ht="15">
@@ -5957,7 +5954,7 @@
         <v>6</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="250" spans="1:5" ht="15">
@@ -5974,7 +5971,7 @@
         <v>6</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="251" spans="1:5" ht="15">
@@ -5991,7 +5988,7 @@
         <v>6</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="252" spans="1:5" ht="15">
@@ -6008,7 +6005,7 @@
         <v>6</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="253" spans="1:5" ht="15">
@@ -6025,7 +6022,7 @@
         <v>3</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="254" spans="1:5" ht="15">
@@ -6042,7 +6039,7 @@
         <v>6</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="255" spans="1:5" ht="15">
@@ -6059,7 +6056,7 @@
         <v>6</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="256" spans="1:5" ht="15">
@@ -6076,7 +6073,7 @@
         <v>6</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="257" spans="1:5" ht="15">
@@ -6093,7 +6090,7 @@
         <v>6</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="258" spans="1:5" ht="15">
@@ -6110,7 +6107,7 @@
         <v>6</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="259" spans="1:5" ht="15">
@@ -6127,7 +6124,7 @@
         <v>6</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="260" spans="1:5" ht="15">
@@ -6144,7 +6141,7 @@
         <v>3</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="261" spans="1:5" ht="15">
@@ -6161,7 +6158,7 @@
         <v>6</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="262" spans="1:5" ht="15">
@@ -6178,7 +6175,7 @@
         <v>6</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="263" spans="1:5" ht="15">
@@ -6195,7 +6192,7 @@
         <v>6</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="264" spans="1:5" ht="15">
@@ -6212,7 +6209,7 @@
         <v>6</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="265" spans="1:5" ht="15">
@@ -6229,7 +6226,7 @@
         <v>3</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="266" spans="1:5" ht="15">
@@ -6246,7 +6243,7 @@
         <v>3</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="267" spans="1:5" ht="15">
@@ -6263,7 +6260,7 @@
         <v>6</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="268" spans="1:5" ht="15">
@@ -6280,7 +6277,7 @@
         <v>6</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="269" spans="1:5" ht="15">
@@ -6297,7 +6294,7 @@
         <v>6</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="270" spans="1:5" ht="15">
@@ -6314,7 +6311,7 @@
         <v>6</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="271" spans="1:5" ht="15">
@@ -6331,7 +6328,7 @@
         <v>42</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="272" spans="1:5" ht="15">
@@ -6348,7 +6345,7 @@
         <v>3</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="273" spans="1:5" ht="15">
@@ -6365,7 +6362,7 @@
         <v>3</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="274" spans="1:5" ht="15">
@@ -6382,7 +6379,7 @@
         <v>6</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="275" spans="1:5" ht="15">
@@ -6399,7 +6396,7 @@
         <v>6</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="276" spans="1:5" ht="15">
@@ -6416,7 +6413,7 @@
         <v>6</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="277" spans="1:5" ht="15">
@@ -6433,7 +6430,7 @@
         <v>6</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="278" spans="1:5" ht="15">
@@ -6450,7 +6447,7 @@
         <v>6</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -6467,7 +6464,7 @@
         <v>6</v>
       </c>
       <c r="E279" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -6484,7 +6481,7 @@
         <v>6</v>
       </c>
       <c r="E280" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="281" spans="1:5" ht="15">
@@ -6501,7 +6498,7 @@
         <v>6</v>
       </c>
       <c r="E281" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="282" spans="1:5" ht="15">
@@ -6518,7 +6515,7 @@
         <v>3</v>
       </c>
       <c r="E282" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="283" spans="1:5" ht="15">
@@ -6535,7 +6532,7 @@
         <v>6</v>
       </c>
       <c r="E283" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="284" spans="1:5" ht="15">
@@ -6552,7 +6549,7 @@
         <v>3</v>
       </c>
       <c r="E284" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="285" spans="1:5" ht="15">
@@ -6569,7 +6566,7 @@
         <v>6</v>
       </c>
       <c r="E285" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="286" spans="1:5" ht="15">
@@ -6586,7 +6583,7 @@
         <v>3</v>
       </c>
       <c r="E286" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="287" spans="1:5" ht="15">
@@ -6603,7 +6600,7 @@
         <v>3</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="288" spans="1:5" ht="15">
@@ -6620,7 +6617,7 @@
         <v>3</v>
       </c>
       <c r="E288" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="289" spans="1:5" ht="15">
@@ -6637,7 +6634,7 @@
         <v>3</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="290" spans="1:5" ht="15">
@@ -6654,7 +6651,7 @@
         <v>6</v>
       </c>
       <c r="E290" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="291" spans="1:5" ht="15">
@@ -6671,7 +6668,7 @@
         <v>6</v>
       </c>
       <c r="E291" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="292" spans="1:5" ht="15">
@@ -6688,7 +6685,7 @@
         <v>3</v>
       </c>
       <c r="E292" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="293" spans="1:5" ht="15">
@@ -6705,7 +6702,7 @@
         <v>3</v>
       </c>
       <c r="E293" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="294" spans="1:5" ht="15">
@@ -6722,7 +6719,7 @@
         <v>3</v>
       </c>
       <c r="E294" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="295" spans="1:5" ht="15">
@@ -6739,7 +6736,7 @@
         <v>6</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="296" spans="1:5" ht="15">
@@ -6756,7 +6753,7 @@
         <v>3</v>
       </c>
       <c r="E296" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="297" spans="1:5" ht="15">
@@ -6773,7 +6770,7 @@
         <v>6</v>
       </c>
       <c r="E297" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="298" spans="1:5" ht="15">
@@ -6790,7 +6787,7 @@
         <v>6</v>
       </c>
       <c r="E298" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="299" spans="1:5" ht="15">
@@ -6807,7 +6804,7 @@
         <v>6</v>
       </c>
       <c r="E299" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="300" spans="1:5" ht="15">
@@ -6824,7 +6821,7 @@
         <v>6</v>
       </c>
       <c r="E300" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="301" spans="1:5" ht="15">
@@ -6841,7 +6838,7 @@
         <v>6</v>
       </c>
       <c r="E301" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="302" spans="1:5" ht="15">
@@ -6858,7 +6855,7 @@
         <v>3</v>
       </c>
       <c r="E302" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="303" spans="1:5" ht="15">
@@ -6875,7 +6872,7 @@
         <v>6</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="304" spans="1:5" ht="15">
@@ -6892,7 +6889,7 @@
         <v>6</v>
       </c>
       <c r="E304" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="305" spans="1:5" ht="15">
@@ -6909,7 +6906,7 @@
         <v>3</v>
       </c>
       <c r="E305" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="306" spans="1:5" ht="15">
@@ -6926,7 +6923,7 @@
         <v>6</v>
       </c>
       <c r="E306" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="307" spans="1:5" ht="15">
@@ -6943,7 +6940,7 @@
         <v>6</v>
       </c>
       <c r="E307" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="308" spans="1:5" ht="15">
@@ -6960,7 +6957,7 @@
         <v>6</v>
       </c>
       <c r="E308" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="309" spans="1:5" ht="15">
@@ -6977,7 +6974,7 @@
         <v>6</v>
       </c>
       <c r="E309" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="310" spans="1:5" ht="15">
@@ -6994,7 +6991,7 @@
         <v>3</v>
       </c>
       <c r="E310" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="311" spans="1:5" ht="15">
@@ -7011,7 +7008,7 @@
         <v>3</v>
       </c>
       <c r="E311" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="312" spans="1:5" ht="15">
@@ -7028,7 +7025,7 @@
         <v>6</v>
       </c>
       <c r="E312" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="313" spans="1:5" ht="15">
@@ -7045,7 +7042,7 @@
         <v>6</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="314" spans="1:5" ht="15">
@@ -7062,7 +7059,7 @@
         <v>6</v>
       </c>
       <c r="E314" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="315" spans="1:5" ht="15">
@@ -7079,7 +7076,7 @@
         <v>6</v>
       </c>
       <c r="E315" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="316" spans="1:5" ht="15">
@@ -7096,7 +7093,7 @@
         <v>6</v>
       </c>
       <c r="E316" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="317" spans="1:5" ht="15">
@@ -7113,7 +7110,7 @@
         <v>6</v>
       </c>
       <c r="E317" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="318" spans="1:5" ht="15">
@@ -7130,7 +7127,7 @@
         <v>6</v>
       </c>
       <c r="E318" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="319" spans="1:5" ht="15">
@@ -7147,7 +7144,7 @@
         <v>3</v>
       </c>
       <c r="E319" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="320" spans="1:5" ht="15">
@@ -7164,7 +7161,7 @@
         <v>6</v>
       </c>
       <c r="E320" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="321" spans="1:5" ht="15">
@@ -7181,7 +7178,7 @@
         <v>6</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="322" spans="1:5" ht="15">
@@ -7198,7 +7195,7 @@
         <v>6</v>
       </c>
       <c r="E322" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="323" spans="1:5" ht="15">
@@ -7215,7 +7212,7 @@
         <v>6</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="324" spans="1:5" ht="15">
@@ -7232,7 +7229,7 @@
         <v>3</v>
       </c>
       <c r="E324" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="325" spans="1:5" ht="15">
@@ -7249,7 +7246,7 @@
         <v>3</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="326" spans="1:5" ht="15">
@@ -7266,7 +7263,7 @@
         <v>6</v>
       </c>
       <c r="E326" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="327" spans="1:5" ht="15">
@@ -7283,7 +7280,7 @@
         <v>6</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="328" spans="1:5" ht="15">
@@ -7300,7 +7297,7 @@
         <v>6</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="329" spans="1:5" ht="15">
@@ -7317,7 +7314,7 @@
         <v>6</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="330" spans="1:5" ht="15">
@@ -7334,7 +7331,7 @@
         <v>42</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="331" spans="1:5" ht="15">
@@ -7351,7 +7348,7 @@
         <v>6</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="332" spans="1:5" ht="15">
@@ -7368,7 +7365,7 @@
         <v>42</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="333" spans="1:5" ht="15">
@@ -7385,7 +7382,7 @@
         <v>42</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="334" spans="1:5" ht="15">
@@ -7402,7 +7399,7 @@
         <v>6</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="335" spans="1:5" ht="15">
@@ -7419,7 +7416,7 @@
         <v>6</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="336" spans="1:5" ht="15">
@@ -7436,7 +7433,7 @@
         <v>3</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="337" spans="1:5" ht="15">
@@ -7453,7 +7450,7 @@
         <v>6</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="338" spans="1:5" ht="15">
@@ -7470,7 +7467,7 @@
         <v>6</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="339" spans="1:5" ht="15">
@@ -7487,7 +7484,7 @@
         <v>42</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="340" spans="1:5" ht="15">
@@ -7504,7 +7501,7 @@
         <v>192</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="341" spans="1:5" ht="15">
@@ -7521,7 +7518,7 @@
         <v>6</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="342" spans="1:5" ht="15">
@@ -7538,7 +7535,7 @@
         <v>42</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="343" spans="1:5" ht="15">
@@ -7555,7 +7552,7 @@
         <v>6</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="344" spans="1:5" ht="15">
@@ -7572,7 +7569,7 @@
         <v>6</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="345" spans="1:5" ht="15">
@@ -7589,7 +7586,7 @@
         <v>6</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="346" spans="1:5" ht="15">
@@ -7606,7 +7603,7 @@
         <v>3</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="347" spans="1:5" ht="15">
@@ -7623,7 +7620,7 @@
         <v>6</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="348" spans="1:5" ht="15">
@@ -7640,7 +7637,7 @@
         <v>6</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="349" spans="1:5" ht="15">
@@ -7657,7 +7654,7 @@
         <v>3</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="350" spans="1:5" ht="15">
@@ -7674,7 +7671,7 @@
         <v>3</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="351" spans="1:5" ht="15">
@@ -7691,7 +7688,7 @@
         <v>6</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="352" spans="1:5" ht="15">
@@ -7708,7 +7705,7 @@
         <v>31</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="353" spans="1:5" ht="15">
@@ -7725,7 +7722,7 @@
         <v>6</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="354" spans="1:5" ht="15">
@@ -7742,7 +7739,7 @@
         <v>3</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="355" spans="1:5" ht="15">
@@ -7759,7 +7756,7 @@
         <v>3</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="356" spans="1:5" ht="15">
@@ -7776,7 +7773,7 @@
         <v>3</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="357" spans="1:5" ht="15">
@@ -7793,7 +7790,7 @@
         <v>6</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="358" spans="1:5" ht="15">
@@ -7810,7 +7807,7 @@
         <v>6</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="359" spans="1:5" ht="15">
@@ -7827,7 +7824,7 @@
         <v>6</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="360" spans="1:5" ht="15">
@@ -7844,7 +7841,7 @@
         <v>192</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="361" spans="1:5" ht="15">
@@ -7861,7 +7858,7 @@
         <v>3</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="362" spans="1:5" ht="15">
@@ -7878,7 +7875,7 @@
         <v>3</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="363" spans="1:5" ht="15">
@@ -7895,7 +7892,7 @@
         <v>42</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="364" spans="1:5" ht="15">
@@ -7912,7 +7909,7 @@
         <v>6</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="365" spans="1:5" ht="15">
@@ -7929,7 +7926,7 @@
         <v>31</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="366" spans="1:5" ht="15">
@@ -7946,7 +7943,7 @@
         <v>6</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="367" spans="1:5" ht="15">
@@ -7963,7 +7960,7 @@
         <v>42</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="368" spans="1:5" ht="15">
@@ -7980,7 +7977,7 @@
         <v>192</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="369" spans="1:5" ht="15">
@@ -7997,7 +7994,7 @@
         <v>39</v>
       </c>
       <c r="E369" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="370" spans="1:5" ht="15">
@@ -8014,7 +8011,7 @@
         <v>6</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="371" spans="1:5" ht="15">
@@ -8031,7 +8028,7 @@
         <v>6</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="372" spans="1:5" ht="15">
@@ -8048,7 +8045,7 @@
         <v>6</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="373" spans="1:5" ht="15">
@@ -8065,7 +8062,7 @@
         <v>42</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="374" spans="1:5" ht="15">
@@ -8082,7 +8079,7 @@
         <v>6</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="375" spans="1:5" ht="15">
@@ -8099,7 +8096,7 @@
         <v>6</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="376" spans="1:5" ht="15">
@@ -8116,7 +8113,7 @@
         <v>6</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="377" spans="1:5" ht="15">
@@ -8133,7 +8130,7 @@
         <v>6</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="378" spans="1:5" ht="15">
@@ -8150,7 +8147,7 @@
         <v>6</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="379" spans="1:5" ht="15">
@@ -8167,7 +8164,7 @@
         <v>6</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="380" spans="1:5" ht="15">
@@ -8184,7 +8181,7 @@
         <v>3</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="381" spans="1:5" ht="15">
@@ -8201,7 +8198,7 @@
         <v>6</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="382" spans="1:5" ht="15">
@@ -8218,7 +8215,7 @@
         <v>3</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="383" spans="1:5" ht="15">
@@ -8235,7 +8232,7 @@
         <v>6</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="384" spans="1:5" ht="15">
@@ -8252,7 +8249,7 @@
         <v>6</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="385" spans="1:5" ht="15">
@@ -8269,7 +8266,7 @@
         <v>6</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="386" spans="1:5" ht="15">
@@ -8286,7 +8283,7 @@
         <v>6</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="387" spans="1:5" ht="15">
@@ -8303,7 +8300,7 @@
         <v>6</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="388" spans="1:5" ht="15">
@@ -8320,7 +8317,7 @@
         <v>3</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="389" spans="1:5" ht="15">
@@ -8337,7 +8334,7 @@
         <v>42</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="390" spans="1:5" ht="15">
@@ -8354,7 +8351,7 @@
         <v>6</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="391" spans="1:5" ht="15">
@@ -8371,7 +8368,7 @@
         <v>3</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="392" spans="1:5" ht="15">
@@ -8388,7 +8385,7 @@
         <v>3</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="393" spans="1:5" ht="15">
@@ -8405,7 +8402,7 @@
         <v>3</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="394" spans="1:5" ht="15">
@@ -8422,7 +8419,7 @@
         <v>6</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="395" spans="1:5" ht="15">
@@ -8439,7 +8436,7 @@
         <v>3</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="396" spans="1:5" ht="15">
@@ -8456,7 +8453,7 @@
         <v>3</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="397" spans="1:5" ht="15">
@@ -8473,7 +8470,7 @@
         <v>3</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="398" spans="1:5" ht="15">
@@ -8490,7 +8487,7 @@
         <v>3</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="399" spans="1:5" ht="15">
@@ -8507,7 +8504,7 @@
         <v>6</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="400" spans="1:5" ht="15">
@@ -8524,7 +8521,7 @@
         <v>3</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="401" spans="1:5" ht="15">
@@ -8541,7 +8538,7 @@
         <v>42</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="402" spans="1:5" ht="15">
@@ -8558,7 +8555,7 @@
         <v>3</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="403" spans="1:5" ht="15">
@@ -8575,7 +8572,7 @@
         <v>3</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="404" spans="1:5" ht="15">
@@ -8592,7 +8589,7 @@
         <v>6</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="405" spans="1:5" ht="15">
@@ -8609,7 +8606,7 @@
         <v>3</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="406" spans="1:5" ht="15">
@@ -8626,7 +8623,7 @@
         <v>3</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="407" spans="1:5" ht="15">
@@ -8643,7 +8640,7 @@
         <v>3</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="408" spans="1:5" ht="15">
@@ -8660,7 +8657,7 @@
         <v>3</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="409" spans="1:5" ht="15">
@@ -8677,7 +8674,7 @@
         <v>3</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="410" spans="1:5" ht="15">
@@ -8694,7 +8691,7 @@
         <v>3</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="411" spans="1:5" ht="15">
@@ -8711,7 +8708,7 @@
         <v>3</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="412" spans="1:5" ht="15">
@@ -8728,7 +8725,7 @@
         <v>3</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="413" spans="1:5" ht="15">
@@ -8745,7 +8742,7 @@
         <v>3</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="414" spans="1:5" ht="15">
@@ -8762,7 +8759,7 @@
         <v>6</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="415" spans="1:5" ht="15">
@@ -8779,7 +8776,7 @@
         <v>6</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="416" spans="1:5" ht="15">
@@ -8796,7 +8793,7 @@
         <v>3</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="417" spans="1:5" ht="15">
@@ -8813,7 +8810,7 @@
         <v>3</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="418" spans="1:5" ht="15">
@@ -8830,7 +8827,7 @@
         <v>3</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="419" spans="1:5" ht="15">
@@ -8847,7 +8844,7 @@
         <v>3</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="420" spans="1:5" ht="15">
@@ -8864,7 +8861,7 @@
         <v>3</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="421" spans="1:5" ht="15">
@@ -8881,7 +8878,7 @@
         <v>3</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="422" spans="1:5" ht="15">
@@ -8898,7 +8895,7 @@
         <v>6</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="423" spans="1:5" ht="15">
@@ -8915,7 +8912,7 @@
         <v>3</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="424" spans="1:5" ht="15">
@@ -8932,7 +8929,7 @@
         <v>3</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="425" spans="1:5" ht="15">
@@ -8949,7 +8946,7 @@
         <v>3</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="426" spans="1:5" ht="15">
@@ -8966,7 +8963,7 @@
         <v>6</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="427" spans="1:5" ht="15">
@@ -8983,7 +8980,7 @@
         <v>3</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="428" spans="1:5" ht="15">
@@ -9000,7 +8997,7 @@
         <v>3</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="429" spans="1:5" ht="15">
@@ -9017,7 +9014,7 @@
         <v>6</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="430" spans="1:5" ht="15">
@@ -9034,7 +9031,7 @@
         <v>6</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="431" spans="1:5" ht="15">
@@ -9051,7 +9048,7 @@
         <v>3</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="432" spans="1:5" ht="15">
@@ -9068,7 +9065,7 @@
         <v>3</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="433" spans="1:5" ht="15">
@@ -9085,7 +9082,7 @@
         <v>6</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="434" spans="1:5" ht="15">
@@ -9102,7 +9099,7 @@
         <v>3</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="435" spans="1:5" ht="15">
@@ -9119,7 +9116,7 @@
         <v>6</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="436" spans="1:5" ht="15">
@@ -9136,7 +9133,7 @@
         <v>3</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="437" spans="1:5" ht="15">
@@ -9153,7 +9150,7 @@
         <v>6</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="438" spans="1:5" ht="15">
@@ -9170,7 +9167,7 @@
         <v>6</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="439" spans="1:5" ht="15">
@@ -9187,7 +9184,7 @@
         <v>6</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="440" spans="1:5" ht="15">
@@ -9204,7 +9201,7 @@
         <v>42</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="441" spans="1:5" ht="15">
@@ -9221,7 +9218,7 @@
         <v>6</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="442" spans="1:5" ht="15">
@@ -9238,7 +9235,7 @@
         <v>6</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="443" spans="1:5" ht="15">
@@ -9255,7 +9252,7 @@
         <v>3</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="444" spans="1:5" ht="15">
@@ -9272,7 +9269,7 @@
         <v>3</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="445" spans="1:5" ht="15">
@@ -9289,7 +9286,7 @@
         <v>3</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="446" spans="1:5" ht="15">
@@ -9306,7 +9303,7 @@
         <v>3</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="447" spans="1:5" ht="15">
@@ -9323,7 +9320,7 @@
         <v>3</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="448" spans="1:5" ht="15">
@@ -9340,7 +9337,7 @@
         <v>3</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="449" spans="1:5" ht="15">
@@ -9357,7 +9354,7 @@
         <v>3</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="450" spans="1:5" ht="15">
@@ -9374,7 +9371,7 @@
         <v>3</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="451" spans="1:5" ht="15">
@@ -9391,7 +9388,7 @@
         <v>3</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="452" spans="1:5" ht="15">
@@ -9408,7 +9405,7 @@
         <v>6</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="453" spans="1:5" ht="15">
@@ -9425,7 +9422,7 @@
         <v>3</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="454" spans="1:5" ht="15">
@@ -9442,7 +9439,7 @@
         <v>3</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="455" spans="1:5" ht="15">
@@ -9459,7 +9456,7 @@
         <v>3</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="456" spans="1:5" ht="15">
@@ -9476,7 +9473,7 @@
         <v>6</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="457" spans="1:5" ht="15">
@@ -9493,7 +9490,7 @@
         <v>3</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="458" spans="1:5" ht="15">
@@ -9510,7 +9507,7 @@
         <v>3</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="459" spans="1:5" ht="15">
@@ -9527,7 +9524,7 @@
         <v>6</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="460" spans="1:5" ht="15">
@@ -9544,7 +9541,7 @@
         <v>3</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="461" spans="1:5" ht="15">
@@ -9561,7 +9558,7 @@
         <v>3</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="462" spans="1:5" ht="15">
@@ -9578,7 +9575,7 @@
         <v>6</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="463" spans="1:5" ht="15">
@@ -9595,7 +9592,7 @@
         <v>6</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="464" spans="1:5" ht="15">
@@ -9612,7 +9609,7 @@
         <v>3</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="465" spans="1:5" ht="15">
@@ -9629,7 +9626,7 @@
         <v>3</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="466" spans="1:5" ht="15">
@@ -9646,7 +9643,7 @@
         <v>3</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="467" spans="1:5" ht="15">
@@ -9663,7 +9660,7 @@
         <v>3</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="468" spans="1:5" ht="15">
@@ -9680,7 +9677,7 @@
         <v>3</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="469" spans="1:5" ht="15">
@@ -9697,7 +9694,7 @@
         <v>3</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="470" spans="1:5" ht="15">
@@ -9714,7 +9711,7 @@
         <v>3</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="471" spans="1:5" ht="15">
@@ -9731,7 +9728,7 @@
         <v>3</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="472" spans="1:5" ht="15">
@@ -9748,7 +9745,7 @@
         <v>6</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="473" spans="1:5" ht="15">
@@ -9765,7 +9762,7 @@
         <v>6</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="474" spans="1:5" ht="15">
@@ -9782,7 +9779,7 @@
         <v>3</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="475" spans="1:5" ht="15">
@@ -9799,7 +9796,7 @@
         <v>3</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="476" spans="1:5" ht="15">
@@ -9816,7 +9813,7 @@
         <v>3</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="477" spans="1:5" ht="15">
@@ -9833,7 +9830,7 @@
         <v>3</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="478" spans="1:5" ht="15">
@@ -9850,7 +9847,7 @@
         <v>3</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="479" spans="1:5" ht="15">
@@ -9867,7 +9864,7 @@
         <v>3</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="480" spans="1:5" ht="15">
@@ -9884,7 +9881,7 @@
         <v>3</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="481" spans="1:5" ht="15">
@@ -9901,7 +9898,7 @@
         <v>3</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="482" spans="1:5" ht="15">
@@ -9918,7 +9915,7 @@
         <v>3</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="483" spans="1:5" ht="15">
@@ -9935,7 +9932,7 @@
         <v>3</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="484" spans="1:5" ht="15">
@@ -9952,7 +9949,7 @@
         <v>3</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="485" spans="1:5" ht="15">
@@ -9969,7 +9966,7 @@
         <v>3</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="486" spans="1:5" ht="15">
@@ -9986,7 +9983,7 @@
         <v>3</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="487" spans="1:5" ht="15">
@@ -10003,7 +10000,7 @@
         <v>3</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="488" spans="1:5" ht="15">
@@ -10020,7 +10017,7 @@
         <v>3</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="489" spans="1:5" ht="15">
@@ -10037,7 +10034,7 @@
         <v>3</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="490" spans="1:5" ht="15">
@@ -10054,7 +10051,7 @@
         <v>3</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="491" spans="1:5" ht="15">
@@ -10071,7 +10068,7 @@
         <v>3</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="492" spans="1:5" ht="15">
@@ -10088,7 +10085,7 @@
         <v>3</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="493" spans="1:5" ht="15">
@@ -10105,7 +10102,7 @@
         <v>6</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="494" spans="1:5" ht="15">
@@ -10122,7 +10119,7 @@
         <v>6</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="495" spans="1:5" ht="15">
@@ -10139,7 +10136,7 @@
         <v>3</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="496" spans="1:5" ht="15">
@@ -10156,7 +10153,7 @@
         <v>6</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="497" spans="1:5" ht="15">
@@ -10173,7 +10170,7 @@
         <v>3</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="498" spans="1:5" ht="15">
@@ -10190,7 +10187,7 @@
         <v>3</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="499" spans="1:5" ht="15">
@@ -10207,7 +10204,7 @@
         <v>3</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="500" spans="1:5" ht="15">
@@ -10224,7 +10221,7 @@
         <v>3</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="501" spans="1:5" ht="15">
@@ -10241,7 +10238,7 @@
         <v>3</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="502" spans="1:5" ht="15">
@@ -10258,7 +10255,7 @@
         <v>3</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="503" spans="1:5" ht="15">
@@ -10275,7 +10272,7 @@
         <v>6</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="504" spans="1:5" ht="15">
@@ -10292,7 +10289,7 @@
         <v>3</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="505" spans="1:5" ht="15">
@@ -10309,7 +10306,7 @@
         <v>6</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="506" spans="1:5" ht="15">
@@ -10326,7 +10323,7 @@
         <v>6</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="507" spans="1:5" ht="15">
@@ -10343,7 +10340,7 @@
         <v>3</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="508" spans="1:5" ht="15">
@@ -10360,7 +10357,7 @@
         <v>6</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="509" spans="1:5" ht="15">
@@ -10377,7 +10374,7 @@
         <v>6</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="510" spans="1:5" ht="15">
@@ -10394,7 +10391,7 @@
         <v>6</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="511" spans="1:5" ht="15">
@@ -10411,7 +10408,7 @@
         <v>6</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="512" spans="1:5" ht="15">
@@ -10428,7 +10425,7 @@
         <v>6</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="513" spans="1:5" ht="15">
@@ -10445,7 +10442,7 @@
         <v>31</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="514" spans="1:5" ht="15">
@@ -10462,7 +10459,7 @@
         <v>3</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="515" spans="1:5" ht="15">
@@ -10479,7 +10476,7 @@
         <v>42</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="516" spans="1:5" ht="15">
@@ -10496,7 +10493,7 @@
         <v>42</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="517" spans="1:5" ht="15">
@@ -10513,7 +10510,7 @@
         <v>6</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="518" spans="1:5" ht="15">
@@ -10530,7 +10527,7 @@
         <v>192</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="519" spans="1:5" ht="15">
@@ -10547,7 +10544,7 @@
         <v>42</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="520" spans="1:5" ht="15">
@@ -10564,7 +10561,7 @@
         <v>6</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="521" spans="1:5" ht="15">
@@ -10581,7 +10578,7 @@
         <v>3</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="522" spans="1:5" ht="15">
@@ -10598,7 +10595,7 @@
         <v>42</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="523" spans="1:5" ht="15">
@@ -10615,7 +10612,7 @@
         <v>42</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="524" spans="1:5" ht="15">
@@ -10632,7 +10629,7 @@
         <v>6</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="525" spans="1:5" ht="15">
@@ -10649,7 +10646,7 @@
         <v>192</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="526" spans="1:5" ht="15">
@@ -10666,7 +10663,7 @@
         <v>31</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="527" spans="1:5" ht="15">
@@ -10683,7 +10680,7 @@
         <v>42</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="528" spans="1:5" ht="15">
@@ -10700,7 +10697,7 @@
         <v>42</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="529" spans="1:5" ht="15">
@@ -10717,7 +10714,7 @@
         <v>42</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="530" spans="1:5" ht="15">
@@ -10734,7 +10731,7 @@
         <v>6</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="531" spans="1:5" ht="15">
@@ -10751,7 +10748,7 @@
         <v>6</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="532" spans="1:5" ht="15">
@@ -10768,7 +10765,7 @@
         <v>6</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="533" spans="1:5" ht="15">
@@ -10785,7 +10782,7 @@
         <v>6</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="534" spans="1:5" ht="15">
@@ -10802,7 +10799,7 @@
         <v>6</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="535" spans="1:5" ht="15">
@@ -10819,7 +10816,7 @@
         <v>6</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="536" spans="1:5" ht="15">
@@ -10836,7 +10833,7 @@
         <v>6</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="537" spans="1:5" ht="15">
@@ -10853,7 +10850,7 @@
         <v>3</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="538" spans="1:5" ht="15">
@@ -10870,7 +10867,7 @@
         <v>42</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="539" spans="1:5" ht="15">
@@ -10887,7 +10884,7 @@
         <v>3</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="540" spans="1:5" ht="15">
@@ -10904,7 +10901,7 @@
         <v>6</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="541" spans="1:5" ht="15">
@@ -10921,7 +10918,7 @@
         <v>42</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="542" spans="1:5" ht="15">
@@ -10938,7 +10935,7 @@
         <v>31</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="543" spans="1:5">
@@ -10955,7 +10952,7 @@
         <v>42</v>
       </c>
       <c r="E543" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="544" spans="1:5" ht="15">
@@ -10972,7 +10969,7 @@
         <v>3</v>
       </c>
       <c r="E544" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="545" spans="1:5" ht="15">
@@ -10989,7 +10986,7 @@
         <v>6</v>
       </c>
       <c r="E545" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="546" spans="1:5" ht="15">
@@ -11006,15 +11003,15 @@
         <v>42</v>
       </c>
       <c r="E546" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="547" spans="1:5">
       <c r="A547" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B547" s="6" t="s">
-        <v>362</v>
+      <c r="B547" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="C547" s="3" t="s">
         <v>29</v>
@@ -11023,7 +11020,7 @@
         <v>3</v>
       </c>
       <c r="E547" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="548" spans="1:5" ht="15">
@@ -11040,15 +11037,15 @@
         <v>6</v>
       </c>
       <c r="E548" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="549" spans="1:5" ht="15">
       <c r="A549" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B549" s="6" t="s">
-        <v>362</v>
+      <c r="B549" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="C549" s="3" t="s">
         <v>29</v>
@@ -11057,7 +11054,7 @@
         <v>6</v>
       </c>
       <c r="E549" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="550" spans="1:5" ht="15">
@@ -11074,7 +11071,7 @@
         <v>6</v>
       </c>
       <c r="E550" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="551" spans="1:5">
@@ -11091,7 +11088,7 @@
         <v>3</v>
       </c>
       <c r="E551" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="552" spans="1:5">
@@ -11108,12 +11105,12 @@
         <v>6</v>
       </c>
       <c r="E552" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="553" spans="1:5" ht="15">
       <c r="A553" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B553" s="8" t="s">
         <v>121</v>
@@ -11125,7 +11122,7 @@
         <v>3</v>
       </c>
       <c r="E553" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="554" spans="1:5" ht="15">
@@ -11142,7 +11139,7 @@
         <v>6</v>
       </c>
       <c r="E554" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="555" spans="1:5" ht="15">
@@ -11159,7 +11156,7 @@
         <v>6</v>
       </c>
       <c r="E555" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="556" spans="1:5" ht="15">
@@ -11176,7 +11173,7 @@
         <v>6</v>
       </c>
       <c r="E556" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="557" spans="1:5">
@@ -11193,7 +11190,7 @@
         <v>42</v>
       </c>
       <c r="E557" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="558" spans="1:5" ht="15">
@@ -11210,7 +11207,7 @@
         <v>3</v>
       </c>
       <c r="E558" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="559" spans="1:5" ht="15">
@@ -11227,7 +11224,7 @@
         <v>3</v>
       </c>
       <c r="E559" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="560" spans="1:5" ht="15">
@@ -11244,7 +11241,7 @@
         <v>6</v>
       </c>
       <c r="E560" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="561" spans="1:5" ht="15">
@@ -11261,7 +11258,7 @@
         <v>3</v>
       </c>
       <c r="E561" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="562" spans="1:5" ht="15">
@@ -11278,7 +11275,7 @@
         <v>6</v>
       </c>
       <c r="E562" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="563" spans="1:5" ht="15">
@@ -11295,7 +11292,7 @@
         <v>3</v>
       </c>
       <c r="E563" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="564" spans="1:5">
@@ -11312,12 +11309,12 @@
         <v>31</v>
       </c>
       <c r="E564" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="565" spans="1:5" ht="15">
       <c r="A565" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B565" s="8" t="s">
         <v>121</v>
@@ -11329,7 +11326,7 @@
         <v>6</v>
       </c>
       <c r="E565" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="566" spans="1:5">
@@ -11346,7 +11343,7 @@
         <v>42</v>
       </c>
       <c r="E566" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="567" spans="1:5" ht="15">
@@ -11363,7 +11360,7 @@
         <v>6</v>
       </c>
       <c r="E567" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="568" spans="1:5">
@@ -11380,7 +11377,7 @@
         <v>6</v>
       </c>
       <c r="E568" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -11397,7 +11394,7 @@
         <v>6</v>
       </c>
       <c r="E569" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="570" spans="1:5" ht="15">
@@ -11414,15 +11411,15 @@
         <v>6</v>
       </c>
       <c r="E570" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="571" spans="1:5" ht="15">
       <c r="A571" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B571" s="6" t="s">
-        <v>362</v>
+      <c r="B571" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="C571" s="3" t="s">
         <v>29</v>
@@ -11431,7 +11428,7 @@
         <v>6</v>
       </c>
       <c r="E571" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="572" spans="1:5">
@@ -11448,7 +11445,7 @@
         <v>6</v>
       </c>
       <c r="E572" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="573" spans="1:5">
@@ -11465,7 +11462,7 @@
         <v>6</v>
       </c>
       <c r="E573" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="574" spans="1:5">
@@ -11482,7 +11479,7 @@
         <v>6</v>
       </c>
       <c r="E574" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="575" spans="1:5" ht="15">
@@ -11499,7 +11496,7 @@
         <v>6</v>
       </c>
       <c r="E575" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="576" spans="1:5" ht="15">
@@ -11516,12 +11513,12 @@
         <v>6</v>
       </c>
       <c r="E576" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="577" spans="1:5">
       <c r="A577" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B577" s="8" t="s">
         <v>76</v>
@@ -11533,12 +11530,12 @@
         <v>3</v>
       </c>
       <c r="E577" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="578" spans="1:5">
       <c r="A578" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B578" s="3" t="s">
         <v>28</v>
@@ -11550,7 +11547,7 @@
         <v>6</v>
       </c>
       <c r="E578" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -11567,7 +11564,7 @@
         <v>42</v>
       </c>
       <c r="E579" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="580" spans="1:5">
@@ -11584,7 +11581,7 @@
         <v>6</v>
       </c>
       <c r="E580" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="581" spans="1:5" ht="15">
@@ -11601,7 +11598,7 @@
         <v>6</v>
       </c>
       <c r="E581" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="582" spans="1:5" ht="15">
@@ -11618,15 +11615,15 @@
         <v>192</v>
       </c>
       <c r="E582" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="583" spans="1:5">
       <c r="A583" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B583" s="6" t="s">
-        <v>362</v>
+      <c r="B583" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="C583" s="3" t="s">
         <v>29</v>
@@ -11635,7 +11632,7 @@
         <v>6</v>
       </c>
       <c r="E583" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="584" spans="1:5">
@@ -11652,7 +11649,7 @@
         <v>6</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -11669,7 +11666,7 @@
         <v>6</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="586" spans="1:5">
@@ -11686,7 +11683,7 @@
         <v>6</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -11703,7 +11700,7 @@
         <v>6</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="588" spans="1:5">
@@ -11720,12 +11717,12 @@
         <v>6</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="589" spans="1:5" ht="15">
       <c r="A589" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>105</v>
@@ -11737,12 +11734,12 @@
         <v>3</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="590" spans="1:5" ht="15">
       <c r="A590" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B590" s="1" t="s">
         <v>248</v>
@@ -11754,16 +11751,16 @@
         <v>3</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="591" spans="1:5" ht="15">
       <c r="A591" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B591" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B591" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C591" t="s">
         <v>29</v>
       </c>
@@ -11771,16 +11768,16 @@
         <v>6</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="592" spans="1:5">
       <c r="A592" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B592" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B592" s="2" t="s">
-        <v>382</v>
-      </c>
       <c r="C592" t="s">
         <v>29</v>
       </c>
@@ -11788,7 +11785,7 @@
         <v>3</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="593" spans="1:5" ht="15">
@@ -11805,12 +11802,12 @@
         <v>6</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="594" spans="1:5" ht="15">
       <c r="A594" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>105</v>
@@ -11822,12 +11819,12 @@
         <v>6</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="595" spans="1:5" ht="15">
       <c r="A595" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B595" s="1" t="s">
         <v>248</v>
@@ -11839,7 +11836,7 @@
         <v>6</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="596" spans="1:5" ht="15">
@@ -11856,7 +11853,7 @@
         <v>3</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="597" spans="1:5" ht="15">
@@ -11873,12 +11870,12 @@
         <v>3</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="598" spans="1:5" ht="15">
       <c r="A598" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B598" s="1" t="s">
         <v>58</v>
@@ -11890,12 +11887,12 @@
         <v>6</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="599" spans="1:5" ht="15">
       <c r="A599" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B599" s="1" t="s">
         <v>229</v>
@@ -11907,7 +11904,7 @@
         <v>3</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="600" spans="1:5" ht="15">
@@ -11924,15 +11921,15 @@
         <v>3</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="601" spans="1:5" ht="15">
       <c r="A601" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C601" t="s">
         <v>29</v>
@@ -11941,15 +11938,15 @@
         <v>3</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="602" spans="1:5" ht="15">
       <c r="A602" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C602" t="s">
         <v>29</v>
@@ -11958,15 +11955,15 @@
         <v>3</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="603" spans="1:5" ht="15">
       <c r="A603" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C603" t="s">
         <v>29</v>
@@ -11975,15 +11972,15 @@
         <v>3</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="604" spans="1:5" ht="15">
       <c r="A604" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C604" t="s">
         <v>29</v>
@@ -11992,15 +11989,15 @@
         <v>3</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="605" spans="1:5" ht="15">
       <c r="A605" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C605" t="s">
         <v>29</v>
@@ -12009,15 +12006,15 @@
         <v>6</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="606" spans="1:5" ht="15">
       <c r="A606" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C606" t="s">
         <v>29</v>
@@ -12026,15 +12023,15 @@
         <v>3</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="607" spans="1:5" ht="15">
       <c r="A607" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B607" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C607" t="s">
         <v>29</v>
@@ -12043,15 +12040,15 @@
         <v>3</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="608" spans="1:5" ht="15">
       <c r="A608" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C608" t="s">
         <v>29</v>
@@ -12060,15 +12057,15 @@
         <v>3</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="609" spans="1:5" ht="15">
       <c r="A609" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C609" t="s">
         <v>29</v>
@@ -12077,7 +12074,7 @@
         <v>3</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="610" spans="1:5">
@@ -12094,7 +12091,7 @@
         <v>3</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="611" spans="1:5" ht="15">
@@ -12111,12 +12108,12 @@
         <v>3</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="612" spans="1:5" ht="15">
       <c r="A612" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B612" s="1" t="s">
         <v>354</v>
@@ -12128,12 +12125,12 @@
         <v>6</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="613" spans="1:5" ht="15">
       <c r="A613" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B613" s="1" t="s">
         <v>105</v>
@@ -12145,12 +12142,12 @@
         <v>6</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="614" spans="1:5" ht="15">
       <c r="A614" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B614" s="1" t="s">
         <v>328</v>
@@ -12162,12 +12159,12 @@
         <v>6</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="615" spans="1:5" ht="15">
       <c r="A615" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B615" s="1" t="s">
         <v>328</v>
@@ -12179,7 +12176,7 @@
         <v>6</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="616" spans="1:5" ht="15">
@@ -12196,7 +12193,7 @@
         <v>42</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5488BB17-25B3-4E62-9DB8-FDFA76785C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D880B4B-2866-4D31-8C92-A67F701BF0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3085" uniqueCount="399">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1715,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E616"/>
+  <dimension ref="A1:E617"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -12196,6 +12196,23 @@
         <v>367</v>
       </c>
     </row>
+    <row r="617" spans="1:5" ht="15">
+      <c r="A617" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C617" t="s">
+        <v>29</v>
+      </c>
+      <c r="D617" t="s">
+        <v>3</v>
+      </c>
+      <c r="E617" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D880B4B-2866-4D31-8C92-A67F701BF0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3222D4D9-F203-4C0D-ACB3-DA4110F4AB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3085" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3095" uniqueCount="401">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1236,6 +1236,12 @@
   </si>
   <si>
     <t>Ice Cauldron</t>
+  </si>
+  <si>
+    <t>Order of the Sacred Torch</t>
+  </si>
+  <si>
+    <t>Seraph </t>
   </si>
 </sst>
 </file>
@@ -1715,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E617"/>
+  <dimension ref="A1:E619"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -12213,6 +12219,40 @@
         <v>367</v>
       </c>
     </row>
+    <row r="618" spans="1:5" ht="15">
+      <c r="A618" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C618" t="s">
+        <v>29</v>
+      </c>
+      <c r="D618" t="s">
+        <v>6</v>
+      </c>
+      <c r="E618" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5" ht="15">
+      <c r="A619" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C619" t="s">
+        <v>29</v>
+      </c>
+      <c r="D619" t="s">
+        <v>6</v>
+      </c>
+      <c r="E619" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3222D4D9-F203-4C0D-ACB3-DA4110F4AB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E46DA85-B83C-4F0D-B4C9-723B8CA319B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3095" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3175" uniqueCount="412">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1242,6 +1242,39 @@
   </si>
   <si>
     <t>Seraph </t>
+  </si>
+  <si>
+    <t>Chaos Lord</t>
+  </si>
+  <si>
+    <t>Tinder Wall </t>
+  </si>
+  <si>
+    <t>Stampede </t>
+  </si>
+  <si>
+    <t>Pentagram of the Ages</t>
+  </si>
+  <si>
+    <t>Reclamation </t>
+  </si>
+  <si>
+    <t>Glaciers</t>
+  </si>
+  <si>
+    <t>Fiery Justice</t>
+  </si>
+  <si>
+    <t>Ashen Ghoul</t>
+  </si>
+  <si>
+    <t>Fyndhorn Elder</t>
+  </si>
+  <si>
+    <t>Knight of Stromgald</t>
+  </si>
+  <si>
+    <t>Monsoon </t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E619"/>
+  <dimension ref="A1:E635"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -10615,7 +10648,7 @@
         <v>29</v>
       </c>
       <c r="D523" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>367</v>
@@ -12250,6 +12283,278 @@
         <v>6</v>
       </c>
       <c r="E619" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5" ht="15">
+      <c r="A620" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C620" t="s">
+        <v>29</v>
+      </c>
+      <c r="D620" t="s">
+        <v>3</v>
+      </c>
+      <c r="E620" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5" ht="15">
+      <c r="A621" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D621" t="s">
+        <v>42</v>
+      </c>
+      <c r="E621" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" ht="15">
+      <c r="A622" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D622" t="s">
+        <v>42</v>
+      </c>
+      <c r="E622" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" ht="15">
+      <c r="A623" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D623" t="s">
+        <v>42</v>
+      </c>
+      <c r="E623" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5" ht="15">
+      <c r="A624" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C624" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D624" t="s">
+        <v>31</v>
+      </c>
+      <c r="E624" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" ht="15">
+      <c r="A625" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C625" t="s">
+        <v>29</v>
+      </c>
+      <c r="D625" t="s">
+        <v>39</v>
+      </c>
+      <c r="E625" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" ht="15">
+      <c r="A626" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C626" t="s">
+        <v>29</v>
+      </c>
+      <c r="D626" t="s">
+        <v>3</v>
+      </c>
+      <c r="E626" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" ht="15">
+      <c r="A627" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D627" t="s">
+        <v>6</v>
+      </c>
+      <c r="E627" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" ht="15">
+      <c r="A628" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D628" t="s">
+        <v>6</v>
+      </c>
+      <c r="E628" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" ht="15">
+      <c r="A629" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C629" t="s">
+        <v>29</v>
+      </c>
+      <c r="D629" t="s">
+        <v>3</v>
+      </c>
+      <c r="E629" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" ht="15">
+      <c r="A630" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C630" t="s">
+        <v>29</v>
+      </c>
+      <c r="D630" t="s">
+        <v>3</v>
+      </c>
+      <c r="E630" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" ht="15">
+      <c r="A631" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C631" t="s">
+        <v>29</v>
+      </c>
+      <c r="D631" t="s">
+        <v>6</v>
+      </c>
+      <c r="E631" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" ht="15">
+      <c r="A632" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C632" t="s">
+        <v>29</v>
+      </c>
+      <c r="D632" t="s">
+        <v>3</v>
+      </c>
+      <c r="E632" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" ht="15">
+      <c r="A633" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C633" t="s">
+        <v>29</v>
+      </c>
+      <c r="D633" t="s">
+        <v>3</v>
+      </c>
+      <c r="E633" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" ht="15">
+      <c r="A634" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C634" t="s">
+        <v>29</v>
+      </c>
+      <c r="D634" t="s">
+        <v>3</v>
+      </c>
+      <c r="E634" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" ht="15">
+      <c r="A635" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C635" t="s">
+        <v>29</v>
+      </c>
+      <c r="D635" t="s">
+        <v>6</v>
+      </c>
+      <c r="E635" s="2" t="s">
         <v>367</v>
       </c>
     </row>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E46DA85-B83C-4F0D-B4C9-723B8CA319B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6D9989-8145-45F4-8EC5-4DAEA95700EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3175" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="421">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1275,6 +1275,33 @@
   </si>
   <si>
     <t>Monsoon </t>
+  </si>
+  <si>
+    <t>Aysen Crusader</t>
+  </si>
+  <si>
+    <t>Narwhal </t>
+  </si>
+  <si>
+    <t>Sengir Autocrat</t>
+  </si>
+  <si>
+    <t>Grandmother Sengir</t>
+  </si>
+  <si>
+    <t>Heart Wolf</t>
+  </si>
+  <si>
+    <t>Mammoth Harness</t>
+  </si>
+  <si>
+    <t>Pillage</t>
+  </si>
+  <si>
+    <t>Bounty of the Hunt</t>
+  </si>
+  <si>
+    <t>Wandering Mage</t>
   </si>
 </sst>
 </file>
@@ -1754,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E635"/>
+  <dimension ref="A1:E644"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -12558,6 +12585,159 @@
         <v>367</v>
       </c>
     </row>
+    <row r="636" spans="1:5" ht="15">
+      <c r="A636" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C636" t="s">
+        <v>29</v>
+      </c>
+      <c r="D636" t="s">
+        <v>3</v>
+      </c>
+      <c r="E636" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" ht="15">
+      <c r="A637" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C637" t="s">
+        <v>29</v>
+      </c>
+      <c r="D637" t="s">
+        <v>6</v>
+      </c>
+      <c r="E637" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" ht="15">
+      <c r="A638" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C638" t="s">
+        <v>29</v>
+      </c>
+      <c r="D638" t="s">
+        <v>6</v>
+      </c>
+      <c r="E638" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" ht="15">
+      <c r="A639" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C639" t="s">
+        <v>29</v>
+      </c>
+      <c r="D639" t="s">
+        <v>6</v>
+      </c>
+      <c r="E639" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" ht="15">
+      <c r="A640" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C640" t="s">
+        <v>29</v>
+      </c>
+      <c r="D640" t="s">
+        <v>6</v>
+      </c>
+      <c r="E640" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" ht="15">
+      <c r="A641" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C641" t="s">
+        <v>29</v>
+      </c>
+      <c r="D641" t="s">
+        <v>6</v>
+      </c>
+      <c r="E641" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" ht="15">
+      <c r="A642" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C642" t="s">
+        <v>29</v>
+      </c>
+      <c r="D642" t="s">
+        <v>6</v>
+      </c>
+      <c r="E642" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" ht="15">
+      <c r="A643" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C643" t="s">
+        <v>29</v>
+      </c>
+      <c r="D643" t="s">
+        <v>3</v>
+      </c>
+      <c r="E643" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" ht="15">
+      <c r="A644" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C644" t="s">
+        <v>29</v>
+      </c>
+      <c r="D644" t="s">
+        <v>6</v>
+      </c>
+      <c r="E644" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6D9989-8145-45F4-8EC5-4DAEA95700EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51AC8B20-106C-436C-93EC-BE4E090E8CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3250" uniqueCount="425">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1302,6 +1302,18 @@
   </si>
   <si>
     <t>Wandering Mage</t>
+  </si>
+  <si>
+    <t>Balduvian Trading Post</t>
+  </si>
+  <si>
+    <t>Sheltered Valley</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>Control Magic</t>
   </si>
 </sst>
 </file>
@@ -1781,7 +1793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E644"/>
+  <dimension ref="A1:E650"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -12738,6 +12750,108 @@
         <v>367</v>
       </c>
     </row>
+    <row r="645" spans="1:5" ht="15">
+      <c r="A645" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C645" t="s">
+        <v>29</v>
+      </c>
+      <c r="D645" t="s">
+        <v>3</v>
+      </c>
+      <c r="E645" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" ht="15">
+      <c r="A646" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C646" t="s">
+        <v>29</v>
+      </c>
+      <c r="D646" t="s">
+        <v>6</v>
+      </c>
+      <c r="E646" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" ht="15">
+      <c r="A647" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C647" t="s">
+        <v>29</v>
+      </c>
+      <c r="D647" t="s">
+        <v>6</v>
+      </c>
+      <c r="E647" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" ht="15">
+      <c r="A648" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C648" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D648" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E648" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" ht="15">
+      <c r="A649" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C649" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D649" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E649" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" ht="15">
+      <c r="A650" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C650" t="s">
+        <v>29</v>
+      </c>
+      <c r="D650" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E650" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51AC8B20-106C-436C-93EC-BE4E090E8CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E201C4-49F0-42CA-86B8-DE8FD94971C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3250" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3255" uniqueCount="425">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1793,7 +1793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E650"/>
+  <dimension ref="A1:E651"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -12852,6 +12852,23 @@
         <v>366</v>
       </c>
     </row>
+    <row r="651" spans="1:5" ht="15">
+      <c r="A651" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D651" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E651" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E201C4-49F0-42CA-86B8-DE8FD94971C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED90378-5D55-4B8A-A56D-E211478FBC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3255" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="428">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1314,6 +1314,15 @@
   </si>
   <si>
     <t>Control Magic</t>
+  </si>
+  <si>
+    <t>Nightmare </t>
+  </si>
+  <si>
+    <t>Mana Flare</t>
+  </si>
+  <si>
+    <t>Instill Energy</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1444,6 +1453,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1793,7 +1808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E651"/>
+  <dimension ref="A1:E656"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -12869,6 +12884,91 @@
         <v>366</v>
       </c>
     </row>
+    <row r="652" spans="1:5" ht="15">
+      <c r="A652" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D652" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E652" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" ht="15">
+      <c r="A653" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C653" t="s">
+        <v>29</v>
+      </c>
+      <c r="D653" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E653" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" ht="15">
+      <c r="A654" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D654" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E654" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" ht="15">
+      <c r="A655" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C655" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D655" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E655" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" ht="15">
+      <c r="A656" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C656" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D656" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E656" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED90378-5D55-4B8A-A56D-E211478FBC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F4D8DA-EFA6-43E9-A437-1F582836AC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3285" uniqueCount="428">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1425,7 +1425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1453,12 +1453,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1808,7 +1802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E656"/>
+  <dimension ref="A1:E657"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -12936,16 +12930,16 @@
       </c>
     </row>
     <row r="655" spans="1:5" ht="15">
-      <c r="A655" s="11" t="s">
+      <c r="A655" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B655" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C655" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D655" s="12" t="s">
+      <c r="C655" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D655" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E655" s="2" t="s">
@@ -12959,13 +12953,30 @@
       <c r="B656" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C656" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D656" s="12" t="s">
+      <c r="C656" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D656" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E656" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5" ht="15">
+      <c r="A657" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C657" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D657" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E657" s="2" t="s">
         <v>366</v>
       </c>
     </row>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F4D8DA-EFA6-43E9-A437-1F582836AC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7DD079-CC41-4864-9C40-CB7E3742CA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3285" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3820" uniqueCount="463">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1323,13 +1323,118 @@
   </si>
   <si>
     <t>Instill Energy</t>
+  </si>
+  <si>
+    <t>Land's Edge</t>
+  </si>
+  <si>
+    <t>Erhnam Djinn</t>
+  </si>
+  <si>
+    <t>Dakkon Blackblade</t>
+  </si>
+  <si>
+    <t>Tormod's Crypt</t>
+  </si>
+  <si>
+    <t>Urza's Mine (V.1)</t>
+  </si>
+  <si>
+    <t>Urza's Mine (V.2)</t>
+  </si>
+  <si>
+    <t>Urza's Mine (V.3)</t>
+  </si>
+  <si>
+    <t>Urza's Mine (V.4)</t>
+  </si>
+  <si>
+    <t>Urza's Power Plant (V.3)</t>
+  </si>
+  <si>
+    <t>Urza's Power Plant (V.1)</t>
+  </si>
+  <si>
+    <t>Urza's Power Plant (V.2)</t>
+  </si>
+  <si>
+    <t>Urza's Power Plant (V.4)</t>
+  </si>
+  <si>
+    <t>Urza's Tower (V.4)</t>
+  </si>
+  <si>
+    <t>Urza's Tower (V.1)</t>
+  </si>
+  <si>
+    <t>Urza's Tower (V.2)</t>
+  </si>
+  <si>
+    <t>Urza's Tower (V.3)</t>
+  </si>
+  <si>
+    <t>Tetravus</t>
+  </si>
+  <si>
+    <t>Unsummon </t>
+  </si>
+  <si>
+    <t>Time Elemental</t>
+  </si>
+  <si>
+    <t>Recall</t>
+  </si>
+  <si>
+    <t>Energy Flux</t>
+  </si>
+  <si>
+    <t>Hymn to Tourach (V.4)</t>
+  </si>
+  <si>
+    <t>Order of the Ebon Hand (V.3)</t>
+  </si>
+  <si>
+    <t>Order of the Ebon Hand (V.2)</t>
+  </si>
+  <si>
+    <t>Order of the Ebon Hand (V.1)</t>
+  </si>
+  <si>
+    <t>Paralyze </t>
+  </si>
+  <si>
+    <t>Drain Life</t>
+  </si>
+  <si>
+    <t>Tranquility </t>
+  </si>
+  <si>
+    <t>Hurricane </t>
+  </si>
+  <si>
+    <t>Scavenger Folk</t>
+  </si>
+  <si>
+    <t>Whirling Dervish </t>
+  </si>
+  <si>
+    <t>Karma</t>
+  </si>
+  <si>
+    <t>Circle of Protection: Black</t>
+  </si>
+  <si>
+    <t>Circle of Protection: Green</t>
+  </si>
+  <si>
+    <t>Circle of Protection: Red</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1355,6 +1460,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="6"/>
+      <color rgb="FFB0B3B8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1425,7 +1537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1453,6 +1565,25 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1802,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E657"/>
+  <dimension ref="A1:E764"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -12980,6 +13111,1825 @@
         <v>366</v>
       </c>
     </row>
+    <row r="658" spans="1:5" ht="15">
+      <c r="A658" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C658" t="s">
+        <v>2</v>
+      </c>
+      <c r="D658" t="s">
+        <v>6</v>
+      </c>
+      <c r="E658" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" ht="15">
+      <c r="A659" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C659" t="s">
+        <v>2</v>
+      </c>
+      <c r="D659" t="s">
+        <v>6</v>
+      </c>
+      <c r="E659" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" ht="15">
+      <c r="A660" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C660" t="s">
+        <v>2</v>
+      </c>
+      <c r="D660" t="s">
+        <v>6</v>
+      </c>
+      <c r="E660" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" ht="15">
+      <c r="A661" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C661" t="s">
+        <v>2</v>
+      </c>
+      <c r="D661" t="s">
+        <v>6</v>
+      </c>
+      <c r="E661" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="662" spans="1:5" ht="15">
+      <c r="A662" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C662" t="s">
+        <v>2</v>
+      </c>
+      <c r="D662" t="s">
+        <v>6</v>
+      </c>
+      <c r="E662" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" ht="15">
+      <c r="A663" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C663" t="s">
+        <v>2</v>
+      </c>
+      <c r="D663" t="s">
+        <v>31</v>
+      </c>
+      <c r="E663" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="664" spans="1:5" ht="15">
+      <c r="A664" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C664" t="s">
+        <v>2</v>
+      </c>
+      <c r="D664" t="s">
+        <v>3</v>
+      </c>
+      <c r="E664" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="665" spans="1:5" ht="15">
+      <c r="A665" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C665" t="s">
+        <v>2</v>
+      </c>
+      <c r="D665" t="s">
+        <v>3</v>
+      </c>
+      <c r="E665" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="666" spans="1:5" ht="15">
+      <c r="A666" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C666" t="s">
+        <v>2</v>
+      </c>
+      <c r="D666" t="s">
+        <v>6</v>
+      </c>
+      <c r="E666" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="667" spans="1:5" ht="15">
+      <c r="A667" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C667" t="s">
+        <v>2</v>
+      </c>
+      <c r="D667" t="s">
+        <v>6</v>
+      </c>
+      <c r="E667" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="668" spans="1:5" ht="15">
+      <c r="A668" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C668" t="s">
+        <v>2</v>
+      </c>
+      <c r="D668" t="s">
+        <v>6</v>
+      </c>
+      <c r="E668" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="669" spans="1:5" ht="15">
+      <c r="A669" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C669" t="s">
+        <v>2</v>
+      </c>
+      <c r="D669" t="s">
+        <v>6</v>
+      </c>
+      <c r="E669" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="670" spans="1:5" ht="15">
+      <c r="A670" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C670" t="s">
+        <v>2</v>
+      </c>
+      <c r="D670" t="s">
+        <v>42</v>
+      </c>
+      <c r="E670" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" ht="15">
+      <c r="A671" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C671" t="s">
+        <v>2</v>
+      </c>
+      <c r="D671" t="s">
+        <v>6</v>
+      </c>
+      <c r="E671" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" ht="15">
+      <c r="A672" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C672" t="s">
+        <v>2</v>
+      </c>
+      <c r="D672" t="s">
+        <v>6</v>
+      </c>
+      <c r="E672" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" ht="15">
+      <c r="A673" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C673" t="s">
+        <v>2</v>
+      </c>
+      <c r="D673" t="s">
+        <v>6</v>
+      </c>
+      <c r="E673" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" ht="15">
+      <c r="A674" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C674" t="s">
+        <v>2</v>
+      </c>
+      <c r="D674" t="s">
+        <v>6</v>
+      </c>
+      <c r="E674" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" ht="15">
+      <c r="A675" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C675" t="s">
+        <v>2</v>
+      </c>
+      <c r="D675" t="s">
+        <v>3</v>
+      </c>
+      <c r="E675" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" ht="15">
+      <c r="A676" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C676" t="s">
+        <v>2</v>
+      </c>
+      <c r="D676" t="s">
+        <v>6</v>
+      </c>
+      <c r="E676" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" ht="15">
+      <c r="A677" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C677" t="s">
+        <v>2</v>
+      </c>
+      <c r="D677" t="s">
+        <v>6</v>
+      </c>
+      <c r="E677" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" ht="15">
+      <c r="A678" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C678" t="s">
+        <v>2</v>
+      </c>
+      <c r="D678" t="s">
+        <v>42</v>
+      </c>
+      <c r="E678" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" ht="15">
+      <c r="A679" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C679" t="s">
+        <v>2</v>
+      </c>
+      <c r="D679" t="s">
+        <v>42</v>
+      </c>
+      <c r="E679" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5" ht="15">
+      <c r="A680" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C680" t="s">
+        <v>2</v>
+      </c>
+      <c r="D680" t="s">
+        <v>6</v>
+      </c>
+      <c r="E680" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" ht="15">
+      <c r="A681" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C681" t="s">
+        <v>2</v>
+      </c>
+      <c r="D681" t="s">
+        <v>42</v>
+      </c>
+      <c r="E681" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" ht="15">
+      <c r="A682" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C682" t="s">
+        <v>2</v>
+      </c>
+      <c r="D682" t="s">
+        <v>6</v>
+      </c>
+      <c r="E682" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5" ht="15">
+      <c r="A683" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C683" t="s">
+        <v>2</v>
+      </c>
+      <c r="D683" t="s">
+        <v>6</v>
+      </c>
+      <c r="E683" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5" ht="15">
+      <c r="A684" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C684" t="s">
+        <v>2</v>
+      </c>
+      <c r="D684" t="s">
+        <v>42</v>
+      </c>
+      <c r="E684" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5" ht="15">
+      <c r="A685" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C685" t="s">
+        <v>29</v>
+      </c>
+      <c r="D685" t="s">
+        <v>6</v>
+      </c>
+      <c r="E685" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5">
+      <c r="A686" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B686" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C686" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D686" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E686" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5">
+      <c r="A687" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B687" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C687" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D687" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E687" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" ht="15">
+      <c r="A688" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C688" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D688" t="s">
+        <v>3</v>
+      </c>
+      <c r="E688" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="689" spans="1:5" ht="15">
+      <c r="A689" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C689" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D689" t="s">
+        <v>3</v>
+      </c>
+      <c r="E689" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="690" spans="1:5" ht="15">
+      <c r="A690" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C690" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D690" t="s">
+        <v>3</v>
+      </c>
+      <c r="E690" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="691" spans="1:5" ht="15">
+      <c r="A691" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C691" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D691" t="s">
+        <v>6</v>
+      </c>
+      <c r="E691" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" ht="15">
+      <c r="A692" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C692" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D692" t="s">
+        <v>3</v>
+      </c>
+      <c r="E692" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" ht="15">
+      <c r="A693" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C693" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D693" t="s">
+        <v>3</v>
+      </c>
+      <c r="E693" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" ht="15">
+      <c r="A694" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C694" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D694" t="s">
+        <v>3</v>
+      </c>
+      <c r="E694" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" ht="15">
+      <c r="A695" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C695" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D695" t="s">
+        <v>3</v>
+      </c>
+      <c r="E695" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="696" spans="1:5" ht="15">
+      <c r="A696" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C696" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D696" t="s">
+        <v>3</v>
+      </c>
+      <c r="E696" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="697" spans="1:5" ht="15">
+      <c r="A697" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C697" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D697" t="s">
+        <v>3</v>
+      </c>
+      <c r="E697" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="698" spans="1:5" ht="15">
+      <c r="A698" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C698" t="s">
+        <v>29</v>
+      </c>
+      <c r="D698" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E698" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="699" spans="1:5" ht="15">
+      <c r="A699" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C699" t="s">
+        <v>29</v>
+      </c>
+      <c r="D699" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E699" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="700" spans="1:5" ht="15">
+      <c r="A700" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C700" t="s">
+        <v>29</v>
+      </c>
+      <c r="D700" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E700" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="701" spans="1:5" ht="15">
+      <c r="A701" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C701" t="s">
+        <v>29</v>
+      </c>
+      <c r="D701" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E701" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="702" spans="1:5" ht="15">
+      <c r="A702" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C702" t="s">
+        <v>2</v>
+      </c>
+      <c r="D702" t="s">
+        <v>3</v>
+      </c>
+      <c r="E702" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="703" spans="1:5" ht="15">
+      <c r="A703" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C703" t="s">
+        <v>29</v>
+      </c>
+      <c r="D703" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E703" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="704" spans="1:5" ht="15">
+      <c r="A704" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C704" t="s">
+        <v>29</v>
+      </c>
+      <c r="D704" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E704" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="705" spans="1:5" ht="15">
+      <c r="A705" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C705" t="s">
+        <v>29</v>
+      </c>
+      <c r="D705" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E705" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="706" spans="1:5">
+      <c r="A706" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="B706" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C706" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D706" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E706" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="707" spans="1:5" ht="15">
+      <c r="A707" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B707" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C707" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D707" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E707" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="708" spans="1:5" ht="15">
+      <c r="A708" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B708" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C708" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D708" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E708" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="709" spans="1:5" ht="15">
+      <c r="A709" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B709" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C709" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D709" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E709" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="710" spans="1:5" ht="15">
+      <c r="A710" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B710" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C710" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D710" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E710" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="711" spans="1:5" ht="15">
+      <c r="A711" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C711" t="s">
+        <v>29</v>
+      </c>
+      <c r="D711" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E711" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="712" spans="1:5" ht="15">
+      <c r="A712" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C712" t="s">
+        <v>29</v>
+      </c>
+      <c r="D712" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E712" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="713" spans="1:5" ht="15">
+      <c r="A713" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C713" t="s">
+        <v>29</v>
+      </c>
+      <c r="D713" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E713" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" ht="15">
+      <c r="A714" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C714" t="s">
+        <v>29</v>
+      </c>
+      <c r="D714" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E714" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" ht="15">
+      <c r="A715" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C715" t="s">
+        <v>29</v>
+      </c>
+      <c r="D715" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E715" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="716" spans="1:5" ht="15">
+      <c r="A716" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C716" t="s">
+        <v>29</v>
+      </c>
+      <c r="D716" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E716" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="717" spans="1:5" ht="15">
+      <c r="A717" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C717" t="s">
+        <v>29</v>
+      </c>
+      <c r="D717" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E717" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="718" spans="1:5" ht="15">
+      <c r="A718" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C718" t="s">
+        <v>29</v>
+      </c>
+      <c r="D718" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E718" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="719" spans="1:5" ht="15">
+      <c r="A719" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C719" t="s">
+        <v>29</v>
+      </c>
+      <c r="D719" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E719" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="720" spans="1:5" ht="15">
+      <c r="A720" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C720" t="s">
+        <v>29</v>
+      </c>
+      <c r="D720" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E720" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="721" spans="1:5" ht="15">
+      <c r="A721" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C721" t="s">
+        <v>29</v>
+      </c>
+      <c r="D721" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E721" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="722" spans="1:5" ht="15">
+      <c r="A722" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C722" t="s">
+        <v>29</v>
+      </c>
+      <c r="D722" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E722" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="723" spans="1:5" ht="15">
+      <c r="A723" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C723" t="s">
+        <v>29</v>
+      </c>
+      <c r="D723" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E723" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="724" spans="1:5" ht="15">
+      <c r="A724" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C724" t="s">
+        <v>29</v>
+      </c>
+      <c r="D724" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E724" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="725" spans="1:5" ht="15">
+      <c r="A725" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C725" t="s">
+        <v>29</v>
+      </c>
+      <c r="D725" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E725" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="726" spans="1:5" ht="15">
+      <c r="A726" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C726" t="s">
+        <v>29</v>
+      </c>
+      <c r="D726" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E726" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5" ht="15">
+      <c r="A727" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C727" t="s">
+        <v>29</v>
+      </c>
+      <c r="D727" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E727" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="728" spans="1:5" ht="15">
+      <c r="A728" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C728" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D728" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E728" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="729" spans="1:5" ht="15">
+      <c r="A729" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C729" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D729" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E729" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="730" spans="1:5" ht="15">
+      <c r="A730" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C730" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D730" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E730" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="731" spans="1:5" ht="15">
+      <c r="A731" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C731" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D731" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E731" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="732" spans="1:5" ht="15">
+      <c r="A732" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C732" t="s">
+        <v>29</v>
+      </c>
+      <c r="D732" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E732" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="733" spans="1:5" ht="15">
+      <c r="A733" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C733" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D733" t="s">
+        <v>3</v>
+      </c>
+      <c r="E733" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="734" spans="1:5" ht="15">
+      <c r="A734" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C734" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D734" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E734" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="735" spans="1:5" ht="15">
+      <c r="A735" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C735" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D735" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E735" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="736" spans="1:5" ht="15">
+      <c r="A736" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C736" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D736" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E736" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="737" spans="1:5" ht="15">
+      <c r="A737" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C737" t="s">
+        <v>2</v>
+      </c>
+      <c r="D737" t="s">
+        <v>6</v>
+      </c>
+      <c r="E737" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="738" spans="1:5" ht="15">
+      <c r="A738" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C738" t="s">
+        <v>2</v>
+      </c>
+      <c r="D738" t="s">
+        <v>6</v>
+      </c>
+      <c r="E738" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="739" spans="1:5" ht="15">
+      <c r="A739" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B739" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C739" t="s">
+        <v>2</v>
+      </c>
+      <c r="D739" t="s">
+        <v>3</v>
+      </c>
+      <c r="E739" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="740" spans="1:5" ht="15">
+      <c r="A740" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B740" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C740" t="s">
+        <v>2</v>
+      </c>
+      <c r="D740" t="s">
+        <v>6</v>
+      </c>
+      <c r="E740" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="741" spans="1:5" ht="15">
+      <c r="A741" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B741" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C741" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D741" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E741" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="742" spans="1:5" ht="15">
+      <c r="A742" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B742" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C742" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D742" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E742" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="743" spans="1:5" ht="15">
+      <c r="A743" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C743" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D743" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E743" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="744" spans="1:5" ht="15">
+      <c r="A744" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B744" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C744" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D744" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E744" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="745" spans="1:5" ht="15">
+      <c r="A745" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B745" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C745" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D745" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E745" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="746" spans="1:5" ht="15">
+      <c r="A746" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B746" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C746" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D746" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E746" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="747" spans="1:5" ht="15">
+      <c r="A747" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C747" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D747" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E747" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="748" spans="1:5" ht="15">
+      <c r="A748" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B748" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C748" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D748" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E748" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="749" spans="1:5" ht="15">
+      <c r="A749" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C749" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D749" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E749" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="750" spans="1:5" ht="15">
+      <c r="A750" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C750" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D750" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E750" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="751" spans="1:5">
+      <c r="A751" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B751" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C751" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D751" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E751" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="752" spans="1:5">
+      <c r="A752" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B752" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C752" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D752" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E752" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="753" spans="1:5">
+      <c r="A753" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B753" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C753" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D753" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E753" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="754" spans="1:5">
+      <c r="A754" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B754" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C754" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D754" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E754" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="755" spans="1:5">
+      <c r="A755" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="B755" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C755" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D755" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E755" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="756" spans="1:5">
+      <c r="A756" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="B756" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C756" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D756" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E756" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="757" spans="1:5">
+      <c r="A757" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="B757" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C757" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D757" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E757" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="758" spans="1:5">
+      <c r="A758" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B758" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C758" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D758" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E758" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="759" spans="1:5">
+      <c r="A759" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B759" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C759" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D759" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E759" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="760" spans="1:5" ht="15">
+      <c r="A760" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C760" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D760" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E760" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="761" spans="1:5" ht="15">
+      <c r="A761" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C761" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D761" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E761" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="762" spans="1:5" ht="15">
+      <c r="A762" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C762" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D762" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E762" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="763" spans="1:5" ht="15">
+      <c r="A763" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C763" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D763" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E763" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="764" spans="1:5" ht="15">
+      <c r="A764" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C764" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D764" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E764" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7DD079-CC41-4864-9C40-CB7E3742CA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6214CFB-E563-423A-8FC2-139FD5978ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3820" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4030" uniqueCount="482">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1428,6 +1428,63 @@
   </si>
   <si>
     <t>Circle of Protection: Red</t>
+  </si>
+  <si>
+    <t>Dragon Whelp</t>
+  </si>
+  <si>
+    <t>Ironclaw Orcs</t>
+  </si>
+  <si>
+    <t>Goblin Balloon Brigade</t>
+  </si>
+  <si>
+    <t>Goblins of the Flarg</t>
+  </si>
+  <si>
+    <t>Goblin Digging Team</t>
+  </si>
+  <si>
+    <t>Goblin Grenade (V.3)</t>
+  </si>
+  <si>
+    <t>Goblin Grenade (V.1)</t>
+  </si>
+  <si>
+    <t>Goblin Grenade (V.2)</t>
+  </si>
+  <si>
+    <t>Flashfires </t>
+  </si>
+  <si>
+    <t>Shatter</t>
+  </si>
+  <si>
+    <t>White Knight</t>
+  </si>
+  <si>
+    <t>Order of Leitbur (V.1)</t>
+  </si>
+  <si>
+    <t>Order of Leitbur (V.2)</t>
+  </si>
+  <si>
+    <t>Order of Leitbur (V.3)</t>
+  </si>
+  <si>
+    <t>Icatian Javelineers (V.1)</t>
+  </si>
+  <si>
+    <t>Icatian Javelineers (V.2)</t>
+  </si>
+  <si>
+    <t>Icatian Javelineers (V.3)</t>
+  </si>
+  <si>
+    <t>Ruins of Trokair</t>
+  </si>
+  <si>
+    <t>Repentant Blacksmith</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1545,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1533,11 +1590,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1568,22 +1634,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1933,7 +1987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E764"/>
+  <dimension ref="A1:E806"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -13588,16 +13642,16 @@
       </c>
     </row>
     <row r="686" spans="1:5">
-      <c r="A686" s="12" t="s">
+      <c r="A686" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B686" s="13" t="s">
+      <c r="B686" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C686" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D686" s="13" t="s">
+      <c r="C686" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D686" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E686" s="2" t="s">
@@ -13605,16 +13659,16 @@
       </c>
     </row>
     <row r="687" spans="1:5">
-      <c r="A687" s="12" t="s">
+      <c r="A687" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B687" s="13" t="s">
+      <c r="B687" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C687" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D687" s="13" t="s">
+      <c r="C687" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D687" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E687" s="2" t="s">
@@ -13628,7 +13682,7 @@
       <c r="B688" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C688" s="13" t="s">
+      <c r="C688" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D688" t="s">
@@ -13645,7 +13699,7 @@
       <c r="B689" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C689" s="13" t="s">
+      <c r="C689" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D689" t="s">
@@ -13662,7 +13716,7 @@
       <c r="B690" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C690" s="13" t="s">
+      <c r="C690" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D690" t="s">
@@ -13679,7 +13733,7 @@
       <c r="B691" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C691" s="13" t="s">
+      <c r="C691" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D691" t="s">
@@ -13696,7 +13750,7 @@
       <c r="B692" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C692" s="13" t="s">
+      <c r="C692" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D692" t="s">
@@ -13713,7 +13767,7 @@
       <c r="B693" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C693" s="13" t="s">
+      <c r="C693" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D693" t="s">
@@ -13730,7 +13784,7 @@
       <c r="B694" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C694" s="13" t="s">
+      <c r="C694" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D694" t="s">
@@ -13747,7 +13801,7 @@
       <c r="B695" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C695" s="13" t="s">
+      <c r="C695" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D695" t="s">
@@ -13764,7 +13818,7 @@
       <c r="B696" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C696" s="13" t="s">
+      <c r="C696" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D696" t="s">
@@ -13781,7 +13835,7 @@
       <c r="B697" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C697" s="13" t="s">
+      <c r="C697" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D697" t="s">
@@ -13928,19 +13982,19 @@
       </c>
     </row>
     <row r="706" spans="1:5">
-      <c r="A706" s="14" t="s">
+      <c r="A706" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="B706" s="15" t="s">
+      <c r="B706" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C706" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D706" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E706" s="16" t="s">
+      <c r="C706" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D706" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E706" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -13948,16 +14002,16 @@
       <c r="A707" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B707" s="15" t="s">
+      <c r="B707" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C707" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D707" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E707" s="16" t="s">
+      <c r="C707" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D707" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E707" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -13965,16 +14019,16 @@
       <c r="A708" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B708" s="15" t="s">
+      <c r="B708" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C708" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D708" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E708" s="16" t="s">
+      <c r="C708" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D708" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E708" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -13982,16 +14036,16 @@
       <c r="A709" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B709" s="15" t="s">
+      <c r="B709" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C709" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D709" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E709" s="16" t="s">
+      <c r="C709" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D709" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E709" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -13999,16 +14053,16 @@
       <c r="A710" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B710" s="15" t="s">
+      <c r="B710" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C710" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D710" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E710" s="16" t="s">
+      <c r="C710" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D710" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E710" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -14022,10 +14076,10 @@
       <c r="C711" t="s">
         <v>29</v>
       </c>
-      <c r="D711" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E711" s="16" t="s">
+      <c r="D711" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E711" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -14039,10 +14093,10 @@
       <c r="C712" t="s">
         <v>29</v>
       </c>
-      <c r="D712" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E712" s="16" t="s">
+      <c r="D712" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E712" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -14059,7 +14113,7 @@
       <c r="D713" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E713" s="16" t="s">
+      <c r="E713" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -14076,7 +14130,7 @@
       <c r="D714" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E714" s="16" t="s">
+      <c r="E714" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -14093,7 +14147,7 @@
       <c r="D715" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E715" s="16" t="s">
+      <c r="E715" s="10" t="s">
         <v>373</v>
       </c>
     </row>
@@ -14107,7 +14161,7 @@
       <c r="C716" t="s">
         <v>29</v>
       </c>
-      <c r="D716" s="15" t="s">
+      <c r="D716" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E716" s="2" t="s">
@@ -14124,7 +14178,7 @@
       <c r="C717" t="s">
         <v>29</v>
       </c>
-      <c r="D717" s="15" t="s">
+      <c r="D717" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E717" s="2" t="s">
@@ -14141,7 +14195,7 @@
       <c r="C718" t="s">
         <v>29</v>
       </c>
-      <c r="D718" s="15" t="s">
+      <c r="D718" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E718" s="2" t="s">
@@ -14158,7 +14212,7 @@
       <c r="C719" t="s">
         <v>29</v>
       </c>
-      <c r="D719" s="15" t="s">
+      <c r="D719" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E719" s="2" t="s">
@@ -14175,7 +14229,7 @@
       <c r="C720" t="s">
         <v>29</v>
       </c>
-      <c r="D720" s="15" t="s">
+      <c r="D720" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E720" s="2" t="s">
@@ -14192,7 +14246,7 @@
       <c r="C721" t="s">
         <v>29</v>
       </c>
-      <c r="D721" s="15" t="s">
+      <c r="D721" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E721" s="2" t="s">
@@ -14209,7 +14263,7 @@
       <c r="C722" t="s">
         <v>29</v>
       </c>
-      <c r="D722" s="15" t="s">
+      <c r="D722" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E722" s="2" t="s">
@@ -14226,7 +14280,7 @@
       <c r="C723" t="s">
         <v>29</v>
       </c>
-      <c r="D723" s="15" t="s">
+      <c r="D723" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E723" s="2" t="s">
@@ -14243,7 +14297,7 @@
       <c r="C724" t="s">
         <v>29</v>
       </c>
-      <c r="D724" s="15" t="s">
+      <c r="D724" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E724" s="2" t="s">
@@ -14260,7 +14314,7 @@
       <c r="C725" t="s">
         <v>29</v>
       </c>
-      <c r="D725" s="15" t="s">
+      <c r="D725" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E725" s="2" t="s">
@@ -14277,7 +14331,7 @@
       <c r="C726" t="s">
         <v>29</v>
       </c>
-      <c r="D726" s="15" t="s">
+      <c r="D726" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E726" s="2" t="s">
@@ -14294,7 +14348,7 @@
       <c r="C727" t="s">
         <v>29</v>
       </c>
-      <c r="D727" s="15" t="s">
+      <c r="D727" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E727" s="2" t="s">
@@ -14308,10 +14362,10 @@
       <c r="B728" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C728" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D728" s="15" t="s">
+      <c r="C728" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D728" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E728" s="2" t="s">
@@ -14325,10 +14379,10 @@
       <c r="B729" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C729" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D729" s="15" t="s">
+      <c r="C729" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D729" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E729" s="2" t="s">
@@ -14342,10 +14396,10 @@
       <c r="B730" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C730" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D730" s="15" t="s">
+      <c r="C730" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D730" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E730" s="2" t="s">
@@ -14359,10 +14413,10 @@
       <c r="B731" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C731" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D731" s="15" t="s">
+      <c r="C731" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D731" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E731" s="2" t="s">
@@ -14379,7 +14433,7 @@
       <c r="C732" t="s">
         <v>29</v>
       </c>
-      <c r="D732" s="15" t="s">
+      <c r="D732" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E732" s="2" t="s">
@@ -14393,7 +14447,7 @@
       <c r="B733" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C733" s="13" t="s">
+      <c r="C733" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D733" t="s">
@@ -14410,10 +14464,10 @@
       <c r="B734" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C734" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D734" s="15" t="s">
+      <c r="C734" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D734" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E734" s="2" t="s">
@@ -14427,10 +14481,10 @@
       <c r="B735" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C735" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D735" s="15" t="s">
+      <c r="C735" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D735" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E735" s="2" t="s">
@@ -14444,10 +14498,10 @@
       <c r="B736" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C736" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D736" s="15" t="s">
+      <c r="C736" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D736" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E736" s="2" t="s">
@@ -14591,16 +14645,16 @@
       </c>
     </row>
     <row r="745" spans="1:5" ht="15">
-      <c r="A745" s="14" t="s">
+      <c r="A745" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B745" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C745" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D745" s="15" t="s">
+      <c r="C745" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D745" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E745" s="7" t="s">
@@ -14608,16 +14662,16 @@
       </c>
     </row>
     <row r="746" spans="1:5" ht="15">
-      <c r="A746" s="14" t="s">
+      <c r="A746" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B746" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C746" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D746" s="15" t="s">
+      <c r="C746" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D746" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E746" s="7" t="s">
@@ -14625,16 +14679,16 @@
       </c>
     </row>
     <row r="747" spans="1:5" ht="15">
-      <c r="A747" s="14" t="s">
+      <c r="A747" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B747" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C747" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D747" s="15" t="s">
+      <c r="C747" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D747" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E747" s="7" t="s">
@@ -14642,16 +14696,16 @@
       </c>
     </row>
     <row r="748" spans="1:5" ht="15">
-      <c r="A748" s="14" t="s">
+      <c r="A748" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B748" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C748" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D748" s="15" t="s">
+      <c r="C748" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D748" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E748" s="7" t="s">
@@ -14665,10 +14719,10 @@
       <c r="B749" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C749" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D749" s="15" t="s">
+      <c r="C749" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D749" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E749" s="7" t="s">
@@ -14682,10 +14736,10 @@
       <c r="B750" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C750" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D750" s="15" t="s">
+      <c r="C750" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D750" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E750" s="7" t="s">
@@ -14693,16 +14747,16 @@
       </c>
     </row>
     <row r="751" spans="1:5">
-      <c r="A751" s="12" t="s">
+      <c r="A751" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B751" s="13" t="s">
+      <c r="B751" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C751" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D751" s="13" t="s">
+      <c r="C751" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D751" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E751" s="7" t="s">
@@ -14710,16 +14764,16 @@
       </c>
     </row>
     <row r="752" spans="1:5">
-      <c r="A752" s="12" t="s">
+      <c r="A752" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B752" s="13" t="s">
+      <c r="B752" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C752" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D752" s="13" t="s">
+      <c r="C752" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D752" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E752" s="7" t="s">
@@ -14727,16 +14781,16 @@
       </c>
     </row>
     <row r="753" spans="1:5">
-      <c r="A753" s="12" t="s">
+      <c r="A753" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B753" s="13" t="s">
+      <c r="B753" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C753" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D753" s="13" t="s">
+      <c r="C753" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D753" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E753" s="7" t="s">
@@ -14744,16 +14798,16 @@
       </c>
     </row>
     <row r="754" spans="1:5">
-      <c r="A754" s="12" t="s">
+      <c r="A754" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B754" s="13" t="s">
+      <c r="B754" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C754" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D754" s="13" t="s">
+      <c r="C754" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D754" s="3" t="s">
         <v>192</v>
       </c>
       <c r="E754" s="7" t="s">
@@ -14761,16 +14815,16 @@
       </c>
     </row>
     <row r="755" spans="1:5">
-      <c r="A755" s="17" t="s">
+      <c r="A755" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B755" s="13" t="s">
+      <c r="B755" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C755" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D755" s="13" t="s">
+      <c r="C755" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D755" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E755" s="7" t="s">
@@ -14778,16 +14832,16 @@
       </c>
     </row>
     <row r="756" spans="1:5">
-      <c r="A756" s="17" t="s">
+      <c r="A756" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B756" s="13" t="s">
+      <c r="B756" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C756" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D756" s="13" t="s">
+      <c r="C756" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D756" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E756" s="7" t="s">
@@ -14795,10 +14849,10 @@
       </c>
     </row>
     <row r="757" spans="1:5">
-      <c r="A757" s="17" t="s">
+      <c r="A757" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B757" s="17" t="s">
+      <c r="B757" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C757" s="3" t="s">
@@ -14812,10 +14866,10 @@
       </c>
     </row>
     <row r="758" spans="1:5">
-      <c r="A758" s="17" t="s">
+      <c r="A758" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B758" s="17" t="s">
+      <c r="B758" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C758" s="3" t="s">
@@ -14829,10 +14883,10 @@
       </c>
     </row>
     <row r="759" spans="1:5">
-      <c r="A759" s="17" t="s">
+      <c r="A759" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B759" s="17" t="s">
+      <c r="B759" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C759" s="3" t="s">
@@ -14852,10 +14906,10 @@
       <c r="B760" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C760" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D760" s="15" t="s">
+      <c r="C760" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D760" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E760" s="7" t="s">
@@ -14869,10 +14923,10 @@
       <c r="B761" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C761" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D761" s="15" t="s">
+      <c r="C761" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D761" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E761" s="7" t="s">
@@ -14886,10 +14940,10 @@
       <c r="B762" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C762" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D762" s="15" t="s">
+      <c r="C762" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D762" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E762" s="7" t="s">
@@ -14903,10 +14957,10 @@
       <c r="B763" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C763" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D763" s="15" t="s">
+      <c r="C763" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D763" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E763" s="7" t="s">
@@ -14920,14 +14974,728 @@
       <c r="B764" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C764" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D764" s="15" t="s">
+      <c r="C764" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D764" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E764" s="7" t="s">
         <v>375</v>
+      </c>
+    </row>
+    <row r="765" spans="1:5" ht="15">
+      <c r="A765" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C765" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D765" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E765" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="766" spans="1:5" ht="15">
+      <c r="A766" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C766" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D766" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E766" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="767" spans="1:5" ht="15">
+      <c r="A767" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C767" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D767" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E767" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="768" spans="1:5" ht="15">
+      <c r="A768" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C768" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D768" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E768" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="769" spans="1:5" ht="15">
+      <c r="A769" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C769" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D769" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E769" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="770" spans="1:5" ht="15">
+      <c r="A770" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C770" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D770" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E770" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="771" spans="1:5" ht="15">
+      <c r="A771" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C771" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D771" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E771" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="772" spans="1:5" ht="15">
+      <c r="A772" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C772" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D772" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E772" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="773" spans="1:5" ht="15">
+      <c r="A773" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B773" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C773" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D773" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E773" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="774" spans="1:5" ht="15">
+      <c r="A774" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C774" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D774" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E774" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="775" spans="1:5" ht="15">
+      <c r="A775" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C775" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D775" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E775" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="776" spans="1:5" ht="15">
+      <c r="A776" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C776" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D776" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E776" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="777" spans="1:5" ht="15">
+      <c r="A777" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C777" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D777" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E777" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="778" spans="1:5" ht="15">
+      <c r="A778" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C778" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D778" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E778" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="779" spans="1:5" ht="15">
+      <c r="A779" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C779" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D779" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E779" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="780" spans="1:5" ht="15">
+      <c r="A780" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C780" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D780" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E780" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="781" spans="1:5" ht="15">
+      <c r="A781" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C781" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D781" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E781" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="782" spans="1:5" ht="15">
+      <c r="A782" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C782" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D782" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E782" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="783" spans="1:5" ht="15">
+      <c r="A783" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C783" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D783" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E783" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="784" spans="1:5" ht="15">
+      <c r="A784" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C784" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D784" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E784" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="785" spans="1:5" ht="15">
+      <c r="A785" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B785" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C785" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D785" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E785" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="786" spans="1:5" ht="15">
+      <c r="A786" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B786" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C786" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D786" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E786" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="787" spans="1:5" ht="15">
+      <c r="A787" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B787" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C787" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D787" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E787" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="788" spans="1:5" ht="15">
+      <c r="A788" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B788" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C788" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D788" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E788" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="789" spans="1:5" ht="15">
+      <c r="A789" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C789" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D789" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E789" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="790" spans="1:5" ht="15">
+      <c r="A790" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C790" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D790" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E790" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="791" spans="1:5" ht="15">
+      <c r="A791" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C791" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D791" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E791" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="792" spans="1:5" ht="15">
+      <c r="A792" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B792" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C792" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D792" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E792" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="793" spans="1:5" ht="15">
+      <c r="A793" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B793" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C793" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D793" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E793" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="794" spans="1:5" ht="15">
+      <c r="A794" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B794" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C794" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D794" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E794" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="795" spans="1:5" ht="15">
+      <c r="A795" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B795" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C795" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D795" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E795" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="796" spans="1:5" ht="15">
+      <c r="A796" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B796" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C796" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D796" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E796" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="797" spans="1:5" ht="15">
+      <c r="A797" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B797" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C797" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D797" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E797" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="798" spans="1:5" ht="15">
+      <c r="A798" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B798" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C798" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D798" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E798" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="799" spans="1:5" ht="15">
+      <c r="A799" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B799" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C799" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D799" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E799" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="800" spans="1:5" ht="15">
+      <c r="A800" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B800" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C800" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D800" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E800" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="801" spans="1:5" ht="15">
+      <c r="A801" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B801" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C801" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D801" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E801" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="802" spans="1:5" ht="15">
+      <c r="A802" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B802" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C802" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D802" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E802" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="803" spans="1:5" ht="15">
+      <c r="A803" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B803" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C803" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D803" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E803" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="804" spans="1:5" ht="15">
+      <c r="A804" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B804" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C804" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D804" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E804" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="805" spans="1:5" ht="15">
+      <c r="A805" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B805" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C805" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D805" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E805" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="806" spans="1:5" ht="15">
+      <c r="A806" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B806" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C806" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D806" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E806" s="12" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6214CFB-E563-423A-8FC2-139FD5978ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADD0415-8C94-437E-BAAA-1A371B40EDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4030" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="508">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1485,6 +1485,84 @@
   </si>
   <si>
     <t>Repentant Blacksmith</t>
+  </si>
+  <si>
+    <t>Spectral Guardian</t>
+  </si>
+  <si>
+    <t>Dark Ritual </t>
+  </si>
+  <si>
+    <t>Dwarven Miner</t>
+  </si>
+  <si>
+    <t>Telim'Tor</t>
+  </si>
+  <si>
+    <t>Volcanic Dragon</t>
+  </si>
+  <si>
+    <t>Uktabi Wildcats</t>
+  </si>
+  <si>
+    <t>Wall of Roots</t>
+  </si>
+  <si>
+    <t>Benthic Djinn</t>
+  </si>
+  <si>
+    <t>Energy Bolt</t>
+  </si>
+  <si>
+    <t>Rocky Tar Pit</t>
+  </si>
+  <si>
+    <t>Mountain Valley</t>
+  </si>
+  <si>
+    <t>Eye of Singularity</t>
+  </si>
+  <si>
+    <t>Zhalfirin Crusader</t>
+  </si>
+  <si>
+    <t>Flooded Shoreline</t>
+  </si>
+  <si>
+    <t>Impulse</t>
+  </si>
+  <si>
+    <t>Prosperity </t>
+  </si>
+  <si>
+    <t>Rainbow Efreet</t>
+  </si>
+  <si>
+    <t>Vision Charm</t>
+  </si>
+  <si>
+    <t>Crypt Rats</t>
+  </si>
+  <si>
+    <t>Bogardan Phoenix</t>
+  </si>
+  <si>
+    <t>Fireblast</t>
+  </si>
+  <si>
+    <t>Ogre Enforcer</t>
+  </si>
+  <si>
+    <t>Katabatic Winds</t>
+  </si>
+  <si>
+    <t>Quirion Druid</t>
+  </si>
+  <si>
+    <t>Uktabi Orangutan</t>
+  </si>
+  <si>
+    <t>Snake Basket</t>
   </si>
 </sst>
 </file>
@@ -1603,7 +1681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1634,10 +1712,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1987,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E806"/>
+  <dimension ref="A1:E846"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -15419,7 +15500,7 @@
       <c r="C790" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D790" s="13" t="s">
+      <c r="D790" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E790" s="12" t="s">
@@ -15436,7 +15517,7 @@
       <c r="C791" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D791" s="13" t="s">
+      <c r="D791" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E791" s="12" t="s">
@@ -15453,7 +15534,7 @@
       <c r="C792" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D792" s="13" t="s">
+      <c r="D792" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E792" s="12" t="s">
@@ -15470,7 +15551,7 @@
       <c r="C793" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D793" s="13" t="s">
+      <c r="D793" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E793" s="12" t="s">
@@ -15487,7 +15568,7 @@
       <c r="C794" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D794" s="13" t="s">
+      <c r="D794" s="2" t="s">
         <v>192</v>
       </c>
       <c r="E794" s="12" t="s">
@@ -15504,7 +15585,7 @@
       <c r="C795" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D795" s="13" t="s">
+      <c r="D795" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E795" s="12" t="s">
@@ -15521,7 +15602,7 @@
       <c r="C796" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D796" s="13" t="s">
+      <c r="D796" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E796" s="12" t="s">
@@ -15538,7 +15619,7 @@
       <c r="C797" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D797" s="13" t="s">
+      <c r="D797" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E797" s="12" t="s">
@@ -15555,7 +15636,7 @@
       <c r="C798" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D798" s="13" t="s">
+      <c r="D798" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E798" s="12" t="s">
@@ -15572,7 +15653,7 @@
       <c r="C799" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D799" s="13" t="s">
+      <c r="D799" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E799" s="12" t="s">
@@ -15589,7 +15670,7 @@
       <c r="C800" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D800" s="13" t="s">
+      <c r="D800" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E800" s="12" t="s">
@@ -15640,7 +15721,7 @@
       <c r="C803" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D803" s="13" t="s">
+      <c r="D803" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E803" s="12" t="s">
@@ -15657,7 +15738,7 @@
       <c r="C804" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D804" s="13" t="s">
+      <c r="D804" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E804" s="12" t="s">
@@ -15674,7 +15755,7 @@
       <c r="C805" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D805" s="13" t="s">
+      <c r="D805" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E805" s="12" t="s">
@@ -15696,6 +15777,686 @@
       </c>
       <c r="E806" s="12" t="s">
         <v>374</v>
+      </c>
+    </row>
+    <row r="807" spans="1:5" ht="15">
+      <c r="A807" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B807" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C807" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D807" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E807" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="808" spans="1:5" ht="15">
+      <c r="A808" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B808" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C808" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D808" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E808" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="809" spans="1:5" ht="15">
+      <c r="A809" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B809" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C809" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D809" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E809" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="810" spans="1:5" ht="15">
+      <c r="A810" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C810" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D810" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E810" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="811" spans="1:5" ht="15">
+      <c r="A811" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B811" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C811" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D811" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E811" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="812" spans="1:5" ht="15">
+      <c r="A812" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B812" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C812" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D812" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E812" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="813" spans="1:5" ht="15">
+      <c r="A813" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B813" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C813" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D813" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E813" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="814" spans="1:5" ht="15">
+      <c r="A814" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B814" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C814" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D814" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E814" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="815" spans="1:5" ht="15">
+      <c r="A815" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B815" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C815" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D815" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E815" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="816" spans="1:5" ht="15">
+      <c r="A816" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B816" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C816" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D816" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E816" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="817" spans="1:5" ht="15">
+      <c r="A817" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B817" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C817" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D817" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E817" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="818" spans="1:5" ht="15">
+      <c r="A818" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B818" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C818" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D818" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E818" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="819" spans="1:5" ht="15">
+      <c r="A819" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B819" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C819" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D819" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E819" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="820" spans="1:5" ht="15">
+      <c r="A820" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B820" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C820" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D820" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E820" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="821" spans="1:5" ht="15">
+      <c r="A821" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B821" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C821" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D821" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E821" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="822" spans="1:5" ht="15">
+      <c r="A822" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B822" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C822" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D822" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E822" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="823" spans="1:5" ht="15">
+      <c r="A823" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B823" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C823" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D823" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E823" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="824" spans="1:5" ht="15">
+      <c r="A824" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B824" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C824" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D824" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E824" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="825" spans="1:5" ht="15">
+      <c r="A825" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B825" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C825" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D825" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E825" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="826" spans="1:5" ht="15">
+      <c r="A826" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B826" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C826" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D826" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E826" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="827" spans="1:5" ht="15">
+      <c r="A827" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B827" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C827" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D827" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E827" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="828" spans="1:5" ht="15">
+      <c r="A828" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B828" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C828" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D828" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E828" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="829" spans="1:5" ht="15">
+      <c r="A829" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C829" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D829" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E829" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="830" spans="1:5" ht="15">
+      <c r="A830" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B830" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C830" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D830" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E830" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="831" spans="1:5" ht="15">
+      <c r="A831" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B831" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C831" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D831" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E831" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="832" spans="1:5" ht="15">
+      <c r="A832" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B832" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C832" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D832" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E832" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="833" spans="1:5" ht="15">
+      <c r="A833" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B833" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C833" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D833" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E833" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="834" spans="1:5" ht="15">
+      <c r="A834" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C834" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D834" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E834" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="835" spans="1:5" ht="15">
+      <c r="A835" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B835" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C835" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D835" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E835" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="836" spans="1:5" ht="15">
+      <c r="A836" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B836" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C836" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D836" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E836" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="837" spans="1:5" ht="15">
+      <c r="A837" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B837" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C837" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D837" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E837" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="838" spans="1:5" ht="15">
+      <c r="A838" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B838" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C838" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D838" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E838" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="839" spans="1:5" ht="15">
+      <c r="A839" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B839" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C839" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D839" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E839" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="840" spans="1:5" ht="15">
+      <c r="A840" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B840" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C840" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D840" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E840" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="841" spans="1:5" ht="15">
+      <c r="A841" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C841" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D841" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E841" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="842" spans="1:5" ht="15">
+      <c r="A842" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C842" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D842" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E842" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="843" spans="1:5" ht="15">
+      <c r="A843" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C843" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D843" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E843" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="844" spans="1:5" ht="15">
+      <c r="A844" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B844" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C844" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D844" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E844" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="845" spans="1:5" ht="15">
+      <c r="A845" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B845" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C845" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D845" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E845" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="846" spans="1:5" ht="15">
+      <c r="A846" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B846" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C846" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D846" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E846" s="13" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADD0415-8C94-437E-BAAA-1A371B40EDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FFD26A-5E2F-4ADB-BA14-EAC59D09C293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4380" uniqueCount="528">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1563,6 +1563,66 @@
   </si>
   <si>
     <t>Snake Basket</t>
+  </si>
+  <si>
+    <t>Urza's Power Plant</t>
+  </si>
+  <si>
+    <t>Alabaster Dragon</t>
+  </si>
+  <si>
+    <t>Teferi's Veil</t>
+  </si>
+  <si>
+    <t>Dense Foliage</t>
+  </si>
+  <si>
+    <t>Veteran Explorer</t>
+  </si>
+  <si>
+    <t>Vitalize </t>
+  </si>
+  <si>
+    <t>Mind Stone</t>
+  </si>
+  <si>
+    <t>Bösium Strip</t>
+  </si>
+  <si>
+    <t>Well of Knowledge</t>
+  </si>
+  <si>
+    <t>Chill </t>
+  </si>
+  <si>
+    <t>Perish </t>
+  </si>
+  <si>
+    <t>Heart Sliver</t>
+  </si>
+  <si>
+    <t>Scorched Earth</t>
+  </si>
+  <si>
+    <t>Earthcraft</t>
+  </si>
+  <si>
+    <t>Choke</t>
+  </si>
+  <si>
+    <t>Winter's Grasp</t>
+  </si>
+  <si>
+    <t>Bottle Gnomes</t>
+  </si>
+  <si>
+    <t>Caldera Lake </t>
+  </si>
+  <si>
+    <t>Altar of Dementia</t>
+  </si>
+  <si>
+    <t>Time Warp</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1713,12 +1773,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2068,7 +2122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E846"/>
+  <dimension ref="A1:E876"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -15792,8 +15846,8 @@
       <c r="D807" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E807" s="13" t="s">
-        <v>367</v>
+      <c r="E807" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="808" spans="1:5" ht="15">
@@ -15809,8 +15863,8 @@
       <c r="D808" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E808" s="13" t="s">
-        <v>367</v>
+      <c r="E808" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="809" spans="1:5" ht="15">
@@ -15826,8 +15880,8 @@
       <c r="D809" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E809" s="13" t="s">
-        <v>367</v>
+      <c r="E809" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="810" spans="1:5" ht="15">
@@ -15843,8 +15897,8 @@
       <c r="D810" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E810" s="13" t="s">
-        <v>367</v>
+      <c r="E810" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="811" spans="1:5" ht="15">
@@ -15860,8 +15914,8 @@
       <c r="D811" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E811" s="13" t="s">
-        <v>367</v>
+      <c r="E811" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="812" spans="1:5" ht="15">
@@ -15877,8 +15931,8 @@
       <c r="D812" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E812" s="13" t="s">
-        <v>367</v>
+      <c r="E812" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="813" spans="1:5" ht="15">
@@ -15894,8 +15948,8 @@
       <c r="D813" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E813" s="13" t="s">
-        <v>367</v>
+      <c r="E813" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="814" spans="1:5" ht="15">
@@ -15911,8 +15965,8 @@
       <c r="D814" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E814" s="13" t="s">
-        <v>367</v>
+      <c r="E814" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="815" spans="1:5" ht="15">
@@ -15928,8 +15982,8 @@
       <c r="D815" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E815" s="13" t="s">
-        <v>367</v>
+      <c r="E815" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="816" spans="1:5" ht="15">
@@ -15945,8 +15999,8 @@
       <c r="D816" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E816" s="13" t="s">
-        <v>367</v>
+      <c r="E816" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="817" spans="1:5" ht="15">
@@ -15962,8 +16016,8 @@
       <c r="D817" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E817" s="13" t="s">
-        <v>367</v>
+      <c r="E817" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="818" spans="1:5" ht="15">
@@ -15979,8 +16033,8 @@
       <c r="D818" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E818" s="13" t="s">
-        <v>367</v>
+      <c r="E818" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="819" spans="1:5" ht="15">
@@ -15996,8 +16050,8 @@
       <c r="D819" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E819" s="13" t="s">
-        <v>367</v>
+      <c r="E819" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="820" spans="1:5" ht="15">
@@ -16013,8 +16067,8 @@
       <c r="D820" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E820" s="13" t="s">
-        <v>367</v>
+      <c r="E820" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="821" spans="1:5" ht="15">
@@ -16027,11 +16081,11 @@
       <c r="C821" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D821" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E821" s="13" t="s">
-        <v>367</v>
+      <c r="D821" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E821" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="822" spans="1:5" ht="15">
@@ -16044,11 +16098,11 @@
       <c r="C822" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D822" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E822" s="13" t="s">
-        <v>367</v>
+      <c r="D822" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E822" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="823" spans="1:5" ht="15">
@@ -16061,11 +16115,11 @@
       <c r="C823" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D823" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E823" s="13" t="s">
-        <v>367</v>
+      <c r="D823" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E823" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="824" spans="1:5" ht="15">
@@ -16078,11 +16132,11 @@
       <c r="C824" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D824" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E824" s="13" t="s">
-        <v>367</v>
+      <c r="D824" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E824" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="825" spans="1:5" ht="15">
@@ -16095,11 +16149,11 @@
       <c r="C825" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D825" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E825" s="13" t="s">
-        <v>367</v>
+      <c r="D825" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E825" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="826" spans="1:5" ht="15">
@@ -16112,11 +16166,11 @@
       <c r="C826" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D826" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E826" s="13" t="s">
-        <v>367</v>
+      <c r="D826" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E826" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="827" spans="1:5" ht="15">
@@ -16129,11 +16183,11 @@
       <c r="C827" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D827" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E827" s="13" t="s">
-        <v>367</v>
+      <c r="D827" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E827" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="828" spans="1:5" ht="15">
@@ -16146,11 +16200,11 @@
       <c r="C828" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D828" s="14" t="s">
+      <c r="D828" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E828" s="13" t="s">
-        <v>367</v>
+      <c r="E828" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="829" spans="1:5" ht="15">
@@ -16163,11 +16217,11 @@
       <c r="C829" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D829" s="14" t="s">
+      <c r="D829" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E829" s="13" t="s">
-        <v>367</v>
+      <c r="E829" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="830" spans="1:5" ht="15">
@@ -16180,11 +16234,11 @@
       <c r="C830" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D830" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E830" s="13" t="s">
-        <v>367</v>
+      <c r="D830" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E830" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="831" spans="1:5" ht="15">
@@ -16197,11 +16251,11 @@
       <c r="C831" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D831" s="14" t="s">
+      <c r="D831" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E831" s="13" t="s">
-        <v>367</v>
+      <c r="E831" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="832" spans="1:5" ht="15">
@@ -16214,11 +16268,11 @@
       <c r="C832" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D832" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E832" s="13" t="s">
-        <v>367</v>
+      <c r="D832" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E832" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="833" spans="1:5" ht="15">
@@ -16231,11 +16285,11 @@
       <c r="C833" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D833" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E833" s="13" t="s">
-        <v>367</v>
+      <c r="D833" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E833" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="834" spans="1:5" ht="15">
@@ -16248,11 +16302,11 @@
       <c r="C834" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D834" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E834" s="13" t="s">
-        <v>367</v>
+      <c r="D834" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E834" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="835" spans="1:5" ht="15">
@@ -16265,11 +16319,11 @@
       <c r="C835" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D835" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E835" s="13" t="s">
-        <v>367</v>
+      <c r="D835" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E835" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="836" spans="1:5" ht="15">
@@ -16282,11 +16336,11 @@
       <c r="C836" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D836" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E836" s="13" t="s">
-        <v>367</v>
+      <c r="D836" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E836" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="837" spans="1:5" ht="15">
@@ -16299,11 +16353,11 @@
       <c r="C837" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D837" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E837" s="13" t="s">
-        <v>367</v>
+      <c r="D837" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E837" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="838" spans="1:5" ht="15">
@@ -16316,11 +16370,11 @@
       <c r="C838" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D838" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E838" s="13" t="s">
-        <v>367</v>
+      <c r="D838" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E838" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="839" spans="1:5" ht="15">
@@ -16333,11 +16387,11 @@
       <c r="C839" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D839" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E839" s="13" t="s">
-        <v>367</v>
+      <c r="D839" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E839" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="840" spans="1:5" ht="15">
@@ -16350,11 +16404,11 @@
       <c r="C840" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D840" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E840" s="13" t="s">
-        <v>367</v>
+      <c r="D840" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E840" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="841" spans="1:5" ht="15">
@@ -16367,11 +16421,11 @@
       <c r="C841" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D841" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E841" s="13" t="s">
-        <v>367</v>
+      <c r="D841" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E841" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="842" spans="1:5" ht="15">
@@ -16384,11 +16438,11 @@
       <c r="C842" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D842" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E842" s="13" t="s">
-        <v>367</v>
+      <c r="D842" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E842" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="843" spans="1:5" ht="15">
@@ -16401,11 +16455,11 @@
       <c r="C843" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D843" s="14" t="s">
+      <c r="D843" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E843" s="13" t="s">
-        <v>367</v>
+      <c r="E843" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="844" spans="1:5" ht="15">
@@ -16418,11 +16472,11 @@
       <c r="C844" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D844" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E844" s="13" t="s">
-        <v>367</v>
+      <c r="D844" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E844" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="845" spans="1:5" ht="15">
@@ -16435,11 +16489,11 @@
       <c r="C845" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D845" s="14" t="s">
+      <c r="D845" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E845" s="13" t="s">
-        <v>367</v>
+      <c r="E845" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="846" spans="1:5" ht="15">
@@ -16452,11 +16506,521 @@
       <c r="C846" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D846" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E846" s="13" t="s">
-        <v>367</v>
+      <c r="D846" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E846" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="847" spans="1:5" ht="15">
+      <c r="A847" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B847" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C847" t="s">
+        <v>29</v>
+      </c>
+      <c r="D847" t="s">
+        <v>6</v>
+      </c>
+      <c r="E847" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="848" spans="1:5" ht="15">
+      <c r="A848" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B848" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C848" t="s">
+        <v>29</v>
+      </c>
+      <c r="D848" t="s">
+        <v>3</v>
+      </c>
+      <c r="E848" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="849" spans="1:5" ht="15">
+      <c r="A849" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B849" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C849" t="s">
+        <v>29</v>
+      </c>
+      <c r="D849" t="s">
+        <v>3</v>
+      </c>
+      <c r="E849" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="850" spans="1:5" ht="15">
+      <c r="A850" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B850" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C850" t="s">
+        <v>231</v>
+      </c>
+      <c r="D850" t="s">
+        <v>3</v>
+      </c>
+      <c r="E850" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="851" spans="1:5" ht="15">
+      <c r="A851" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B851" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C851" t="s">
+        <v>29</v>
+      </c>
+      <c r="D851" t="s">
+        <v>3</v>
+      </c>
+      <c r="E851" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="852" spans="1:5" ht="15">
+      <c r="A852" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B852" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C852" t="s">
+        <v>29</v>
+      </c>
+      <c r="D852" t="s">
+        <v>6</v>
+      </c>
+      <c r="E852" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="853" spans="1:5" ht="15">
+      <c r="A853" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B853" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C853" t="s">
+        <v>29</v>
+      </c>
+      <c r="D853" t="s">
+        <v>6</v>
+      </c>
+      <c r="E853" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="854" spans="1:5" ht="15">
+      <c r="A854" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B854" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C854" t="s">
+        <v>29</v>
+      </c>
+      <c r="D854" t="s">
+        <v>3</v>
+      </c>
+      <c r="E854" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="855" spans="1:5" ht="15">
+      <c r="A855" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B855" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C855" t="s">
+        <v>29</v>
+      </c>
+      <c r="D855" t="s">
+        <v>3</v>
+      </c>
+      <c r="E855" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="856" spans="1:5" ht="15">
+      <c r="A856" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B856" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C856" t="s">
+        <v>29</v>
+      </c>
+      <c r="D856" t="s">
+        <v>3</v>
+      </c>
+      <c r="E856" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="857" spans="1:5" ht="15">
+      <c r="A857" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B857" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C857" t="s">
+        <v>29</v>
+      </c>
+      <c r="D857" t="s">
+        <v>3</v>
+      </c>
+      <c r="E857" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="858" spans="1:5" ht="15">
+      <c r="A858" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B858" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C858" t="s">
+        <v>29</v>
+      </c>
+      <c r="D858" t="s">
+        <v>6</v>
+      </c>
+      <c r="E858" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="859" spans="1:5" ht="15">
+      <c r="A859" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B859" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C859" t="s">
+        <v>29</v>
+      </c>
+      <c r="D859" t="s">
+        <v>6</v>
+      </c>
+      <c r="E859" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="860" spans="1:5" ht="15">
+      <c r="A860" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B860" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C860" t="s">
+        <v>29</v>
+      </c>
+      <c r="D860" t="s">
+        <v>6</v>
+      </c>
+      <c r="E860" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="861" spans="1:5" ht="15">
+      <c r="A861" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B861" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C861" t="s">
+        <v>29</v>
+      </c>
+      <c r="D861" t="s">
+        <v>6</v>
+      </c>
+      <c r="E861" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="862" spans="1:5" ht="15">
+      <c r="A862" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B862" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C862" t="s">
+        <v>29</v>
+      </c>
+      <c r="D862" t="s">
+        <v>3</v>
+      </c>
+      <c r="E862" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="863" spans="1:5" ht="15">
+      <c r="A863" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B863" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C863" t="s">
+        <v>29</v>
+      </c>
+      <c r="D863" t="s">
+        <v>6</v>
+      </c>
+      <c r="E863" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="864" spans="1:5" ht="15">
+      <c r="A864" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B864" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C864" t="s">
+        <v>29</v>
+      </c>
+      <c r="D864" t="s">
+        <v>3</v>
+      </c>
+      <c r="E864" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="865" spans="1:5" ht="15">
+      <c r="A865" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B865" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C865" t="s">
+        <v>29</v>
+      </c>
+      <c r="D865" t="s">
+        <v>3</v>
+      </c>
+      <c r="E865" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="866" spans="1:5" ht="15">
+      <c r="A866" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C866" t="s">
+        <v>29</v>
+      </c>
+      <c r="D866" t="s">
+        <v>3</v>
+      </c>
+      <c r="E866" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="867" spans="1:5" ht="15">
+      <c r="A867" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B867" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C867" t="s">
+        <v>29</v>
+      </c>
+      <c r="D867" t="s">
+        <v>6</v>
+      </c>
+      <c r="E867" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="868" spans="1:5" ht="15">
+      <c r="A868" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B868" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C868" t="s">
+        <v>29</v>
+      </c>
+      <c r="D868" t="s">
+        <v>192</v>
+      </c>
+      <c r="E868" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="869" spans="1:5" ht="15">
+      <c r="A869" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B869" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C869" t="s">
+        <v>29</v>
+      </c>
+      <c r="D869" t="s">
+        <v>6</v>
+      </c>
+      <c r="E869" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="870" spans="1:5" ht="15">
+      <c r="A870" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B870" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C870" t="s">
+        <v>29</v>
+      </c>
+      <c r="D870" t="s">
+        <v>42</v>
+      </c>
+      <c r="E870" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="871" spans="1:5" ht="15">
+      <c r="A871" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B871" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C871" t="s">
+        <v>29</v>
+      </c>
+      <c r="D871" t="s">
+        <v>6</v>
+      </c>
+      <c r="E871" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="872" spans="1:5" ht="15">
+      <c r="A872" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B872" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C872" t="s">
+        <v>29</v>
+      </c>
+      <c r="D872" t="s">
+        <v>3</v>
+      </c>
+      <c r="E872" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="873" spans="1:5" ht="15">
+      <c r="A873" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B873" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C873" t="s">
+        <v>29</v>
+      </c>
+      <c r="D873" t="s">
+        <v>3</v>
+      </c>
+      <c r="E873" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="874" spans="1:5" ht="15">
+      <c r="A874" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B874" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C874" t="s">
+        <v>29</v>
+      </c>
+      <c r="D874" t="s">
+        <v>3</v>
+      </c>
+      <c r="E874" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="875" spans="1:5" ht="15">
+      <c r="A875" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B875" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C875" t="s">
+        <v>29</v>
+      </c>
+      <c r="D875" t="s">
+        <v>6</v>
+      </c>
+      <c r="E875" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="876" spans="1:5" ht="15">
+      <c r="A876" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B876" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C876" t="s">
+        <v>29</v>
+      </c>
+      <c r="D876" t="s">
+        <v>6</v>
+      </c>
+      <c r="E876" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FFD26A-5E2F-4ADB-BA14-EAC59D09C293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940515BC-B5EE-4747-8828-E52F6ACF1642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4380" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4385" uniqueCount="528">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2122,7 +2122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E876"/>
+  <dimension ref="A1:E877"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -17023,6 +17023,23 @@
         <v>368</v>
       </c>
     </row>
+    <row r="877" spans="1:5" ht="15">
+      <c r="A877" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B877" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C877" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D877" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E877" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940515BC-B5EE-4747-8828-E52F6ACF1642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B261438-5604-44A6-84E2-9DF90693E1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4385" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5295" uniqueCount="584">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1623,13 +1623,181 @@
   </si>
   <si>
     <t>Time Warp</t>
+  </si>
+  <si>
+    <t>Artifact Ward</t>
+  </si>
+  <si>
+    <t>Reconstruction</t>
+  </si>
+  <si>
+    <t>Artifact Possession</t>
+  </si>
+  <si>
+    <t>Orcish Mechanics</t>
+  </si>
+  <si>
+    <t>Argothian Treefolk</t>
+  </si>
+  <si>
+    <t>Amulet of Kroog</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Clay Statue</t>
+  </si>
+  <si>
+    <t>Dragon Engine</t>
+  </si>
+  <si>
+    <t>Tablet of Epityr</t>
+  </si>
+  <si>
+    <t>Urza's Chalice</t>
+  </si>
+  <si>
+    <t>Yotian Soldier</t>
+  </si>
+  <si>
+    <t>Pirate Ship</t>
+  </si>
+  <si>
+    <t>Kird Ape</t>
+  </si>
+  <si>
+    <t>Crumble</t>
+  </si>
+  <si>
+    <t>Island (V.3)</t>
+  </si>
+  <si>
+    <t>Plains (V.3)</t>
+  </si>
+  <si>
+    <t>Swamp (V.2)</t>
+  </si>
+  <si>
+    <t>Mountain (V.3)</t>
+  </si>
+  <si>
+    <t>Mountain (V.2)</t>
+  </si>
+  <si>
+    <t>Power Surge</t>
+  </si>
+  <si>
+    <t>Titania's Song</t>
+  </si>
+  <si>
+    <t>Millstone </t>
+  </si>
+  <si>
+    <t>Disrupting Scepter</t>
+  </si>
+  <si>
+    <t>Amrou Kithkin</t>
+  </si>
+  <si>
+    <t>Legends </t>
+  </si>
+  <si>
+    <t>Clergy of the Holy Nimbus</t>
+  </si>
+  <si>
+    <t>Anti-Magic Aura</t>
+  </si>
+  <si>
+    <t>Flash Counter</t>
+  </si>
+  <si>
+    <t>Gaseous Form</t>
+  </si>
+  <si>
+    <t>Glyph of Delusion</t>
+  </si>
+  <si>
+    <t>Remove Soul</t>
+  </si>
+  <si>
+    <t>Wall of Vapor</t>
+  </si>
+  <si>
+    <t>Transmutation</t>
+  </si>
+  <si>
+    <t>Active Volcano</t>
+  </si>
+  <si>
+    <t>Blazing Effigy</t>
+  </si>
+  <si>
+    <t>Pyrotechnics </t>
+  </si>
+  <si>
+    <t>Raging Bull</t>
+  </si>
+  <si>
+    <t>The Brute</t>
+  </si>
+  <si>
+    <t>Wall of Earth</t>
+  </si>
+  <si>
+    <t>Aisling Leprechaun</t>
+  </si>
+  <si>
+    <t>Fire Sprites</t>
+  </si>
+  <si>
+    <t>Subdue</t>
+  </si>
+  <si>
+    <t>Rust</t>
+  </si>
+  <si>
+    <t>Fire and Brimstone</t>
+  </si>
+  <si>
+    <t>Electric Eel</t>
+  </si>
+  <si>
+    <t>Ghost Ship</t>
+  </si>
+  <si>
+    <t>Banshee</t>
+  </si>
+  <si>
+    <t>The Fallen</t>
+  </si>
+  <si>
+    <t>Goblin Caves</t>
+  </si>
+  <si>
+    <t>Orc General</t>
+  </si>
+  <si>
+    <t>People of the Woods</t>
+  </si>
+  <si>
+    <t>Scarwood Hag</t>
+  </si>
+  <si>
+    <t>Whippoorwill</t>
+  </si>
+  <si>
+    <t>Standing Stones</t>
+  </si>
+  <si>
+    <t>Evil Presence </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1663,6 +1831,13 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="26.85"/>
+      <color rgb="FFE4E6EB"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1683,7 +1858,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1737,11 +1912,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1773,6 +1957,33 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2122,7 +2333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E877"/>
+  <dimension ref="A1:E1059"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -2754,7 +2965,7 @@
         <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>365</v>
@@ -15744,8 +15955,8 @@
       <c r="D801" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E801" s="7" t="s">
-        <v>375</v>
+      <c r="E801" s="12" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="802" spans="1:5" ht="15">
@@ -15761,8 +15972,8 @@
       <c r="D802" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E802" s="7" t="s">
-        <v>375</v>
+      <c r="E802" s="12" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="803" spans="1:5" ht="15">
@@ -17038,6 +17249,3100 @@
       </c>
       <c r="E877" s="2" t="s">
         <v>368</v>
+      </c>
+    </row>
+    <row r="878" spans="1:5" ht="15">
+      <c r="A878" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="B878" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C878" t="s">
+        <v>2</v>
+      </c>
+      <c r="D878" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E878" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="879" spans="1:5" ht="15">
+      <c r="A879" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="B879" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C879" t="s">
+        <v>2</v>
+      </c>
+      <c r="D879" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E879" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="880" spans="1:5" ht="15">
+      <c r="A880" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="B880" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C880" t="s">
+        <v>2</v>
+      </c>
+      <c r="D880" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E880" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="881" spans="1:5" ht="15">
+      <c r="A881" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="B881" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C881" t="s">
+        <v>2</v>
+      </c>
+      <c r="D881" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E881" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="882" spans="1:5" ht="15">
+      <c r="A882" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B882" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C882" t="s">
+        <v>2</v>
+      </c>
+      <c r="D882" t="s">
+        <v>3</v>
+      </c>
+      <c r="E882" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="883" spans="1:5" ht="15">
+      <c r="A883" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B883" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C883" t="s">
+        <v>2</v>
+      </c>
+      <c r="D883" t="s">
+        <v>6</v>
+      </c>
+      <c r="E883" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="884" spans="1:5" ht="15">
+      <c r="A884" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B884" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C884" t="s">
+        <v>2</v>
+      </c>
+      <c r="D884" t="s">
+        <v>3</v>
+      </c>
+      <c r="E884" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="885" spans="1:5" ht="15">
+      <c r="A885" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B885" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C885" t="s">
+        <v>2</v>
+      </c>
+      <c r="D885" t="s">
+        <v>6</v>
+      </c>
+      <c r="E885" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="886" spans="1:5" ht="15">
+      <c r="A886" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B886" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C886" t="s">
+        <v>2</v>
+      </c>
+      <c r="D886" t="s">
+        <v>3</v>
+      </c>
+      <c r="E886" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="887" spans="1:5" ht="15">
+      <c r="A887" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B887" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C887" t="s">
+        <v>2</v>
+      </c>
+      <c r="D887" t="s">
+        <v>3</v>
+      </c>
+      <c r="E887" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="888" spans="1:5" ht="15">
+      <c r="A888" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B888" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C888" t="s">
+        <v>2</v>
+      </c>
+      <c r="D888" t="s">
+        <v>6</v>
+      </c>
+      <c r="E888" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="889" spans="1:5" ht="15">
+      <c r="A889" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B889" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C889" t="s">
+        <v>2</v>
+      </c>
+      <c r="D889" t="s">
+        <v>3</v>
+      </c>
+      <c r="E889" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="890" spans="1:5" ht="77">
+      <c r="A890" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="B890" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C890" t="s">
+        <v>2</v>
+      </c>
+      <c r="D890" t="s">
+        <v>6</v>
+      </c>
+      <c r="E890" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="891" spans="1:5" ht="77">
+      <c r="A891" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="B891" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C891" t="s">
+        <v>2</v>
+      </c>
+      <c r="D891" t="s">
+        <v>6</v>
+      </c>
+      <c r="E891" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="892" spans="1:5" ht="15">
+      <c r="A892" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B892" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C892" t="s">
+        <v>2</v>
+      </c>
+      <c r="D892" t="s">
+        <v>6</v>
+      </c>
+      <c r="E892" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="893" spans="1:5" ht="15">
+      <c r="A893" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B893" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C893" t="s">
+        <v>2</v>
+      </c>
+      <c r="D893" t="s">
+        <v>3</v>
+      </c>
+      <c r="E893" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="894" spans="1:5" ht="15">
+      <c r="A894" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B894" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C894" t="s">
+        <v>2</v>
+      </c>
+      <c r="D894" t="s">
+        <v>6</v>
+      </c>
+      <c r="E894" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="895" spans="1:5" ht="15">
+      <c r="A895" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B895" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C895" t="s">
+        <v>2</v>
+      </c>
+      <c r="D895" t="s">
+        <v>6</v>
+      </c>
+      <c r="E895" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="896" spans="1:5" ht="77">
+      <c r="A896" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="B896" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C896" t="s">
+        <v>2</v>
+      </c>
+      <c r="D896" t="s">
+        <v>6</v>
+      </c>
+      <c r="E896" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="897" spans="1:5" ht="77">
+      <c r="A897" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="B897" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C897" t="s">
+        <v>2</v>
+      </c>
+      <c r="D897" t="s">
+        <v>6</v>
+      </c>
+      <c r="E897" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="898" spans="1:5" ht="15">
+      <c r="A898" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B898" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C898" t="s">
+        <v>2</v>
+      </c>
+      <c r="D898" t="s">
+        <v>6</v>
+      </c>
+      <c r="E898" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="899" spans="1:5" ht="15">
+      <c r="A899" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B899" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C899" t="s">
+        <v>2</v>
+      </c>
+      <c r="D899" t="s">
+        <v>42</v>
+      </c>
+      <c r="E899" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="900" spans="1:5" ht="15">
+      <c r="A900" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B900" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C900" t="s">
+        <v>2</v>
+      </c>
+      <c r="D900" t="s">
+        <v>31</v>
+      </c>
+      <c r="E900" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="901" spans="1:5" ht="15">
+      <c r="A901" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B901" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C901" t="s">
+        <v>29</v>
+      </c>
+      <c r="D901" t="s">
+        <v>192</v>
+      </c>
+      <c r="E901" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="902" spans="1:5" ht="15">
+      <c r="A902" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B902" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C902" t="s">
+        <v>29</v>
+      </c>
+      <c r="D902" t="s">
+        <v>6</v>
+      </c>
+      <c r="E902" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="903" spans="1:5" ht="15">
+      <c r="A903" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B903" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C903" t="s">
+        <v>29</v>
+      </c>
+      <c r="D903" t="s">
+        <v>3</v>
+      </c>
+      <c r="E903" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="904" spans="1:5" ht="15">
+      <c r="A904" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B904" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C904" t="s">
+        <v>29</v>
+      </c>
+      <c r="D904" t="s">
+        <v>3</v>
+      </c>
+      <c r="E904" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="905" spans="1:5" ht="15">
+      <c r="A905" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B905" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C905" t="s">
+        <v>29</v>
+      </c>
+      <c r="D905" t="s">
+        <v>3</v>
+      </c>
+      <c r="E905" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="906" spans="1:5" ht="15">
+      <c r="A906" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B906" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C906" t="s">
+        <v>29</v>
+      </c>
+      <c r="D906" t="s">
+        <v>3</v>
+      </c>
+      <c r="E906" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="907" spans="1:5">
+      <c r="A907" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B907" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C907" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D907" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E907" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="908" spans="1:5">
+      <c r="A908" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="B908" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C908" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D908" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E908" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="909" spans="1:5">
+      <c r="A909" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B909" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C909" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D909" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E909" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="910" spans="1:5">
+      <c r="A910" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B910" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C910" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D910" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E910" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="911" spans="1:5">
+      <c r="A911" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B911" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C911" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D911" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E911" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="912" spans="1:5">
+      <c r="A912" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B912" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C912" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D912" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E912" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="913" spans="1:5">
+      <c r="A913" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B913" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C913" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D913" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E913" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="914" spans="1:5">
+      <c r="A914" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B914" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C914" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D914" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E914" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="915" spans="1:5">
+      <c r="A915" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B915" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C915" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D915" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E915" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="916" spans="1:5">
+      <c r="A916" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B916" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C916" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D916" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E916" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="917" spans="1:5">
+      <c r="A917" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B917" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C917" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D917" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E917" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="918" spans="1:5">
+      <c r="A918" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B918" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C918" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D918" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E918" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="919" spans="1:5">
+      <c r="A919" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B919" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C919" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D919" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E919" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="920" spans="1:5">
+      <c r="A920" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B920" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C920" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D920" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E920" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="921" spans="1:5">
+      <c r="A921" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="B921" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C921" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D921" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E921" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="922" spans="1:5">
+      <c r="A922" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="B922" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C922" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D922" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E922" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="923" spans="1:5">
+      <c r="A923" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="B923" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C923" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D923" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E923" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="924" spans="1:5">
+      <c r="A924" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="B924" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C924" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D924" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E924" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="925" spans="1:5">
+      <c r="A925" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B925" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C925" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D925" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E925" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="926" spans="1:5">
+      <c r="A926" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B926" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C926" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D926" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E926" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="927" spans="1:5">
+      <c r="A927" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B927" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C927" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D927" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E927" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="928" spans="1:5">
+      <c r="A928" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B928" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C928" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D928" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E928" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="929" spans="1:5">
+      <c r="A929" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B929" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C929" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D929" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E929" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="930" spans="1:5">
+      <c r="A930" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B930" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C930" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D930" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E930" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="931" spans="1:5">
+      <c r="A931" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B931" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C931" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D931" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E931" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="932" spans="1:5">
+      <c r="A932" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B932" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C932" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D932" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E932" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="933" spans="1:5">
+      <c r="A933" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B933" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C933" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D933" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E933" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="934" spans="1:5">
+      <c r="A934" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B934" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C934" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D934" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E934" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="935" spans="1:5">
+      <c r="A935" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B935" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C935" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D935" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E935" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="936" spans="1:5">
+      <c r="A936" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B936" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C936" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D936" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E936" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="937" spans="1:5">
+      <c r="A937" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B937" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C937" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D937" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E937" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="938" spans="1:5">
+      <c r="A938" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B938" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C938" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D938" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E938" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="939" spans="1:5">
+      <c r="A939" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B939" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C939" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D939" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E939" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="940" spans="1:5">
+      <c r="A940" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B940" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C940" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D940" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E940" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="941" spans="1:5">
+      <c r="A941" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B941" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C941" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D941" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E941" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="942" spans="1:5">
+      <c r="A942" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B942" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C942" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D942" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E942" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="943" spans="1:5">
+      <c r="A943" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B943" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C943" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D943" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E943" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="944" spans="1:5">
+      <c r="A944" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B944" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C944" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D944" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E944" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="945" spans="1:5">
+      <c r="A945" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B945" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C945" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D945" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E945" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="946" spans="1:5">
+      <c r="A946" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B946" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C946" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D946" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E946" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="947" spans="1:5">
+      <c r="A947" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B947" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C947" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D947" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E947" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="948" spans="1:5">
+      <c r="A948" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B948" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C948" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D948" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E948" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="949" spans="1:5">
+      <c r="A949" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B949" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C949" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D949" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E949" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="950" spans="1:5">
+      <c r="A950" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B950" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C950" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D950" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E950" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="951" spans="1:5">
+      <c r="A951" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B951" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C951" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D951" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E951" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="952" spans="1:5">
+      <c r="A952" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B952" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C952" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D952" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E952" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="953" spans="1:5">
+      <c r="A953" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B953" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C953" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D953" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E953" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="954" spans="1:5">
+      <c r="A954" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B954" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C954" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D954" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E954" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="955" spans="1:5">
+      <c r="A955" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B955" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C955" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D955" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E955" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="956" spans="1:5">
+      <c r="A956" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B956" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C956" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D956" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E956" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="957" spans="1:5">
+      <c r="A957" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B957" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C957" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D957" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E957" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="958" spans="1:5">
+      <c r="A958" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B958" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C958" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D958" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E958" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="959" spans="1:5">
+      <c r="A959" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B959" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C959" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D959" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E959" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="960" spans="1:5">
+      <c r="A960" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B960" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C960" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D960" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E960" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="961" spans="1:5">
+      <c r="A961" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B961" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C961" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D961" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E961" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="962" spans="1:5">
+      <c r="A962" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B962" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C962" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D962" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E962" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="963" spans="1:5">
+      <c r="A963" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B963" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C963" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D963" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E963" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="964" spans="1:5">
+      <c r="A964" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B964" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C964" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D964" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E964" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="965" spans="1:5">
+      <c r="A965" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B965" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C965" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D965" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E965" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="966" spans="1:5">
+      <c r="A966" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B966" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C966" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D966" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E966" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="967" spans="1:5">
+      <c r="A967" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B967" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C967" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D967" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E967" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="968" spans="1:5">
+      <c r="A968" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B968" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C968" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D968" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E968" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="969" spans="1:5">
+      <c r="A969" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B969" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C969" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D969" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E969" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="970" spans="1:5">
+      <c r="A970" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B970" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C970" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D970" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E970" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="971" spans="1:5">
+      <c r="A971" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B971" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C971" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D971" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E971" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="972" spans="1:5">
+      <c r="A972" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B972" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C972" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D972" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E972" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="973" spans="1:5">
+      <c r="A973" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B973" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C973" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D973" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E973" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="974" spans="1:5">
+      <c r="A974" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B974" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C974" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D974" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E974" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="975" spans="1:5">
+      <c r="A975" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B975" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C975" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D975" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E975" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="976" spans="1:5">
+      <c r="A976" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B976" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C976" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D976" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E976" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="977" spans="1:5">
+      <c r="A977" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B977" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C977" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D977" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E977" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="978" spans="1:5">
+      <c r="A978" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B978" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C978" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D978" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E978" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="979" spans="1:5">
+      <c r="A979" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B979" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C979" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D979" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E979" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="980" spans="1:5">
+      <c r="A980" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B980" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C980" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D980" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E980" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="981" spans="1:5">
+      <c r="A981" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B981" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C981" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D981" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E981" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="982" spans="1:5">
+      <c r="A982" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B982" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C982" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D982" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E982" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="983" spans="1:5">
+      <c r="A983" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B983" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C983" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D983" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E983" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="984" spans="1:5">
+      <c r="A984" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B984" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C984" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D984" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E984" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="985" spans="1:5">
+      <c r="A985" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B985" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C985" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D985" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E985" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="986" spans="1:5">
+      <c r="A986" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B986" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C986" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D986" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E986" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="987" spans="1:5">
+      <c r="A987" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B987" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C987" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D987" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E987" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="988" spans="1:5">
+      <c r="A988" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="B988" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C988" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D988" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E988" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="989" spans="1:5">
+      <c r="A989" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B989" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C989" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D989" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E989" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="990" spans="1:5">
+      <c r="A990" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B990" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C990" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D990" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E990" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="991" spans="1:5">
+      <c r="A991" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B991" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C991" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D991" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E991" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="992" spans="1:5">
+      <c r="A992" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B992" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C992" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D992" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E992" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="993" spans="1:5">
+      <c r="A993" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B993" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C993" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D993" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E993" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="994" spans="1:5">
+      <c r="A994" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B994" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C994" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D994" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E994" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="995" spans="1:5">
+      <c r="A995" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B995" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C995" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D995" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E995" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="996" spans="1:5">
+      <c r="A996" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="B996" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C996" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D996" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E996" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="997" spans="1:5">
+      <c r="A997" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="B997" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C997" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D997" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E997" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="998" spans="1:5">
+      <c r="A998" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="B998" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C998" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D998" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E998" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="999" spans="1:5">
+      <c r="A999" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="B999" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C999" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D999" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E999" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:5">
+      <c r="A1000" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1000" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1000" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1000" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1000" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:5">
+      <c r="A1001" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1001" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1001" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1001" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1001" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:5">
+      <c r="A1002" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1002" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1002" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1002" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1002" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:5">
+      <c r="A1003" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1003" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1003" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1003" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1003" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:5">
+      <c r="A1004" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1004" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1004" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1004" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1004" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:5">
+      <c r="A1005" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1005" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1005" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1005" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1005" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:5">
+      <c r="A1006" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1006" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1006" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1006" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1006" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:5">
+      <c r="A1007" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1007" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1007" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1007" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1007" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:5">
+      <c r="A1008" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1008" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1008" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1008" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1008" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:5">
+      <c r="A1009" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1009" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1009" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1009" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1009" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:5">
+      <c r="A1010" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1010" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1010" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1010" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1010" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:5">
+      <c r="A1011" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1011" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1011" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1011" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1011" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:5">
+      <c r="A1012" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1012" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1012" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1012" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1012" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:5">
+      <c r="A1013" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1013" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1013" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1013" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1013" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:5">
+      <c r="A1014" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1014" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1014" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1014" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1014" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:5">
+      <c r="A1015" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1015" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1015" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1015" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1015" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:5">
+      <c r="A1016" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1016" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1016" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1016" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1016" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:5">
+      <c r="A1017" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1017" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1017" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1017" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1017" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:5">
+      <c r="A1018" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1018" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1018" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1018" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1018" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:5" ht="15">
+      <c r="A1019" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B1019" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1019" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1019" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1019" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:5" ht="15">
+      <c r="A1020" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1020" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1020" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1020" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1020" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:5" ht="15">
+      <c r="A1021" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B1021" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1021" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1021" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1021" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:5" ht="15">
+      <c r="A1022" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B1022" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1022" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1022" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1022" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:5" ht="15">
+      <c r="A1023" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1023" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1023" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1023" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1023" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:5" ht="15">
+      <c r="A1024" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B1024" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1024" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1024" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1024" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:5" ht="15">
+      <c r="A1025" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B1025" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1025" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1025" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1025" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:5" ht="15">
+      <c r="A1026" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B1026" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1026" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1026" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1026" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:5" ht="15">
+      <c r="A1027" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B1027" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1027" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1027" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1027" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:5" ht="15">
+      <c r="A1028" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B1028" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1028" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1028" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1028" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:5" ht="15">
+      <c r="A1029" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B1029" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1029" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1029" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1029" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:5" ht="15">
+      <c r="A1030" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B1030" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1030" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1030" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1030" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:5" ht="15">
+      <c r="A1031" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B1031" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1031" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1031" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1031" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:5" ht="15">
+      <c r="A1032" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B1032" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1032" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1032" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1032" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:5" ht="15">
+      <c r="A1033" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B1033" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1033" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1033" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1033" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:5" ht="15">
+      <c r="A1034" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B1034" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1034" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1034" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1034" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:5" ht="15">
+      <c r="A1035" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B1035" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1035" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1035" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1035" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:5" ht="15">
+      <c r="A1036" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B1036" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1036" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1036" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1036" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:5" ht="15">
+      <c r="A1037" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B1037" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1037" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1037" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1037" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:5" ht="15">
+      <c r="A1038" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B1038" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1038" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1038" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1038" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:5" ht="15">
+      <c r="A1039" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B1039" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1039" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1039" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1039" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:5" ht="15">
+      <c r="A1040" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B1040" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1040" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1040" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1040" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:5" ht="15">
+      <c r="A1041" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B1041" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1041" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1041" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1041" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:5" ht="15">
+      <c r="A1042" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B1042" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1042" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1042" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1042" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:5" ht="15">
+      <c r="A1043" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B1043" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1043" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1043" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1043" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:5" ht="15">
+      <c r="A1044" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B1044" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1044" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1044" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1044" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:5" ht="15">
+      <c r="A1045" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B1045" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1045" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1045" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1045" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:5" ht="15">
+      <c r="A1046" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B1046" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1046" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1046" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1046" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:5" ht="15">
+      <c r="A1047" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B1047" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1047" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1047" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1047" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:5" ht="15">
+      <c r="A1048" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B1048" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1048" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1048" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1048" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:5" ht="15">
+      <c r="A1049" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B1049" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1049" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1049" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1049" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:5" ht="15">
+      <c r="A1050" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B1050" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1050" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1050" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1050" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:5" ht="15">
+      <c r="A1051" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B1051" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1051" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1051" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1051" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:5" ht="15">
+      <c r="A1052" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B1052" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1052" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1052" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1052" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:5" ht="15">
+      <c r="A1053" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B1053" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1053" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1053" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1053" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:5" ht="15">
+      <c r="A1054" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B1054" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1054" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1054" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1054" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:5" ht="15">
+      <c r="A1055" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B1055" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1055" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1055" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1055" s="20" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:5" ht="15">
+      <c r="A1056" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1056" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1056" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1056" s="20" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:5" ht="15">
+      <c r="A1057" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1057" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1057" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1057" s="20" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:5" ht="15">
+      <c r="A1058" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1058" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1058" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1058" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1058" s="20" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:5" ht="15">
+      <c r="A1059" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1059" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1059" s="2" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B261438-5604-44A6-84E2-9DF90693E1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B05A57-1855-4644-AF4F-2FBA94DB0B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5295" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5300" uniqueCount="584">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1925,7 +1925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1962,28 +1962,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2333,7 +2321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1059"/>
+  <dimension ref="A1:E1060"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -17745,1906 +17733,1906 @@
       </c>
     </row>
     <row r="907" spans="1:5">
-      <c r="A907" s="14" t="s">
+      <c r="A907" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B907" s="15" t="s">
+      <c r="B907" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C907" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D907" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E907" s="16" t="s">
+      <c r="C907" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D907" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E907" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="908" spans="1:5">
-      <c r="A908" s="14" t="s">
+      <c r="A908" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="B908" s="15" t="s">
+      <c r="B908" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C908" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D908" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E908" s="16" t="s">
+      <c r="C908" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D908" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E908" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="909" spans="1:5">
-      <c r="A909" s="14" t="s">
+      <c r="A909" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B909" s="15" t="s">
+      <c r="B909" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C909" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D909" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E909" s="18" t="s">
+      <c r="C909" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D909" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E909" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="910" spans="1:5">
-      <c r="A910" s="14" t="s">
+      <c r="A910" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B910" s="15" t="s">
+      <c r="B910" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C910" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D910" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E910" s="18" t="s">
+      <c r="C910" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D910" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E910" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="911" spans="1:5">
-      <c r="A911" s="14" t="s">
+      <c r="A911" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B911" s="15" t="s">
+      <c r="B911" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C911" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D911" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E911" s="18" t="s">
+      <c r="C911" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D911" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E911" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="912" spans="1:5">
-      <c r="A912" s="14" t="s">
+      <c r="A912" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B912" s="15" t="s">
+      <c r="B912" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C912" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D912" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E912" s="18" t="s">
+      <c r="C912" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D912" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E912" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="913" spans="1:5">
-      <c r="A913" s="14" t="s">
+      <c r="A913" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B913" s="15" t="s">
+      <c r="B913" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C913" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D913" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E913" s="18" t="s">
+      <c r="C913" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D913" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E913" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="914" spans="1:5">
-      <c r="A914" s="14" t="s">
+      <c r="A914" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B914" s="15" t="s">
+      <c r="B914" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C914" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D914" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E914" s="18" t="s">
+      <c r="C914" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D914" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E914" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="915" spans="1:5">
-      <c r="A915" s="14" t="s">
+      <c r="A915" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B915" s="15" t="s">
+      <c r="B915" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C915" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D915" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E915" s="18" t="s">
+      <c r="C915" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D915" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E915" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="916" spans="1:5">
-      <c r="A916" s="14" t="s">
+      <c r="A916" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B916" s="15" t="s">
+      <c r="B916" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C916" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D916" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E916" s="18" t="s">
+      <c r="C916" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D916" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E916" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="917" spans="1:5">
-      <c r="A917" s="14" t="s">
+      <c r="A917" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B917" s="15" t="s">
+      <c r="B917" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C917" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D917" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E917" s="18" t="s">
+      <c r="C917" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D917" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E917" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="918" spans="1:5">
-      <c r="A918" s="14" t="s">
+      <c r="A918" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B918" s="15" t="s">
+      <c r="B918" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C918" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D918" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E918" s="18" t="s">
+      <c r="C918" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D918" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E918" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="919" spans="1:5">
-      <c r="A919" s="14" t="s">
+      <c r="A919" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B919" s="15" t="s">
+      <c r="B919" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C919" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D919" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E919" s="18" t="s">
+      <c r="C919" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D919" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E919" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="920" spans="1:5">
-      <c r="A920" s="14" t="s">
+      <c r="A920" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B920" s="15" t="s">
+      <c r="B920" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C920" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D920" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E920" s="18" t="s">
+      <c r="C920" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D920" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E920" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="921" spans="1:5">
-      <c r="A921" s="14" t="s">
+      <c r="A921" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="B921" s="15" t="s">
+      <c r="B921" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C921" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D921" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E921" s="18" t="s">
+      <c r="C921" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D921" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E921" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="922" spans="1:5">
-      <c r="A922" s="14" t="s">
+      <c r="A922" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="B922" s="15" t="s">
+      <c r="B922" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C922" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D922" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E922" s="18" t="s">
+      <c r="C922" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D922" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E922" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="923" spans="1:5">
-      <c r="A923" s="14" t="s">
+      <c r="A923" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="B923" s="15" t="s">
+      <c r="B923" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C923" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D923" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E923" s="18" t="s">
+      <c r="C923" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D923" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E923" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="924" spans="1:5">
-      <c r="A924" s="14" t="s">
+      <c r="A924" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="B924" s="15" t="s">
+      <c r="B924" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C924" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D924" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E924" s="18" t="s">
+      <c r="C924" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D924" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E924" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="925" spans="1:5">
-      <c r="A925" s="14" t="s">
+      <c r="A925" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B925" s="15" t="s">
+      <c r="B925" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C925" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D925" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E925" s="16" t="s">
+      <c r="C925" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D925" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E925" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="926" spans="1:5">
-      <c r="A926" s="14" t="s">
+      <c r="A926" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B926" s="15" t="s">
+      <c r="B926" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C926" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D926" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E926" s="16" t="s">
+      <c r="C926" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D926" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E926" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="927" spans="1:5">
-      <c r="A927" s="14" t="s">
+      <c r="A927" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B927" s="15" t="s">
+      <c r="B927" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C927" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D927" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E927" s="16" t="s">
+      <c r="C927" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D927" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E927" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="928" spans="1:5">
-      <c r="A928" s="14" t="s">
+      <c r="A928" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B928" s="15" t="s">
+      <c r="B928" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C928" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D928" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E928" s="16" t="s">
+      <c r="C928" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D928" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E928" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="929" spans="1:5">
-      <c r="A929" s="14" t="s">
+      <c r="A929" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B929" s="15" t="s">
+      <c r="B929" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C929" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D929" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E929" s="16" t="s">
+      <c r="C929" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D929" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E929" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="930" spans="1:5">
-      <c r="A930" s="14" t="s">
+      <c r="A930" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B930" s="15" t="s">
+      <c r="B930" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C930" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D930" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E930" s="16" t="s">
+      <c r="C930" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D930" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E930" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="931" spans="1:5">
-      <c r="A931" s="14" t="s">
+      <c r="A931" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B931" s="15" t="s">
+      <c r="B931" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C931" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D931" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E931" s="16" t="s">
+      <c r="C931" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D931" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E931" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="932" spans="1:5">
-      <c r="A932" s="14" t="s">
+      <c r="A932" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B932" s="15" t="s">
+      <c r="B932" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C932" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D932" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E932" s="16" t="s">
+      <c r="C932" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D932" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E932" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="933" spans="1:5">
-      <c r="A933" s="14" t="s">
+      <c r="A933" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B933" s="15" t="s">
+      <c r="B933" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C933" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D933" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E933" s="16" t="s">
+      <c r="C933" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D933" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E933" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="934" spans="1:5">
-      <c r="A934" s="14" t="s">
+      <c r="A934" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B934" s="15" t="s">
+      <c r="B934" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C934" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D934" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E934" s="16" t="s">
+      <c r="C934" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D934" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E934" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="935" spans="1:5">
-      <c r="A935" s="14" t="s">
+      <c r="A935" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B935" s="15" t="s">
+      <c r="B935" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C935" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D935" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E935" s="16" t="s">
+      <c r="C935" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D935" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E935" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="936" spans="1:5">
-      <c r="A936" s="14" t="s">
+      <c r="A936" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B936" s="15" t="s">
+      <c r="B936" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C936" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D936" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E936" s="16" t="s">
+      <c r="C936" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D936" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E936" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="937" spans="1:5">
-      <c r="A937" s="14" t="s">
+      <c r="A937" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B937" s="15" t="s">
+      <c r="B937" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C937" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D937" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E937" s="16" t="s">
+      <c r="C937" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D937" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E937" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="938" spans="1:5">
-      <c r="A938" s="14" t="s">
+      <c r="A938" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B938" s="15" t="s">
+      <c r="B938" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C938" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D938" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E938" s="16" t="s">
+      <c r="C938" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D938" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E938" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="939" spans="1:5">
-      <c r="A939" s="14" t="s">
+      <c r="A939" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B939" s="15" t="s">
+      <c r="B939" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C939" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D939" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E939" s="16" t="s">
+      <c r="C939" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D939" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E939" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="940" spans="1:5">
-      <c r="A940" s="14" t="s">
+      <c r="A940" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B940" s="15" t="s">
+      <c r="B940" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C940" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D940" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E940" s="16" t="s">
+      <c r="C940" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D940" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E940" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="941" spans="1:5">
-      <c r="A941" s="14" t="s">
+      <c r="A941" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B941" s="15" t="s">
+      <c r="B941" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C941" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D941" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E941" s="16" t="s">
+      <c r="C941" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D941" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E941" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="942" spans="1:5">
-      <c r="A942" s="14" t="s">
+      <c r="A942" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B942" s="15" t="s">
+      <c r="B942" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C942" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D942" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E942" s="16" t="s">
+      <c r="C942" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D942" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E942" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="943" spans="1:5">
-      <c r="A943" s="14" t="s">
+      <c r="A943" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B943" s="15" t="s">
+      <c r="B943" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C943" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D943" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E943" s="16" t="s">
+      <c r="C943" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D943" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E943" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="944" spans="1:5">
-      <c r="A944" s="14" t="s">
+      <c r="A944" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B944" s="15" t="s">
+      <c r="B944" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C944" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D944" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E944" s="16" t="s">
+      <c r="C944" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D944" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E944" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="945" spans="1:5">
-      <c r="A945" s="14" t="s">
+      <c r="A945" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B945" s="15" t="s">
+      <c r="B945" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C945" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D945" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E945" s="16" t="s">
+      <c r="C945" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D945" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E945" s="10" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="946" spans="1:5">
-      <c r="A946" s="19" t="s">
+      <c r="A946" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B946" s="15" t="s">
+      <c r="B946" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C946" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D946" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E946" s="16" t="s">
+      <c r="C946" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D946" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E946" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="947" spans="1:5">
-      <c r="A947" s="19" t="s">
+      <c r="A947" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="B947" s="15" t="s">
+      <c r="B947" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C947" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D947" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E947" s="16" t="s">
+      <c r="C947" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D947" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E947" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="948" spans="1:5">
-      <c r="A948" s="19" t="s">
+      <c r="A948" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B948" s="15" t="s">
+      <c r="B948" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C948" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D948" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E948" s="16" t="s">
+      <c r="C948" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D948" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E948" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="949" spans="1:5">
-      <c r="A949" s="19" t="s">
+      <c r="A949" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B949" s="15" t="s">
+      <c r="B949" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C949" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D949" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E949" s="16" t="s">
+      <c r="C949" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D949" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E949" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="950" spans="1:5">
-      <c r="A950" s="19" t="s">
+      <c r="A950" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B950" s="15" t="s">
+      <c r="B950" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C950" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D950" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E950" s="16" t="s">
+      <c r="C950" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D950" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E950" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="951" spans="1:5">
-      <c r="A951" s="19" t="s">
+      <c r="A951" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B951" s="15" t="s">
+      <c r="B951" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C951" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D951" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E951" s="16" t="s">
+      <c r="C951" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D951" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E951" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="952" spans="1:5">
-      <c r="A952" s="19" t="s">
+      <c r="A952" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="B952" s="15" t="s">
+      <c r="B952" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C952" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D952" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E952" s="16" t="s">
+      <c r="C952" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D952" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E952" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="953" spans="1:5">
-      <c r="A953" s="19" t="s">
+      <c r="A953" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="B953" s="15" t="s">
+      <c r="B953" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C953" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D953" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E953" s="16" t="s">
+      <c r="C953" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D953" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E953" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="954" spans="1:5">
-      <c r="A954" s="19" t="s">
+      <c r="A954" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="B954" s="15" t="s">
+      <c r="B954" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C954" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D954" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E954" s="16" t="s">
+      <c r="C954" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D954" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E954" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="955" spans="1:5">
-      <c r="A955" s="19" t="s">
+      <c r="A955" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="B955" s="15" t="s">
+      <c r="B955" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C955" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D955" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E955" s="16" t="s">
+      <c r="C955" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D955" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E955" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="956" spans="1:5">
-      <c r="A956" s="19" t="s">
+      <c r="A956" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="B956" s="15" t="s">
+      <c r="B956" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C956" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D956" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E956" s="16" t="s">
+      <c r="C956" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D956" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E956" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="957" spans="1:5">
-      <c r="A957" s="19" t="s">
+      <c r="A957" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="B957" s="15" t="s">
+      <c r="B957" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C957" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D957" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E957" s="16" t="s">
+      <c r="C957" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D957" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E957" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="958" spans="1:5">
-      <c r="A958" s="19" t="s">
+      <c r="A958" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B958" s="15" t="s">
+      <c r="B958" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C958" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D958" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E958" s="16" t="s">
+      <c r="C958" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D958" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E958" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="959" spans="1:5">
-      <c r="A959" s="19" t="s">
+      <c r="A959" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B959" s="15" t="s">
+      <c r="B959" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C959" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D959" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E959" s="16" t="s">
+      <c r="C959" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D959" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E959" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="960" spans="1:5">
-      <c r="A960" s="19" t="s">
+      <c r="A960" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B960" s="15" t="s">
+      <c r="B960" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C960" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D960" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E960" s="16" t="s">
+      <c r="C960" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D960" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E960" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="961" spans="1:5">
-      <c r="A961" s="19" t="s">
+      <c r="A961" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B961" s="15" t="s">
+      <c r="B961" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C961" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D961" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E961" s="16" t="s">
+      <c r="C961" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D961" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E961" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="962" spans="1:5">
-      <c r="A962" s="19" t="s">
+      <c r="A962" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B962" s="15" t="s">
+      <c r="B962" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C962" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D962" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E962" s="16" t="s">
+      <c r="C962" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D962" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E962" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="963" spans="1:5">
-      <c r="A963" s="19" t="s">
+      <c r="A963" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B963" s="15" t="s">
+      <c r="B963" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C963" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D963" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E963" s="16" t="s">
+      <c r="C963" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D963" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E963" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="964" spans="1:5">
-      <c r="A964" s="19" t="s">
+      <c r="A964" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B964" s="15" t="s">
+      <c r="B964" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C964" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D964" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E964" s="16" t="s">
+      <c r="C964" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D964" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E964" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="965" spans="1:5">
-      <c r="A965" s="19" t="s">
+      <c r="A965" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B965" s="15" t="s">
+      <c r="B965" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C965" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D965" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E965" s="16" t="s">
+      <c r="C965" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D965" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E965" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="966" spans="1:5">
-      <c r="A966" s="19" t="s">
+      <c r="A966" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B966" s="15" t="s">
+      <c r="B966" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C966" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D966" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E966" s="16" t="s">
+      <c r="C966" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D966" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E966" s="10" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="967" spans="1:5">
-      <c r="A967" s="19" t="s">
+      <c r="A967" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B967" s="15" t="s">
+      <c r="B967" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C967" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D967" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E967" s="16" t="s">
+      <c r="C967" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D967" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E967" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="968" spans="1:5">
-      <c r="A968" s="19" t="s">
+      <c r="A968" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B968" s="15" t="s">
+      <c r="B968" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C968" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D968" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E968" s="16" t="s">
+      <c r="C968" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D968" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E968" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="969" spans="1:5">
-      <c r="A969" s="19" t="s">
+      <c r="A969" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B969" s="15" t="s">
+      <c r="B969" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C969" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D969" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E969" s="16" t="s">
+      <c r="C969" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D969" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E969" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="970" spans="1:5">
-      <c r="A970" s="19" t="s">
+      <c r="A970" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B970" s="15" t="s">
+      <c r="B970" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C970" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D970" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E970" s="16" t="s">
+      <c r="C970" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D970" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E970" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="971" spans="1:5">
-      <c r="A971" s="19" t="s">
+      <c r="A971" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B971" s="15" t="s">
+      <c r="B971" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C971" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D971" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E971" s="16" t="s">
+      <c r="C971" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D971" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E971" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="972" spans="1:5">
-      <c r="A972" s="19" t="s">
+      <c r="A972" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B972" s="15" t="s">
+      <c r="B972" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C972" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D972" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E972" s="16" t="s">
+      <c r="C972" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D972" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E972" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="973" spans="1:5">
-      <c r="A973" s="19" t="s">
+      <c r="A973" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B973" s="15" t="s">
+      <c r="B973" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C973" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D973" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E973" s="16" t="s">
+      <c r="C973" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D973" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E973" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="974" spans="1:5">
-      <c r="A974" s="19" t="s">
+      <c r="A974" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B974" s="15" t="s">
+      <c r="B974" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C974" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D974" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E974" s="16" t="s">
+      <c r="C974" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D974" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E974" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="975" spans="1:5">
-      <c r="A975" s="19" t="s">
+      <c r="A975" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B975" s="15" t="s">
+      <c r="B975" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C975" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D975" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E975" s="16" t="s">
+      <c r="C975" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D975" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E975" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="976" spans="1:5">
-      <c r="A976" s="19" t="s">
+      <c r="A976" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B976" s="15" t="s">
+      <c r="B976" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C976" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D976" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E976" s="16" t="s">
+      <c r="C976" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D976" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E976" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="977" spans="1:5">
-      <c r="A977" s="19" t="s">
+      <c r="A977" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B977" s="15" t="s">
+      <c r="B977" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C977" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D977" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E977" s="16" t="s">
+      <c r="C977" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D977" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E977" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="978" spans="1:5">
-      <c r="A978" s="19" t="s">
+      <c r="A978" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B978" s="15" t="s">
+      <c r="B978" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C978" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D978" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E978" s="16" t="s">
+      <c r="C978" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D978" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E978" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="979" spans="1:5">
-      <c r="A979" s="19" t="s">
+      <c r="A979" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B979" s="15" t="s">
+      <c r="B979" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C979" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D979" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E979" s="16" t="s">
+      <c r="C979" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D979" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E979" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="980" spans="1:5">
-      <c r="A980" s="19" t="s">
+      <c r="A980" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B980" s="15" t="s">
+      <c r="B980" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C980" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D980" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E980" s="16" t="s">
+      <c r="C980" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D980" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E980" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="981" spans="1:5">
-      <c r="A981" s="19" t="s">
+      <c r="A981" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B981" s="15" t="s">
+      <c r="B981" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C981" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D981" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E981" s="16" t="s">
+      <c r="C981" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D981" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E981" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="982" spans="1:5">
-      <c r="A982" s="19" t="s">
+      <c r="A982" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B982" s="15" t="s">
+      <c r="B982" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C982" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D982" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E982" s="16" t="s">
+      <c r="C982" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D982" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E982" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="983" spans="1:5">
-      <c r="A983" s="19" t="s">
+      <c r="A983" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B983" s="15" t="s">
+      <c r="B983" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C983" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D983" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E983" s="16" t="s">
+      <c r="C983" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D983" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E983" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="984" spans="1:5">
-      <c r="A984" s="19" t="s">
+      <c r="A984" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B984" s="15" t="s">
+      <c r="B984" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C984" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D984" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E984" s="16" t="s">
+      <c r="C984" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D984" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E984" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="985" spans="1:5">
-      <c r="A985" s="19" t="s">
+      <c r="A985" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B985" s="15" t="s">
+      <c r="B985" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C985" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D985" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E985" s="16" t="s">
+      <c r="C985" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D985" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E985" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="986" spans="1:5">
-      <c r="A986" s="19" t="s">
+      <c r="A986" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B986" s="15" t="s">
+      <c r="B986" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C986" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D986" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E986" s="16" t="s">
+      <c r="C986" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D986" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E986" s="10" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="987" spans="1:5">
-      <c r="A987" s="19" t="s">
+      <c r="A987" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B987" s="15" t="s">
+      <c r="B987" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C987" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D987" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E987" s="16" t="s">
+      <c r="C987" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D987" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E987" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="988" spans="1:5">
-      <c r="A988" s="19" t="s">
+      <c r="A988" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="B988" s="15" t="s">
+      <c r="B988" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C988" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D988" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E988" s="16" t="s">
+      <c r="C988" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D988" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E988" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="989" spans="1:5">
-      <c r="A989" s="19" t="s">
+      <c r="A989" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="B989" s="15" t="s">
+      <c r="B989" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C989" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D989" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E989" s="16" t="s">
+      <c r="C989" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D989" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E989" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="990" spans="1:5">
-      <c r="A990" s="19" t="s">
+      <c r="A990" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B990" s="15" t="s">
+      <c r="B990" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C990" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D990" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E990" s="16" t="s">
+      <c r="C990" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D990" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E990" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="991" spans="1:5">
-      <c r="A991" s="19" t="s">
+      <c r="A991" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B991" s="15" t="s">
+      <c r="B991" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C991" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D991" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E991" s="16" t="s">
+      <c r="C991" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D991" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E991" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="992" spans="1:5">
-      <c r="A992" s="19" t="s">
+      <c r="A992" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B992" s="15" t="s">
+      <c r="B992" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C992" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D992" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E992" s="16" t="s">
+      <c r="C992" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D992" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E992" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="993" spans="1:5">
-      <c r="A993" s="19" t="s">
+      <c r="A993" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B993" s="15" t="s">
+      <c r="B993" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C993" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D993" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E993" s="16" t="s">
+      <c r="C993" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D993" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E993" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="994" spans="1:5">
-      <c r="A994" s="19" t="s">
+      <c r="A994" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B994" s="15" t="s">
+      <c r="B994" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C994" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D994" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E994" s="16" t="s">
+      <c r="C994" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D994" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E994" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="995" spans="1:5">
-      <c r="A995" s="19" t="s">
+      <c r="A995" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B995" s="15" t="s">
+      <c r="B995" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C995" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D995" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E995" s="16" t="s">
+      <c r="C995" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D995" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E995" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="996" spans="1:5">
-      <c r="A996" s="19" t="s">
+      <c r="A996" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="B996" s="15" t="s">
+      <c r="B996" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C996" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D996" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E996" s="16" t="s">
+      <c r="C996" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D996" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E996" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="997" spans="1:5">
-      <c r="A997" s="19" t="s">
+      <c r="A997" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="B997" s="15" t="s">
+      <c r="B997" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C997" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D997" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E997" s="16" t="s">
+      <c r="C997" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D997" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E997" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="998" spans="1:5">
-      <c r="A998" s="19" t="s">
+      <c r="A998" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="B998" s="15" t="s">
+      <c r="B998" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C998" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D998" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E998" s="16" t="s">
+      <c r="C998" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D998" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E998" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="999" spans="1:5">
-      <c r="A999" s="19" t="s">
+      <c r="A999" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="B999" s="15" t="s">
+      <c r="B999" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C999" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D999" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E999" s="16" t="s">
+      <c r="C999" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D999" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E999" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1000" spans="1:5">
-      <c r="A1000" s="19" t="s">
+      <c r="A1000" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="B1000" s="15" t="s">
+      <c r="B1000" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1000" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1000" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1000" s="16" t="s">
+      <c r="C1000" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1000" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1000" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1001" spans="1:5">
-      <c r="A1001" s="19" t="s">
+      <c r="A1001" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="B1001" s="15" t="s">
+      <c r="B1001" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1001" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1001" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1001" s="16" t="s">
+      <c r="C1001" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1001" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1001" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1002" spans="1:5">
-      <c r="A1002" s="19" t="s">
+      <c r="A1002" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="B1002" s="15" t="s">
+      <c r="B1002" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1002" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1002" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1002" s="16" t="s">
+      <c r="C1002" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1002" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1002" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1003" spans="1:5">
-      <c r="A1003" s="19" t="s">
+      <c r="A1003" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="B1003" s="15" t="s">
+      <c r="B1003" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1003" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1003" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1003" s="16" t="s">
+      <c r="C1003" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1003" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1003" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1004" spans="1:5">
-      <c r="A1004" s="19" t="s">
+      <c r="A1004" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="B1004" s="15" t="s">
+      <c r="B1004" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1004" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1004" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1004" s="16" t="s">
+      <c r="C1004" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1004" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1004" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1005" spans="1:5">
-      <c r="A1005" s="19" t="s">
+      <c r="A1005" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="B1005" s="15" t="s">
+      <c r="B1005" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1005" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1005" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1005" s="16" t="s">
+      <c r="C1005" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1005" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1005" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1006" spans="1:5">
-      <c r="A1006" s="19" t="s">
+      <c r="A1006" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="B1006" s="15" t="s">
+      <c r="B1006" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1006" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1006" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1006" s="16" t="s">
+      <c r="C1006" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1006" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1006" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1007" spans="1:5">
-      <c r="A1007" s="19" t="s">
+      <c r="A1007" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="B1007" s="15" t="s">
+      <c r="B1007" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1007" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1007" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1007" s="16" t="s">
+      <c r="C1007" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1007" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1007" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1008" spans="1:5">
-      <c r="A1008" s="19" t="s">
+      <c r="A1008" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="B1008" s="15" t="s">
+      <c r="B1008" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1008" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1008" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1008" s="16" t="s">
+      <c r="C1008" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1008" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1008" s="10" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="1009" spans="1:5">
-      <c r="A1009" s="19" t="s">
+      <c r="A1009" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B1009" s="15" t="s">
+      <c r="B1009" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1009" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1009" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1009" s="16" t="s">
+      <c r="C1009" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1009" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1009" s="10" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="1010" spans="1:5">
-      <c r="A1010" s="19" t="s">
+      <c r="A1010" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B1010" s="15" t="s">
+      <c r="B1010" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1010" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1010" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1010" s="16" t="s">
+      <c r="C1010" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1010" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1010" s="10" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="1011" spans="1:5">
-      <c r="A1011" s="19" t="s">
+      <c r="A1011" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B1011" s="15" t="s">
+      <c r="B1011" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1011" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1011" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1011" s="16" t="s">
+      <c r="C1011" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1011" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1011" s="10" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="1012" spans="1:5">
-      <c r="A1012" s="19" t="s">
+      <c r="A1012" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B1012" s="15" t="s">
+      <c r="B1012" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1012" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1012" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1012" s="16" t="s">
+      <c r="C1012" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1012" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1012" s="10" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="1013" spans="1:5">
-      <c r="A1013" s="14" t="s">
+      <c r="A1013" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B1013" s="15" t="s">
+      <c r="B1013" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C1013" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1013" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1013" s="16" t="s">
+      <c r="C1013" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1013" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1013" s="10" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="1014" spans="1:5">
-      <c r="A1014" s="14" t="s">
+      <c r="A1014" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B1014" s="15" t="s">
+      <c r="B1014" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1014" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1014" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1014" s="16" t="s">
+      <c r="C1014" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1014" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1014" s="10" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="1015" spans="1:5">
-      <c r="A1015" s="14" t="s">
+      <c r="A1015" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B1015" s="15" t="s">
+      <c r="B1015" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1015" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1015" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1015" s="16" t="s">
+      <c r="C1015" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1015" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1015" s="10" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="1016" spans="1:5">
-      <c r="A1016" s="14" t="s">
+      <c r="A1016" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B1016" s="15" t="s">
+      <c r="B1016" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1016" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1016" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1016" s="16" t="s">
+      <c r="C1016" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1016" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1016" s="10" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="1017" spans="1:5">
-      <c r="A1017" s="14" t="s">
+      <c r="A1017" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B1017" s="15" t="s">
+      <c r="B1017" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1017" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1017" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1017" s="16" t="s">
+      <c r="C1017" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1017" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1017" s="10" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="1018" spans="1:5">
-      <c r="A1018" s="14" t="s">
+      <c r="A1018" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B1018" s="15" t="s">
+      <c r="B1018" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1018" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1018" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1018" s="16" t="s">
+      <c r="C1018" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1018" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1018" s="10" t="s">
         <v>375</v>
       </c>
     </row>
@@ -19652,16 +19640,16 @@
       <c r="A1019" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B1019" s="15" t="s">
+      <c r="B1019" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1019" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1019" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1019" s="16" t="s">
+      <c r="C1019" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1019" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1019" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19669,16 +19657,16 @@
       <c r="A1020" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B1020" s="15" t="s">
+      <c r="B1020" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1020" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1020" s="15" t="s">
+      <c r="C1020" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1020" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E1020" s="16" t="s">
+      <c r="E1020" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19686,16 +19674,16 @@
       <c r="A1021" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B1021" s="15" t="s">
+      <c r="B1021" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1021" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1021" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1021" s="16" t="s">
+      <c r="C1021" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1021" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1021" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19703,16 +19691,16 @@
       <c r="A1022" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B1022" s="15" t="s">
+      <c r="B1022" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1022" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1022" s="15" t="s">
+      <c r="C1022" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1022" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E1022" s="16" t="s">
+      <c r="E1022" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19720,16 +19708,16 @@
       <c r="A1023" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1023" s="15" t="s">
+      <c r="B1023" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1023" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1023" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1023" s="16" t="s">
+      <c r="C1023" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1023" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1023" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19737,16 +19725,16 @@
       <c r="A1024" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B1024" s="15" t="s">
+      <c r="B1024" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1024" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1024" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1024" s="16" t="s">
+      <c r="C1024" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1024" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1024" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19757,13 +19745,13 @@
       <c r="B1025" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1025" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1025" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1025" s="16" t="s">
+      <c r="C1025" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1025" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1025" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19774,13 +19762,13 @@
       <c r="B1026" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1026" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1026" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1026" s="16" t="s">
+      <c r="C1026" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1026" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1026" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19791,13 +19779,13 @@
       <c r="B1027" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1027" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1027" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1027" s="16" t="s">
+      <c r="C1027" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1027" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1027" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19808,13 +19796,13 @@
       <c r="B1028" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1028" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1028" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1028" s="16" t="s">
+      <c r="C1028" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1028" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1028" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19825,13 +19813,13 @@
       <c r="B1029" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1029" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1029" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1029" s="16" t="s">
+      <c r="C1029" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1029" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1029" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19842,13 +19830,13 @@
       <c r="B1030" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1030" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1030" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1030" s="16" t="s">
+      <c r="C1030" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1030" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1030" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19859,13 +19847,13 @@
       <c r="B1031" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1031" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1031" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1031" s="16" t="s">
+      <c r="C1031" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1031" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1031" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19876,13 +19864,13 @@
       <c r="B1032" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1032" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1032" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1032" s="16" t="s">
+      <c r="C1032" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1032" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1032" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19893,13 +19881,13 @@
       <c r="B1033" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1033" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1033" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1033" s="16" t="s">
+      <c r="C1033" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1033" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1033" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19910,13 +19898,13 @@
       <c r="B1034" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1034" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1034" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1034" s="16" t="s">
+      <c r="C1034" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1034" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1034" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19927,13 +19915,13 @@
       <c r="B1035" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1035" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1035" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1035" s="16" t="s">
+      <c r="C1035" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1035" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1035" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19944,13 +19932,13 @@
       <c r="B1036" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1036" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1036" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1036" s="16" t="s">
+      <c r="C1036" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1036" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1036" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19961,13 +19949,13 @@
       <c r="B1037" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1037" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1037" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1037" s="16" t="s">
+      <c r="C1037" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1037" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1037" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19978,13 +19966,13 @@
       <c r="B1038" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1038" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1038" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1038" s="16" t="s">
+      <c r="C1038" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1038" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1038" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -19995,13 +19983,13 @@
       <c r="B1039" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1039" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1039" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1039" s="16" t="s">
+      <c r="C1039" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1039" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1039" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20012,13 +20000,13 @@
       <c r="B1040" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1040" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1040" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1040" s="16" t="s">
+      <c r="C1040" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1040" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1040" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20029,13 +20017,13 @@
       <c r="B1041" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1041" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1041" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1041" s="16" t="s">
+      <c r="C1041" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1041" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1041" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20046,13 +20034,13 @@
       <c r="B1042" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1042" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1042" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1042" s="16" t="s">
+      <c r="C1042" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1042" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1042" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20063,13 +20051,13 @@
       <c r="B1043" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C1043" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1043" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1043" s="16" t="s">
+      <c r="C1043" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1043" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1043" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20080,13 +20068,13 @@
       <c r="B1044" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1044" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1044" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1044" s="16" t="s">
+      <c r="C1044" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1044" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1044" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20097,13 +20085,13 @@
       <c r="B1045" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1045" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1045" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1045" s="16" t="s">
+      <c r="C1045" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1045" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1045" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20114,13 +20102,13 @@
       <c r="B1046" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1046" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1046" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1046" s="16" t="s">
+      <c r="C1046" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1046" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1046" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20131,13 +20119,13 @@
       <c r="B1047" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1047" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1047" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1047" s="16" t="s">
+      <c r="C1047" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1047" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1047" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20148,13 +20136,13 @@
       <c r="B1048" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1048" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1048" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1048" s="16" t="s">
+      <c r="C1048" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1048" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1048" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20165,13 +20153,13 @@
       <c r="B1049" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1049" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1049" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1049" s="16" t="s">
+      <c r="C1049" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1049" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1049" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20182,13 +20170,13 @@
       <c r="B1050" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1050" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1050" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1050" s="16" t="s">
+      <c r="C1050" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1050" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1050" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20199,13 +20187,13 @@
       <c r="B1051" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1051" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1051" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1051" s="16" t="s">
+      <c r="C1051" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1051" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1051" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20216,13 +20204,13 @@
       <c r="B1052" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1052" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1052" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1052" s="16" t="s">
+      <c r="C1052" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1052" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1052" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20233,13 +20221,13 @@
       <c r="B1053" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1053" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1053" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1053" s="16" t="s">
+      <c r="C1053" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1053" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1053" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20250,13 +20238,13 @@
       <c r="B1054" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1054" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1054" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1054" s="16" t="s">
+      <c r="C1054" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1054" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1054" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20267,13 +20255,13 @@
       <c r="B1055" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C1055" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1055" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1055" s="20" t="s">
+      <c r="C1055" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1055" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1055" s="15" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20290,7 +20278,7 @@
       <c r="D1056" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1056" s="20" t="s">
+      <c r="E1056" s="15" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20307,7 +20295,7 @@
       <c r="D1057" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1057" s="20" t="s">
+      <c r="E1057" s="15" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20318,13 +20306,13 @@
       <c r="B1058" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1058" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1058" s="21" t="s">
+      <c r="C1058" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1058" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E1058" s="20" t="s">
+      <c r="E1058" s="15" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20342,6 +20330,23 @@
         <v>42</v>
       </c>
       <c r="E1059" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:5">
+      <c r="A1060" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1060" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1060" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1060" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1060" s="2" t="s">
         <v>365</v>
       </c>
     </row>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B05A57-1855-4644-AF4F-2FBA94DB0B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C140C2-C36E-4E6A-BCAB-478DC2DF37A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5300" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5420" uniqueCount="596">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1791,6 +1791,42 @@
   </si>
   <si>
     <t>Evil Presence </t>
+  </si>
+  <si>
+    <t>Sage of Lat-Nam</t>
+  </si>
+  <si>
+    <t>Rukh Egg (V.2)</t>
+  </si>
+  <si>
+    <t>Gaea's Touch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue Elemental Blast </t>
+  </si>
+  <si>
+    <t>Righteousness</t>
+  </si>
+  <si>
+    <t>Tourach's Gate</t>
+  </si>
+  <si>
+    <t>Goblin Chirurgeon (V.2)</t>
+  </si>
+  <si>
+    <t>Goblin Chirurgeon (V.3)</t>
+  </si>
+  <si>
+    <t>Goblin Grenade (V.3) </t>
+  </si>
+  <si>
+    <t>Goblin Grenade (V.1) </t>
+  </si>
+  <si>
+    <t>Ebon Stronghold</t>
+  </si>
+  <si>
+    <t>Delif's Cube</t>
   </si>
 </sst>
 </file>
@@ -1925,7 +1961,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1968,10 +2004,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2321,7 +2360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1060"/>
+  <dimension ref="A1:E1084"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -20334,20 +20373,428 @@
       </c>
     </row>
     <row r="1060" spans="1:5">
-      <c r="A1060" s="16" t="s">
+      <c r="A1060" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B1060" s="17" t="s">
+      <c r="B1060" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1060" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1060" s="17" t="s">
+      <c r="C1060" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1060" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1060" s="2" t="s">
         <v>365</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:5" ht="15">
+      <c r="A1061" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1061" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1061" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:5">
+      <c r="A1062" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1062" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1062" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1062" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1062" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:5" ht="15">
+      <c r="A1063" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B1063" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1063" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1063" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1063" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:5" ht="15">
+      <c r="A1064" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1064" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1064" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1064" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:5" ht="15">
+      <c r="A1065" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1065" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1065" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1065" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:5" ht="15">
+      <c r="A1066" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1066" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1066" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1066" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:5" ht="15">
+      <c r="A1067" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1067" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1067" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1067" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:5" ht="15">
+      <c r="A1068" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1068" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1068" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1068" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:5" ht="15">
+      <c r="A1069" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1069" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1069" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1069" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:5" ht="15">
+      <c r="A1070" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1070" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1070" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1070" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:5" ht="15">
+      <c r="A1071" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B1071" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1071" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1071" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:5" ht="15">
+      <c r="A1072" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1072" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1072" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1072" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1072" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:5" ht="15">
+      <c r="A1073" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1073" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1073" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1073" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:5" ht="15">
+      <c r="A1074" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1074" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1074" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1074" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:5" ht="15">
+      <c r="A1075" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1075" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1075" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1075" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:5" ht="15">
+      <c r="A1076" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1076" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1076" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1076" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:5" ht="15">
+      <c r="A1077" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1077" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1077" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1077" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:5" ht="15">
+      <c r="A1078" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B1078" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1078" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1078" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:5" ht="15">
+      <c r="A1079" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B1079" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1079" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1079" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:5" ht="15">
+      <c r="A1080" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B1080" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1080" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1080" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:5" ht="15">
+      <c r="A1081" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1081" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1081" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1081" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:5" ht="15">
+      <c r="A1082" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B1082" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1082" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1082" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:5" ht="15">
+      <c r="A1083" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1083" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1083" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1083" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:5" ht="15">
+      <c r="A1084" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B1084" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1084" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1084" s="2" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C140C2-C36E-4E6A-BCAB-478DC2DF37A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFE0949-4EC9-42C9-8D95-6D1AC1E83093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5420" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5610" uniqueCount="612">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1827,6 +1827,54 @@
   </si>
   <si>
     <t>Delif's Cube</t>
+  </si>
+  <si>
+    <t>Oath of Ghouls</t>
+  </si>
+  <si>
+    <t>Hidden Retreat</t>
+  </si>
+  <si>
+    <t>Nomads en-Kor</t>
+  </si>
+  <si>
+    <t>Mana Leak</t>
+  </si>
+  <si>
+    <t>Wall of Tears</t>
+  </si>
+  <si>
+    <t>Megrim </t>
+  </si>
+  <si>
+    <t>Wall of Souls </t>
+  </si>
+  <si>
+    <t>Jinxed Ring</t>
+  </si>
+  <si>
+    <t>Portcullis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carnophage </t>
+  </si>
+  <si>
+    <t>Dauthi Warlord</t>
+  </si>
+  <si>
+    <t>Pit Spawn</t>
+  </si>
+  <si>
+    <t>Spike Cannibal</t>
+  </si>
+  <si>
+    <t>Mogg Assassin</t>
+  </si>
+  <si>
+    <t>Manabond </t>
+  </si>
+  <si>
+    <t>Thopter Squadron</t>
   </si>
 </sst>
 </file>
@@ -1961,7 +2009,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2004,13 +2052,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2360,7 +2402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1084"/>
+  <dimension ref="A1:E1122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -20407,19 +20449,19 @@
       </c>
     </row>
     <row r="1062" spans="1:5">
-      <c r="A1062" s="16" t="s">
+      <c r="A1062" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B1062" s="17" t="s">
+      <c r="B1062" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C1062" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1062" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1062" s="18" t="s">
+      <c r="C1062" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1062" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1062" s="10" t="s">
         <v>365</v>
       </c>
     </row>
@@ -20795,6 +20837,652 @@
       </c>
       <c r="E1084" s="2" t="s">
         <v>366</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:5" ht="15">
+      <c r="A1085" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1085" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1085" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1085" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1085" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:5" ht="15">
+      <c r="A1086" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1086" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1086" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:5" ht="15">
+      <c r="A1087" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1087" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1087" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:5" ht="15">
+      <c r="A1088" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1088" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1088" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:5" ht="15">
+      <c r="A1089" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1089" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1089" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1089" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:5" ht="15">
+      <c r="A1090" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1090" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1090" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1090" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:5" ht="15">
+      <c r="A1091" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1091" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1091" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1091" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:5" ht="15">
+      <c r="A1092" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1092" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1092" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1092" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:5" ht="15">
+      <c r="A1093" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1093" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1093" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1093" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:5" ht="15">
+      <c r="A1094" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B1094" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1094" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:5" ht="15">
+      <c r="A1095" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1095" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1095" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:5" ht="15">
+      <c r="A1096" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B1096" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1096" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:5" ht="15">
+      <c r="A1097" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1097" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1097" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:5" ht="15">
+      <c r="A1098" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1098" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1098" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1098" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:5" ht="15">
+      <c r="A1099" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1099" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1099" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:5" ht="15">
+      <c r="A1100" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1100" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1100" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1100" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:5" ht="15">
+      <c r="A1101" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B1101" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1101" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1101" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:5" ht="15">
+      <c r="A1102" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1102" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1102" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1102" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:5" ht="15">
+      <c r="A1103" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1103" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1103" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1103" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:5" ht="15">
+      <c r="A1104" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B1104" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1104" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1104" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:5" ht="15">
+      <c r="A1105" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1105" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1105" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1105" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:5" ht="15">
+      <c r="A1106" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1106" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1106" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1106" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:5" ht="15">
+      <c r="A1107" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B1107" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1107" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1107" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:5" ht="15">
+      <c r="A1108" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B1108" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1108" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:5" ht="15">
+      <c r="A1109" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1109" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1109" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1109" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:5" ht="15">
+      <c r="A1110" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1110" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1110" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1110" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:5" ht="15">
+      <c r="A1111" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B1111" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1111" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1111" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:5" ht="15">
+      <c r="A1112" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1112" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1112" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1112" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:5" ht="15">
+      <c r="A1113" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1113" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1113" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1113" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:5" ht="15">
+      <c r="A1114" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1114" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1114" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1114" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:5" ht="15">
+      <c r="A1115" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1115" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1115" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1115" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:5" ht="15">
+      <c r="A1116" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1116" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1116" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1116" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:5" ht="15">
+      <c r="A1117" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1117" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1117" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1117" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:5" ht="15">
+      <c r="A1118" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1118" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1118" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1118" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:5" ht="15">
+      <c r="A1119" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1119" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1119" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1119" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:5" ht="15">
+      <c r="A1120" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1120" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1120" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1120" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:5" ht="15">
+      <c r="A1121" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1121" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1121" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1121" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:5" ht="15">
+      <c r="A1122" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B1122" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1122" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1122" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFE0949-4EC9-42C9-8D95-6D1AC1E83093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F9F63B-25D8-4B5D-B181-2E63441358CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5610" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6370" uniqueCount="640">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1875,6 +1875,90 @@
   </si>
   <si>
     <t>Thopter Squadron</t>
+  </si>
+  <si>
+    <t>Chaos Confetti</t>
+  </si>
+  <si>
+    <t>Rock Lobster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presence of the Master </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telepathy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turnabout </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pestilence </t>
+  </si>
+  <si>
+    <t>Shivan Hellkite</t>
+  </si>
+  <si>
+    <t>Argothian Elder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child of Gaea </t>
+  </si>
+  <si>
+    <t>Citanul Hierophants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citanul Flute </t>
+  </si>
+  <si>
+    <t>Claws of Gix</t>
+  </si>
+  <si>
+    <t>Thran Turbine</t>
+  </si>
+  <si>
+    <t>Umbilicus </t>
+  </si>
+  <si>
+    <t>Island (V.4)</t>
+  </si>
+  <si>
+    <t>Plains (V.4)</t>
+  </si>
+  <si>
+    <t>Swamp (V.4)</t>
+  </si>
+  <si>
+    <t>Mountain (V.4)</t>
+  </si>
+  <si>
+    <t>Forest (V.4)</t>
+  </si>
+  <si>
+    <t>Transmute Artifact</t>
+  </si>
+  <si>
+    <t>Bone Shredder</t>
+  </si>
+  <si>
+    <t>Avalanche Riders</t>
+  </si>
+  <si>
+    <t>Ghitu Encampment</t>
+  </si>
+  <si>
+    <t>Last-Ditch Effort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosperity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitalize </t>
+  </si>
+  <si>
+    <t>Snow-Covered Mountain</t>
+  </si>
+  <si>
+    <t>Snow-Covered Forest </t>
   </si>
 </sst>
 </file>
@@ -2009,7 +2093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2050,9 +2134,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2402,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1122"/>
+  <dimension ref="A1:E1274"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -20914,7 +20995,7 @@
       <c r="B1089" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C1089" s="16" t="s">
+      <c r="C1089" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D1089" t="s">
@@ -20931,7 +21012,7 @@
       <c r="B1090" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C1090" s="16" t="s">
+      <c r="C1090" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D1090" t="s">
@@ -20948,7 +21029,7 @@
       <c r="B1091" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C1091" s="16" t="s">
+      <c r="C1091" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D1091" t="s">
@@ -20965,7 +21046,7 @@
       <c r="B1092" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C1092" s="16" t="s">
+      <c r="C1092" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D1092" t="s">
@@ -20982,7 +21063,7 @@
       <c r="B1093" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C1093" s="16" t="s">
+      <c r="C1093" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D1093" t="s">
@@ -21483,6 +21564,2590 @@
       </c>
       <c r="E1122" s="2" t="s">
         <v>369</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:5" ht="15">
+      <c r="A1123" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1123" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1123" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1123" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:5" ht="15">
+      <c r="A1124" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B1124" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1124" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1124" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:5" ht="15">
+      <c r="A1125" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1125" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1125" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1125" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:5" ht="15">
+      <c r="A1126" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B1126" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1126" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1126" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:5" ht="15">
+      <c r="A1127" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1127" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1127" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1127" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:5" ht="15">
+      <c r="A1128" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1128" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1128" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1128" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:5" ht="15">
+      <c r="A1129" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B1129" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1129" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:5" ht="15">
+      <c r="A1130" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1130" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1130" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1130" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:5" ht="15">
+      <c r="A1131" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B1131" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1131" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1131" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:5" ht="15">
+      <c r="A1132" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B1132" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1132" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1132" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1132" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:5" ht="15">
+      <c r="A1133" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B1133" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1133" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1133" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:5" ht="15">
+      <c r="A1134" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B1134" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1134" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1134" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:5" ht="15">
+      <c r="A1135" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B1135" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1135" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1135" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:5" ht="15">
+      <c r="A1136" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B1136" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1136" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1136" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:5" ht="15">
+      <c r="A1137" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1137" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1137" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:5" ht="15">
+      <c r="A1138" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1138" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1138" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1138" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:5" ht="15">
+      <c r="A1139" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1139" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1139" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1139" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:5" ht="15">
+      <c r="A1140" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1140" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1140" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1140" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:5" ht="15">
+      <c r="A1141" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1141" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1141" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1141" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:5" ht="15">
+      <c r="A1142" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1142" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1142" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1142" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:5" ht="15">
+      <c r="A1143" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1143" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1143" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1143" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:5" ht="15">
+      <c r="A1144" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B1144" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1144" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1144" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:5" ht="15">
+      <c r="A1145" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1145" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1145" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1145" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:5" ht="15">
+      <c r="A1146" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1146" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1146" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1146" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:5" ht="15">
+      <c r="A1147" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1147" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1147" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1147" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:5" ht="15">
+      <c r="A1148" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1148" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1148" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1148" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:5" ht="15">
+      <c r="A1149" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1149" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1149" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1149" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:5" ht="15">
+      <c r="A1150" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1150" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1150" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1150" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:5" ht="15">
+      <c r="A1151" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1151" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1151" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1151" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:5" ht="15">
+      <c r="A1152" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B1152" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1152" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1152" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:5" ht="15">
+      <c r="A1153" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1153" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1153" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1153" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:5" ht="15">
+      <c r="A1154" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1154" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1154" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1154" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:5" ht="15">
+      <c r="A1155" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1155" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1155" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1155" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:5" ht="15">
+      <c r="A1156" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B1156" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1156" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1156" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:5" ht="15">
+      <c r="A1157" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B1157" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1157" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1157" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:5" ht="15">
+      <c r="A1158" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1158" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1158" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1158" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:5" ht="15">
+      <c r="A1159" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B1159" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1159" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1159" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:5" ht="15">
+      <c r="A1160" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B1160" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1160" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1160" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:5" ht="15">
+      <c r="A1161" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B1161" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1161" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:5" ht="15">
+      <c r="A1162" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B1162" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1162" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:5" ht="15">
+      <c r="A1163" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B1163" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1163" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1163" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:5" ht="15">
+      <c r="A1164" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B1164" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1164" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1164" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:5" ht="15">
+      <c r="A1165" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B1165" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1165" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1165" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:5" ht="15">
+      <c r="A1166" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B1166" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1166" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1166" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:5" ht="15">
+      <c r="A1167" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B1167" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1167" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1167" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:5" ht="15">
+      <c r="A1168" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1168" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1168" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1168" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:5" ht="15">
+      <c r="A1169" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1169" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1169" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1169" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:5" ht="15">
+      <c r="A1170" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1170" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1170" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1170" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:5" ht="15">
+      <c r="A1171" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B1171" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1171" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1171" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:5" ht="15">
+      <c r="A1172" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1172" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1172" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1172" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:5" ht="15">
+      <c r="A1173" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1173" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1173" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:5" ht="15">
+      <c r="A1174" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1174" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1174" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1174" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:5" ht="15">
+      <c r="A1175" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1175" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1175" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1175" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:5" ht="15">
+      <c r="A1176" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1176" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1176" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1176" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:5" ht="15">
+      <c r="A1177" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1177" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1177" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1177" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:5" ht="15">
+      <c r="A1178" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1178" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1178" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1178" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:5" ht="15">
+      <c r="A1179" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1179" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1179" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1179" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:5" ht="15">
+      <c r="A1180" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1180" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1180" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1180" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:5" ht="15">
+      <c r="A1181" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1181" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1181" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1181" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:5" ht="15">
+      <c r="A1182" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1182" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1182" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1182" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:5" ht="15">
+      <c r="A1183" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1183" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1183" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1183" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1183" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:5" ht="15">
+      <c r="A1184" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1184" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1184" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1184" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1184" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:5" ht="15">
+      <c r="A1185" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1185" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1185" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1185" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1185" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:5" ht="15">
+      <c r="A1186" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1186" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1186" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1186" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1186" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:5" ht="15">
+      <c r="A1187" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B1187" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1187" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1187" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1187" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:5" ht="15">
+      <c r="A1188" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1188" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1188" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1188" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1188" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:5" ht="15">
+      <c r="A1189" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1189" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1189" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1189" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1189" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:5" ht="15">
+      <c r="A1190" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1190" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1190" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1190" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1190" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:5" ht="15">
+      <c r="A1191" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1191" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1191" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1191" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1191" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:5" ht="15">
+      <c r="A1192" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B1192" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1192" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1192" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1192" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:5" ht="15">
+      <c r="A1193" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1193" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1193" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1193" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:5" ht="15">
+      <c r="A1194" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1194" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1194" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1194" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:5" ht="15">
+      <c r="A1195" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1195" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1195" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1195" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:5" ht="15">
+      <c r="A1196" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1196" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1196" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1196" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:5" ht="15">
+      <c r="A1197" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1197" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1197" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1197" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:5" ht="15">
+      <c r="A1198" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1198" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1198" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1198" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:5" ht="15">
+      <c r="A1199" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1199" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1199" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1199" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:5" ht="15">
+      <c r="A1200" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1200" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1200" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1200" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:5" ht="15">
+      <c r="A1201" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1201" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1201" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1201" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:5" ht="15">
+      <c r="A1202" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1202" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1202" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1202" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:5" ht="15">
+      <c r="A1203" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B1203" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1203" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1203" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:5" ht="15">
+      <c r="A1204" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1204" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1204" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:5" ht="15">
+      <c r="A1205" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1205" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1205" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1205" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:5" ht="15">
+      <c r="A1206" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1206" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1206" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:5" ht="15">
+      <c r="A1207" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1207" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1207" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:5" ht="15">
+      <c r="A1208" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1208" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1208" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:5" ht="15">
+      <c r="A1209" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1209" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1209" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:5" ht="15">
+      <c r="A1210" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1210" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1210" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:5" ht="15">
+      <c r="A1211" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1211" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1211" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:5" ht="15">
+      <c r="A1212" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1212" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1212" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:5" ht="15">
+      <c r="A1213" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B1213" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1213" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:5" ht="15">
+      <c r="A1214" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1214" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1214" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:5" ht="15">
+      <c r="A1215" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1215" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1215" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:5" ht="15">
+      <c r="A1216" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1216" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1216" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1216" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:5" ht="15">
+      <c r="A1217" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1217" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1217" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:5" ht="15">
+      <c r="A1218" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1218" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1218" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:5" ht="15">
+      <c r="A1219" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1219" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1219" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:5" ht="15">
+      <c r="A1220" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1220" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1220" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:5" ht="15">
+      <c r="A1221" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B1221" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1221" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:5" ht="15">
+      <c r="A1222" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1222" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1222" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:5" ht="15">
+      <c r="A1223" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1223" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1223" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:5" ht="15">
+      <c r="A1224" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1224" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1224" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:5" ht="15">
+      <c r="A1225" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B1225" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1225" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:5" ht="15">
+      <c r="A1226" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1226" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1226" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:5" ht="15">
+      <c r="A1227" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1227" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1227" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:5" ht="15">
+      <c r="A1228" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1228" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1228" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:5" ht="15">
+      <c r="A1229" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1229" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1229" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:5" ht="15">
+      <c r="A1230" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1230" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1230" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:5" ht="15">
+      <c r="A1231" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1231" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1231" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:5" ht="15">
+      <c r="A1232" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1232" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1232" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:5" ht="15">
+      <c r="A1233" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1233" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1233" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:5" ht="15">
+      <c r="A1234" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1234" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1234" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:5" ht="15">
+      <c r="A1235" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1235" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1235" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:5" ht="15">
+      <c r="A1236" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1236" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1236" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:5" ht="15">
+      <c r="A1237" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1237" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1237" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:5" ht="15">
+      <c r="A1238" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1238" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1238" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:5" ht="15">
+      <c r="A1239" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1239" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1239" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:5" ht="15">
+      <c r="A1240" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B1240" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1240" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:5" ht="15">
+      <c r="A1241" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1241" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1241" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:5" ht="15">
+      <c r="A1242" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1242" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1242" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:5" ht="15">
+      <c r="A1243" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1243" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1243" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:5" ht="15">
+      <c r="A1244" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B1244" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1244" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:5" ht="15">
+      <c r="A1245" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1245" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1245" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:5" ht="15">
+      <c r="A1246" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1246" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1246" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:5" ht="15">
+      <c r="A1247" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1247" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1247" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:5" ht="15">
+      <c r="A1248" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1248" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1248" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:5" ht="15">
+      <c r="A1249" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1249" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1249" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:5" ht="15">
+      <c r="A1250" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1250" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1250" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:5" ht="15">
+      <c r="A1251" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1251" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1251" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:5" ht="15">
+      <c r="A1252" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1252" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1252" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:5" ht="15">
+      <c r="A1253" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1253" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1253" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:5" ht="15">
+      <c r="A1254" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1254" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1254" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:5" ht="15">
+      <c r="A1255" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1255" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1255" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:5" ht="15">
+      <c r="A1256" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1256" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1256" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:5" ht="15">
+      <c r="A1257" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B1257" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1257" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:5" ht="15">
+      <c r="A1258" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1258" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1258" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:5" ht="15">
+      <c r="A1259" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1259" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1259" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:5" ht="15">
+      <c r="A1260" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1260" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1260" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:5" ht="15">
+      <c r="A1261" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B1261" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1261" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:5" ht="15">
+      <c r="A1262" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B1262" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1262" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:5" ht="15">
+      <c r="A1263" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1263" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1263" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:5" ht="15">
+      <c r="A1264" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1264" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1264" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:5" ht="15">
+      <c r="A1265" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1265" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1265" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:5" ht="15">
+      <c r="A1266" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1266" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1266" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:5" ht="15">
+      <c r="A1267" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1267" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1267" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:5" ht="15">
+      <c r="A1268" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1268" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1268" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:5" ht="15">
+      <c r="A1269" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1269" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1269" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:5" ht="15">
+      <c r="A1270" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1270" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1270" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:5" ht="15">
+      <c r="A1271" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1271" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1271" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:5" ht="15">
+      <c r="A1272" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1272" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1272" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:5" ht="15">
+      <c r="A1273" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1273" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1273" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:5" ht="15">
+      <c r="A1274" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1274" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1274" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F9F63B-25D8-4B5D-B181-2E63441358CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358727C4-E28F-4352-9671-A31433EDC21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6370" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7265" uniqueCount="667">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -1959,6 +1959,87 @@
   </si>
   <si>
     <t>Snow-Covered Forest </t>
+  </si>
+  <si>
+    <t>BR Black Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badlands </t>
+  </si>
+  <si>
+    <t>Chronicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maze of Ith </t>
+  </si>
+  <si>
+    <t>Uthden Troll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sedge Troll </t>
+  </si>
+  <si>
+    <t>Mountain (V.3) </t>
+  </si>
+  <si>
+    <t>Mountain (V.2) </t>
+  </si>
+  <si>
+    <t>BG Black Green</t>
+  </si>
+  <si>
+    <t>Blight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weakness </t>
+  </si>
+  <si>
+    <t>Cursed Land</t>
+  </si>
+  <si>
+    <t>Elves of Deep Shadow</t>
+  </si>
+  <si>
+    <t>Bayou</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>Wild Growth</t>
+  </si>
+  <si>
+    <t>Dark Heart of the Wood</t>
+  </si>
+  <si>
+    <t>Fallen Angel</t>
+  </si>
+  <si>
+    <t>RG Red Green</t>
+  </si>
+  <si>
+    <t>Tropical Island</t>
+  </si>
+  <si>
+    <t>Volcanic Island</t>
+  </si>
+  <si>
+    <t>Tranquility</t>
+  </si>
+  <si>
+    <t>Emerald Dragonfly</t>
+  </si>
+  <si>
+    <t>WR White Red</t>
+  </si>
+  <si>
+    <t>Plateau</t>
+  </si>
+  <si>
+    <t>Diamond Valley</t>
+  </si>
+  <si>
+    <t>Earthquake</t>
   </si>
 </sst>
 </file>
@@ -2093,7 +2174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2134,6 +2215,34 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2483,7 +2592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1274"/>
+  <dimension ref="A1:E1474"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -3189,23 +3298,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
         <v>40</v>
@@ -3223,57 +3315,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
         <v>43</v>
@@ -3461,40 +3502,6 @@
         <v>373</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2" t="s">
         <v>46</v>
@@ -3801,23 +3808,6 @@
         <v>373</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2" t="s">
         <v>45</v>
@@ -4158,23 +4148,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2" t="s">
         <v>40</v>
@@ -4430,40 +4403,6 @@
         <v>373</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2" t="s">
         <v>82</v>
@@ -7711,40 +7650,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="15">
-      <c r="A308" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C308" t="s">
-        <v>2</v>
-      </c>
-      <c r="D308" t="s">
-        <v>6</v>
-      </c>
-      <c r="E308" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" ht="15">
-      <c r="A309" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B309" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C309" t="s">
-        <v>2</v>
-      </c>
-      <c r="D309" t="s">
-        <v>6</v>
-      </c>
-      <c r="E309" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="310" spans="1:5" ht="15">
       <c r="A310" s="1" t="s">
         <v>172</v>
@@ -7779,74 +7684,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="15">
-      <c r="A312" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C312" t="s">
-        <v>2</v>
-      </c>
-      <c r="D312" t="s">
-        <v>6</v>
-      </c>
-      <c r="E312" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5" ht="15">
-      <c r="A313" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B313" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C313" t="s">
-        <v>2</v>
-      </c>
-      <c r="D313" t="s">
-        <v>6</v>
-      </c>
-      <c r="E313" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" ht="15">
-      <c r="A314" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C314" t="s">
-        <v>2</v>
-      </c>
-      <c r="D314" t="s">
-        <v>6</v>
-      </c>
-      <c r="E314" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" ht="15">
-      <c r="A315" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C315" t="s">
-        <v>2</v>
-      </c>
-      <c r="D315" t="s">
-        <v>6</v>
-      </c>
-      <c r="E315" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="316" spans="1:5" ht="15">
       <c r="A316" s="1" t="s">
         <v>175</v>
@@ -17860,23 +17697,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="905" spans="1:5" ht="15">
-      <c r="A905" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B905" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C905" t="s">
-        <v>29</v>
-      </c>
-      <c r="D905" t="s">
-        <v>3</v>
-      </c>
-      <c r="E905" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="906" spans="1:5" ht="15">
       <c r="A906" s="1" t="s">
         <v>542</v>
@@ -20410,23 +20230,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1055" spans="1:5" ht="15">
-      <c r="A1055" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="B1055" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1055" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1055" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1055" s="15" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1056" spans="1:5" ht="15">
       <c r="A1056" s="1" t="s">
         <v>166</v>
@@ -20546,23 +20349,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1063" spans="1:5" ht="15">
-      <c r="A1063" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="B1063" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1063" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1063" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1063" s="15" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1064" spans="1:5" ht="15">
       <c r="A1064" s="1" t="s">
         <v>584</v>
@@ -21039,40 +20825,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1092" spans="1:5" ht="15">
-      <c r="A1092" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1092" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1092" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1092" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1092" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="1093" spans="1:5" ht="15">
-      <c r="A1093" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1093" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1093" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1093" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1093" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1094" spans="1:5" ht="15">
       <c r="A1094" s="1" t="s">
         <v>597</v>
@@ -24148,6 +23900,3406 @@
       </c>
       <c r="E1274" s="2" t="s">
         <v>367</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:5" ht="15">
+      <c r="A1275" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B1275" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1275" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:5" ht="15">
+      <c r="A1276" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B1276" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1276" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:5" ht="15">
+      <c r="A1277" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1277" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1277" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:5" ht="15">
+      <c r="A1278" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1278" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1278" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:5" ht="15">
+      <c r="A1279" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B1279" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1279" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:5">
+      <c r="A1280" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1280" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1280" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1280" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1280" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:5" ht="15">
+      <c r="A1281" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1281" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1281" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:5" ht="15">
+      <c r="A1282" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1282" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1282" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:5" ht="15">
+      <c r="A1283" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B1283" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1283" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:5" ht="15">
+      <c r="A1284" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B1284" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1284" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:5" ht="15">
+      <c r="A1285" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1285" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1285" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:5" ht="15">
+      <c r="A1286" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B1286" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1286" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:5" ht="15">
+      <c r="A1287" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B1287" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1287" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:5" ht="15">
+      <c r="A1288" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B1288" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1288" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:5" ht="15">
+      <c r="A1289" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B1289" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1289" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:5" ht="15">
+      <c r="A1290" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1290" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1290" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:5" ht="15">
+      <c r="A1291" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1291" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1291" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:5" ht="15">
+      <c r="A1292" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1292" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1292" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:5" ht="15">
+      <c r="A1293" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1293" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1293" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:5" ht="15">
+      <c r="A1294" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1294" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1294" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:5" ht="15">
+      <c r="A1295" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1295" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1295" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:5">
+      <c r="A1296" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1296" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1296" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1296" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1296" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:5">
+      <c r="A1297" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1297" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1297" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1297" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1297" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:5">
+      <c r="A1298" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1298" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1298" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1298" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1298" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:5">
+      <c r="A1299" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1299" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1299" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1299" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1299" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:5">
+      <c r="A1300" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1300" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1300" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1300" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1300" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:5">
+      <c r="A1301" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1301" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1301" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1301" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1301" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:5">
+      <c r="A1302" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1302" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1302" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1302" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1302" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:5">
+      <c r="A1303" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1303" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1303" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1303" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1303" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:5" ht="15">
+      <c r="A1304" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1304" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1304" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:5">
+      <c r="A1305" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1305" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1305" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1305" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1305" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:5">
+      <c r="A1306" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1306" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1306" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1306" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1306" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:5">
+      <c r="A1307" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1307" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1307" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1307" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1307" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:5">
+      <c r="A1308" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1308" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1308" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1308" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1308" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:5">
+      <c r="A1309" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1309" s="22" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1309" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1309" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1309" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:5">
+      <c r="A1310" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1310" s="22" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1310" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1310" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1310" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:5" ht="15">
+      <c r="A1311" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1311" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1311" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:5">
+      <c r="A1312" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1312" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1312" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1312" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1312" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:5" ht="15">
+      <c r="A1313" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1313" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1313" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1313" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1313" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:5" ht="15">
+      <c r="A1314" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1314" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1314" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1314" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1314" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:5">
+      <c r="A1315" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1315" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1315" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:5">
+      <c r="A1316" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1316" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1316" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:5">
+      <c r="A1317" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1317" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1317" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:5">
+      <c r="A1318" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1318" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1318" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1318" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1318" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:5" ht="15">
+      <c r="A1319" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1319" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1319" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1319" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1319" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:5" ht="15">
+      <c r="A1320" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1320" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1320" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1320" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1320" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:5" ht="15">
+      <c r="A1321" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1321" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1321" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1321" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:5">
+      <c r="A1322" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1322" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1322" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1322" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1322" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:5" ht="15">
+      <c r="A1323" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B1323" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1323" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:5" ht="15">
+      <c r="A1324" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B1324" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1324" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:5" ht="15">
+      <c r="A1325" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B1325" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1325" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:5" ht="15">
+      <c r="A1326" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B1326" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1326" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1326" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:5" ht="15">
+      <c r="A1327" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B1327" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1327" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1327" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:5" ht="15">
+      <c r="A1328" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B1328" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1328" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1328" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:5" ht="15">
+      <c r="A1329" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1329" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1329" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1329" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:5" ht="15">
+      <c r="A1330" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1330" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1330" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1330" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:5" ht="15">
+      <c r="A1331" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1331" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1331" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1331" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:5" ht="15">
+      <c r="A1332" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1332" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1332" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1332" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:5" ht="15">
+      <c r="A1333" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1333" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1333" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1333" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:5" ht="15">
+      <c r="A1334" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1334" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1334" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1334" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:5" ht="15">
+      <c r="A1335" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1335" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1335" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1335" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:5" ht="15">
+      <c r="A1336" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1336" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1336" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1336" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:5" ht="15">
+      <c r="A1337" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B1337" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1337" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1337" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1337" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:5" ht="15">
+      <c r="A1338" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B1338" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1338" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1338" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1338" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:5" ht="15">
+      <c r="A1339" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B1339" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1339" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1339" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1339" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:5" ht="15">
+      <c r="A1340" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B1340" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1340" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1340" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1340" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:5" ht="15">
+      <c r="A1341" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B1341" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1341" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1341" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1341" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:5" ht="15">
+      <c r="A1342" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B1342" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1342" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1342" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1342" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:5" ht="15">
+      <c r="A1343" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B1343" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1343" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1343" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1343" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:5" ht="15">
+      <c r="A1344" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B1344" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1344" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1344" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1344" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:5" ht="15">
+      <c r="A1345" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B1345" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1345" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1345" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1345" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:5" ht="15">
+      <c r="A1346" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B1346" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1346" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1346" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1346" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:5" ht="15">
+      <c r="A1347" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B1347" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1347" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1347" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1347" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:5" ht="15">
+      <c r="A1348" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B1348" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1348" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1348" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1348" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:5" ht="15">
+      <c r="A1349" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1349" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1349" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1349" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:5" ht="15">
+      <c r="A1350" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B1350" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1350" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1350" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1350" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:5" ht="15">
+      <c r="A1351" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B1351" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1351" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1351" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1351" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:5" ht="15">
+      <c r="A1352" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B1352" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1352" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1352" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1352" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:5" ht="15">
+      <c r="A1353" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B1353" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1353" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1353" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1353" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:5" ht="15">
+      <c r="A1354" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B1354" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1354" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1354" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1354" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:5" ht="15">
+      <c r="A1355" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1355" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1355" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1355" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1355" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:5" ht="15">
+      <c r="A1356" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1356" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1356" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1356" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:5" ht="15">
+      <c r="A1357" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B1357" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1357" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1357" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1357" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:5">
+      <c r="A1358" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1358" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1358" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1358" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1358" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:5">
+      <c r="A1359" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1359" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1359" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1359" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1359" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:5">
+      <c r="A1360" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1360" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1360" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1360" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1360" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:5">
+      <c r="A1361" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1361" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1361" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1361" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1361" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:5" ht="15">
+      <c r="A1362" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1362" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1362" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1362" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:5" ht="15">
+      <c r="A1363" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1363" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1363" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1363" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:5" ht="15">
+      <c r="A1364" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1364" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1364" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1364" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:5" ht="15">
+      <c r="A1365" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1365" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1365" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1365" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1365" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:5">
+      <c r="A1366" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1366" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1366" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1366" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1366" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:5">
+      <c r="A1367" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1367" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1367" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1367" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1367" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:5">
+      <c r="A1368" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1368" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1368" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1368" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1368" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:5" ht="15">
+      <c r="A1369" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1369" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1369" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1369" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:5" ht="15">
+      <c r="A1370" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1370" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1370" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1370" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:5">
+      <c r="A1371" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1371" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1371" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1371" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1371" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:5">
+      <c r="A1372" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1372" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1372" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1372" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1372" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:5">
+      <c r="A1373" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1373" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1373" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1373" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1373" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:5">
+      <c r="A1374" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1374" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1374" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1374" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1374" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:5" ht="15">
+      <c r="A1375" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1375" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1375" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1375" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1375" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:5" ht="15">
+      <c r="A1376" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1376" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1376" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1376" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1376" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:5" ht="15">
+      <c r="A1377" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1377" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1377" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1377" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:5" ht="15">
+      <c r="A1378" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1378" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1378" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1378" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1378" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:5" ht="15">
+      <c r="A1379" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1379" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1379" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1379" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1379" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:5" ht="15">
+      <c r="A1380" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1380" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1380" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1380" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1380" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:5" ht="15">
+      <c r="A1381" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1381" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1381" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1381" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1381" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:5" ht="15">
+      <c r="A1382" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1382" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1382" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1382" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1382" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:5" ht="15">
+      <c r="A1383" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1383" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1383" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1383" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1383" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:5" ht="15">
+      <c r="A1384" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1384" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1384" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1384" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1384" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:5" ht="15">
+      <c r="A1385" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1385" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1385" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1385" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1385" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:5" ht="15">
+      <c r="A1386" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1386" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1386" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1386" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1386" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:5" ht="15">
+      <c r="A1387" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1387" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1387" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1387" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1387" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:5" ht="15">
+      <c r="A1388" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1388" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1388" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1388" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1388" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:5" ht="15">
+      <c r="A1389" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1389" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1389" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1389" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1389" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:5">
+      <c r="A1390" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1390" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1390" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1390" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1390" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:5" ht="15">
+      <c r="A1391" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1391" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1391" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1391" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1391" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:5" ht="15">
+      <c r="A1392" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1392" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1392" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1392" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1392" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:5" ht="15">
+      <c r="A1393" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1393" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1393" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1393" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1393" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:5" ht="15">
+      <c r="A1394" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1394" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1394" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1394" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1394" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:5" ht="15">
+      <c r="A1395" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1395" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1395" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1395" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1395" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:5" ht="15">
+      <c r="A1396" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1396" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1396" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1396" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1396" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:5" ht="15">
+      <c r="A1397" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1397" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1397" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1397" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1397" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:5" ht="15">
+      <c r="A1398" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1398" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1398" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1398" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1398" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:5" ht="15">
+      <c r="A1399" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B1399" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1399" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1399" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1399" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:5" ht="15">
+      <c r="A1400" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B1400" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1400" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1400" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1400" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:5" ht="15">
+      <c r="A1401" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1401" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1401" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:5" ht="15">
+      <c r="A1402" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B1402" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1402" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1402" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:5" ht="15">
+      <c r="A1403" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1403" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1403" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1403" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:5" ht="15">
+      <c r="A1404" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B1404" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1404" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1404" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1404" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:5" ht="15">
+      <c r="A1405" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1405" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1405" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1405" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:5" ht="15">
+      <c r="A1406" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B1406" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1406" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1406" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:5" ht="15">
+      <c r="A1407" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1407" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1407" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1407" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:5" ht="15">
+      <c r="A1408" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B1408" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1408" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1408" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:5" ht="15">
+      <c r="A1409" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B1409" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1409" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1409" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:5" ht="15">
+      <c r="A1410" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B1410" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1410" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1410" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1410" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:5" ht="15">
+      <c r="A1411" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1411" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1411" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1411" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:5" ht="15">
+      <c r="A1412" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1412" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1412" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:5" ht="15">
+      <c r="A1413" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1413" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1413" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1413" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:5" ht="15">
+      <c r="A1414" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1414" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1414" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1414" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:5" ht="15">
+      <c r="A1415" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1415" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1415" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1415" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1415" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:5" ht="15">
+      <c r="A1416" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1416" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1416" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:5" ht="15">
+      <c r="A1417" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1417" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1417" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1417" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1417" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:5" ht="15">
+      <c r="A1418" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1418" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1418" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:5" ht="15">
+      <c r="A1419" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B1419" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1419" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1419" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:5" ht="15">
+      <c r="A1420" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1420" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1420" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1420" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1420" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:5" ht="15">
+      <c r="A1421" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1421" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1421" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1421" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1421" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:5" ht="15">
+      <c r="A1422" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1422" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1422" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1422" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1422" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:5" ht="15">
+      <c r="A1423" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1423" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1423" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1423" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1423" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:5" ht="15">
+      <c r="A1424" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1424" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1424" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1424" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1424" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:5" ht="15">
+      <c r="A1425" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1425" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1425" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1425" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1425" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:5" ht="15">
+      <c r="A1426" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1426" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1426" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1426" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1426" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:5" ht="15">
+      <c r="A1427" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B1427" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1427" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1427" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1427" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:5" ht="15">
+      <c r="A1428" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1428" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1428" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1428" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1428" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:5" ht="15">
+      <c r="A1429" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B1429" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1429" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1429" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:5" ht="15">
+      <c r="A1430" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1430" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1430" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1430" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:5" ht="15">
+      <c r="A1431" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1431" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1431" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1431" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1431" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:5" ht="15">
+      <c r="A1432" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1432" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1432" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1432" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1432" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:5" ht="15">
+      <c r="A1433" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1433" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1433" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1433" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1433" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:5" ht="15">
+      <c r="A1434" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1434" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1434" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1434" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1434" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:5" ht="15">
+      <c r="A1435" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1435" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1435" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1435" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1435" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:5" ht="15">
+      <c r="A1436" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1436" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1436" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1436" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1436" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:5" ht="15">
+      <c r="A1437" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1437" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1437" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1437" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1437" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:5" ht="15">
+      <c r="A1438" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1438" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1438" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1438" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1438" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:5" ht="15">
+      <c r="A1439" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1439" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1439" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1439" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1439" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:5" ht="15">
+      <c r="A1440" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1440" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1440" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1440" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1440" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:5" ht="15">
+      <c r="A1441" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1441" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1441" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1441" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1441" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:5" ht="15">
+      <c r="A1442" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1442" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1442" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1442" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1442" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:5" ht="15">
+      <c r="A1443" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1443" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1443" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1443" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1443" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:5" ht="15">
+      <c r="A1444" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B1444" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1444" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1444" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1444" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:5" ht="15">
+      <c r="A1445" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B1445" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1445" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1445" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1445" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:5" ht="15">
+      <c r="A1446" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1446" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1446" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1446" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1446" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:5" ht="15">
+      <c r="A1447" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1447" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1447" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1447" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1447" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:5" ht="15">
+      <c r="A1448" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1448" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1448" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1448" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1448" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:5" ht="15">
+      <c r="A1449" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1449" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1449" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1449" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1449" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:5" ht="15">
+      <c r="A1450" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1450" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1450" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1450" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1450" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:5" ht="15">
+      <c r="A1451" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1451" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1451" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1451" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1451" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:5" ht="15">
+      <c r="A1452" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1452" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1452" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1452" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1452" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:5" ht="15">
+      <c r="A1453" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1453" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1453" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1453" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1453" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:5" ht="15">
+      <c r="A1454" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1454" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1454" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1454" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1454" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:5" ht="15">
+      <c r="A1455" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1455" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1455" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1455" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1455" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:5" ht="15">
+      <c r="A1456" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1456" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1456" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1456" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1456" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:5" ht="15">
+      <c r="A1457" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1457" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1457" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1457" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1457" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:5" ht="15">
+      <c r="A1458" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1458" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1458" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1458" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1458" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:5" ht="15">
+      <c r="A1459" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1459" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1459" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1459" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1459" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:5" ht="15">
+      <c r="A1460" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1460" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1460" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1460" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1460" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:5" ht="15">
+      <c r="A1461" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1461" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1461" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1461" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1461" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:5" ht="15">
+      <c r="A1462" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1462" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1462" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1462" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1462" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:5" ht="15">
+      <c r="A1463" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1463" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1463" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1463" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1463" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:5" ht="15">
+      <c r="A1464" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1464" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1464" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1464" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1464" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:5" ht="15">
+      <c r="A1465" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1465" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1465" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1465" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1465" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:5" ht="15">
+      <c r="A1466" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1466" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1466" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1466" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1466" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:5" ht="15">
+      <c r="A1467" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1467" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1467" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1467" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1467" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:5" ht="15">
+      <c r="A1468" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1468" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1468" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1468" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1468" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:5" ht="15">
+      <c r="A1469" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1469" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1469" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1469" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1469" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:5" ht="15">
+      <c r="A1470" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1470" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1470" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1470" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1470" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:5" ht="15">
+      <c r="A1471" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1471" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1471" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1471" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1471" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:5" ht="15">
+      <c r="A1472" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1472" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1472" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1472" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1472" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:5" ht="15">
+      <c r="A1473" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1473" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1473" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1473" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1473" s="25" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:5" ht="15">
+      <c r="A1474" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1474" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1474" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1474" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1474" s="25" t="s">
+        <v>663</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358727C4-E28F-4352-9671-A31433EDC21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6BA105-7BE2-4F2C-88C2-636F75B778BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7265" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7550" uniqueCount="669">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2040,6 +2040,12 @@
   </si>
   <si>
     <t>Earthquake</t>
+  </si>
+  <si>
+    <t>Lion's Eye Diamond</t>
+  </si>
+  <si>
+    <t>Warp Artifact</t>
   </si>
 </sst>
 </file>
@@ -2174,7 +2180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2217,34 +2223,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2263,13 +2241,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E3A1B72-86A8-4DFD-8879-567FFC9FD99E}" name="CollectionTable" displayName="CollectionTable" ref="A2:E125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CD7D939B-8383-49E3-AA94-62B30567A07E}" name="CollectionTable3" displayName="CollectionTable3" ref="A2:E125">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{EE1C50BD-064E-4522-9D0B-4633B36785C8}" name="Artifact Blast"/>
-    <tableColumn id="2" xr3:uid="{8CA90749-E92E-4160-B2D6-403EE9CBCFC2}" name="Antiquities"/>
-    <tableColumn id="3" xr3:uid="{86E07A04-B23B-4E5A-8758-329ED23559AC}" name="English"/>
-    <tableColumn id="4" xr3:uid="{E4A32223-1371-4BA4-9683-1D055BF0226D}" name="EX"/>
-    <tableColumn id="5" xr3:uid="{A7FA048E-2907-4449-A685-854C14E27ADE}" name="Classeur 1"/>
+    <tableColumn id="1" xr3:uid="{793795F6-2B86-46A9-B6AC-358E14FCAE92}" name="Artifact Blast"/>
+    <tableColumn id="2" xr3:uid="{EB57E740-B9C7-44EE-A09E-0BA14C4655A7}" name="Antiquities"/>
+    <tableColumn id="3" xr3:uid="{077FFB98-2393-4C48-9B83-B6B1EF86B4D0}" name="English"/>
+    <tableColumn id="4" xr3:uid="{9AC44415-BC0F-430A-99E8-FEF26BB6C0D5}" name="EX"/>
+    <tableColumn id="5" xr3:uid="{2C803579-D7EF-4580-9294-9A484CF401B1}" name="Classeur 1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2592,7 +2570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1474"/>
+  <dimension ref="A1:E1531"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -23988,16 +23966,16 @@
       </c>
     </row>
     <row r="1280" spans="1:5">
-      <c r="A1280" s="16" t="s">
+      <c r="A1280" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B1280" s="17" t="s">
+      <c r="B1280" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C1280" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1280" s="17" t="s">
+      <c r="C1280" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1280" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1280" s="2" t="s">
@@ -24073,7 +24051,7 @@
       </c>
     </row>
     <row r="1285" spans="1:5" ht="15">
-      <c r="A1285" s="18" t="s">
+      <c r="A1285" s="1" t="s">
         <v>191</v>
       </c>
       <c r="B1285" s="1" t="s">
@@ -24260,16 +24238,16 @@
       </c>
     </row>
     <row r="1296" spans="1:5">
-      <c r="A1296" s="16" t="s">
+      <c r="A1296" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B1296" s="17" t="s">
+      <c r="B1296" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1296" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1296" s="17" t="s">
+      <c r="C1296" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1296" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1296" s="2" t="s">
@@ -24277,16 +24255,16 @@
       </c>
     </row>
     <row r="1297" spans="1:5">
-      <c r="A1297" s="16" t="s">
+      <c r="A1297" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B1297" s="17" t="s">
+      <c r="B1297" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C1297" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1297" s="17" t="s">
+      <c r="C1297" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1297" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1297" s="2" t="s">
@@ -24294,16 +24272,16 @@
       </c>
     </row>
     <row r="1298" spans="1:5">
-      <c r="A1298" s="16" t="s">
+      <c r="A1298" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B1298" s="17" t="s">
+      <c r="B1298" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1298" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1298" s="17" t="s">
+      <c r="C1298" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1298" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1298" s="2" t="s">
@@ -24311,16 +24289,16 @@
       </c>
     </row>
     <row r="1299" spans="1:5">
-      <c r="A1299" s="19" t="s">
+      <c r="A1299" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B1299" s="20" t="s">
+      <c r="B1299" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C1299" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1299" s="17" t="s">
+      <c r="C1299" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1299" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1299" s="2" t="s">
@@ -24328,16 +24306,16 @@
       </c>
     </row>
     <row r="1300" spans="1:5">
-      <c r="A1300" s="19" t="s">
+      <c r="A1300" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B1300" s="20" t="s">
+      <c r="B1300" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C1300" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1300" s="17" t="s">
+      <c r="C1300" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1300" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1300" s="2" t="s">
@@ -24345,16 +24323,16 @@
       </c>
     </row>
     <row r="1301" spans="1:5">
-      <c r="A1301" s="19" t="s">
+      <c r="A1301" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B1301" s="17" t="s">
+      <c r="B1301" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1301" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1301" s="20" t="s">
+      <c r="C1301" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1301" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E1301" s="2" t="s">
@@ -24362,16 +24340,16 @@
       </c>
     </row>
     <row r="1302" spans="1:5">
-      <c r="A1302" s="21" t="s">
+      <c r="A1302" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B1302" s="17" t="s">
+      <c r="B1302" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1302" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1302" s="20" t="s">
+      <c r="C1302" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1302" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E1302" s="2" t="s">
@@ -24379,16 +24357,16 @@
       </c>
     </row>
     <row r="1303" spans="1:5">
-      <c r="A1303" s="21" t="s">
+      <c r="A1303" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B1303" s="22" t="s">
+      <c r="B1303" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C1303" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1303" s="20" t="s">
+      <c r="C1303" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1303" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E1303" s="2" t="s">
@@ -24413,16 +24391,16 @@
       </c>
     </row>
     <row r="1305" spans="1:5">
-      <c r="A1305" s="16" t="s">
+      <c r="A1305" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B1305" s="17" t="s">
+      <c r="B1305" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1305" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1305" s="20" t="s">
+      <c r="C1305" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1305" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E1305" s="2" t="s">
@@ -24430,16 +24408,16 @@
       </c>
     </row>
     <row r="1306" spans="1:5">
-      <c r="A1306" s="16" t="s">
+      <c r="A1306" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B1306" s="17" t="s">
+      <c r="B1306" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1306" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1306" s="20" t="s">
+      <c r="C1306" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1306" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E1306" s="2" t="s">
@@ -24447,16 +24425,16 @@
       </c>
     </row>
     <row r="1307" spans="1:5">
-      <c r="A1307" s="16" t="s">
+      <c r="A1307" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B1307" s="17" t="s">
+      <c r="B1307" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1307" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1307" s="20" t="s">
+      <c r="C1307" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1307" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E1307" s="2" t="s">
@@ -24464,16 +24442,16 @@
       </c>
     </row>
     <row r="1308" spans="1:5">
-      <c r="A1308" s="16" t="s">
+      <c r="A1308" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B1308" s="17" t="s">
+      <c r="B1308" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C1308" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1308" s="20" t="s">
+      <c r="C1308" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1308" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E1308" s="2" t="s">
@@ -24481,16 +24459,16 @@
       </c>
     </row>
     <row r="1309" spans="1:5">
-      <c r="A1309" s="22" t="s">
+      <c r="A1309" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B1309" s="22" t="s">
+      <c r="B1309" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="C1309" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1309" s="23" t="s">
+      <c r="C1309" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1309" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E1309" s="2" t="s">
@@ -24498,16 +24476,16 @@
       </c>
     </row>
     <row r="1310" spans="1:5">
-      <c r="A1310" s="22" t="s">
+      <c r="A1310" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B1310" s="22" t="s">
+      <c r="B1310" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="C1310" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1310" s="23" t="s">
+      <c r="C1310" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1310" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E1310" s="2" t="s">
@@ -24532,16 +24510,16 @@
       </c>
     </row>
     <row r="1312" spans="1:5">
-      <c r="A1312" s="22" t="s">
+      <c r="A1312" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B1312" s="17" t="s">
+      <c r="B1312" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1312" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1312" s="20" t="s">
+      <c r="C1312" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1312" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E1312" s="2" t="s">
@@ -24552,13 +24530,13 @@
       <c r="A1313" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B1313" s="17" t="s">
+      <c r="B1313" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1313" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1313" s="20" t="s">
+      <c r="C1313" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1313" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E1313" s="2" t="s">
@@ -24569,13 +24547,13 @@
       <c r="A1314" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1314" s="17" t="s">
+      <c r="B1314" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1314" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1314" s="20" t="s">
+      <c r="C1314" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1314" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E1314" s="2" t="s">
@@ -24586,7 +24564,7 @@
       <c r="A1315" t="s">
         <v>88</v>
       </c>
-      <c r="B1315" s="22" t="s">
+      <c r="B1315" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C1315" t="s">
@@ -24603,7 +24581,7 @@
       <c r="A1316" t="s">
         <v>88</v>
       </c>
-      <c r="B1316" s="22" t="s">
+      <c r="B1316" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C1316" t="s">
@@ -24620,7 +24598,7 @@
       <c r="A1317" t="s">
         <v>103</v>
       </c>
-      <c r="B1317" s="22" t="s">
+      <c r="B1317" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C1317" t="s">
@@ -24637,13 +24615,13 @@
       <c r="A1318" t="s">
         <v>645</v>
       </c>
-      <c r="B1318" s="17" t="s">
+      <c r="B1318" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1318" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1318" s="20" t="s">
+      <c r="C1318" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1318" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E1318" s="2" t="s">
@@ -24654,13 +24632,13 @@
       <c r="A1319" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1319" s="17" t="s">
+      <c r="B1319" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1319" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1319" s="20" t="s">
+      <c r="C1319" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1319" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E1319" s="2" t="s">
@@ -24671,13 +24649,13 @@
       <c r="A1320" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1320" s="17" t="s">
+      <c r="B1320" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1320" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1320" s="20" t="s">
+      <c r="C1320" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1320" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E1320" s="2" t="s">
@@ -24702,16 +24680,16 @@
       </c>
     </row>
     <row r="1322" spans="1:5">
-      <c r="A1322" s="19" t="s">
+      <c r="A1322" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B1322" s="17" t="s">
+      <c r="B1322" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1322" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1322" s="20" t="s">
+      <c r="C1322" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1322" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E1322" s="2" t="s">
@@ -25113,13 +25091,13 @@
       <c r="A1346" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B1346" s="17" t="s">
+      <c r="B1346" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1346" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1346" s="20" t="s">
+      <c r="C1346" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1346" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E1346" s="15" t="s">
@@ -25130,13 +25108,13 @@
       <c r="A1347" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B1347" s="17" t="s">
+      <c r="B1347" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1347" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1347" s="20" t="s">
+      <c r="C1347" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1347" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E1347" s="15" t="s">
@@ -25283,7 +25261,7 @@
       <c r="A1356" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B1356" s="17" t="s">
+      <c r="B1356" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C1356" t="s">
@@ -25314,16 +25292,16 @@
       </c>
     </row>
     <row r="1358" spans="1:5">
-      <c r="A1358" s="16" t="s">
+      <c r="A1358" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B1358" s="17" t="s">
+      <c r="B1358" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1358" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1358" s="17" t="s">
+      <c r="C1358" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1358" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E1358" s="15" t="s">
@@ -25331,16 +25309,16 @@
       </c>
     </row>
     <row r="1359" spans="1:5">
-      <c r="A1359" s="19" t="s">
+      <c r="A1359" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B1359" s="20" t="s">
+      <c r="B1359" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1359" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1359" s="20" t="s">
+      <c r="C1359" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1359" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E1359" s="15" t="s">
@@ -25348,16 +25326,16 @@
       </c>
     </row>
     <row r="1360" spans="1:5">
-      <c r="A1360" s="16" t="s">
+      <c r="A1360" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B1360" s="17" t="s">
+      <c r="B1360" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1360" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1360" s="17" t="s">
+      <c r="C1360" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1360" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E1360" s="15" t="s">
@@ -25365,16 +25343,16 @@
       </c>
     </row>
     <row r="1361" spans="1:5">
-      <c r="A1361" s="19" t="s">
+      <c r="A1361" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B1361" s="20" t="s">
+      <c r="B1361" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C1361" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1361" s="20" t="s">
+      <c r="C1361" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1361" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E1361" s="15" t="s">
@@ -25450,16 +25428,16 @@
       </c>
     </row>
     <row r="1366" spans="1:5">
-      <c r="A1366" s="16" t="s">
+      <c r="A1366" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B1366" s="17" t="s">
+      <c r="B1366" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1366" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1366" s="17" t="s">
+      <c r="C1366" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1366" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1366" s="15" t="s">
@@ -25467,16 +25445,16 @@
       </c>
     </row>
     <row r="1367" spans="1:5">
-      <c r="A1367" s="16" t="s">
+      <c r="A1367" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B1367" s="17" t="s">
+      <c r="B1367" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C1367" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1367" s="17" t="s">
+      <c r="C1367" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1367" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1367" s="15" t="s">
@@ -25484,16 +25462,16 @@
       </c>
     </row>
     <row r="1368" spans="1:5">
-      <c r="A1368" s="16" t="s">
+      <c r="A1368" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B1368" s="17" t="s">
+      <c r="B1368" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C1368" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1368" s="17" t="s">
+      <c r="C1368" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1368" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1368" s="15" t="s">
@@ -25790,7 +25768,7 @@
       </c>
     </row>
     <row r="1386" spans="1:5" ht="15">
-      <c r="A1386" s="18" t="s">
+      <c r="A1386" s="1" t="s">
         <v>541</v>
       </c>
       <c r="B1386" s="1" t="s">
@@ -25807,7 +25785,7 @@
       </c>
     </row>
     <row r="1387" spans="1:5" ht="15">
-      <c r="A1387" s="18" t="s">
+      <c r="A1387" s="1" t="s">
         <v>541</v>
       </c>
       <c r="B1387" s="1" t="s">
@@ -25824,7 +25802,7 @@
       </c>
     </row>
     <row r="1388" spans="1:5" ht="15">
-      <c r="A1388" s="18" t="s">
+      <c r="A1388" s="1" t="s">
         <v>541</v>
       </c>
       <c r="B1388" s="1" t="s">
@@ -25841,7 +25819,7 @@
       </c>
     </row>
     <row r="1389" spans="1:5" ht="15">
-      <c r="A1389" s="18" t="s">
+      <c r="A1389" s="1" t="s">
         <v>541</v>
       </c>
       <c r="B1389" s="1" t="s">
@@ -25939,7 +25917,7 @@
         <v>6</v>
       </c>
       <c r="E1394" s="10" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
     </row>
     <row r="1395" spans="1:5" ht="15">
@@ -26034,7 +26012,7 @@
       <c r="B1400" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1400" s="24" t="s">
+      <c r="C1400" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1400" s="6" t="s">
@@ -26102,7 +26080,7 @@
       <c r="B1404" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="C1404" s="24" t="s">
+      <c r="C1404" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1404" s="6" t="s">
@@ -26125,7 +26103,7 @@
       <c r="D1405" t="s">
         <v>42</v>
       </c>
-      <c r="E1405" s="25" t="s">
+      <c r="E1405" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26142,7 +26120,7 @@
       <c r="D1406" t="s">
         <v>42</v>
       </c>
-      <c r="E1406" s="25" t="s">
+      <c r="E1406" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26159,7 +26137,7 @@
       <c r="D1407" t="s">
         <v>6</v>
       </c>
-      <c r="E1407" s="25" t="s">
+      <c r="E1407" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26176,7 +26154,7 @@
       <c r="D1408" t="s">
         <v>3</v>
       </c>
-      <c r="E1408" s="25" t="s">
+      <c r="E1408" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26193,7 +26171,7 @@
       <c r="D1409" t="s">
         <v>6</v>
       </c>
-      <c r="E1409" s="25" t="s">
+      <c r="E1409" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26210,7 +26188,7 @@
       <c r="D1410" t="s">
         <v>6</v>
       </c>
-      <c r="E1410" s="25" t="s">
+      <c r="E1410" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26227,7 +26205,7 @@
       <c r="D1411" t="s">
         <v>3</v>
       </c>
-      <c r="E1411" s="25" t="s">
+      <c r="E1411" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26244,7 +26222,7 @@
       <c r="D1412" t="s">
         <v>42</v>
       </c>
-      <c r="E1412" s="25" t="s">
+      <c r="E1412" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26261,7 +26239,7 @@
       <c r="D1413" t="s">
         <v>6</v>
       </c>
-      <c r="E1413" s="25" t="s">
+      <c r="E1413" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26278,7 +26256,7 @@
       <c r="D1414" t="s">
         <v>6</v>
       </c>
-      <c r="E1414" s="25" t="s">
+      <c r="E1414" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26295,7 +26273,7 @@
       <c r="D1415" t="s">
         <v>6</v>
       </c>
-      <c r="E1415" s="25" t="s">
+      <c r="E1415" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26312,7 +26290,7 @@
       <c r="D1416" t="s">
         <v>3</v>
       </c>
-      <c r="E1416" s="25" t="s">
+      <c r="E1416" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26329,7 +26307,7 @@
       <c r="D1417" t="s">
         <v>6</v>
       </c>
-      <c r="E1417" s="25" t="s">
+      <c r="E1417" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26346,7 +26324,7 @@
       <c r="D1418" t="s">
         <v>6</v>
       </c>
-      <c r="E1418" s="25" t="s">
+      <c r="E1418" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26363,7 +26341,7 @@
       <c r="D1419" t="s">
         <v>6</v>
       </c>
-      <c r="E1419" s="25" t="s">
+      <c r="E1419" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26380,7 +26358,7 @@
       <c r="D1420" t="s">
         <v>6</v>
       </c>
-      <c r="E1420" s="25" t="s">
+      <c r="E1420" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26397,7 +26375,7 @@
       <c r="D1421" t="s">
         <v>6</v>
       </c>
-      <c r="E1421" s="25" t="s">
+      <c r="E1421" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26408,13 +26386,13 @@
       <c r="B1422" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1422" s="24" t="s">
+      <c r="C1422" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1422" t="s">
         <v>3</v>
       </c>
-      <c r="E1422" s="25" t="s">
+      <c r="E1422" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26425,13 +26403,13 @@
       <c r="B1423" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1423" s="24" t="s">
+      <c r="C1423" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1423" t="s">
         <v>6</v>
       </c>
-      <c r="E1423" s="25" t="s">
+      <c r="E1423" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26442,13 +26420,13 @@
       <c r="B1424" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1424" s="24" t="s">
+      <c r="C1424" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1424" t="s">
         <v>6</v>
       </c>
-      <c r="E1424" s="25" t="s">
+      <c r="E1424" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26459,13 +26437,13 @@
       <c r="B1425" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1425" s="24" t="s">
+      <c r="C1425" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1425" t="s">
         <v>6</v>
       </c>
-      <c r="E1425" s="25" t="s">
+      <c r="E1425" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26482,7 +26460,7 @@
       <c r="D1426" t="s">
         <v>6</v>
       </c>
-      <c r="E1426" s="25" t="s">
+      <c r="E1426" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26493,13 +26471,13 @@
       <c r="B1427" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1427" s="24" t="s">
+      <c r="C1427" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1427" t="s">
         <v>6</v>
       </c>
-      <c r="E1427" s="25" t="s">
+      <c r="E1427" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26516,7 +26494,7 @@
       <c r="D1428" t="s">
         <v>6</v>
       </c>
-      <c r="E1428" s="25" t="s">
+      <c r="E1428" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26533,7 +26511,7 @@
       <c r="D1429" t="s">
         <v>6</v>
       </c>
-      <c r="E1429" s="25" t="s">
+      <c r="E1429" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26550,7 +26528,7 @@
       <c r="D1430" t="s">
         <v>6</v>
       </c>
-      <c r="E1430" s="25" t="s">
+      <c r="E1430" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26567,7 +26545,7 @@
       <c r="D1431" t="s">
         <v>6</v>
       </c>
-      <c r="E1431" s="25" t="s">
+      <c r="E1431" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26584,7 +26562,7 @@
       <c r="D1432" t="s">
         <v>6</v>
       </c>
-      <c r="E1432" s="25" t="s">
+      <c r="E1432" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26601,7 +26579,7 @@
       <c r="D1433" t="s">
         <v>6</v>
       </c>
-      <c r="E1433" s="25" t="s">
+      <c r="E1433" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26618,7 +26596,7 @@
       <c r="D1434" t="s">
         <v>6</v>
       </c>
-      <c r="E1434" s="25" t="s">
+      <c r="E1434" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26635,7 +26613,7 @@
       <c r="D1435" t="s">
         <v>6</v>
       </c>
-      <c r="E1435" s="25" t="s">
+      <c r="E1435" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26652,7 +26630,7 @@
       <c r="D1436" t="s">
         <v>6</v>
       </c>
-      <c r="E1436" s="25" t="s">
+      <c r="E1436" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26669,7 +26647,7 @@
       <c r="D1437" t="s">
         <v>6</v>
       </c>
-      <c r="E1437" s="25" t="s">
+      <c r="E1437" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26686,7 +26664,7 @@
       <c r="D1438" t="s">
         <v>6</v>
       </c>
-      <c r="E1438" s="25" t="s">
+      <c r="E1438" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26703,7 +26681,7 @@
       <c r="D1439" t="s">
         <v>6</v>
       </c>
-      <c r="E1439" s="25" t="s">
+      <c r="E1439" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26720,7 +26698,7 @@
       <c r="D1440" t="s">
         <v>6</v>
       </c>
-      <c r="E1440" s="25" t="s">
+      <c r="E1440" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26737,7 +26715,7 @@
       <c r="D1441" t="s">
         <v>6</v>
       </c>
-      <c r="E1441" s="25" t="s">
+      <c r="E1441" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26754,7 +26732,7 @@
       <c r="D1442" t="s">
         <v>6</v>
       </c>
-      <c r="E1442" s="25" t="s">
+      <c r="E1442" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26771,7 +26749,7 @@
       <c r="D1443" t="s">
         <v>6</v>
       </c>
-      <c r="E1443" s="25" t="s">
+      <c r="E1443" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26788,7 +26766,7 @@
       <c r="D1444" t="s">
         <v>6</v>
       </c>
-      <c r="E1444" s="25" t="s">
+      <c r="E1444" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26805,7 +26783,7 @@
       <c r="D1445" t="s">
         <v>6</v>
       </c>
-      <c r="E1445" s="25" t="s">
+      <c r="E1445" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26816,13 +26794,13 @@
       <c r="B1446" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="C1446" s="24" t="s">
+      <c r="C1446" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1446" t="s">
         <v>6</v>
       </c>
-      <c r="E1446" s="25" t="s">
+      <c r="E1446" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26833,13 +26811,13 @@
       <c r="B1447" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="C1447" s="24" t="s">
+      <c r="C1447" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1447" t="s">
         <v>6</v>
       </c>
-      <c r="E1447" s="25" t="s">
+      <c r="E1447" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26856,7 +26834,7 @@
       <c r="D1448" t="s">
         <v>6</v>
       </c>
-      <c r="E1448" s="25" t="s">
+      <c r="E1448" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26873,7 +26851,7 @@
       <c r="D1449" t="s">
         <v>6</v>
       </c>
-      <c r="E1449" s="25" t="s">
+      <c r="E1449" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26890,7 +26868,7 @@
       <c r="D1450" t="s">
         <v>31</v>
       </c>
-      <c r="E1450" s="25" t="s">
+      <c r="E1450" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26907,7 +26885,7 @@
       <c r="D1451" t="s">
         <v>3</v>
       </c>
-      <c r="E1451" s="25" t="s">
+      <c r="E1451" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26918,13 +26896,13 @@
       <c r="B1452" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1452" s="24" t="s">
+      <c r="C1452" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1452" t="s">
         <v>6</v>
       </c>
-      <c r="E1452" s="25" t="s">
+      <c r="E1452" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26935,13 +26913,13 @@
       <c r="B1453" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1453" s="24" t="s">
+      <c r="C1453" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1453" t="s">
         <v>6</v>
       </c>
-      <c r="E1453" s="25" t="s">
+      <c r="E1453" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26952,13 +26930,13 @@
       <c r="B1454" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1454" s="24" t="s">
+      <c r="C1454" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1454" t="s">
         <v>6</v>
       </c>
-      <c r="E1454" s="25" t="s">
+      <c r="E1454" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26969,13 +26947,13 @@
       <c r="B1455" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1455" s="24" t="s">
+      <c r="C1455" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1455" t="s">
         <v>6</v>
       </c>
-      <c r="E1455" s="25" t="s">
+      <c r="E1455" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -26992,7 +26970,7 @@
       <c r="D1456" t="s">
         <v>42</v>
       </c>
-      <c r="E1456" s="25" t="s">
+      <c r="E1456" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27009,7 +26987,7 @@
       <c r="D1457" t="s">
         <v>6</v>
       </c>
-      <c r="E1457" s="25" t="s">
+      <c r="E1457" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27026,7 +27004,7 @@
       <c r="D1458" t="s">
         <v>6</v>
       </c>
-      <c r="E1458" s="25" t="s">
+      <c r="E1458" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27043,7 +27021,7 @@
       <c r="D1459" t="s">
         <v>6</v>
       </c>
-      <c r="E1459" s="25" t="s">
+      <c r="E1459" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27060,7 +27038,7 @@
       <c r="D1460" t="s">
         <v>3</v>
       </c>
-      <c r="E1460" s="25" t="s">
+      <c r="E1460" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27077,7 +27055,7 @@
       <c r="D1461" t="s">
         <v>6</v>
       </c>
-      <c r="E1461" s="25" t="s">
+      <c r="E1461" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27094,7 +27072,7 @@
       <c r="D1462" t="s">
         <v>6</v>
       </c>
-      <c r="E1462" s="25" t="s">
+      <c r="E1462" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27111,7 +27089,7 @@
       <c r="D1463" t="s">
         <v>3</v>
       </c>
-      <c r="E1463" s="25" t="s">
+      <c r="E1463" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27128,7 +27106,7 @@
       <c r="D1464" t="s">
         <v>6</v>
       </c>
-      <c r="E1464" s="25" t="s">
+      <c r="E1464" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27145,7 +27123,7 @@
       <c r="D1465" t="s">
         <v>6</v>
       </c>
-      <c r="E1465" s="25" t="s">
+      <c r="E1465" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27162,7 +27140,7 @@
       <c r="D1466" t="s">
         <v>3</v>
       </c>
-      <c r="E1466" s="25" t="s">
+      <c r="E1466" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27179,7 +27157,7 @@
       <c r="D1467" t="s">
         <v>6</v>
       </c>
-      <c r="E1467" s="25" t="s">
+      <c r="E1467" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27196,7 +27174,7 @@
       <c r="D1468" t="s">
         <v>6</v>
       </c>
-      <c r="E1468" s="25" t="s">
+      <c r="E1468" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27213,7 +27191,7 @@
       <c r="D1469" t="s">
         <v>6</v>
       </c>
-      <c r="E1469" s="25" t="s">
+      <c r="E1469" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27230,7 +27208,7 @@
       <c r="D1470" t="s">
         <v>6</v>
       </c>
-      <c r="E1470" s="25" t="s">
+      <c r="E1470" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27247,7 +27225,7 @@
       <c r="D1471" t="s">
         <v>6</v>
       </c>
-      <c r="E1471" s="25" t="s">
+      <c r="E1471" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27264,7 +27242,7 @@
       <c r="D1472" t="s">
         <v>6</v>
       </c>
-      <c r="E1472" s="25" t="s">
+      <c r="E1472" s="8" t="s">
         <v>663</v>
       </c>
     </row>
@@ -27281,8 +27259,8 @@
       <c r="D1473" t="s">
         <v>6</v>
       </c>
-      <c r="E1473" s="25" t="s">
-        <v>663</v>
+      <c r="E1473" s="2" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="1474" spans="1:5" ht="15">
@@ -27298,8 +27276,977 @@
       <c r="D1474" t="s">
         <v>3</v>
       </c>
-      <c r="E1474" s="25" t="s">
+      <c r="E1474" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:5" ht="15">
+      <c r="A1475" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B1475" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1475" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1475" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1475" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:5" ht="15">
+      <c r="A1476" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B1476" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1476" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1476" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:5" ht="15">
+      <c r="A1477" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B1477" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1477" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1477" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:5" ht="15">
+      <c r="A1478" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B1478" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1478" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1478" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:5" ht="15">
+      <c r="A1479" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1479" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1479" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1479" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1479" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:5" ht="15">
+      <c r="A1480" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1480" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1480" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1480" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1480" s="8" t="s">
         <v>663</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:5" ht="15">
+      <c r="A1481" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B1481" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1481" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1481" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:5" ht="15">
+      <c r="A1482" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B1482" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1482" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1482" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:5" ht="15">
+      <c r="A1483" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B1483" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1483" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1483" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:5" ht="15">
+      <c r="A1484" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1484" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1484" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1484" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:5" ht="15">
+      <c r="A1485" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1485" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1485" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1485" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:5" ht="15">
+      <c r="A1486" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1486" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1486" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1486" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:5" ht="15">
+      <c r="A1487" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B1487" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1487" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1487" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1487" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:5" ht="15">
+      <c r="A1488" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1488" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1488" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1488" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1488" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:5" ht="15">
+      <c r="A1489" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1489" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1489" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1489" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1489" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:5">
+      <c r="A1490" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1490" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1490" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1490" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1490" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:5">
+      <c r="A1491" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1491" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1491" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1491" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1491" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:5" ht="15">
+      <c r="A1492" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1492" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1492" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1492" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1492" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:5" ht="15">
+      <c r="A1493" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1493" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1493" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1493" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1493" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:5" ht="15">
+      <c r="A1494" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B1494" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1494" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1494" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1494" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:5" ht="15">
+      <c r="A1495" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B1495" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1495" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1495" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1495" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:5" ht="15">
+      <c r="A1496" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B1496" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1496" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1496" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1496" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:5" ht="15">
+      <c r="A1497" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1497" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1497" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1497" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1497" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:5" ht="15">
+      <c r="A1498" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1498" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1498" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1498" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1498" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:5" ht="15">
+      <c r="A1499" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1499" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1499" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1499" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1499" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:5" ht="15">
+      <c r="A1500" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1500" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1500" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1500" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:5" ht="15">
+      <c r="A1501" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1501" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1501" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1501" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:5" ht="15">
+      <c r="A1502" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1502" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1502" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1502" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:5" ht="15">
+      <c r="A1503" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1503" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1503" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1503" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:5" ht="15">
+      <c r="A1504" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1504" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1504" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1504" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:5" ht="15">
+      <c r="A1505" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1505" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1505" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1505" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1505" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:5" ht="15">
+      <c r="A1506" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1506" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1506" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1506" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:5" ht="15">
+      <c r="A1507" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1507" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1507" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1507" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1507" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:5" ht="15">
+      <c r="A1508" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1508" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1508" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1508" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1508" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:5" ht="15">
+      <c r="A1509" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1509" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1509" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1509" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1509" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:5" ht="15">
+      <c r="A1510" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1510" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1510" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1510" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:5" ht="15">
+      <c r="A1511" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1511" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1511" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1511" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:5" ht="15">
+      <c r="A1512" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1512" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1512" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1512" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1512" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:5" ht="15">
+      <c r="A1513" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1513" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1513" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1513" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1513" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:5" ht="15">
+      <c r="A1514" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1514" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1514" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1514" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1514" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:5" ht="15">
+      <c r="A1515" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1515" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1515" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1515" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1515" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:5" ht="15">
+      <c r="A1516" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1516" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1516" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1516" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1516" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:5" ht="15">
+      <c r="A1517" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B1517" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1517" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1517" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1517" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:5" ht="15">
+      <c r="A1518" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1518" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1518" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1518" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1518" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:5" ht="15">
+      <c r="A1519" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1519" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1519" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1519" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1519" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:5" ht="15">
+      <c r="A1520" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1520" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1520" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1520" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1520" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:5" ht="15">
+      <c r="A1521" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1521" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1521" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1521" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1521" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:5" ht="15">
+      <c r="A1522" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1522" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1522" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1522" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1522" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:5" ht="15">
+      <c r="A1523" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1523" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1523" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1523" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1523" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:5" ht="15">
+      <c r="A1524" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1524" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1524" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1524" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1524" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:5" ht="15">
+      <c r="A1525" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1525" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1525" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1525" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:5" ht="15">
+      <c r="A1526" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1526" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1526" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1526" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:5" ht="15">
+      <c r="A1527" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1527" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1527" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1527" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:5" ht="15">
+      <c r="A1528" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1528" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1528" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1528" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:5" ht="15">
+      <c r="A1529" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1529" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1529" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1529" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:5" ht="15">
+      <c r="A1530" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1530" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1530" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1530" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:5" ht="15">
+      <c r="A1531" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1531" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1531" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1531" s="7" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
